--- a/docs/tax_updates_export.xlsx
+++ b/docs/tax_updates_export.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K59"/>
+  <dimension ref="A1:K95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -511,12 +511,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -526,17 +526,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Foreign outflows in July were the lowest in the GCC - EnterpriseAM</t>
+          <t>Cyprus tax alerts - Deloitte</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — Big 4 UAE Tax Commentary</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE8tRko4Unh0QWI1ekpUTHJ3QmktT1dyWXd2S2REcHZIZVVvd2Rtdm1WSkUtQUtacjlnSGlLdWtIMk0tVVNxU1ZKTU1qSVdpc2NOUjBGWUh5STBrM0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPR3dMcm02YVpKS2NHZC1YZlJaV2VXZHJMYjNzVzRNa0NfSDNXaFhJcUNseDFYaUVRNVNpdmd5Rm1jbE04d2psTWRBMjZrOUxQQ19fOXdSeXF5cXpPN3NYRWxqMEJ0aFNGcWl4OTJfSU9mSnNxRXRXZHFxY3ZfaHJrNA?oc=5</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -556,12 +556,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -571,17 +571,17 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>UAE extends small business tax relief until 2029 - Yahoo Finance</t>
+          <t>World Tax Rankings Middle East 2027 released: challenger firms surge in UAE - International Tax Review</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — Big 4 UAE Tax Commentary</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNM2FhblZZVW5LVzI2bmRYWFhadXJ5bGU2OU54U3UzTmpGWmlweXlYTVVSWHpXaXU5YnJLNlh0STNsNmhYdG9feTdsN2xKNWlNSGZRM3loRllITXB4U0ljUkpyYllpLU9jQUZVOVdab1Rocml1OWxsa1lKWE00Wk42QWZRejVCaTk4QllWdTJTMWxJd2RKbVZiWHo4UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQUWp5dVloOUQ4anZfTkR4NnJUYkZYdk1ZU2xDb1h6ZE5Wb3pzRzVxQklBNi1tTC1KWndLRlhpdVBaQmJzZ0FaRFVsNUQ3VXFDOWlRSGRMY3FHM0djMk9TRVQweThXS0lsSmxGN0xOT3V4ckZVNjRuTzVMOGJBSjN0Q1lwOTEtSXBwcm9zTTZUc1MxbVRpd2tRMlFjTE41b0EwTFRxSUg0TjlDTm93RU9WUDJFYm9sS3UtVm5XdWhmTVhndTF1dDdNZHUtWDB6Y2RpeFd5bnk3UzV4VHdwckNra1BoRWk3OVQxMjM5TWFaVkRlSjQ?oc=5</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -601,12 +601,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>UAE seizes 8.45m non-compliant tobacco and drink products in six-month tax drive - Gulf News</t>
+          <t>Cross-border Tax Talks - PwC</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — Big 4 UAE Tax Commentary</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOeXEwYUYyRVl3dzRiREtKU01zOTFJNXZCNVpNcE5wYTUxRUN3U1A0SkxudUUxYkI0WHUzUmZoelZBLUJSaUFFcno2WFc5bzNBR2FQZU4zSkFuMTNWbkcyMVNMdXc3dmplcVNLdDRsN2xDdng3ZFg2UnFiREgzZHIwUFlpUkhxdXdkeG0ySXJQS2Q2LWJJRGxrbWZMT3AxTU9KWWM1OS1qQ2FET0oyQjhhZFNXX3RDWklhU3VrdTM2aTRRcFIxdXlWOHJB0gHcAUFVX3lxTFA5OFBJbzlhcVVXbXNwNWtBamtpbFdwbVkxdHFtSTJXWk9TR3kxZ0F6UFVtQy1EYnpaZUM2Vmp1enVjeFJoSjR1ekpMenVHdEhaTlhGdmxKUzQwV1BsQnpiNXg0UDRpTndaTjE2RTJBNzFIbzNEZExXWlhmVnpYT2VTbmFsNldOZVlzX3BsaU5xUUplai13SEl2RUdpNG0tWTJOd1BCQkVaUVowX0NiZHF3VU1BLU5VcVpBb2RoRXVERGdaYmxhMmhEd3MxNVRoekNKQ3hZeEhyWkUwQUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNajMxUTZjZ2tOVUFvYThvdWY2RmE1UmFoV05XbTR1ak5FUXB5Z3FRV2RKdGtuVzZhR1Jva1lKQU5IUmVDMlo1dzNSQlc4TExYbkRudlZQT1haTXZWOGNmXzFPTF90c0luOFNrbWZxa0t5VElhM3NOY21CaS11UmFfVFdtVlRON1hRYjlDY2UxMFR2YVhBQno5Mk05NmJFel9DQXl2RXNsZWxhTTZxMmtycHJtNkdDWjNxX3Y2QU1TWTV5MEFTZFhJQw?oc=5</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -646,17 +646,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>UAE Extends Small Business Relief for Corporate Tax Purposes Until 2029 - entARABI</t>
+          <t>Federal Tax Authority issues new guide on scope and registration for Top-Up Tax on multinational enterprises - برق الإمارات</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — FTA Announcements</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOV0NzYjBEMHBFM0dLeTRxdURMWjYtZUZ2OXpSTENyYVozcGpPWkVBb09JaU1pQjAtWEVTdlcyQ1VjbmNGc2NiT05jWFUxMTNFVzFJMHlHQlY3VmxDaU9XUVZwY21yS1ZFYldWckFZallwVDU3Y1ZzLVNKbndvMXVGckJFMnRWNUtNOTFzRlgzUDhMbHFpMEZsRk9XejN4S3F4cld0aTJPdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQaFhsTDBvVWFWcHJNaWQxdFZoWnpxN0ExT0EtNENrZng3TTh4UFVleDhwOFd3Q05OY09UaXUxNS12YXljOUd3WXl6MWVUdlY5RXhWc3pEYVhBRDZPbjNhX2U4VjJLcUtncVFwMnBZUE55M1ZLLWxhMzFZQnNRYTFleGo3SDhFYWpmYTJ4dWg2dTEyNUkyT3JVQVZVa0JtcU5hdUNKZE52N25XdlNLckRWMThRQTRwQm5ZenFYUEFFYXVBeWhxMTlfNWFieFViR2FpSE84ZDVJcVR5VHhqbGVz?oc=5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -691,32 +691,32 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Transfer Pricing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Tax Insights: Canada introduces a simplified transfer pricing documentation regime - PwC</t>
+          <t>APR, Korea's leading beauty company, showed an 11.8 billion won increase in operating profit in the - 매일경제</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>News — Big 4 UAE Tax Commentary</t>
+          <t>News — IFRS Standards</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOVm8yXzZQUVY4R2djbXBUdHQ0aFUyQnFaSHNxSkFCbTNxNmxSVTZVUHRxa1lvVnF2Nlk2bmhTQ2w4ejJaTVR2NUY4S3VsajBFTEV2dkRwbk9BbEh1MWtwczNVNHgtQm1yaFJwc2NlZldqM053NGhwbE1TLWR3eDNIQ3V2ZzhTQ2JmbVJlNlliMkRoalBfYzQ3WHdVaXR2R2MzNEw1dGRQNzFfRWxTWklzYkJNYVZKVjFMclFQQjIzMUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTFBtVnRiOXljUWlKOUtMcC0tQjNycVJxaGJMUTBPZXFwYkFPeHM1Q1R4eXhmNzZGMzhnbVFrNFNZSFAtMjRiYVB2TzNRVXJ2dW8?oc=5</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -736,12 +736,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -751,17 +751,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Canada launches public consultations on steel imports and imposes surtax on wood cabinets and vanities - EY</t>
+          <t>Ind AS 118: Big Changes to Financial Reporting Soon - TradingView</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>News — Big 4 UAE Tax Commentary</t>
+          <t>News — IFRS Standards</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNMy1qdEVRaXhDVUZ4c3FTNUlCS0F0SEhoRnQtRk5BTnB1d2VFSmZSUk95RmRSdEw4LUFBV1FwYTIwbTVLZHdqOEdkcDhRb29fWDc1cGN0ZFA3a0habW9iY0NWam9LZmtfa3c2NDlLZ3N1MVJYWWRwejlhM1ViSndzZg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPa3pEaDB3Q21YU3FhSFQ0ekVZc1pwT00zQXFTbGE1MXkzX3NjazJ5TGZXelg4WnZocTlUZzVDMWp1aFlzNk4yMHIwMGR2d3dBUldzem5pY2xtLUVZckJJa1Rfc0c4MnJxX0YxckZIZWNNY09LVnh5RFVGMko0VEdrSXh2ZWlTdjdsQVlHTWotcGs2X0w0ZVRPbmNyVDdEc085SVNsYjJCR1NkR3M?oc=5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -781,17 +781,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>UAE extends Small Business Relief for corporate tax - Absolute Geeks</t>
+          <t>UAE Publishes Monthly Fine for Businesses that Miss e-Invoicing Deadline - Legit News</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>News — FTA Announcements</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPWU10OExoZmlXRjdCamp5VHROMnNDb1dKN1I3NE85dTI4aU84VjVvczlyanRyWEw4OVBuOWpVa1NJZm9qQ2hSZl9YYlhxOGNEYXBCeDlGQVF1RUV1TWJlSGVmdnpHRktyS2ktV2IwQ0s3T3hZMzV4Ni03aGdvVTNHZFhEYThmRE5uclJqR1BKUF90MXktS2xEaXctR0RsLXphM0g0REdvWHY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOcmtkbU5IdUxaZFVXUXVJWno3dERSaEJ2X0xKbGlCSi1rVUt1TDNNQUdiTkcwdEN6YlR6Y1FpeU10WWY2aGhWQ3gycGFOcGRQTUdUbE5BTWxfOGtHcXRRejN6WWktN2FmbjZTTmpsUENidjNEaTktTkVSbVQxRDNBZHNoM3ltLVVjTnUtWC1MdTBXX0EtWWM4NnJwQQ?oc=5</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -826,17 +826,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Spotify forecasts slower growth despite AI investment - Gulf Business</t>
+          <t>Dh5,000 fine a month: UAE firms have 5 days to appoint e-invoicing provider - Khaleej Times</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>News — FTA Announcements</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNQUhDU0xPaGxHNTZZdDNmRFRsTndvQThIUkRVV0hyTkpVbWhFNXdsZ2hjUXFrNzByWEc1ZUdITm1FYkM2N3k5MW5paDBud1RfNGF4MXNIdlluaVktTVRfd0RlZzJpUmc0UlZ2WUlKU1VDTUdELXpoelU0Z2kteENFZjVfcWx5YmhLc21jS3J5VXVkeEZ3UXRV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNTGtGYXoyUURCNlQzTzZldFhpUGJIb25mYjVQOXdsNXdDNVRQV1dZVW9EdFJ2aVNsRnQ4c1JsYjgzcWszU2JlbGNYa2p5SUl2UVptQnYyZ0hnQk9KM3BBS0VxNmY2d043bWEzb0ZPM3M1bks5RDFSQjlhNnNYMDRVMmU0SWFCQmZCU18wOWc4bG5yeVNIOE5Fazl4UU9sMjkxclROLVFvQ1l0ckFRaWhMRNIBuAFBVV95cUxNQjIyZmFMNm13T2dZMUpyOVplTWlrVTBEX3N2TS1iaGVQV2hSNFZXbkI4VW1DdDQ2ckcxSEtmRjA3YTA1Unc0dHY4WTBVRGNiRnlCN1RsRzFwQXl2bTJaaFhaYmptVDlQc0lkQ1RvNzViOW9nTGlxZUhnN21WcDBteXlHVm9mdXBqSXcyajhFdmYtZWt1MGlmamQwOEJkTUp6VDZsRkh5YnEyVjVGOHlmenRrb1psT1Vv?oc=5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -871,17 +871,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>UAE Sets Minimum Excise Price for E-Liquids - Vaping360</t>
+          <t>UAE FTA urges e-Invoicing compliance as AED5,000 monthly penalty applies - Emirates 24|7</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>News — FTA Announcements</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE9HS2ZoOFFrdlRtX3N4ZXM5UlpzLTFKc21Pdi1CVkhNYW1PNGozMDBVYVZ0VjlrUDNCMFRQRG1hOGpPNllSd0dpX0dhNm02a3drdmZneHpQOUhtUkxXWlFBcDlETkt0dF9xalFRMldrVWZMSXh5NHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQNFV2ZnJIZjdaTm1YS1RtRVN5UzZCZXNZcE9WOWlBV2U4d1BtQUg1SUNhcWJxWWRBRmZLVDl1SGNCbjhTdW1rRGFJUzhlX1dvQ2NkeldjNmdyNHNFLXAydHpUVG4yXzREQk1EN3l0cWpJZlo2RVBLQW5RZEFVMlQ5bXJ4eTBvSS1SVEtxd3RYUnppOUctcktBbTl3T2lOenVFcy1nN0VpaHk3QnQtZldlYzlIS3QxeTJCcDhwMW9xclRRVEtWNVZfZFdveF93UdIBzgFBVV95cUxQNFV2ZnJIZjdaTm1YS1RtRVN5UzZCZXNZcE9WOWlBV2U4d1BtQUg1SUNhcWJxWWRBRmZLVDl1SGNCbjhTdW1rRGFJUzhlX1dvQ2NkeldjNmdyNHNFLXAydHpUVG4yXzREQk1EN3l0cWpJZlo2RVBLQW5RZEFVMlQ5bXJ4eTBvSS1SVEtxd3RYUnppOUctcktBbTl3T2lOenVFcy1nN0VpaHk3QnQtZldlYzlIS3QxeTJCcDhwMW9xclRRVEtWNVZfZFdveF93UQ?oc=5</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -916,12 +916,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>E-Invoicing Readiness Checklist: How UAE Businesses Can Prepare Before the Deadline - NewsBreak: Local News &amp; Alerts</t>
+          <t>DigiTax partners with Supy to help UAE restaurants adopt e-invoicing - Caterer Middle East</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPQmFubHpKbnIzS2N1cVJkbFA5bDRWcUhzQ0lYazZ3Z0ZBazZKQzVoTjRxZXBrMFNNSGNXTGp4ZG1EZ0xTTGFwanZQZkxvbjA5UFQxYkNBLWF6bEtDSlB5UlcyNU9fc2E1VTRNMWtTYnRyOFRlTUxjRlVlcEVwRVdDb05OQlo4VC1GcUpqUkpmVzhsUmc0RGJrZlJWN0tCMXVQc0d5dTEtT055TFRDT3c5R2pUN1hpaEF3R21TOHo2d1pNZldNcUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQOU1EY2p6d1B0WW9WUFljUmF4dzdCVnVMNE50QjZ0QkJDeUFNYy1DLWl5bU5hdVphdmtOMmNuenVqVHNacTRTeFZqbUFvS3VFOGMzUlZ6VFFsZnJ4V0MxWGZLWkJiT295aWxaaUFjeS14LWlDeE5UYWliQW9nMFRBVWZkUEdHMlp1NWNTN3NadG9LNUwzck5Ja1F3LUlrN2Q3V2RZcEhKY05vejA?oc=5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -961,17 +961,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>A jumpy July - EnterpriseAM</t>
+          <t>UAE e-invoicing: Oct 30 provider deadline looms for firms with Dhs50m+ revenue - Gulf Business</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBCcFdtSjE1bW5pMlREMHVqWTYwcW1xajViLWZvTmU1MUk0MUZiX2pPay12Nm5RS0tzdmJjYU9VY2hjUi10enNsYk1qcEZqc3FQc3dEZE1CaTJRYTJvVWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNd1M0bzNJcTEybmx2M29pY01HRWxvUURNZmxjemd1WDByOGUzSDVmUW4xUnljZnRlQXZBYW1FdW5ubnd0N01wWTVpNjRDR2xzY0lWcGlDd2ZhLV9BNjZsOTJBME5jbTVoUkJUWjdYbVZjaGhoUktjWUYzNkdvRDNyMldoQXN0V3R2WGFOT0wwbkpSX1ZnTVE1YV8xdklwMlROQ2xiR01EU0xaNUlCYXV1TWFYT1FYUQ?oc=5</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1006,17 +1006,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Another Hormuz workaround - EnterpriseAM</t>
+          <t>UAE e-invoicing rules: Key deadlines for businesses in 2026 and 2027 - Arabian Business</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5iUjRXRTlrdVBXOHUyRWlYc2ttOXdYaVktOE5ZU1YxMnRLcnlHeWRPdl9CQmRkR3Bqc21aeFlWMmdFcGdjanc3d2RNTnRGcWdKVGdxQTZmeC02clJoSXJJaGJlUUM5TW5pQjRORkVpRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPMXU4Vm5ScFJWd2tINmI3WEI1X1pwRFU0R2NyYXFra1d1bXFFTWhiVExCdS16SVRNelZOSlB5SG5GaHZTZzhzendZZHV4aDc4WHMyZ2kzcTEwekZDNG0yenlUaWwzUEs4blp6bHlPYXRZMFZLQzZRbG5idHB0a3F0Sw?oc=5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1051,17 +1051,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>UAE e-invoicing: How digital invoices will transform business - Khaleej Times</t>
+          <t>How tourists can claim UAE VAT refunds in one business day - Travels Dubai</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQMjFwZTd6MkpqcXZKaEwxZV9fUlZWSEtSeVdIQXN6YXFPMURFMWZhOHc0NWFuWlRfd1ZNX2doQVBpbXBqRFBTOVNNcjVTYVpOcEozYmtoaWxDUHVoUFFNT1RBWEI3RzJybmFWejFNcEcxYXpybDBiUzRLUk85ajBkOHIydnBjOUV6NEVJUjZkQTNOQ0Fud1BjdGtUNVpwTmlTazdyNWZmaXRwTkthY1Nac1RPWU90T3lMemJJNHp5VdIBvwFBVV95cUxQMjFwZTd6MkpqcXZKaEwxZV9fUlZWSEtSeVdIQXN6YXFPMURFMWZhOHc0NWFuWlRfd1ZNX2doQVBpbXBqRFBTOVNNcjVTYVpOcEozYmtoaWxDUHVoUFFNT1RBWEI3RzJybmFWejFNcEcxYXpybDBiUzRLUk85ajBkOHIydnBjOUV6NEVJUjZkQTNOQ0Fud1BjdGtUNVpwTmlTazdyNWZmaXRwTkthY1Nac1RPWU90T3lMemJJNHp5VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQUWpQaFlPcE8tQ3ZpWVhKZHBmTGlzVWRtcmdXOWdxcDlGcjZnSWsxa193SXhyQ3duMFphOGt5a1lFRFhveGRpVmlUQ1I4cjhmQTN1aXh5Nks1anFfV0Zua0JBaG44T1lNTWZlRGhtWFRJZkRVV2F3MGJ0RnloVDMtQWlnZGdrQTRBUEVnQUEwYkU0dlhoT2Fn?oc=5</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1096,17 +1096,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1116,12 +1116,12 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>More investments in Adnoc’s fleet, Indian IPOs, and Egypt’s North Coast - EnterpriseAM</t>
+          <t>"Smarter and simpler": UAE speeds up VAT refunds for tourists shopping in Dubai - Tuko News</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1RdV9pa3ZIMmpRWnFlcXRaeTRnSy1zZUp0enVScm1nc0hMX3UwTEdEOG9oQy00UUJiSUR4WENleElGQVVmLXh3ZE10b09nQWphT0IzNHNJb0h3Q0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOR0ZWZkx0b2hxUzJfSlEwNEl4YWlSOEVreHVFZmEwMWxia2xYX1BxNThjczJ4bEk3S1lkRy1ZREZTV1FXNDZ2N29tcUxYVWxIZ3lZWkl4VHgtdUZ0QXYwcmFwMlVId19pX0lxWFpMT1hVVkxDZHIxR1NYemlyZ3Y2dG9Iczg3Q0tVcEtfVDlTVm9IQkxwMlQ1eEpRaUdBQmx5R0xQNXZ4QnotSHpYWnZYTlJYX3o?oc=5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1141,17 +1141,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>FTA Directive No. 5 of 2026 - Crowe</t>
+          <t>UAE launches paperless, AI-powered VAT refund app for tourists - Khaleej Times</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE40S0RnRzF2d1dBSmNHdkNNQXZQQmlOYWNOSk5OWnlVNUN3ZDB5UHBUV29RXzNvaF9pVFNQZ2FwTUdocGhxMXp1T3gxMUFycGNESFA1bXNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNZWdmNWZuVEo5Uk9mUEQybHRrODZ4M1plWloxXy0wWDRtMlp0WDdlVzkzOEgzMHNxdm1kSXJZcWZSVklxX0pKV3dHSnhMOEs3aXFZYzUwSXdxa2JFcXphbnhmVG10cHJURUFaVkw0dHk5RHF3b0o0QklQQ1ZoNVE3UXRMNnhsbTJyUDdRbDBKTmlhVFdTSUVEN2RXc9IBowFBVV95cUxNbmFfQTNJbmpFSVhLcndEbHQxcGVqcnhzSEVnenJod09jelNLSHVSLVE4dVdtTHlHOFMtcmRjTVVnd2p5cU0ycEFEbWdHbVVoVWdGbVRvRUh5WGpGT0xQVWRaUklXdloySmd2QWRYNlV5UFlPYWhnRF9KM2tsWl9wek9RQ1ZuVVRWaXJkb3F4cHVCMkhfMDFOU0NGNTQtOFV4MGhv?oc=5</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1186,17 +1186,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Digital currency and VAT: New UAE rules for businesses to consider - thenationalnews.com</t>
+          <t>UAE Launches AI-Powered Tax Refund App For Tourists At Three Major Airports - Travel and Leisure Asia</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQamI1MElzOEtNS1ZjVWR3VGpjZjNUZjBXbjQwZkJIZ3AwOFVqckl0WWFQN2JpaEg5XzRTUTBVMDFOeVhMaUZxYW9GUnBFNW55WnhKd2ZKOVZoekRBWUNqQkp3dGFPZ2JQcWY5SjVlRUJuTURfcVN5aUNXVmthdUh4cHlJbFNHN3lyT1VTU2l2Nk92U09JZFh3eXp0c29jTlJNZW1VLTZBR2h5WmdBTjFuNGczZkZwdDY1QWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNeXpZdm5uSHczcUh4UGJ1LU1kWUpJaVBKTFVrcVBBWlVrSlI4aWJzbGRTWHp0bkVQNWlMQ3dWUU44LUpqOTloZjZoN1JEeWwwSHg2YXk3Wm5xOEJTNklQb05UZHBUeUdETWxWWHlvT0dtVEVwODNwZWpFN1RPRzVkWFlYWk9BNExmU0pibXlJY1FFalQzbXVrUk9IMGZ1clhCSEdrTU55YkZ3dXBob2VzcXBsbC1qTm9OQS05d0ZTOWFySjjSAcMBQVVfeXFMTXl6WXZubkh3M3FIeFBidS1NZFlKSWlQSkxVa3FQQVpVa0pSOGlic2xkU1h6dG5FUDVpTEN3VlFOOC1Kajk5aGY2aDdSRHlsMEh4NmF5N1pucThCUzZJUG9OVGRwVHlHRE1sVlh5b09HbVRFcDgzcGVqRTdUT0c1ZFhZWFpPQTRMZlNKYm15SWNRRWpUM211a1JPSDBmdXJYQkhHa01OeWJGd3VwaG9lc3FwbGwtak5vTkEtOXdGUzlhcko4?oc=5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1231,17 +1231,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,12 +1251,12 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Air India turbulence injures passengers on Phuket-Delhi flight - Gulf Business</t>
+          <t>UAE: Claiming VAT Refunds For Tourists Just Got Simpler With New AI-Powered Digital Platform! - Curly Tales</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOUk92b3hCQVZybGNndXNJOF9ZX0Z3TGl5NnRuXzE5NlBRb3czZXM2SkxXb3ZQSGNOdGo2a2U2b040ZVFDcFBqbzdvaFFZaVdBbFgwQkJOOEhDNzF6VXY1OU9Ca2t2Z1ZnQlhscXNXTVhDaWY3b2lvMUlEWFhkXzVxaDR3b191OUx2aTVKcEttYkFGTjRzRVpnbFJvLUZhYmNLTFJJNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxORDJuVlViQjVHZ3JEMUxXV2NqVjBhbXVSWk1WWm1CMUVqU0RLX0JMNjctNnE1Q1FmSEhVZnNUcFFrLVBGQjJSWHF6UDJlVTJObFNhcDFRcnh3WFZMTEVycjZ3S2NEZnpqT180dFpHZ0VCeXgzdVd5QW5Yd0w3QUdHOXI5WE9NUzFPYlVYY0RTZ3NhU2kzWWRramVROTRQdmsxNk1zblRXY1ZOTVVnQlFicXNFTnRsWlYwWnBNd2Y3WV9EbFJlYi1UN2Z1dzlpSnfSAdQBQVVfeXFMTVJyVkVYR05PQldudW1QSzJsS0V5aW0yZVNyRmQ1YmhBaDhMVmtoNTJfSnZTdUV0amhlQ2lTa1pxbnpWRTA5aG9DaDhEdExWTDRrVmszb1gyTkNLY1RUMThXNEM2eXhKa2ZmUDNxbGM1YlVLQXl6c0MyaW5KQ2tQMGxMQ0dmM25iN3U3MUZKazN3X0lNeU83ZXJwTkE5REViLVZJZzJqcGVaLTJXWV9nWE9EVmJqSVJHV05XaXMtTkRjbTkzZml3bkNTdjFnYWVjU1E4SzY?oc=5</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1276,17 +1276,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>UAE Business: UAE extends small business relief for corporate tax until December 2029 - Gulf Daily News</t>
+          <t>UAE Launches AI-Powered Tourist VAT Refund Platform Across Three Airports - Konsulteer</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNVm43RXV5MWlfOTE5TjdqQjhtd3pzUnRIdmJycExNbXV6REpoRjQ5MlNiRENNemM5SG5VbUhJbnVXenhQXzFhRGgtNXE3QjRWWHhCcTJsZ0lfUW5ZTWNWcjdZQnZSSDM0VVdvVDY0ejBPMklPTUkzdTdXX090b1RQY21nbmdUQUtuZG42RHBxRWdCb05xNkdBT2xUVk1SNWN0cG1NbnhKNlBxSl96T3BzOU91cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOaTNXUlc5Yk5IdGN4RF9PeDN3Nkc3WnducVRwSEczbFlhb2dLXzlKNWFsdEh4VlQxZTRNRl9VQjhYZDgwWU51dmRjZVhYUFR1WFBKcWltSTZwcEp5N3ZYVkNRNWZVaTU3UXNBZzZqTVFrN2pMci1jZGhRemRGSnVRLTZsNW1Rc05Ic3NGd21nLU85VVJFLVR5MzZrOWI4Mkc2anZqb042c0xqUGc3?oc=5</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1321,17 +1321,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1341,12 +1341,12 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>UAE extends corporate tax relief for small businesses until 2029 - Khaleej Times</t>
+          <t>UAE cuts tourist VAT refund time to one business day with new AI platform - Gulf Business</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNMDNwUlhpclFxaFJkdkkzR0s5MVh4WHZOUDdfZzZtNTBFb2RIcklxMF91Tkp2NGRxRlZMM3BubEZGc0g5LXpsQUhHQy01eGcxTllzc1k1S1NqeFMtYXM4YlBmREttNlhsS0hmd2JXN0l2UjFEQ3B5M1pfRTVpOGw0Z1pPMTNHd0tHQ25ZNjNGZmVaZnhzZUJueE9sQ2dNNGVaUDVjTdIBrAFBVV95cUxNbWJjeHFtRU9DbExyNHRRY1NEUXB2WnZRZ1V2TlFhQ010T3RhSmptR2ItaDhxVnEta0NITUJyS3ppaGgyQ2FkclQwRFhCaWNnLUhNb21YaDVGLWZZNThic2hpN0MzNTI4cXI3RjYtLVUzN3VHanJUUHdYaEFRWUlvS2w5UVdja3pwd1Q4c2pXWHVPZ0xZVmFCcE43eWl1bG10N0s4UXdpVUhpU0tH?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPZURXSjRhbWwwMzRkaWYyWlJSWkpSUl9nYllHVFJ0RnpDTHR4dGZJY2tlZzVGbEJuYWRjeFlXSm9fMDhDWTJwS2ViMTd2M1dKc2I1aUZmMTVGclB1eUhnRGV4SnlRZzJRWHhGYW80SFM0cWpCTjR5T29PMUNfU2l6MUN2RWlmdXVKTE5fVHkwNDZxVzdJSmdiUngtTlRzZHRqNHpNTkVSYy1Bb0JN?oc=5</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1366,17 +1366,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>UAE extends corporate tax relief for small businesses until 2029 - thenationalnews.com</t>
+          <t>Federal Tax Authority launches world’s first-of-its-kind AI-powered digital platform for tourist tax refunds - Zawya</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQOFMwcEtFYkFkbWxMRnBqX3Y1M2ZOcnJ4Q1FzTHg2b1NDYnU3dzVWMmMycVdhNzJSbTZhaTZ1bjRpN3RYcm9Gb3VIOUxydjN6anFTMU12SHNNcmt1YkhwSk1RVTV6Yk1yS0wtNm9PbVZLNkxmTVRNd3hEOW1xbXdnTlBiX0VJWWhINEw5MHc1eEk4UHhFZHFOZ04zcnZERDZhLXZJQ0VGWS15N080ZXBQYVhDMFU2al9wN1NlNXN2RnFaZEU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxQV0NXYW5reU5Sb1FHRmNDT3dyaXphV2ZORlVZYXNhN1ZQV1FldnhlZGF4VTJpVVJ6c0k4MGRqZE13Rm95S0ZWWkpVQUdlNFpTdDA2cks5akhhZmNZNlFuVU8wVkVJMFhiRUVjNTg5d1dzb2htY05tM0xIb0RhS0dhZ1RaQzZrQ2Z6ZzJJTnlZd19vOTJsU09pamc1TWFqaGFiUFM3Z1JNSGlac0lFeDRrcFpIYWxLN3ZlVjdtc2drS01FRTl1eTdCM3FZdFd1ZU1jODNWYkZ2WHZzZk5USlNVcnlsTXRrcnhaUi1fbUhXWnR6U0FUc3lydXJwNDIyWWc?oc=5</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1411,17 +1411,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>September 1 change: UAE announces new excise price rule for electronic smoking products - Gulf Business</t>
+          <t>UAE Publishes Version 2.0 of E-Invoicing Guidelines - sharedserviceslink</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>News — FTA Announcements</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNMXNESjR5VDVIQ0Qwb0xKUk1xRlhaTmV2RjNfdVpGaDZZYk0wcjdSbC1RRHBUNkRRaGpNOS1mSjR1blVVRHJ6MzdLeUZXM1lMWURyX21CS25DZFN3engwRWZCOFFLUDJydEEwX0pSa1lLSlNqbVlhdk9pNmtvLUh1QzFubU9RVENUNEl3QVdLc2FkRUV6TGFjZmJwLUtiUVd5dlhjVW1SLU43WFI4eGNfZkJCTXBNaEQySVR3QjZuazA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPV1NkTHUycS0tOFh6TF9HVW4yU051Zk1zTExPWTVONTcxemN0WTVBajl3QkxVY3Bocno5N1BVbDFkUlZjQ214VEZQc1Y0eURfMHZzdTNyV0RuRmU0OXA4dU9MMTZhN19POUdvMXJRSld6UDZkbU9YbWNkaTVzeW9DNDNwX25zRGFKMGgwQlBfR3JzQQ?oc=5</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1456,17 +1456,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>UAE small businesses claiming tax relief must still file corporate tax returns - Emirates 24|7</t>
+          <t>UAE's new AI platform to slash VAT refund time for tourists to one day - The National</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>News — FTA Announcements</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOLXJ6YVV3T2dXazExeU04V09UYlk3NmtYT2d3Z2t1X2RPckN0RjVQZE9oNTljdi1rUUlzTDlMalotZ1JWRS03TWVFWlVVS1hyMVlDUEsxYWQ3RWgtdTdUNzVaZjE5WlhVVUhJcjkyaDFVa28yeEN2ejAtVG43dnduV2NDa0k4czRLby1sU2w2ZHZTcGtPZmpiTjRYWXB2VUExMnhreUktUDBZSkZ4LUxZYW9TYXRJc2s0U1QyMtIB1wFBVV95cUxPNWVmQzRQOEJkZnBCZVFDblE2dkFlX1hGNWlnalJBVk5QREJoU0ZvMXZIM1JJYXdLb2lQZFNnejliekY3Y29nN0tLdTUxQ0h0SUFaSVlpOWhuX3dVaHdjX3NPM1pkd2xlVDRMT1VmTHJ4QV9PbmpWRmVHRFpHZ1lyUF9ZWEJTcFJ2LS1QX0hEa0Y3dnJ4S054S211cWRMWWlHVVd2V19wQnhGa2JVR1ZxSFVNVWJMejdESlFZSkxUMGYwQUlyQkpueDlwb2dJYnlqQnZGNklscw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQZVpMLWZ4cmVQdDlnSlZRRERKN0tJbVR5eGVfblhRam5IUGwtXzdIaWJqeWlSNEVNVGozWGpvMm5LSGQ0YXdlVl92YjRPNHhtZDFIQ2swNlRtdzRQeUtTVmE1d1ZfVF9vdXR3N1RvV3ZoLXlZdWFyTENheUtIa0lOTjZTcjUza3VWVmFLaXpEVm1kTkpVandrTE80a0dadG9IMlJsWUhyZHU4U0tMS3I0cVQ0RVM1aTUzWGF4U2pvQQ?oc=5</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1501,17 +1501,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1521,12 +1521,12 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>UAE releases registration requirements for domestic minimum top-up tax - kpmg.com</t>
+          <t>UAE announces major tax refund upgrade: Tourist VAT rules explained - Arabian Business</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>News — FTA Announcements</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPaGJWUy1MU0VZdmd3LTVPTmw0bDYtWlF5a3JCVkFwVnhJRUkxVkdEWUE4X1VZLXg0Tkg4YTlLWHhoOUJYVzJqR3lzUE5Pa1RpSWtjdkRDQ09UeDBoQ3Y2bGlLbkhzTXZ2WlNJeGFSLXNqRUZyRnBfNV9Mbk5UY25hdVZ6VWM2cWRYOEt4bUlnWV9QYkQtOWZudGJaV0ZJZDRVY2JGbTY1T1JTYVhyTGhEdlVuQzlzZkN6ZC1VRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOOV9mdmlpRVVsSTdjRnA2bV9OSGUtNGlvNmgzTWVjSGJiZFkyYmpBQ1h1UE4zY2VGN3FFQ1M3N09ZQm4zc1lTNl8ybDNKTll4c1FweWZlNFBLMFI3aFRfSzAtaHJzVmxSajI4amM1OFBMRUlnWnBfbWZ2a0s1azBieWtybl9VRmVrRmd0VVI4T0tzNWZZbWdCNE5NR3BxZVR0TW1EZ3VCTlBHZw?oc=5</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1546,17 +1546,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>UAE Digital Economy: Why Trust, Not Speed, Now Wins The Race - Menafn</t>
+          <t>UAE launches AI platform to cut tourist VAT refunds to one business day — The National - UA.NEWS</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNbi1OcWZwSTNNYjBRZkJWS1FodlVGTG5oZHB1T3Q2cGRqazRiZGQzeUtlOVB3VXlhNUM1TnhSdW1MVS1uSng1dGFmTlAzb3ZMNXlod0c5bWo2RkdOTW1idm9JQ3dQNTM5Z3FvZl96WlNuVVh4Mmx5NGFNWXBHVFZoWnUyQU9WT01idllWclJqTXE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQYXdJZkJvX3ByM0lXS2ZtYjlHR0poREtsemlTaHdPWGExcVBhQzdNR3kyWmJMNHJsTnVYemRldHg2aG1jdlNidk5sV1JjcldzRF85dzh6ckpHeHdWVHp0SVdzeFZGNFlzdW04Q1dockJ1ajU2bnRFcmdwLUZfbE9iVm0tRE9jQklXM1Qzc2ppV2lDM19vUGUxLU9uc1ZJNm9TcTNlYnFnTzh2RVZyZUFEM0VVdHZWRFNKQmJsX1ZtQlc?oc=5</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1591,12 +1591,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Finance sets e-cigarette liquid excise price - Sharjah24</t>
+          <t>UAE Federal Tax Authority Launches Digital VAT Refund Platform for Tourists - News and Statistics - IndexBox</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBGY1BCNkVheXBxM3RBdWlPNXVULWVaaWdWM3RWWU9JSWI2T3JVMGlMdl94Ync5ekFqdGU1SzAxeEMwaUhJR1hTejhVTFo4blI2Y1d5QzZUaVgwUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOSm9HaWZSWEFFM3BNOW5acHZBT0luQWFnVEo3QUpJR1AwdUNMVjE0V3RXUXptLVVZR1VBN3doSnZlU1RNcU40UmJNVWpfQnVpY3NNRGRqNTM3WVFNRnB5X0g3SXFfbkl0Rk91MEtTWVBRejJDOElIcmxLSG1TcnNaRWdVbUdoS0QtMGVRX0NzSjJOSVJyV1luRVZsRW9ldl80c2VfUkNiempDdw?oc=5</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1636,12 +1636,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>CBUAE injects more liquidity into the banking system - EnterpriseAM</t>
+          <t>XYRA unveils an intuitive AI platform to transform UAE business accounting - Gulf News</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPRVF2amFoSUlsRENGenUxcUlxRU9NeU9QWlJhUkExb1k0cExublF1YUdrM2dJc0FySm9zQmgyQUtKU092bkpYT1I1bUhaMkxGR2o2SFVnckhIR2d4RGQzOUJnb19tZERINThyZ0NrQ1A0WUttandLcmN0QUlUaTFVZ1djMnUxdEp4SmNGMjM1Zl9HX1k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPeHRnSjFza2hMY1l3Q3p2dGtXYkRZRW5qTmFaZkJqTW1YZjU5Rzlva1pjTEJSMEg5MVlZd0pCdENvc2p4OXVGdWdBSEd6Q0gyWTFZS2JoUVVpaVVDa3hsYmNSaE1XWlZJWmZua3lOUVprakhMZFZmR1JsYjFTeDM5YWY2VGtLSmtCT3BOaS05aWRXV0k5NUJVanRpcFQ1MzJIdGVUcTd0cG55ZkpheGIxVjI3MlcwRHp0cmZOUEJPanVSUDNmWW1IUElMb1RYdExIOWFNd1lZcmU2X3hXSTYwVEhR0gH0AUFVX3lxTE9lZTBHQThBcUxrMHRBZkROUzQtaW9WMWVmaVhPdk9wYmtkZlYzVEJ0Z2FuWk1CVTFka0pZOTQxYlVMdzFXNVQxbWdIaURLWmY4RGNRM3FCaFRKbVF6akpqRmVabE9BX095Rk5tV0NZN3lRTm42bzNJR1dxUnJleklmd2E0bm9FUnVGTWxwUE05T2d4ZEVhUnBYVzNvazZHbWFWY29FSXVhU1NMTloweUlpdWZIYTl6b3BSaks4d2NrUFJQUzlqX2lzRFctMTF1ZnprRHZMMkNkRmFYbndEMl9YNHV0aXB0N0h1cU1YRHFPRE4zNWU?oc=5</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1681,17 +1681,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1701,12 +1701,12 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>The Taxation Society partners with Tally Solutions to strengthen UAE's finance and tax professional community - khaleejtimes.com</t>
+          <t>UAE tourist VAT refunds cut to one business day with new AI platform - Gulf News</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNMXRpRGhpQXJvUkZhQU1IcTF6Z0JtLW16cTQ1d24zZWlwQTlPMHNCeG8tY0NLc1JGcXdjT2g5V01YM3hOVmtZYzBJeThiR3hhSDRpdGdwaDhsVC1WMDFTSWN0SWdhc3hiWTRSQmV0blZEZkowYWdoSU1BaUJ6Y01ZZ2ZrWlNRc2JtUllnc0huTF92aWdmbEp4bTRvRV9fN2xTU2dmMjdLSk43ZlFlcEtuWTBKQXdFTU5pMlRnWE55VFBwcTc0STRtcFluS3Ffek1oM2NRQ1dYemVkTktESkJRSVJ30gHqAUFVX3lxTE85ZnVhMjFKMWdhenV1YlFiRGtpVTBIdjRvLVNLRFBjTHBPUnVfeG5sUGxIcWVlSlhUTEVibFV2UXdWbEg5TGNmS3hBYnczSEctV3BBT2pZT3dpcDJUeGczWE9xQ1dweV9hc1hwQnhHQkFWUDRrb0FzV0tVdmZhZ0pLZC14YlVJZjBYQmcwbUZWeG55dnhpOFliT0wxYkQ0bzl1VEhiVUpQNjQ4TVN0bFhPRERROXB5NUZZQ0VRS08tY0VmSDdLRFQzMHZ0dEZtamJ5dmp1OGZ6SmNxQjZrck8wRWs2U1A0TFJZdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPTHpETlBMdE1Kb2FWR0ZBdG5jRldvV1ZOWFpJYnMyVWhlQ1hTUE43dkV5UTJIWVA3eVFER0pKNXZHYTVXc3h4eVJ2R09YYVh3dEpkb2k3cXlyYWQyU3pPS0dvSjZhSkNmS1hpM0UwU0VXbEx6d2hydlh3SUJ4amkzQ3RlVGRtRTlqdGdjdW9rMVJkUG5PazRPdkZuY25mdHVoakZIZWFfcWNaLThEeXNyazVhTnVPckJZbXg40gHOAUFVX3lxTFBpcjZEUUktS3kzU1JHZzctTGFPTWZ2WG5PTGc0N21xLWoyS3gybHEzY0hMYU9XeGh2QUE0Z1NRSURaV0xhUkV6Y2VmbkpCR0VBRjR5c2l4SVpPYnBCQ28zTHNVN0k2aWhXcnpMYjFCaFJyUzQ3OUVJM0Q5YVBOS0JZbUV2ZXJVcS1xX2dnUGlYZ3NBaDVmREZyV3QxeTk3VnVUNDJfbG9fekhjX25MOEVhSERXSTk1a0x5THRXT3V2RmRtbkRXd0dTXzEzNWlR?oc=5</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1726,17 +1726,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1746,12 +1746,12 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>MoF extends Small Business Relief for corporate tax until end-2029 - Sharjah24</t>
+          <t>UAE e-invoicing deadline: Businesses face Dh5,000 monthly fines for delays - Gulf News</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFA4N01YTUZ2UGRGVWdDQ3JDM3JLYWJDanVuckdCLVhuQUdqUFo3clA1cGRoTUtubWNpQ0dTOUFSQk5jYzdGcVFYNkNpQjF4ckFVZ2pBc0FXM1Ffa0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPWWVSUnR0QVRxaG1QTlhqa3NxcFNNQkdlNi1lYWVKRjFuOFRQMWNoNnY5Ni1CVWVNYWJjSEc3MVU0Q3h3eC0yQ0lJV2NRQTk1TWF3eThpcHFETEQ0OFg1SmJuYUVaZTVvZ3FHc3VpdW8zcEVtbTJJb1FHSFY5dWFOMk5SU3M5ZUpJNEk1OHQ3X1dxeFhLQ0tEbFRtcDR4dG04NS1aY2huV3BJVzlzeDFReDBKdmJmRjVnV3BkOWNQZ3bSAdMBQVVfeXFMTVFtR1VkanA4NWlBaDVrR1V2bDhlak5IUy16ODQtV24xTUVKdG5Sa0ZoeE42MlFWYjJuSmszT3JTSnd5ajJ1ZG1XQmd0M3hUWW5jczlsQ1hWQ3dNRFNxQUsxRkpfTm00WnBybTRpV3F6WXE4NXJmR3MzZDNOZzNqZzU3NmJKWjRVYzdoLXVGNFU2Tmh5Z3AtcVNUMTh0S0M4YThYVllGdW15MVdsZGM5cDFrS2hsV0JERUxzOXJhWkNEMnlydHhfazRucFhEMkUwVmUwOA?oc=5</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -1771,17 +1771,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Northern Emirates’ property markets cool off + Sidara locks in USD 1.35 bn in firepower - EnterpriseAM</t>
+          <t>UAE VAT rules change staff expense claims: What businesses need to review - Gulf News</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOMDUxZXd1MElSNXdaNDByLW9jbHFIenJCY21PRnhPMUx4YkdyZ1FMREVxenNWZWZUY2p3MHQ5V2xUQmswZ1RuV1g3Q3RHUzdvOFhvOGpST2diQWIwOXFBeXdzc1lYRl9FRDIxdjBjUVR3Y2VEcUdIWXB0amg4YW5qbklORzFMS3J4VUZGelkybDVZcXc0VHlNck4zTXdjR1N1UzZmSk9vSFFoMDJMVENKMFVlWEdvUTEwZFhiZmdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPNjVZSlVOR1Bab1VubGlRNjZGeDNPWmVNSnRSNDlCXzk3bFk0U2dQTUt6dFlMVmY1QkpvWU1XMlVoQTN2MzluUVNxY01BYWtVb3JuYjFNU1dfQjl2X0dDTnJrXzd3eFFpanBCNGk1QS05LVAyVlliZUgzRFJhaHFKaTlsOTBMOExqLWtBUGZDaXFSZmVfZkRPQk9YSzF2VlNiUlJtbU9RWndXLUxjMjhoN1ZwYWYySDZHZkJRNGdTak3SAdMBQVVfeXFMTUhINEdZNjQybDJ5TjhWUkMwNDBmcENESVUxc214S044NTBva0JGVWNJMFFidVczdFVuN0U5d3VIT1dCczVFLW00LUczN080X0xVWmZTbVd2dkxEaWJBZkxuVHFuWjBoeWpDczhpVVJ2ZTVaY0R1dVVtN24tV3R0bU9WVm52M0lBeDQ0T2c3cEdBUjRjRHFkQTdiUl9HTmw2dmNDTk5BRkpjdVN0NlJaRVR6emc1Q2lpQUxocWx3SFFtRDFRZkI4cmMwLW5BTVhwUWNQbw?oc=5</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -1816,12 +1816,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>ClearTax urges UAE businesses to prioritise execution assurance as e-invoicing decisions gather pace - Gulf News</t>
+          <t>UAE e-invoicing deadline in 4 days: Who must comply to avoid Dh5,000 fines - Gulf News</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPTG13TFpCRmpaaWU3ZGxsVEtqakxUUXhSc0ltWUZfOEUyWTcxWGhOZ2doazNZY1V2LWFnSlp0NHpHTXN4emN6TzFWbGlXT09xU0Q3X25BTmpBVVl0Nl9XMFdRUE9HMy1BU3BMRDFIZ1RITkw4d3BSanluZGFHal9CM3h5dDNtTlBtUG9LYXZZWkhILVZhdUpKTHhUd2lMWmVOdVJrREx4UUF4WjNvTW5hSmtBVjVyQVBpblVKa1hKbjhxRTNUVmpUMVpXOFFJSWx1NUZWUWFMYlY2ZjA2Nml6OGV6X2ZGcVhkQkQ00gH-AUFVX3lxTE12b1Q4Qjd0Rks3U1hqOC1GVTZ5RXRUOXB6eVdVd3RMTEV5Q1pRYVRrc19GaG1qY3FXRGhqMkN3N3c2emJyeTFWbEU2QkRSMHR5aWFzNlctUi1mdi1vamRHMHZoWFZlQlRCbEhrT3BLSXlsTXRfYjY4QjVHblFRU0JnZVhlam4xNEF6d0hQVUtmTHFoYnktSW5LS3dqU2VleEh4azlObnoyUTNPd2E0RWc4U0ZhMkRoc1J1c2R6VGJhc1lSYTF0cjhzdnY0Q0tvYk81YnY5UE5CdnBXZTVNQXE4UlZwMkFjbUREaEtRNlF2MWJYVFhaOTFJNTZRUlJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNLWxHNTZNMkNZUTRHY3hWSFRld05JZm9FRzh3TlZsQzNCS2NqX3kwQjBvbFpjUXBCSG8xRmRLUFBhM25YYTVVNXNyQWFmYjdUTk9ndTZCRmY3dDVObUpsLW85bC1pZzUtWGM5UmR3d2hEckZDUDEzdXN2MEN3MXpFa1JaZWRDVGU5aGE3Ul9nVlZPN0FhVGRjSlctX2lnSHNyeDQ3Z2RFTEN6UmRZRXVuMkNBbGRrbFJfaGpZazZQT07SAdMBQVVfeXFMUEhrM2xRZk5Uc2Z2ZkRUV1p3bGpQSkEzaGpaQkdhZ1lrYld2LUMxd3ozdTh6WmxJVkJYNkJCeGxGOURPY2dsbU9RdmphOXpncm03bjZvSWRDeUp0Ykg5NmpOQjUyZ1MwS08xcTdzOXhnSFZGNklnbGxpTk44aldNOFJrNVNuS2trMkphb0xpOXN3ZU13Y0JmN0Q1ZlQtWTZscmNwa0RTbGg4M1M0cHd2R2NXTV9fRFZwQk5aNjMyUF90VXUwX2prR09OaklId0VYSFlHaw?oc=5</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -1861,12 +1861,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>UAE extends small business tax relief until 2029 - theaccountant-online.com</t>
+          <t>Ezat Alnajm on Preparing Crypto Wealth for Greater Tax Transparency - Hubbis</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOMTA1XzlxbnpmYjNMcU01VXV1RjdMOHFuMi1CSVNMYXlaNW9kb2ZMSXZXOEZ1dDlqbmRLR2hXQjNrMDdlaU4teDVRTG1CMmJsY0lDU3V0SWxRZE4tWXZXbV9pR2o5THFMREVyZ3VpY1pTYVhFeUJza1MwOWtVYXB1ckwxQlBRdVF6eURUUHlkblhUNnNoQ3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQRkVXSUFZWnYwTXRYTG5GZUtmN0pZLWx2anJoNTM1VERGZUVha1JZc01kMWxHek92SEVEbkgzeDgyZWh0RXY3VFhuYVJKcTlNeklhQlJvUVB1WXNnMVZ5WUFmY2pxYzNqblZRYkRBemxhdzktaWhwLVNBZFNqOE9RVGlsRm4zazVuVExuUGZtQ19JM2xFRHFldFdxbmN1Sjg?oc=5</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -1906,17 +1906,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1926,12 +1926,12 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Sovos Announces 2026 Partner of the Year Award Winners, Recognizing Excellence in Strategic Collaboration and Innovation - Business Wire</t>
+          <t>Ministerial Decision No. 197 of 2026 - Crowe</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxQRzJIdmQ3VjZqenlUTldPal9HNXdxdTJibTJHWFBhMVBMTWcxbm0yeUhJYzVLd0Z3Yl9pdE1LQzREWm13dXE4ZG1abDFuRkZIdHhIcm4zYXVoOXZIS01KNW5xRU04SUVwMlRnZlBxb3BYQkJMQ01CeXhabEI5U1VfSlpad0ROaVNnTUVnUll2WFhwMkxUa2tidGRxTDlMRm93SlAxVkNoWW84Zk1oeFFoNVdnOWRBZERIZzNSdnVDMGpHZ0MzSXlxZ1JXc2hodEY0aXNoRkNBRldSOGdxSkowdmFoTEplTjBtOUVfeWFtNmpzeDZtR3J2bVk4UWthWFR5VjJRbEM2NA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOMFZaS3RKdnpEdVpQcUtlN1JJWlBuZmxxRkpnZHB4WXFpUGg1cHpjcHdKUzJlM0VTVExnRExWRkowZm5iek1yUHpaY3ZWamZfS3ZpM0tkSW9MTjV0YmxHOFhpeDltbkxENmZLamJkV1ZKMklZUjAySU1aZGVZSnRMamIxejJBdw?oc=5</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -1951,17 +1951,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1971,12 +1971,12 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>UAE E Invoicing Guidelines Updated to Version 1.1 - Crowe</t>
+          <t>Amendments to the UAE electronic invoicing system decision - Simmons &amp; Simmons</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQOGUxa2xtLVY1ejE0azVCMEZSa3lxNHZmajhUdzh5LTQ5NGRqVk5oenBzNmJUSk44X1B0elZ5aDI5YVl4VHpLb2RzdEFRYW9IVmR5dHpOaE1JbWVoNzdvQVpsR0xIalA1MHBaR1NNOVpVSHUyX2t4R0dIVmZiWHlXWg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOUzJMUUdnR2Z0TjQ2eEMteTVMNHpOZndFbEh3T1hJaVQ5Z29HdXRlS3lTcXdRbkFFMnVRdFI5a0QzMzlQM2EzZnBDY1VDLXJUeFI5T1VtQnJ5UEFHTmU1bVA0bWJiMTZwTmhFR21sZzE0WEZReGRwMWRDalVDbm9kVWpVM0VfTmJHeThySXRwYjY0UzZXS1NhT0J2T0tGLVczYjk3Mno2TDZPeU5BbGM3VGR6SDJYR0wydkkxNUtYSzM1a19ocnhlNWQ3VS0?oc=5</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -1996,42 +1996,38 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VAT, E-Invoicing</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>official</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Congo Republic e-invoicing launched - vatcalc.com</t>
+          <t>Ministry of Finance Amends Electronic Invoicing Regulations to Ease the Burden on Businesses</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>Ministry of Finance — News</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>news.google.com</t>
+          <t>mof.gov.ae</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOLTlBQUhqTDJya1ZpUmx5Y0lPRlRHb0VpWW5GYWVBc1JkTGRFbFl0b3N5UGJSdEdXRmwxdld1RlhqSWVremtIU1pWSHNXb2ROejA2TzJYcF9RX29TQVN1akJ5d0cxWFplcmJPYUJTRDgzU2FzenRzMzJldUsyaE9rbzlVUmJMSEc5M1pzSGtR?oc=5</t>
+          <t>https://mof.gov.ae/en/news/ministry-of-finance-amends-electronic-invoicing-regulations-to-ease-the-burden-on-businesses/</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2041,14 +2037,10 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Other</t>
@@ -2056,27 +2048,27 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>official</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Corporate Governance in the UAE - Crowe</t>
+          <t>UAE Breaks into Global Top 10 in IMD’s 2026 Government Support Index</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Transfer Pricing</t>
+          <t>Ministry of Finance — News</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>news.google.com</t>
+          <t>mof.gov.ae</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE4weWRYb0VETFpvMjdhUG9BbU5Wb2JXbzNkLVpxSC1VZHhwYjMwT0F2OFNvQkJNQTFkOG1OamVFZWU0NWpVN3hHb0lldkJWLV9GeThwSjdzNlpnQXp0VDdQbkpnSWFFU3lacVJOeXl3?oc=5</t>
+          <t>https://mof.gov.ae/en/news/uae-breaks-into-global-top-10-in-imds-2026-government-support-index/</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2086,42 +2078,38 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>IFRS / Reporting</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>official</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Shopping online in the UAE? Tourists can now claim tax refunds on Noon orders - The Global Filipino Magazine</t>
+          <t>Ministry of Finance convenes Financial Data Forum 2026 to boost efficiency in final account and financial statement preparation and reinforce the application of international accounting standards</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>Ministry of Finance — News</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>news.google.com</t>
+          <t>mof.gov.ae</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNa1BKRVpJRVZCZm5VNVp2d3h4Rl92ejg0aml0Qy1pTUotYTZ4ZHlaeURMcnRacE9Zc0J2TWt4VktTQWdFV3BlNXBzWmlfMXFEZFRiYWRIMmV3X3ItaWc0T3pzOG52THI4c1RQaDY1RWdNbXItTTUtdlFTS1d6SUpZTVlXM2lOTWtLWXF6TGNSRE9OWkJQSUs3UXFoSEtOa2NpNEJLeTFOektldFVUVHk4cFJCSE5Qdw?oc=5</t>
+          <t>https://mof.gov.ae/en/news/ministry-of-finance-convenes-financial-data-forum-2026-to-boost-efficiency-in-final-account-and-financial-statement-preparation-and-reinforce-the-application-of-international-accounting-standards/</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2131,17 +2119,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2151,12 +2139,12 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Number of retail outlets connected to Digital Tourist VAT Refund System reaches more than 19,300 - Big News Network.com</t>
+          <t>Foreign outflows in July were the lowest in the GCC - EnterpriseAM</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -2166,7 +2154,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNUjRVVzdLOXJQTXpUZDhqeWlQNDAwVDV2ZmJqd3h4cW5ZbXc0cHEzZGJBSWlLOTk0ZlFFbXlVSThCUEtxcGFqUHYzSlRmeXF0bC1XQ1J3VVhKUUkzeVBfNTc4cmQwNmlRYldwUU01YXpmc0pxT0daNWRpRUwtM0N3MlBBR09rRldZZlA5bXVJOXVTcVZSeE5ldWRHSWhna0ZfTTNwZWEwODlFTXRRYnRhOVJVcHJ3dDRuSnZtQlBhc0NMa2dhSzk4b1lBWEx5Uk5Ld2RMaFdmNUY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE8tRko4Unh0QWI1ekpUTHJ3QmktT1dyWXd2S2REcHZIZVVvd2Rtdm1WSkUtQUtacjlnSGlLdWtIMk0tVVNxU1ZKTU1qSVdpc2NOUjBGWUh5STBrM0E?oc=5</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2176,17 +2164,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2196,12 +2184,12 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>UAE tourists can claim VAT refunds at 19,340 stores and on Noon purchases - Gulf News</t>
+          <t>UAE extends small business tax relief until 2029 - Yahoo Finance</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -2211,7 +2199,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQeDRPcDE4QjJaSFU3Qm1wRGVaWXl6cjY2c3YyVDF3TmtqN1RYMkh0WDdoSm56QmlXU21xSllRQWt4WHNFU09vUWZpTEd3dVVMb0UxNy0yZG1ucUF6aXhIZ2dWVXpkVjVqa2hHUGN3VHNZWEticFZMXzNfb2NzaVpwOFFkOVAtNDhBY0xjSUo3bkh0WUg2ZEJ4Q0JDU05Td0FTLWlUWXNfN2JKeGJsTEg3NGFDMzNwT21JZTFGT0V30gHQAUFVX3lxTE9wdElvSG52YzNWWUt6WGJaRkp0LXpmVHpQTFV4WHczVkQtOUhOMWpqRzd2UjgyQjNOSWdMT3QwM1luZzdtNWhXdU91R2lqS0FKcG1hUGExZ1QxWG1SSUo2cWZSWll0bjdpQ2pBOXFjTUMxcjJma0RraGlVbjNjajZRM0h4OVZfM0FUQXNERTQzQm1TS29QVjdiQzM2T19naktoTXhfQ1pvNmx4U2IxVkkxUWF5QmZ4QUxmMXB2bFVvR2RVWm10bjE2SlNaRzJ2VEU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNM2FhblZZVW5LVzI2bmRYWFhadXJ5bGU2OU54U3UzTmpGWmlweXlYTVVSWHpXaXU5YnJLNlh0STNsNmhYdG9feTdsN2xKNWlNSGZRM3loRllITXB4U0ljUkpyYllpLU9jQUZVOVdab1Rocml1OWxsa1lKWE00Wk42QWZRejVCaTk4QllWdTJTMWxJd2RKbVZiWHo4UQ?oc=5</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2221,17 +2209,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2241,7 +2229,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Retail outlets linked to UAE's Digital Tourist VAT Refund System exceed 19,300 - Emirates 24|7</t>
+          <t>UAE seizes 8.45m non-compliant tobacco and drink products in six-month tax drive - Gulf News</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2256,7 +2244,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOcXRBMGsxX1Q5SkJXcEFwWnV3c0VVc19jUnRkWU5yMVlPelltaEhvOWNLcEJxYi1KUExWMVlmZE1FOExZYklsRHU4N3lQZGppMDRnYUFaRU1OWHdwaVpiWWowOENidVJjbDFPeTQyQklzOGM5bXhQbDJrRFg2TkR6bUplTzJNZzl2M3dJT2FEeHVTTVNtTml6UEdoZUFDcVRCZWFHMGg1ejZoSWI1UWFCLV9zREotcmF3V0HSAdQBQVVfeXFMT3Q0RFN0V3FRSlNWV20tMm5hY1N5VHBVWmxzdnZGVXIwZU92VTZVRDVUVkRZM0Q1U1ZNZzFRcFlEWTc2ckk0UjZhcEN4YmZIZndTd284ZDQ3Z2Z4OS1mVGFUX2RwRzgyMWViTjEyQ19wdUxucXEtZWtFRm5tOWpId1VYYlRmd1Rkc2tlb3Q3THR0THZxZWt3Q1ZyTGVvZ2hUUzZPeTBPSzlER3FXR0ZvUnJiWk5vdlpwYlYxdmZjZnNTVEQxM3hSY1pyTGV5Qkk2d2lrejQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOeXEwYUYyRVl3dzRiREtKU01zOTFJNXZCNVpNcE5wYTUxRUN3U1A0SkxudUUxYkI0WHUzUmZoelZBLUJSaUFFcno2WFc5bzNBR2FQZU4zSkFuMTNWbkcyMVNMdXc3dmplcVNLdDRsN2xDdng3ZFg2UnFiREgzZHIwUFlpUkhxdXdkeG0ySXJQS2Q2LWJJRGxrbWZMT3AxTU9KWWM1OS1qQ2FET0oyQjhhZFNXX3RDWklhU3VrdTM2aTRRcFIxdXlWOHJB0gHcAUFVX3lxTFA5OFBJbzlhcVVXbXNwNWtBamtpbFdwbVkxdHFtSTJXWk9TR3kxZ0F6UFVtQy1EYnpaZUM2Vmp1enVjeFJoSjR1ekpMenVHdEhaTlhGdmxKUzQwV1BsQnpiNXg0UDRpTndaTjE2RTJBNzFIbzNEZExXWlhmVnpYT2VTbmFsNldOZVlzX3BsaU5xUUplai13SEl2RUdpNG0tWTJOd1BCQkVaUVowX0NiZHF3VU1BLU5VcVpBb2RoRXVERGdaYmxhMmhEd3MxNVRoekNKQ3hZeEhyWkUwQUg?oc=5</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2266,17 +2254,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2286,12 +2274,12 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Indians, Russians, Turks top list of tourists claiming the most VAT refunds in UAE - khaleejtimes.com</t>
+          <t>UAE Extends Small Business Relief for Corporate Tax Purposes Until 2029 - entARABI</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -2301,7 +2289,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPek9sY1dJUkpRblhiYnJDdDExOW1yREdXd1oyZ1Yxb0FnZlBYNTd3SUxGWnVMenlZVGlqRlIxLUszNk1Jd3BpcF9rVE9XLVF1OWdhY01fd0gteTJFRkVJLVREMjl4ZVRGZHJacUxJREpRN3UxdHFncGhITEQ0MnUzTkhKY2FSZnBnaFUzZDEyRnZOdG1hOWVFX2FLNG9Ca1lGekQzcllxd0FqTUhvTTRZM3MxcElQV0JaMWfSAcIBQVVfeXFMT2FPTEx4WGUzNUNhZWdBa1MzVU5GN1p3SkRwM0o5TWlqenhqVTNhR1Z0bThyN0laMS1tOUhfaG1qMmZpQi1pT3lTNEhKT2l3SklKZ1E3MXkyYVBrMnUwOTh1Y2RxSkFISUdlT1B6Qm1tTV9CUV9YM0xwcTJ2NzVmWUcxaFJ2YzhYeVBjZG1WSG9vcVc2N2tqRzNreHFwWVpaaUdncndzVEVLaE8zeHczU0Jvdl9FazU2NE1CNWZqQmZmekE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOV0NzYjBEMHBFM0dLeTRxdURMWjYtZUZ2OXpSTENyYVozcGpPWkVBb09JaU1pQjAtWEVTdlcyQ1VjbmNGc2NiT05jWFUxMTNFVzFJMHlHQlY3VmxDaU9XUVZwY21yS1ZFYldWckFZallwVDU3Y1ZzLVNKbndvMXVGckJFMnRWNUtNOTFzRlgzUDhMbHFpMEZsRk9XejN4S3F4cld0aTJPdw?oc=5</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2311,32 +2299,32 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Transfer Pricing</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Tourists can now claim VAT refunds at 19,300 retail outlets across the UAE - Gulf Business</t>
+          <t>Tax Insights: Canada introduces a simplified transfer pricing documentation regime - PwC</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — Big 4 UAE Tax Commentary</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -2346,7 +2334,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQV2tyUkVhVzNVUlZ0QW9LdW5PWV9OTEVSN1FHU2c0Um9qbTRDNXFIdmZUaERGcDFPUkkyTVpzWXBQblJHb1VzVERybTh5WkIzcnRoRFo1ZVBicVRMQXpFZXB3VVJRQVZ6UDNNZDItT1RuTXcxYWxtSU1PaGlPNTFNUnpzLXBGX2QxSy1WVjU4alg4Q0dEWmY4WFZ6cEt1a1FZQXpRODFFN0xRT3VwSWFfNw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOVm8yXzZQUVY4R2djbXBUdHQ0aFUyQnFaSHNxSkFCbTNxNmxSVTZVUHRxa1lvVnF2Nlk2bmhTQ2w4ejJaTVR2NUY4S3VsajBFTEV2dkRwbk9BbEh1MWtwczNVNHgtQm1yaFJwc2NlZldqM053NGhwbE1TLWR3eDNIQ3V2ZzhTQ2JmbVJlNlliMkRoalBfYzQ3WHdVaXR2R2MzNEw1dGRQNzFfRWxTWklzYkJNYVZKVjFMclFQQjIzMUU?oc=5</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2356,32 +2344,32 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>UAE tourists can now claim VAT refunds on eligible Noon online shopping purchases - Arabian Business</t>
+          <t>Canada launches public consultations on steel imports and imposes surtax on wood cabinets and vanities - EY</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — Big 4 UAE Tax Commentary</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -2391,7 +2379,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNSk0xOTlEQk5DQm4tczlCUE1jZ1dmamdsaUQ2TUYwWnlNd2JHMjhhVXZVUF8wNGpSVUFRNXhvU01pY01FMlUwWEt0anFyS3Q3QS0wa3BjZE1YLWtkWkpYeUJxVmlaSUhQM0Z3Mk9odUFYenhNRnBZeUkyQ0doNWJ2VGUySGY2dG9kMnlJaWhuWEMzb25aWjA1VXZkLWRwelk1MXJjbjBrV2F1Z29KZTJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNMy1qdEVRaXhDVUZ4c3FTNUlCS0F0SEhoRnQtRk5BTnB1d2VFSmZSUk95RmRSdEw4LUFBV1FwYTIwbTVLZHdqOEdkcDhRb29fWDc1cGN0ZFA3a0habW9iY0NWam9LZmtfa3c2NDlLZ3N1MVJYWWRwejlhM1ViSndzZg?oc=5</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2401,17 +2389,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2421,12 +2409,12 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>FTA issues five binding VAT directives on tax transactions - kpmg.com</t>
+          <t>UAE extends Small Business Relief for corporate tax - Absolute Geeks</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — FTA Announcements</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -2436,7 +2424,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQQXptRUZOQlpWYUZiNzd1QThPVDhlUGM3TF9PU3NKZjUyS2lucEZLUUFKZFpfZVhXLWxteTBKbU1OVEU1WXdPVlViT2ZBb2h5dmlHa0Z2bjd0SzMxa1p6TzF0ajhuVFVSaUpkczUxd1lzeGVCeDNwRnpPbXJVNVNGWHB4UTcwR2dCYTJoWTVSYkJGQmxRZE42cXNmOExtclgxR28tUUdYVFRzaE92?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPWU10OExoZmlXRjdCamp5VHROMnNDb1dKN1I3NE85dTI4aU84VjVvczlyanRyWEw4OVBuOWpVa1NJZm9qQ2hSZl9YYlhxOGNEYXBCeDlGQVF1RUV1TWJlSGVmdnpHRktyS2ktV2IwQ0s3T3hZMzV4Ni03aGdvVTNHZFhEYThmRE5uclJqR1BKUF90MXktS2xEaXctR0RsLXphM0g0REdvWHY?oc=5</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2446,17 +2434,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2466,12 +2454,12 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>UAE extends Corporate Tax Small Business Relief until end of 2029 - travelsdubai.com</t>
+          <t>Spotify forecasts slower growth despite AI investment - Gulf Business</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — FTA Announcements</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -2481,7 +2469,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOYzFrN28yN3RDREhxYV9CVHl3UGU1NlpvSFJqaHJGWVpraVhEOEtqTnZVQk1OTjVjX1djWENocHdtYy1WY1dBSHZncjg3aGxWOXlwcFktaVVxYzBmZllLbzBaLUUxSEpyNW1HX3V5MG9YMWhTcjNfcnZxQ1JKRHZkMjlYSjlmUHk1SGFEYy0tYmlqWE96ajBqUnNSS19TUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNQUhDU0xPaGxHNTZZdDNmRFRsTndvQThIUkRVV0hyTkpVbWhFNXdsZ2hjUXFrNzByWEc1ZUdITm1FYkM2N3k5MW5paDBud1RfNGF4MXNIdlluaVktTVRfd0RlZzJpUmc0UlZ2WUlKU1VDTUdELXpoelU0Z2kteENFZjVfcWx5YmhLc21jS3J5VXVkeEZ3UXRV?oc=5</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2491,12 +2479,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2511,12 +2499,12 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>UAE seizes 3.58 million non-compliant excise goods - Gulf News</t>
+          <t>UAE Sets Minimum Excise Price for E-Liquids - Vaping360</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — FTA Announcements</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -2526,7 +2514,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOOF9vUDk3UXlsY19FUWtOOEJ2V3Awam9fY09zeS1seXpTUUt2Y05TQlVUVjlwYlVuX2hRN3JBM095eTlqZ3pxWWx5ZWJzUzV1bGdCQ21JMzd1bjRIMGRMdHpiZWVOM1lmOVdtSXlicW4wYUNoYjMySjFTNl9OTnRvYWZycGdhODlTcU9sQUpwUEdJcnltNF9nSXpBWkpJbjF0VG1qeVJqTdIBugFBVV95cUxPMDVISGFVMTVqWFFiS0VMTmlzZzlyWXRVUl9BTjBGaWgtS21lN05BdlppYlVNQkNtYmZWaHRIczNlSWRmbXBBdG9zamlobjFhTFh6R2lYZFJ1RUtKWGZqOWpNd21LTmNxaUF1SjVIUm9UNjF6cmwxUGY2ZHFIVHBFdVJNMXcyeFp3dUZ2V1hpVmtnRmZOY29nLWNWQmxsQ0tHUzd0RjRyRUlZeW1adThtZEpPVl9KT1pFRUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE9HS2ZoOFFrdlRtX3N4ZXM5UlpzLTFKc21Pdi1CVkhNYW1PNGozMDBVYVZ0VjlrUDNCMFRQRG1hOGpPNllSd0dpX0dhNm02a3drdmZneHpQOUhtUkxXWlFBcDlETkt0dF9xalFRMldrVWZMSXh5NHc?oc=5</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2536,17 +2524,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2556,12 +2544,12 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>UAE Extends Small Business Relief for Corporate Tax to 2029 - tbreak.com</t>
+          <t>E-Invoicing Readiness Checklist: How UAE Businesses Can Prepare Before the Deadline - NewsBreak: Local News &amp; Alerts</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -2571,7 +2559,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9icS1QSXhYc09ROHVJdzRtdXJTMEdLa0o5Mm5TZ3VxR002a3lTeFR5anZqRmNtcVEyQWxfQ050UFVOZnFBcFdwT1VoNGlVZU9xYkY2WkM5SlpSSnp6QkpHck5rTUxqOXNjNjM0UmFTQkFfOXZySFFON1pCSXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPQmFubHpKbnIzS2N1cVJkbFA5bDRWcUhzQ0lYazZ3Z0ZBazZKQzVoTjRxZXBrMFNNSGNXTGp4ZG1EZ0xTTGFwanZQZkxvbjA5UFQxYkNBLWF6bEtDSlB5UlcyNU9fc2E1VTRNMWtTYnRyOFRlTUxjRlVlcEVwRVdDb05OQlo4VC1GcUpqUkpmVzhsUmc0RGJrZlJWN0tCMXVQc0d5dTEtT055TFRDT3c5R2pUN1hpaEF3R21TOHo2d1pNZldNcUE?oc=5</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -2581,17 +2569,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2601,12 +2589,12 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>UAE extends corporate tax relief for small businesses until end of 2029 - Gulf News</t>
+          <t>A jumpy July - EnterpriseAM</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -2616,7 +2604,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNNEo4Tm9qN1dERmwzZ0tMR0ZOSUVQTkpOTTNiTDc1U2VaSTkyRkExekRzRjUzb2xrelYzV0oydU1qS2JCbHJXd1hxeWhPdmtUN1UtcXRCOHZpSXBxMlBMdFRKbDNxYlNFaVdwRXROTUVxWC1tZUpObDVIZzNVUDEzSUZpNkIxN3ctTDRNWU9xOUx6QXZieFdVV1hkNHhlcldHUzY5b21BZ1J2VTVhMlN2a1V5V1dJRkw1OTItdWo5Qzk5N2lPX1HSAdgBQVVfeXFMTmRQM08wYWhkelVySDhudHZWLWQyZ2lyUG9TNEJhWVV6ejAybDV6QXdvUFR5ZndxZldxWHVDMjRKVm1Ndm0yeE1HZHo1LXoyVFBzMkhuUDZESEw5RUFIaWlfNEdObjNxRlc4VFpOZVQ3RDhhellsdEpYN3pLVzl1d1Fva3R0RWpDb0d5cVN0Z3I3emowS2tNbkplWTh1Z2NvVkRMd0R3STNWV3hrUVFtd3hxdjQxWjI2ZU4wVE9JTzlsWVUwYXlPTmU4YWJmazMxQk93MHVHbGZE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBCcFdtSjE1bW5pMlREMHVqWTYwcW1xajViLWZvTmU1MUk0MUZiX2pPay12Nm5RS0tzdmJjYU9VY2hjUi10enNsYk1qcEZqc3FQc3dEZE1CaTJRYTJvVWc?oc=5</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -2626,17 +2614,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2646,12 +2634,12 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Small businesses in UAE urged to file corporate tax returns before deadline, says FTA - khaleejtimes.com</t>
+          <t>Another Hormuz workaround - EnterpriseAM</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -2661,7 +2649,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOWnJlYmRmRm4xdy0xZ0toMUNUbnhTd3A5UW1pVzhFeXhIM2txamo4NU5qYVYwZGlQcEYwLTJhelBkOEdHajRYSE5PRnZtdmxGWmc0R2JlUVk0eVc0aW53NzdlM08zeWFzTUNocU9UcnY3UTNhTHVzZHhjRXFPZ0ZMMHMyRExEcjFiVVhKVzMxYk9FSHUxdERQRnUyZlJLWXA0ZVHSAaoBQVVfeXFMT3BwVV9lZzBQRTFjWUNVNEFzaUlhOUJuTHByVVRhdjRTbjdpajdOTjRtc2hfOEotMWlSb0FvX1F3azI2czNjMHREWnRJbFptM0F5ZHJkWUFsMW5fMDBsNU1YODgzT2VkMWZacU51MzkxaHJ0S216TF9UR241SnM0OVo2eHlDM0F6V2VfbUt4elZfZVBub2pLNW5fazhqV1hNUnBzRmkxS0NUQVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5iUjRXRTlrdVBXOHUyRWlYc2ttOXdYaVktOE5ZU1YxMnRLcnlHeWRPdl9CQmRkR3Bqc21aeFlWMmdFcGdjanc3d2RNTnRGcWdKVGdxQTZmeC02clJoSXJJaGJlUUM5TW5pQjRORkVpRQ?oc=5</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -2671,17 +2659,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2691,12 +2679,12 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>UAE extends Corporate Tax relief until 2029 for businesses earning up to $817,000 - Arabian Business</t>
+          <t>UAE e-invoicing: How digital invoices will transform business - Khaleej Times</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -2706,7 +2694,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE5SM3FoRTVUSmJwTlpLbi1vOGFPM3RPcXpraXlCUG9iQlhuUUJ2MGRCczd6aDM0MFFNWS0yS2tNNVIxYjd2Y3AxWExhUnJNcHNXT3dLdGhyV2FBQUQwbmZ3YjRZc3NXTkNoLU5HTFRkTWRkSlZ6TEtHbg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQMjFwZTd6MkpqcXZKaEwxZV9fUlZWSEtSeVdIQXN6YXFPMURFMWZhOHc0NWFuWlRfd1ZNX2doQVBpbXBqRFBTOVNNcjVTYVpOcEozYmtoaWxDUHVoUFFNT1RBWEI3RzJybmFWejFNcEcxYXpybDBiUzRLUk85ajBkOHIydnBjOUV6NEVJUjZkQTNOQ0Fud1BjdGtUNVpwTmlTazdyNWZmaXRwTkthY1Nac1RPWU90T3lMemJJNHp5VdIBvwFBVV95cUxQMjFwZTd6MkpqcXZKaEwxZV9fUlZWSEtSeVdIQXN6YXFPMURFMWZhOHc0NWFuWlRfd1ZNX2doQVBpbXBqRFBTOVNNcjVTYVpOcEozYmtoaWxDUHVoUFFNT1RBWEI3RzJybmFWejFNcEcxYXpybDBiUzRLUk85ajBkOHIydnBjOUV6NEVJUjZkQTNOQ0Fud1BjdGtUNVpwTmlTazdyNWZmaXRwTkthY1Nac1RPWU90T3lMemJJNHp5VQ?oc=5</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -2716,17 +2704,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2736,12 +2724,12 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Finance announces extension of small business relief for corporate tax purposes until 31 December 2029 - Zawya</t>
+          <t>More investments in Adnoc’s fleet, Indian IPOs, and Egypt’s North Coast - EnterpriseAM</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -2751,7 +2739,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOWVAwdTI2R09XSWRHaFNWYkNGdUJsSTNnaGpRandNeklubW8zM2h3VkNIcmRiQTVrZUxlSnhydWtqUGVTRS1vYVVQWWJfY2swUzhYOFJrdHVCQTlvTk1LNVBfWjBPbHZxWVU5Q0xQVWFHbTlLYlE0ek1aWFhqaUF3dDlTY2p2T0dtV3gzSXhaWkdFdWFBejA5ZkhDSkVPanZUWDk0d1oxNlJOUkNxMER2M1oyc3Nla2NnUW9WYmFRS04zeGlCcjQ1YVNZT2ZraU5EN0h2ZWRDaklZTjFQUklLWmRGRVFkUjhKUjBybHA5UktLZHFiVnUtOFpuNmhSZ0o3YVV3eld3WQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1RdV9pa3ZIMmpRWnFlcXRaeTRnSy1zZUp0enVScm1nc0hMX3UwTEdEOG9oQy00UUJiSUR4WENleElGQVVmLXh3ZE10b09nQWphT0IzNHNJb0h3Q0E?oc=5</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -2761,17 +2749,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2781,12 +2769,12 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>FTA reminds small businesses to file corporate tax returns - Sharjah24</t>
+          <t>FTA Directive No. 5 of 2026 - Crowe</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -2796,7 +2784,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5NZ1VTdFlkVERkd0pETmFiVUQzZzEySVNaeWFyV2N3MHdhSWZreEZnUDFCYXhiWGtCOVVxMFdWUzhDa3JCU1czenE3QzJzaG0tNU5iMkFmRFRsTUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE40S0RnRzF2d1dBSmNHdkNNQXZQQmlOYWNOSk5OWnlVNUN3ZDB5UHBUV29RXzNvaF9pVFNQZ2FwTUdocGhxMXp1T3gxMUFycGNESFA1bXNR?oc=5</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -2806,17 +2794,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -2826,12 +2814,12 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>UAE extends small business relief for corporate tax until December 2029 - TradeArabia</t>
+          <t>Digital currency and VAT: New UAE rules for businesses to consider - thenationalnews.com</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -2841,7 +2829,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOc3RJWW11LUNyUERIeHh0dTVRVFJySzBoWVB0N1RCdVNpTVpORW03RkVXaG1pdk5HbWJfTDUzYXRIellIdlo4dVBXcXpuZHNrQXZRMk5MMGF1UkpqbGRTbXZRekZTYkU3cHpsdmJHdTVRdFFxSE1aSzZxWW1rb0RuT1RNZzVOWG91OGVTcFZVUGFVLWRUY3JsRnEtYkR4WUJjWnp6NkljSUd2NExsdUYtVA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQamI1MElzOEtNS1ZjVWR3VGpjZjNUZjBXbjQwZkJIZ3AwOFVqckl0WWFQN2JpaEg5XzRTUTBVMDFOeVhMaUZxYW9GUnBFNW55WnhKd2ZKOVZoekRBWUNqQkp3dGFPZ2JQcWY5SjVlRUJuTURfcVN5aUNXVmthdUh4cHlJbFNHN3lyT1VTU2l2Nk92U09JZFh3eXp0c29jTlJNZW1VLTZBR2h5WmdBTjFuNGczZkZwdDY1QWc?oc=5</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -2851,17 +2839,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2871,7 +2859,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>UAE tax warning as thousands of businesses approach Corporate Tax deadline - Arabian Business</t>
+          <t>Air India turbulence injures passengers on Phuket-Delhi flight - Gulf Business</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -2886,7 +2874,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBGbVZOWkkxM2FaVGlfeENJVWJXYzN6SDdmNk9nOFBYWWJDV3N6eGxVcnBRRXc5cDY5Qy1xSnNBQzVHMXR3NGpacEVucjlTMFRSaHc0dG5aZXc1aUVwSXlrTXhFTGd3RWNMbzVpWmdEVUZuUC1N?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOUk92b3hCQVZybGNndXNJOF9ZX0Z3TGl5NnRuXzE5NlBRb3czZXM2SkxXb3ZQSGNOdGo2a2U2b040ZVFDcFBqbzdvaFFZaVdBbFgwQkJOOEhDNzF6VXY1OU9Ca2t2Z1ZnQlhscXNXTVhDaWY3b2lvMUlEWFhkXzVxaDR3b191OUx2aTVKcEttYkFGTjRzRVpnbFJvLUZhYmNLTFJJNg?oc=5</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -2896,12 +2884,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -2916,7 +2904,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>UAE reminds small businesses to file corporate tax returns even if no tax is due - Gulf News</t>
+          <t>UAE Business: UAE extends small business relief for corporate tax until December 2029 - Gulf Daily News</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -2931,7 +2919,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOTm96UlB4Q2xPRlcybWNBanAtYXhxQkg0eHVCNDBvZlZGTWNGNzlSekNuVWZCU1JvOWR4MWxLanJMZEsyRms3NnZDSU90RnZuTkhad3pLLU1XX2VWV215T21HMTBmbVF1X0hmakhwM1BYZVNUQXZEV3A1UmR0QkZxVlJ1VDV5dGVMMFJFSGRxckpYVkVMMmFNMFBBdE9MZnlFSjJ3MDFXNzg2UXd0SUthQlZrd1Zjdy1JTVFkMEZlU0VKc3lzQW84VDBGLXFfVF93SnfSAeQBQVVfeXFMUEpicHFURTEyaDByTG44RGZUZ2R0MGJwRmdpV0hydzNTdkVYd0lFZzNITm9ueldCQ0JUZjZ3dW1TZ0xCSHM1S3c5eXExQlZac3V6bGd5Q1EzWFljOVRrZkJWRV9XcnFQWHdzRHQzWDRiUFhHaXlKMldlZHp5YW9zMHh2emxiX0R3MXdva2NFZ2JwcnVBZk52dEh2UEhvTW9FYzlJQ2xWdWZPQmpteFpaWnNUV0lpUTRiT0hNRXdHQVg1Q1VibWZqVWdocjBVVHJtVVFUbVFBdjJoRndFUS1aMTc5SEVh?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNVm43RXV5MWlfOTE5TjdqQjhtd3pzUnRIdmJycExNbXV6REpoRjQ5MlNiRENNemM5SG5VbUhJbnVXenhQXzFhRGgtNXE3QjRWWHhCcTJsZ0lfUW5ZTWNWcjdZQnZSSDM0VVdvVDY0ejBPMklPTUkzdTdXX090b1RQY21nbmdUQUtuZG42RHBxRWdCb05xNkdBT2xUVk1SNWN0cG1NbnhKNlBxSl96T3BzOU91cw?oc=5</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -2941,17 +2929,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2961,7 +2949,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Federal Tax Authority wins SAP Global Innovation Award - SAP News Center</t>
+          <t>UAE extends corporate tax relief for small businesses until 2029 - Khaleej Times</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -2976,7 +2964,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYWE1ODFVeGZ2UEVVd0IyYXY0ckdPdFp4blEzcm9pZTZ5dm1MUDlocTNzNnd4dTh3cVhQb0o2aHJ2Y2VjTndrd2d6N2t1eW9OTzVtQ2JrcXVwN2NidFd2WUViQlRleTVQQXNpV2VvOVkyMFRINHhnNXpsUWdOcDhDUk1TbkpTajRkcUFGblBfWXhRZVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNMDNwUlhpclFxaFJkdkkzR0s5MVh4WHZOUDdfZzZtNTBFb2RIcklxMF91Tkp2NGRxRlZMM3BubEZGc0g5LXpsQUhHQy01eGcxTllzc1k1S1NqeFMtYXM4YlBmREttNlhsS0hmd2JXN0l2UjFEQ3B5M1pfRTVpOGw0Z1pPMTNHd0tHQ25ZNjNGZmVaZnhzZUJueE9sQ2dNNGVaUDVjTdIBrAFBVV95cUxNbWJjeHFtRU9DbExyNHRRY1NEUXB2WnZRZ1V2TlFhQ010T3RhSmptR2ItaDhxVnEta0NITUJyS3ppaGgyQ2FkclQwRFhCaWNnLUhNb21YaDVGLWZZNThic2hpN0MzNTI4cXI3RjYtLVUzN3VHanJUUHdYaEFRWUlvS2w5UVdja3pwd1Q4c2pXWHVPZ0xZVmFCcE43eWl1bG10N0s4UXdpVUhpU0tH?oc=5</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -2986,38 +2974,42 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr"/>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>official</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Finance Adopts “Aani” and “Jaywan” as New Payment Channels for Federal Service Fees and Fines</t>
+          <t>UAE extends corporate tax relief for small businesses until 2029 - thenationalnews.com</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Ministry of Finance — News</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>mof.gov.ae</t>
+          <t>news.google.com</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>https://mof.gov.ae/en/news/ministry-of-finance-adopts-aani-and-jaywan-as-new-payment-channels-for-federal-service-fees-and-fines/</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQOFMwcEtFYkFkbWxMRnBqX3Y1M2ZOcnJ4Q1FzTHg2b1NDYnU3dzVWMmMycVdhNzJSbTZhaTZ1bjRpN3RYcm9Gb3VIOUxydjN6anFTMU12SHNNcmt1YkhwSk1RVTV6Yk1yS0wtNm9PbVZLNkxmTVRNd3hEOW1xbXdnTlBiX0VJWWhINEw5MHc1eEk4UHhFZHFOZ04zcnZERDZhLXZJQ0VGWS15N080ZXBQYVhDMFU2al9wN1NlNXN2RnFaZEU?oc=5</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -3030,7 +3022,11 @@
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>VAT</t>
@@ -3038,27 +3034,27 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>official</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Finance Announces Decision introduces a Minimum Excise Price for Liquids Used in Electronic Smoking Devices Effective 1 September 2026</t>
+          <t>September 1 change: UAE announces new excise price rule for electronic smoking products - Gulf Business</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Ministry of Finance — News</t>
+          <t>News — FTA Announcements</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>mof.gov.ae</t>
+          <t>news.google.com</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>https://mof.gov.ae/en/news/ministry-of-finance-announces-decision-introduces-a-minimum-excise-price-for-liquids-used-in-electronic-smoking-devices-effective-1-september-2026/</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNMXNESjR5VDVIQ0Qwb0xKUk1xRlhaTmV2RjNfdVpGaDZZYk0wcjdSbC1RRHBUNkRRaGpNOS1mSjR1blVVRHJ6MzdLeUZXM1lMWURyX21CS25DZFN3engwRWZCOFFLUDJydEEwX0pSa1lLSlNqbVlhdk9pNmtvLUh1QzFubU9RVENUNEl3QVdLc2FkRUV6TGFjZmJwLUtiUVd5dlhjVW1SLU43WFI4eGNfZkJCTXBNaEQySVR3QjZuazA?oc=5</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -3071,7 +3067,11 @@
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Corporate Tax</t>
@@ -3079,32 +3079,1640 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>official</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Finance Announces Extension of Small Business Relief for Corporate Tax Purposes until 31 December 2029</t>
+          <t>UAE small businesses claiming tax relief must still file corporate tax returns - Emirates 24|7</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Ministry of Finance — News</t>
+          <t>News — FTA Announcements</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>mof.gov.ae</t>
+          <t>news.google.com</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>https://mof.gov.ae/en/news/ministry-of-finance-announces-extension-of-small-business-relief-for-corporate-tax-purposes-until-31-december-2029/</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOLXJ6YVV3T2dXazExeU04V09UYlk3NmtYT2d3Z2t1X2RPckN0RjVQZE9oNTljdi1rUUlzTDlMalotZ1JWRS03TWVFWlVVS1hyMVlDUEsxYWQ3RWgtdTdUNzVaZjE5WlhVVUhJcjkyaDFVa28yeEN2ejAtVG43dnduV2NDa0k4czRLby1sU2w2ZHZTcGtPZmpiTjRYWXB2VUExMnhreUktUDBZSkZ4LUxZYW9TYXRJc2s0U1QyMtIB1wFBVV95cUxPNWVmQzRQOEJkZnBCZVFDblE2dkFlX1hGNWlnalJBVk5QREJoU0ZvMXZIM1JJYXdLb2lQZFNnejliekY3Y29nN0tLdTUxQ0h0SUFaSVlpOWhuX3dVaHdjX3NPM1pkd2xlVDRMT1VmTHJ4QV9PbmpWRmVHRFpHZ1lyUF9ZWEJTcFJ2LS1QX0hEa0Y3dnJ4S054S211cWRMWWlHVVd2V19wQnhGa2JVR1ZxSFVNVWJMejdESlFZSkxUMGYwQUlyQkpueDlwb2dJYnlqQnZGNklscw?oc=5</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Tax</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>UAE releases registration requirements for domestic minimum top-up tax - kpmg.com</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>News — FTA Announcements</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPaGJWUy1MU0VZdmd3LTVPTmw0bDYtWlF5a3JCVkFwVnhJRUkxVkdEWUE4X1VZLXg0Tkg4YTlLWHhoOUJYVzJqR3lzUE5Pa1RpSWtjdkRDQ09UeDBoQ3Y2bGlLbkhzTXZ2WlNJeGFSLXNqRUZyRnBfNV9Mbk5UY25hdVZ6VWM2cWRYOEt4bUlnWV9QYkQtOWZudGJaV0ZJZDRVY2JGbTY1T1JTYVhyTGhEdlVuQzlzZkN6ZC1VRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>UAE Digital Economy: Why Trust, Not Speed, Now Wins The Race - Menafn</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE E-Invoicing</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNbi1OcWZwSTNNYjBRZkJWS1FodlVGTG5oZHB1T3Q2cGRqazRiZGQzeUtlOVB3VXlhNUM1TnhSdW1MVS1uSng1dGFmTlAzb3ZMNXlod0c5bWo2RkdOTW1idm9JQ3dQNTM5Z3FvZl96WlNuVVh4Mmx5NGFNWXBHVFZoWnUyQU9WT01idllWclJqTXE?oc=5</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Ministry of Finance sets e-cigarette liquid excise price - Sharjah24</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE E-Invoicing</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBGY1BCNkVheXBxM3RBdWlPNXVULWVaaWdWM3RWWU9JSWI2T3JVMGlMdl94Ync5ekFqdGU1SzAxeEMwaUhJR1hTejhVTFo4blI2Y1d5QzZUaVgwUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>CBUAE injects more liquidity into the banking system - EnterpriseAM</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE E-Invoicing</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPRVF2amFoSUlsRENGenUxcUlxRU9NeU9QWlJhUkExb1k0cExublF1YUdrM2dJc0FySm9zQmgyQUtKU092bkpYT1I1bUhaMkxGR2o2SFVnckhIR2d4RGQzOUJnb19tZERINThyZ0NrQ1A0WUttandLcmN0QUlUaTFVZ1djMnUxdEp4SmNGMjM1Zl9HX1k?oc=5</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>The Taxation Society partners with Tally Solutions to strengthen UAE's finance and tax professional community - khaleejtimes.com</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE E-Invoicing</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNMXRpRGhpQXJvUkZhQU1IcTF6Z0JtLW16cTQ1d24zZWlwQTlPMHNCeG8tY0NLc1JGcXdjT2g5V01YM3hOVmtZYzBJeThiR3hhSDRpdGdwaDhsVC1WMDFTSWN0SWdhc3hiWTRSQmV0blZEZkowYWdoSU1BaUJ6Y01ZZ2ZrWlNRc2JtUllnc0huTF92aWdmbEp4bTRvRV9fN2xTU2dmMjdLSk43ZlFlcEtuWTBKQXdFTU5pMlRnWE55VFBwcTc0STRtcFluS3Ffek1oM2NRQ1dYemVkTktESkJRSVJ30gHqAUFVX3lxTE85ZnVhMjFKMWdhenV1YlFiRGtpVTBIdjRvLVNLRFBjTHBPUnVfeG5sUGxIcWVlSlhUTEVibFV2UXdWbEg5TGNmS3hBYnczSEctV3BBT2pZT3dpcDJUeGczWE9xQ1dweV9hc1hwQnhHQkFWUDRrb0FzV0tVdmZhZ0pLZC14YlVJZjBYQmcwbUZWeG55dnhpOFliT0wxYkQ0bzl1VEhiVUpQNjQ4TVN0bFhPRERROXB5NUZZQ0VRS08tY0VmSDdLRFQzMHZ0dEZtamJ5dmp1OGZ6SmNxQjZrck8wRWs2U1A0TFJZdw?oc=5</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Tax</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>MoF extends Small Business Relief for corporate tax until end-2029 - Sharjah24</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE E-Invoicing</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFA4N01YTUZ2UGRGVWdDQ3JDM3JLYWJDanVuckdCLVhuQUdqUFo3clA1cGRoTUtubWNpQ0dTOUFSQk5jYzdGcVFYNkNpQjF4ckFVZ2pBc0FXM1Ffa0k?oc=5</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Northern Emirates’ property markets cool off + Sidara locks in USD 1.35 bn in firepower - EnterpriseAM</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE E-Invoicing</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOMDUxZXd1MElSNXdaNDByLW9jbHFIenJCY21PRnhPMUx4YkdyZ1FMREVxenNWZWZUY2p3MHQ5V2xUQmswZ1RuV1g3Q3RHUzdvOFhvOGpST2diQWIwOXFBeXdzc1lYRl9FRDIxdjBjUVR3Y2VEcUdIWXB0amg4YW5qbklORzFMS3J4VUZGelkybDVZcXc0VHlNck4zTXdjR1N1UzZmSk9vSFFoMDJMVENKMFVlWEdvUTEwZFhiZmdn?oc=5</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>E-Invoicing</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>ClearTax urges UAE businesses to prioritise execution assurance as e-invoicing decisions gather pace - Gulf News</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE E-Invoicing</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPTG13TFpCRmpaaWU3ZGxsVEtqakxUUXhSc0ltWUZfOEUyWTcxWGhOZ2doazNZY1V2LWFnSlp0NHpHTXN4emN6TzFWbGlXT09xU0Q3X25BTmpBVVl0Nl9XMFdRUE9HMy1BU3BMRDFIZ1RITkw4d3BSanluZGFHal9CM3h5dDNtTlBtUG9LYXZZWkhILVZhdUpKTHhUd2lMWmVOdVJrREx4UUF4WjNvTW5hSmtBVjVyQVBpblVKa1hKbjhxRTNUVmpUMVpXOFFJSWx1NUZWUWFMYlY2ZjA2Nml6OGV6X2ZGcVhkQkQ00gH-AUFVX3lxTE12b1Q4Qjd0Rks3U1hqOC1GVTZ5RXRUOXB6eVdVd3RMTEV5Q1pRYVRrc19GaG1qY3FXRGhqMkN3N3c2emJyeTFWbEU2QkRSMHR5aWFzNlctUi1mdi1vamRHMHZoWFZlQlRCbEhrT3BLSXlsTXRfYjY4QjVHblFRU0JnZVhlam4xNEF6d0hQVUtmTHFoYnktSW5LS3dqU2VleEh4azlObnoyUTNPd2E0RWc4U0ZhMkRoc1J1c2R6VGJhc1lSYTF0cjhzdnY0Q0tvYk81YnY5UE5CdnBXZTVNQXE4UlZwMkFjbUREaEtRNlF2MWJYVFhaOTFJNTZRUlJn?oc=5</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>UAE extends small business tax relief until 2029 - theaccountant-online.com</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE E-Invoicing</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOMTA1XzlxbnpmYjNMcU01VXV1RjdMOHFuMi1CSVNMYXlaNW9kb2ZMSXZXOEZ1dDlqbmRLR2hXQjNrMDdlaU4teDVRTG1CMmJsY0lDU3V0SWxRZE4tWXZXbV9pR2o5THFMREVyZ3VpY1pTYVhFeUJza1MwOWtVYXB1ckwxQlBRdVF6eURUUHlkblhUNnNoQ3c?oc=5</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>Sovos Announces 2026 Partner of the Year Award Winners, Recognizing Excellence in Strategic Collaboration and Innovation - Business Wire</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE E-Invoicing</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxQRzJIdmQ3VjZqenlUTldPal9HNXdxdTJibTJHWFBhMVBMTWcxbm0yeUhJYzVLd0Z3Yl9pdE1LQzREWm13dXE4ZG1abDFuRkZIdHhIcm4zYXVoOXZIS01KNW5xRU04SUVwMlRnZlBxb3BYQkJMQ01CeXhabEI5U1VfSlpad0ROaVNnTUVnUll2WFhwMkxUa2tidGRxTDlMRm93SlAxVkNoWW84Zk1oeFFoNVdnOWRBZERIZzNSdnVDMGpHZ0MzSXlxZ1JXc2hodEY0aXNoRkNBRldSOGdxSkowdmFoTEplTjBtOUVfeWFtNmpzeDZtR3J2bVk4UWthWFR5VjJRbEM2NA?oc=5</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>UAE E Invoicing Guidelines Updated to Version 1.1 - Crowe</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE E-Invoicing</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQOGUxa2xtLVY1ejE0azVCMEZSa3lxNHZmajhUdzh5LTQ5NGRqVk5oenBzNmJUSk44X1B0elZ5aDI5YVl4VHpLb2RzdEFRYW9IVmR5dHpOaE1JbWVoNzdvQVpsR0xIalA1MHBaR1NNOVpVSHUyX2t4R0dIVmZiWHlXWg?oc=5</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>VAT, E-Invoicing</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>Congo Republic e-invoicing launched - vatcalc.com</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE E-Invoicing</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOLTlBQUhqTDJya1ZpUmx5Y0lPRlRHb0VpWW5GYWVBc1JkTGRFbFl0b3N5UGJSdEdXRmwxdld1RlhqSWVremtIU1pWSHNXb2ROejA2TzJYcF9RX29TQVN1akJ5d0cxWFplcmJPYUJTRDgzU2FzenRzMzJldUsyaE9rbzlVUmJMSEc5M1pzSGtR?oc=5</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Corporate Governance in the UAE - Crowe</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE Transfer Pricing</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE4weWRYb0VETFpvMjdhUG9BbU5Wb2JXbzNkLVpxSC1VZHhwYjMwT0F2OFNvQkJNQTFkOG1OamVFZWU0NWpVN3hHb0lldkJWLV9GeThwSjdzNlpnQXp0VDdQbkpnSWFFU3lacVJOeXl3?oc=5</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>Shopping online in the UAE? Tourists can now claim tax refunds on Noon orders - The Global Filipino Magazine</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE VAT</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNa1BKRVpJRVZCZm5VNVp2d3h4Rl92ejg0aml0Qy1pTUotYTZ4ZHlaeURMcnRacE9Zc0J2TWt4VktTQWdFV3BlNXBzWmlfMXFEZFRiYWRIMmV3X3ItaWc0T3pzOG52THI4c1RQaDY1RWdNbXItTTUtdlFTS1d6SUpZTVlXM2lOTWtLWXF6TGNSRE9OWkJQSUs3UXFoSEtOa2NpNEJLeTFOektldFVUVHk4cFJCSE5Qdw?oc=5</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Number of retail outlets connected to Digital Tourist VAT Refund System reaches more than 19,300 - Big News Network.com</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE VAT</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNUjRVVzdLOXJQTXpUZDhqeWlQNDAwVDV2ZmJqd3h4cW5ZbXc0cHEzZGJBSWlLOTk0ZlFFbXlVSThCUEtxcGFqUHYzSlRmeXF0bC1XQ1J3VVhKUUkzeVBfNTc4cmQwNmlRYldwUU01YXpmc0pxT0daNWRpRUwtM0N3MlBBR09rRldZZlA5bXVJOXVTcVZSeE5ldWRHSWhna0ZfTTNwZWEwODlFTXRRYnRhOVJVcHJ3dDRuSnZtQlBhc0NMa2dhSzk4b1lBWEx5Uk5Ld2RMaFdmNUY?oc=5</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>UAE tourists can claim VAT refunds at 19,340 stores and on Noon purchases - Gulf News</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE VAT</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQeDRPcDE4QjJaSFU3Qm1wRGVaWXl6cjY2c3YyVDF3TmtqN1RYMkh0WDdoSm56QmlXU21xSllRQWt4WHNFU09vUWZpTEd3dVVMb0UxNy0yZG1ucUF6aXhIZ2dWVXpkVjVqa2hHUGN3VHNZWEticFZMXzNfb2NzaVpwOFFkOVAtNDhBY0xjSUo3bkh0WUg2ZEJ4Q0JDU05Td0FTLWlUWXNfN2JKeGJsTEg3NGFDMzNwT21JZTFGT0V30gHQAUFVX3lxTE9wdElvSG52YzNWWUt6WGJaRkp0LXpmVHpQTFV4WHczVkQtOUhOMWpqRzd2UjgyQjNOSWdMT3QwM1luZzdtNWhXdU91R2lqS0FKcG1hUGExZ1QxWG1SSUo2cWZSWll0bjdpQ2pBOXFjTUMxcjJma0RraGlVbjNjajZRM0h4OVZfM0FUQXNERTQzQm1TS29QVjdiQzM2T19naktoTXhfQ1pvNmx4U2IxVkkxUWF5QmZ4QUxmMXB2bFVvR2RVWm10bjE2SlNaRzJ2VEU?oc=5</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>Retail outlets linked to UAE's Digital Tourist VAT Refund System exceed 19,300 - Emirates 24|7</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE VAT</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOcXRBMGsxX1Q5SkJXcEFwWnV3c0VVc19jUnRkWU5yMVlPelltaEhvOWNLcEJxYi1KUExWMVlmZE1FOExZYklsRHU4N3lQZGppMDRnYUFaRU1OWHdwaVpiWWowOENidVJjbDFPeTQyQklzOGM5bXhQbDJrRFg2TkR6bUplTzJNZzl2M3dJT2FEeHVTTVNtTml6UEdoZUFDcVRCZWFHMGg1ejZoSWI1UWFCLV9zREotcmF3V0HSAdQBQVVfeXFMT3Q0RFN0V3FRSlNWV20tMm5hY1N5VHBVWmxzdnZGVXIwZU92VTZVRDVUVkRZM0Q1U1ZNZzFRcFlEWTc2ckk0UjZhcEN4YmZIZndTd284ZDQ3Z2Z4OS1mVGFUX2RwRzgyMWViTjEyQ19wdUxucXEtZWtFRm5tOWpId1VYYlRmd1Rkc2tlb3Q3THR0THZxZWt3Q1ZyTGVvZ2hUUzZPeTBPSzlER3FXR0ZvUnJiWk5vdlpwYlYxdmZjZnNTVEQxM3hSY1pyTGV5Qkk2d2lrejQ?oc=5</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>Indians, Russians, Turks top list of tourists claiming the most VAT refunds in UAE - khaleejtimes.com</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE VAT</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPek9sY1dJUkpRblhiYnJDdDExOW1yREdXd1oyZ1Yxb0FnZlBYNTd3SUxGWnVMenlZVGlqRlIxLUszNk1Jd3BpcF9rVE9XLVF1OWdhY01fd0gteTJFRkVJLVREMjl4ZVRGZHJacUxJREpRN3UxdHFncGhITEQ0MnUzTkhKY2FSZnBnaFUzZDEyRnZOdG1hOWVFX2FLNG9Ca1lGekQzcllxd0FqTUhvTTRZM3MxcElQV0JaMWfSAcIBQVVfeXFMT2FPTEx4WGUzNUNhZWdBa1MzVU5GN1p3SkRwM0o5TWlqenhqVTNhR1Z0bThyN0laMS1tOUhfaG1qMmZpQi1pT3lTNEhKT2l3SklKZ1E3MXkyYVBrMnUwOTh1Y2RxSkFISUdlT1B6Qm1tTV9CUV9YM0xwcTJ2NzVmWUcxaFJ2YzhYeVBjZG1WSG9vcVc2N2tqRzNreHFwWVpaaUdncndzVEVLaE8zeHczU0Jvdl9FazU2NE1CNWZqQmZmekE?oc=5</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>Tourists can now claim VAT refunds at 19,300 retail outlets across the UAE - Gulf Business</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE VAT</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQV2tyUkVhVzNVUlZ0QW9LdW5PWV9OTEVSN1FHU2c0Um9qbTRDNXFIdmZUaERGcDFPUkkyTVpzWXBQblJHb1VzVERybTh5WkIzcnRoRFo1ZVBicVRMQXpFZXB3VVJRQVZ6UDNNZDItT1RuTXcxYWxtSU1PaGlPNTFNUnpzLXBGX2QxSy1WVjU4alg4Q0dEWmY4WFZ6cEt1a1FZQXpRODFFN0xRT3VwSWFfNw?oc=5</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>UAE tourists can now claim VAT refunds on eligible Noon online shopping purchases - Arabian Business</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE VAT</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNSk0xOTlEQk5DQm4tczlCUE1jZ1dmamdsaUQ2TUYwWnlNd2JHMjhhVXZVUF8wNGpSVUFRNXhvU01pY01FMlUwWEt0anFyS3Q3QS0wa3BjZE1YLWtkWkpYeUJxVmlaSUhQM0Z3Mk9odUFYenhNRnBZeUkyQ0doNWJ2VGUySGY2dG9kMnlJaWhuWEMzb25aWjA1VXZkLWRwelk1MXJjbjBrV2F1Z29KZTJ3?oc=5</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>FTA issues five binding VAT directives on tax transactions - kpmg.com</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE VAT</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQQXptRUZOQlpWYUZiNzd1QThPVDhlUGM3TF9PU3NKZjUyS2lucEZLUUFKZFpfZVhXLWxteTBKbU1OVEU1WXdPVlViT2ZBb2h5dmlHa0Z2bjd0SzMxa1p6TzF0ajhuVFVSaUpkczUxd1lzeGVCeDNwRnpPbXJVNVNGWHB4UTcwR2dCYTJoWTVSYkJGQmxRZE42cXNmOExtclgxR28tUUdYVFRzaE92?oc=5</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Tax</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>UAE extends Corporate Tax Small Business Relief until end of 2029 - travelsdubai.com</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE Corporate Tax</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOYzFrN28yN3RDREhxYV9CVHl3UGU1NlpvSFJqaHJGWVpraVhEOEtqTnZVQk1OTjVjX1djWENocHdtYy1WY1dBSHZncjg3aGxWOXlwcFktaVVxYzBmZllLbzBaLUUxSEpyNW1HX3V5MG9YMWhTcjNfcnZxQ1JKRHZkMjlYSjlmUHk1SGFEYy0tYmlqWE96ajBqUnNSS19TUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>UAE seizes 3.58 million non-compliant excise goods - Gulf News</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE Corporate Tax</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOOF9vUDk3UXlsY19FUWtOOEJ2V3Awam9fY09zeS1seXpTUUt2Y05TQlVUVjlwYlVuX2hRN3JBM095eTlqZ3pxWWx5ZWJzUzV1bGdCQ21JMzd1bjRIMGRMdHpiZWVOM1lmOVdtSXlicW4wYUNoYjMySjFTNl9OTnRvYWZycGdhODlTcU9sQUpwUEdJcnltNF9nSXpBWkpJbjF0VG1qeVJqTdIBugFBVV95cUxPMDVISGFVMTVqWFFiS0VMTmlzZzlyWXRVUl9BTjBGaWgtS21lN05BdlppYlVNQkNtYmZWaHRIczNlSWRmbXBBdG9zamlobjFhTFh6R2lYZFJ1RUtKWGZqOWpNd21LTmNxaUF1SjVIUm9UNjF6cmwxUGY2ZHFIVHBFdVJNMXcyeFp3dUZ2V1hpVmtnRmZOY29nLWNWQmxsQ0tHUzd0RjRyRUlZeW1adThtZEpPVl9KT1pFRUE?oc=5</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Tax</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>UAE Extends Small Business Relief for Corporate Tax to 2029 - tbreak.com</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE Corporate Tax</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9icS1QSXhYc09ROHVJdzRtdXJTMEdLa0o5Mm5TZ3VxR002a3lTeFR5anZqRmNtcVEyQWxfQ050UFVOZnFBcFdwT1VoNGlVZU9xYkY2WkM5SlpSSnp6QkpHck5rTUxqOXNjNjM0UmFTQkFfOXZySFFON1pCSXc?oc=5</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Tax</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>UAE extends corporate tax relief for small businesses until end of 2029 - Gulf News</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE Corporate Tax</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNNEo4Tm9qN1dERmwzZ0tMR0ZOSUVQTkpOTTNiTDc1U2VaSTkyRkExekRzRjUzb2xrelYzV0oydU1qS2JCbHJXd1hxeWhPdmtUN1UtcXRCOHZpSXBxMlBMdFRKbDNxYlNFaVdwRXROTUVxWC1tZUpObDVIZzNVUDEzSUZpNkIxN3ctTDRNWU9xOUx6QXZieFdVV1hkNHhlcldHUzY5b21BZ1J2VTVhMlN2a1V5V1dJRkw1OTItdWo5Qzk5N2lPX1HSAdgBQVVfeXFMTmRQM08wYWhkelVySDhudHZWLWQyZ2lyUG9TNEJhWVV6ejAybDV6QXdvUFR5ZndxZldxWHVDMjRKVm1Ndm0yeE1HZHo1LXoyVFBzMkhuUDZESEw5RUFIaWlfNEdObjNxRlc4VFpOZVQ3RDhhellsdEpYN3pLVzl1d1Fva3R0RWpDb0d5cVN0Z3I3emowS2tNbkplWTh1Z2NvVkRMd0R3STNWV3hrUVFtd3hxdjQxWjI2ZU4wVE9JTzlsWVUwYXlPTmU4YWJmazMxQk93MHVHbGZE?oc=5</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Tax</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>Small businesses in UAE urged to file corporate tax returns before deadline, says FTA - khaleejtimes.com</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE Corporate Tax</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOWnJlYmRmRm4xdy0xZ0toMUNUbnhTd3A5UW1pVzhFeXhIM2txamo4NU5qYVYwZGlQcEYwLTJhelBkOEdHajRYSE5PRnZtdmxGWmc0R2JlUVk0eVc0aW53NzdlM08zeWFzTUNocU9UcnY3UTNhTHVzZHhjRXFPZ0ZMMHMyRExEcjFiVVhKVzMxYk9FSHUxdERQRnUyZlJLWXA0ZVHSAaoBQVVfeXFMT3BwVV9lZzBQRTFjWUNVNEFzaUlhOUJuTHByVVRhdjRTbjdpajdOTjRtc2hfOEotMWlSb0FvX1F3azI2czNjMHREWnRJbFptM0F5ZHJkWUFsMW5fMDBsNU1YODgzT2VkMWZacU51MzkxaHJ0S216TF9UR241SnM0OVo2eHlDM0F6V2VfbUt4elZfZVBub2pLNW5fazhqV1hNUnBzRmkxS0NUQVE?oc=5</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Tax</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>UAE extends Corporate Tax relief until 2029 for businesses earning up to $817,000 - Arabian Business</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE Corporate Tax</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE5SM3FoRTVUSmJwTlpLbi1vOGFPM3RPcXpraXlCUG9iQlhuUUJ2MGRCczd6aDM0MFFNWS0yS2tNNVIxYjd2Y3AxWExhUnJNcHNXT3dLdGhyV2FBQUQwbmZ3YjRZc3NXTkNoLU5HTFRkTWRkSlZ6TEtHbg?oc=5</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Tax</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>Ministry of Finance announces extension of small business relief for corporate tax purposes until 31 December 2029 - Zawya</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE Corporate Tax</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOWVAwdTI2R09XSWRHaFNWYkNGdUJsSTNnaGpRandNeklubW8zM2h3VkNIcmRiQTVrZUxlSnhydWtqUGVTRS1vYVVQWWJfY2swUzhYOFJrdHVCQTlvTk1LNVBfWjBPbHZxWVU5Q0xQVWFHbTlLYlE0ek1aWFhqaUF3dDlTY2p2T0dtV3gzSXhaWkdFdWFBejA5ZkhDSkVPanZUWDk0d1oxNlJOUkNxMER2M1oyc3Nla2NnUW9WYmFRS04zeGlCcjQ1YVNZT2ZraU5EN0h2ZWRDaklZTjFQUklLWmRGRVFkUjhKUjBybHA5UktLZHFiVnUtOFpuNmhSZ0o3YVV3eld3WQ?oc=5</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Tax</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>FTA reminds small businesses to file corporate tax returns - Sharjah24</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE Corporate Tax</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5NZ1VTdFlkVERkd0pETmFiVUQzZzEySVNaeWFyV2N3MHdhSWZreEZnUDFCYXhiWGtCOVVxMFdWUzhDa3JCU1czenE3QzJzaG0tNU5iMkFmRFRsTUU?oc=5</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Tax</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>UAE extends small business relief for corporate tax until December 2029 - TradeArabia</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE Corporate Tax</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOc3RJWW11LUNyUERIeHh0dTVRVFJySzBoWVB0N1RCdVNpTVpORW03RkVXaG1pdk5HbWJfTDUzYXRIellIdlo4dVBXcXpuZHNrQXZRMk5MMGF1UkpqbGRTbXZRekZTYkU3cHpsdmJHdTVRdFFxSE1aSzZxWW1rb0RuT1RNZzVOWG91OGVTcFZVUGFVLWRUY3JsRnEtYkR4WUJjWnp6NkljSUd2NExsdUYtVA?oc=5</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Tax</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>UAE tax warning as thousands of businesses approach Corporate Tax deadline - Arabian Business</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE Corporate Tax</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBGbVZOWkkxM2FaVGlfeENJVWJXYzN6SDdmNk9nOFBYWWJDV3N6eGxVcnBRRXc5cDY5Qy1xSnNBQzVHMXR3NGpacEVucjlTMFRSaHc0dG5aZXc1aUVwSXlrTXhFTGd3RWNMbzVpWmdEVUZuUC1N?oc=5</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Tax</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>UAE reminds small businesses to file corporate tax returns even if no tax is due - Gulf News</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE Corporate Tax</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOTm96UlB4Q2xPRlcybWNBanAtYXhxQkg0eHVCNDBvZlZGTWNGNzlSekNuVWZCU1JvOWR4MWxLanJMZEsyRms3NnZDSU90RnZuTkhad3pLLU1XX2VWV215T21HMTBmbVF1X0hmakhwM1BYZVNUQXZEV3A1UmR0QkZxVlJ1VDV5dGVMMFJFSGRxckpYVkVMMmFNMFBBdE9MZnlFSjJ3MDFXNzg2UXd0SUthQlZrd1Zjdy1JTVFkMEZlU0VKc3lzQW84VDBGLXFfVF93SnfSAeQBQVVfeXFMUEpicHFURTEyaDByTG44RGZUZ2R0MGJwRmdpV0hydzNTdkVYd0lFZzNITm9ueldCQ0JUZjZ3dW1TZ0xCSHM1S3c5eXExQlZac3V6bGd5Q1EzWFljOVRrZkJWRV9XcnFQWHdzRHQzWDRiUFhHaXlKMldlZHp5YW9zMHh2emxiX0R3MXdva2NFZ2JwcnVBZk52dEh2UEhvTW9FYzlJQ2xWdWZPQmpteFpaWnNUV0lpUTRiT0hNRXdHQVg1Q1VibWZqVWdocjBVVHJtVVFUbVFBdjJoRndFUS1aMTc5SEVh?oc=5</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>Federal Tax Authority wins SAP Global Innovation Award - SAP News Center</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE Corporate Tax</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYWE1ODFVeGZ2UEVVd0IyYXY0ckdPdFp4blEzcm9pZTZ5dm1MUDlocTNzNnd4dTh3cVhQb0o2aHJ2Y2VjTndrd2d6N2t1eW9OTzVtQ2JrcXVwN2NidFd2WUViQlRleTVQQXNpV2VvOVkyMFRINHhnNXpsUWdOcDhDUk1TbkpTajRkcUFGblBfWXhRZVU?oc=5</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>official</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>Ministry of Finance Adopts “Aani” and “Jaywan” as New Payment Channels for Federal Service Fees and Fines</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Ministry of Finance — News</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>mof.gov.ae</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>https://mof.gov.ae/en/news/ministry-of-finance-adopts-aani-and-jaywan-as-new-payment-channels-for-federal-service-fees-and-fines/</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>official</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>Ministry of Finance Announces Decision introduces a Minimum Excise Price for Liquids Used in Electronic Smoking Devices Effective 1 September 2026</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Ministry of Finance — News</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>mof.gov.ae</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>https://mof.gov.ae/en/news/ministry-of-finance-announces-decision-introduces-a-minimum-excise-price-for-liquids-used-in-electronic-smoking-devices-effective-1-september-2026/</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Tax</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>official</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>Ministry of Finance Announces Extension of Small Business Relief for Corporate Tax Purposes until 31 December 2029</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Ministry of Finance — News</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>mof.gov.ae</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>https://mof.gov.ae/en/news/ministry-of-finance-announces-extension-of-small-business-relief-for-corporate-tax-purposes-until-31-december-2029/</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/tax_updates_export.xlsx
+++ b/docs/tax_updates_export.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K95"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -511,32 +511,32 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Cyprus tax alerts - Deloitte</t>
+          <t>Prefortune Technologies Announces Odoo UAE Peppol E-Invoicing - openPR.com</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>News — Big 4 UAE Tax Commentary</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPR3dMcm02YVpKS2NHZC1YZlJaV2VXZHJMYjNzVzRNa0NfSDNXaFhJcUNseDFYaUVRNVNpdmd5Rm1jbE04d2psTWRBMjZrOUxQQ19fOXdSeXF5cXpPN3NYRWxqMEJ0aFNGcWl4OTJfSU9mSnNxRXRXZHFxY3ZfaHJrNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQVG9nYjRRdy1xYVZ3cEU4ajVEd3dpaXJYNWNpWFB5eG5Ia054ejBUa0VkNVMwb1I4TUVQdkl3STFTcG9fMS1ObVRHTV91eng2SHBiVGtIZGRZVlRVOHAyVDVoLUJONTlDRDkyaTRocno5M0lwcVBfS283N1lEY0t5eWd0Rld6MzkybWktZEtqWXlaN0w4c2xzbzFzT1NiQQ?oc=5</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -556,32 +556,32 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>World Tax Rankings Middle East 2027 released: challenger firms surge in UAE - International Tax Review</t>
+          <t>From readiness to implementation: 7 steps UAE SMEs should take for e-invoicing - Khaleej Times</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>News — Big 4 UAE Tax Commentary</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQUWp5dVloOUQ4anZfTkR4NnJUYkZYdk1ZU2xDb1h6ZE5Wb3pzRzVxQklBNi1tTC1KWndLRlhpdVBaQmJzZ0FaRFVsNUQ3VXFDOWlRSGRMY3FHM0djMk9TRVQweThXS0lsSmxGN0xOT3V4ckZVNjRuTzVMOGJBSjN0Q1lwOTEtSXBwcm9zTTZUc1MxbVRpd2tRMlFjTE41b0EwTFRxSUg0TjlDTm93RU9WUDJFYm9sS3UtVm5XdWhmTVhndTF1dDdNZHUtWDB6Y2RpeFd5bnk3UzV4VHdwckNra1BoRWk3OVQxMjM5TWFaVkRlSjQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQUkNGMUtUUW55SjEwUnhUYjBycXVyOW9SS1Z0RGFVcTl3VWVMWlMxQ3E3WV95MWt4RUdoOHRQTmxDLXV4Yk1qMjdWUnJxSUNxVURUTWxrd2pWdDBBREZRZGNEVTZvSlB2Z0FuOFZFbGdKX05tT0tFeGx0SHVRQVdWaGE4UU1kdlhVYkZFQzF0R1lFOC0tNTBQTXBybUVLVFNHVEZyMnFwa1RVRUVUakExY0o5Wm80b2RJbFIxNW5TclZpNm1Hanh2RTJOdkF6d9IB1gFBVV95cUxOdTA0Q0pDMnBiTFpZbkcxRnFwZXg3OXdmU0ZQdzBQNEd5ODNtb1VyWndTM3NhMkpQRTJqVVRldEdubm45X1RxTTFGTHl3MWFmZENMZXlxXzRJTXBEOTQ1SENNUkZ5Sk5DZU1OUEljVjFVNWF1NTBwOHNJZE92UFQxZ3hPSEtObXJMcVFieGVBejZneGdiTzJfLURXQXIyM1FwbnJibGFMUG84RkFJZGVPbjZEanhkWTlFT0ljR1MyYnRyYmZKMkMtVGs5VzJOZTlXTm5YcTJB?oc=5</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -601,14 +601,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Other</t>
@@ -616,17 +616,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Cross-border Tax Talks - PwC</t>
+          <t>DP World appoints two independent directors to board - Gulf Business</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>News — Big 4 UAE Tax Commentary</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNajMxUTZjZ2tOVUFvYThvdWY2RmE1UmFoV05XbTR1ak5FUXB5Z3FRV2RKdGtuVzZhR1Jva1lKQU5IUmVDMlo1dzNSQlc4TExYbkRudlZQT1haTXZWOGNmXzFPTF90c0luOFNrbWZxa0t5VElhM3NOY21CaS11UmFfVFdtVlRON1hRYjlDY2UxMFR2YVhBQno5Mk05NmJFel9DQXl2RXNsZWxhTTZxMmtycHJtNkdDWjNxX3Y2QU1TWTV5MEFTZFhJQw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPX2QzdVpCMHdjWXN5M0ZHNEVvVEhGdFd1aEFHNnk1dXZ2ZWRKUHJLVG1pQ0hoTjVaRExrcXpyY2hTbkxFc3Z4aHgtMHB5ZHlValh4dGhNTjdvcnZzdzVDV3pKbUo2TW5HMGExa0hDcUZoSzctUUI5WDhIckx4N2tMVFo2WHpWUVp0NDIxQnNvV1hOX2NiTWZpdVJtelVFYW8?oc=5</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -646,17 +646,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Federal Tax Authority issues new guide on scope and registration for Top-Up Tax on multinational enterprises - برق الإمارات</t>
+          <t>FTA calls for compliance with e-Invoicing deadlines to avoid penalties - www.wam.ae</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>News — FTA Announcements</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQaFhsTDBvVWFWcHJNaWQxdFZoWnpxN0ExT0EtNENrZng3TTh4UFVleDhwOFd3Q05OY09UaXUxNS12YXljOUd3WXl6MWVUdlY5RXhWc3pEYVhBRDZPbjNhX2U4VjJLcUtncVFwMnBZUE55M1ZLLWxhMzFZQnNRYTFleGo3SDhFYWpmYTJ4dWg2dTEyNUkyT3JVQVZVa0JtcU5hdUNKZE52N25XdlNLckRWMThRQTRwQm5ZenFYUEFFYXVBeWhxMTlfNWFieFViR2FpSE84ZDVJcVR5VHhqbGVz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPUDNQWVptSk1uTm9rVFI3ZVYwV3dRMVdXSmJxZVkxZlhBd2FEa1ZaNlJsQzcwaU9tcFNjbTJEWEs5UGJTNzhoWVEyeF90a1ZPcmVJM2RLUDJ3VHRMVU9qZ1ZBbEhPVTNDaklkSkNyVllwVEZ3UTE1N3ExZWNZZWhzQ2p0MkoyQQ?oc=5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -691,17 +691,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -711,12 +711,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>APR, Korea's leading beauty company, showed an 11.8 billion won increase in operating profit in the - 매일경제</t>
+          <t>UAE e-invoicing deadline: Businesses have until October 30 to meet first requirement - Gulf News</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>News — IFRS Standards</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTFBtVnRiOXljUWlKOUtMcC0tQjNycVJxaGJMUTBPZXFwYkFPeHM1Q1R4eXhmNzZGMzhnbVFrNFNZSFAtMjRiYVB2TzNRVXJ2dW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQVlFDSEtCd1I4TTB1M2NIQlBtSUtHWEJGelF2aTctaVpIQzRtcTRDWkt5dkFwRFA3ZHVZc1N0RWF6UzYzMzd2TUJQdXZ3MGpFaE9IOUtrenFhLThTNjByTlpnQ0laeHJXMVpJZ25fcmxGUmRmb0ViRW1DRFJmV3M2elhTWllZM3M4TzNXS01SQjVldDVvTnFDbkdjaVlCcGV2VHAzSnFfS29ldVNRUVJEUU9iTnRqS1ZlemJZNEhhY3RvakY1RGNjd2VpR0R0Z9IB4AFBVV95cUxNSUF6V3NtcTJFd0tRQ1FQbTlxbmdwLXVCd3hlcE05amFITks4Z2RaT0I5Znp2UUN3UjNpbWlKVWNXQ2YydkpjUVBQaHdqZVFQM2tpM0xYWlV5bU1tN3QxbnpwRDhUVmliNmU3dnJ4Uk56ejRuaG1NSWNrRnZFc0gtYTJubVdSaUIxX2Q5TmRmWEZIMkFwTDc0UFpJSWo3TVhtTnBZRzl1RExGTWU5N2l3Y1FmRmd2RU9JUU9WY1dvaWZQdlZQWUpYbC1pY2VFemRJbUVPQ2tWb2cxenVHTFpRSw?oc=5</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -736,17 +736,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -756,12 +756,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Ind AS 118: Big Changes to Financial Reporting Soon - TradingView</t>
+          <t>MIDDLE EAST TAX ALERT | UAE | e-Invoicing Guidelines Version 2.0 - Alvarez &amp; Marsal</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>News — IFRS Standards</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPa3pEaDB3Q21YU3FhSFQ0ekVZc1pwT00zQXFTbGE1MXkzX3NjazJ5TGZXelg4WnZocTlUZzVDMWp1aFlzNk4yMHIwMGR2d3dBUldzem5pY2xtLUVZckJJa1Rfc0c4MnJxX0YxckZIZWNNY09LVnh5RFVGMko0VEdrSXh2ZWlTdjdsQVlHTWotcGs2X0w0ZVRPbmNyVDdEc085SVNsYjJCR1NkR3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPeGtIWGRjTmV2SWU5UkpsektaSno5VVpYVGlpcmdUYW0zNW9lalJfeGk4Y0dacFNQaWZ1dWFpRkVmYTh2SWF5c3ExTW50eUxuNXRLblhLcl9xRWx4aWlYRm14eEFIMTM3UHJ5XzBZNktjRHFuNWFXbEVwWWhGdkhyTDNLbVJscWdXemU3RlhrcncyMHkzckRyV0wxdGRQY254Z1NXUHNfV1JhSkZ2b005WjVR?oc=5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -786,27 +786,27 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>UAE Publishes Monthly Fine for Businesses that Miss e-Invoicing Deadline - Legit News</t>
+          <t>Cyprus tax alerts - Deloitte</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — Big 4 UAE Tax Commentary</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOcmtkbU5IdUxaZFVXUXVJWno3dERSaEJ2X0xKbGlCSi1rVUt1TDNNQUdiTkcwdEN6YlR6Y1FpeU10WWY2aGhWQ3gycGFOcGRQTUdUbE5BTWxfOGtHcXRRejN6WWktN2FmbjZTTmpsUENidjNEaTktTkVSbVQxRDNBZHNoM3ltLVVjTnUtWC1MdTBXX0EtWWM4NnJwQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPR3dMcm02YVpKS2NHZC1YZlJaV2VXZHJMYjNzVzRNa0NfSDNXaFhJcUNseDFYaUVRNVNpdmd5Rm1jbE04d2psTWRBMjZrOUxQQ19fOXdSeXF5cXpPN3NYRWxqMEJ0aFNGcWl4OTJfSU9mSnNxRXRXZHFxY3ZfaHJrNA?oc=5</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -831,27 +831,27 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Dh5,000 fine a month: UAE firms have 5 days to appoint e-invoicing provider - Khaleej Times</t>
+          <t>World Tax Rankings Middle East 2027 released: challenger firms surge in UAE - International Tax Review</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — Big 4 UAE Tax Commentary</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNTGtGYXoyUURCNlQzTzZldFhpUGJIb25mYjVQOXdsNXdDNVRQV1dZVW9EdFJ2aVNsRnQ4c1JsYjgzcWszU2JlbGNYa2p5SUl2UVptQnYyZ0hnQk9KM3BBS0VxNmY2d043bWEzb0ZPM3M1bks5RDFSQjlhNnNYMDRVMmU0SWFCQmZCU18wOWc4bG5yeVNIOE5Fazl4UU9sMjkxclROLVFvQ1l0ckFRaWhMRNIBuAFBVV95cUxNQjIyZmFMNm13T2dZMUpyOVplTWlrVTBEX3N2TS1iaGVQV2hSNFZXbkI4VW1DdDQ2ckcxSEtmRjA3YTA1Unc0dHY4WTBVRGNiRnlCN1RsRzFwQXl2bTJaaFhaYmptVDlQc0lkQ1RvNzViOW9nTGlxZUhnN21WcDBteXlHVm9mdXBqSXcyajhFdmYtZWt1MGlmamQwOEJkTUp6VDZsRkh5YnEyVjVGOHlmenRrb1psT1Vv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQUWp5dVloOUQ4anZfTkR4NnJUYkZYdk1ZU2xDb1h6ZE5Wb3pzRzVxQklBNi1tTC1KWndLRlhpdVBaQmJzZ0FaRFVsNUQ3VXFDOWlRSGRMY3FHM0djMk9TRVQweThXS0lsSmxGN0xOT3V4ckZVNjRuTzVMOGJBSjN0Q1lwOTEtSXBwcm9zTTZUc1MxbVRpd2tRMlFjTE41b0EwTFRxSUg0TjlDTm93RU9WUDJFYm9sS3UtVm5XdWhmTVhndTF1dDdNZHUtWDB6Y2RpeFd5bnk3UzV4VHdwckNra1BoRWk3OVQxMjM5TWFaVkRlSjQ?oc=5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -876,27 +876,27 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>UAE FTA urges e-Invoicing compliance as AED5,000 monthly penalty applies - Emirates 24|7</t>
+          <t>Cross-border Tax Talks - PwC</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — Big 4 UAE Tax Commentary</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQNFV2ZnJIZjdaTm1YS1RtRVN5UzZCZXNZcE9WOWlBV2U4d1BtQUg1SUNhcWJxWWRBRmZLVDl1SGNCbjhTdW1rRGFJUzhlX1dvQ2NkeldjNmdyNHNFLXAydHpUVG4yXzREQk1EN3l0cWpJZlo2RVBLQW5RZEFVMlQ5bXJ4eTBvSS1SVEtxd3RYUnppOUctcktBbTl3T2lOenVFcy1nN0VpaHk3QnQtZldlYzlIS3QxeTJCcDhwMW9xclRRVEtWNVZfZFdveF93UdIBzgFBVV95cUxQNFV2ZnJIZjdaTm1YS1RtRVN5UzZCZXNZcE9WOWlBV2U4d1BtQUg1SUNhcWJxWWRBRmZLVDl1SGNCbjhTdW1rRGFJUzhlX1dvQ2NkeldjNmdyNHNFLXAydHpUVG4yXzREQk1EN3l0cWpJZlo2RVBLQW5RZEFVMlQ5bXJ4eTBvSS1SVEtxd3RYUnppOUctcktBbTl3T2lOenVFcy1nN0VpaHk3QnQtZldlYzlIS3QxeTJCcDhwMW9xclRRVEtWNVZfZFdveF93UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNajMxUTZjZ2tOVUFvYThvdWY2RmE1UmFoV05XbTR1ak5FUXB5Z3FRV2RKdGtuVzZhR1Jva1lKQU5IUmVDMlo1dzNSQlc4TExYbkRudlZQT1haTXZWOGNmXzFPTF90c0luOFNrbWZxa0t5VElhM3NOY21CaS11UmFfVFdtVlRON1hRYjlDY2UxMFR2YVhBQno5Mk05NmJFel9DQXl2RXNsZWxhTTZxMmtycHJtNkdDWjNxX3Y2QU1TWTV5MEFTZFhJQw?oc=5</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -921,12 +921,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -936,12 +936,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>DigiTax partners with Supy to help UAE restaurants adopt e-invoicing - Caterer Middle East</t>
+          <t>Federal Tax Authority issues new guide on scope and registration for Top-Up Tax on multinational enterprises - برق الإمارات</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — FTA Announcements</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQOU1EY2p6d1B0WW9WUFljUmF4dzdCVnVMNE50QjZ0QkJDeUFNYy1DLWl5bU5hdVphdmtOMmNuenVqVHNacTRTeFZqbUFvS3VFOGMzUlZ6VFFsZnJ4V0MxWGZLWkJiT295aWxaaUFjeS14LWlDeE5UYWliQW9nMFRBVWZkUEdHMlp1NWNTN3NadG9LNUwzck5Ja1F3LUlrN2Q3V2RZcEhKY05vejA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQaFhsTDBvVWFWcHJNaWQxdFZoWnpxN0ExT0EtNENrZng3TTh4UFVleDhwOFd3Q05OY09UaXUxNS12YXljOUd3WXl6MWVUdlY5RXhWc3pEYVhBRDZPbjNhX2U4VjJLcUtncVFwMnBZUE55M1ZLLWxhMzFZQnNRYTFleGo3SDhFYWpmYTJ4dWg2dTEyNUkyT3JVQVZVa0JtcU5hdUNKZE52N25XdlNLckRWMThRQTRwQm5ZenFYUEFFYXVBeWhxMTlfNWFieFViR2FpSE84ZDVJcVR5VHhqbGVz?oc=5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -966,12 +966,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>UAE e-invoicing: Oct 30 provider deadline looms for firms with Dhs50m+ revenue - Gulf Business</t>
+          <t>APR, Korea's leading beauty company, showed an 11.8 billion won increase in operating profit in the - 매일경제</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — IFRS Standards</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNd1M0bzNJcTEybmx2M29pY01HRWxvUURNZmxjemd1WDByOGUzSDVmUW4xUnljZnRlQXZBYW1FdW5ubnd0N01wWTVpNjRDR2xzY0lWcGlDd2ZhLV9BNjZsOTJBME5jbTVoUkJUWjdYbVZjaGhoUktjWUYzNkdvRDNyMldoQXN0V3R2WGFOT0wwbkpSX1ZnTVE1YV8xdklwMlROQ2xiR01EU0xaNUlCYXV1TWFYT1FYUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTFBtVnRiOXljUWlKOUtMcC0tQjNycVJxaGJMUTBPZXFwYkFPeHM1Q1R4eXhmNzZGMzhnbVFrNFNZSFAtMjRiYVB2TzNRVXJ2dW8?oc=5</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>UAE e-invoicing rules: Key deadlines for businesses in 2026 and 2027 - Arabian Business</t>
+          <t>Ind AS 118: Big Changes to Financial Reporting Soon - TradingView</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — IFRS Standards</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPMXU4Vm5ScFJWd2tINmI3WEI1X1pwRFU0R2NyYXFra1d1bXFFTWhiVExCdS16SVRNelZOSlB5SG5GaHZTZzhzendZZHV4aDc4WHMyZ2kzcTEwekZDNG0yenlUaWwzUEs4blp6bHlPYXRZMFZLQzZRbG5idHB0a3F0Sw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPa3pEaDB3Q21YU3FhSFQ0ekVZc1pwT00zQXFTbGE1MXkzX3NjazJ5TGZXelg4WnZocTlUZzVDMWp1aFlzNk4yMHIwMGR2d3dBUldzem5pY2xtLUVZckJJa1Rfc0c4MnJxX0YxckZIZWNNY09LVnh5RFVGMko0VEdrSXh2ZWlTdjdsQVlHTWotcGs2X0w0ZVRPbmNyVDdEc085SVNsYjJCR1NkR3M?oc=5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>How tourists can claim UAE VAT refunds in one business day - Travels Dubai</t>
+          <t>UAE Publishes Monthly Fine for Businesses that Miss e-Invoicing Deadline - Legit News</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQUWpQaFlPcE8tQ3ZpWVhKZHBmTGlzVWRtcmdXOWdxcDlGcjZnSWsxa193SXhyQ3duMFphOGt5a1lFRFhveGRpVmlUQ1I4cjhmQTN1aXh5Nks1anFfV0Zua0JBaG44T1lNTWZlRGhtWFRJZkRVV2F3MGJ0RnloVDMtQWlnZGdrQTRBUEVnQUEwYkU0dlhoT2Fn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOcmtkbU5IdUxaZFVXUXVJWno3dERSaEJ2X0xKbGlCSi1rVUt1TDNNQUdiTkcwdEN6YlR6Y1FpeU10WWY2aGhWQ3gycGFOcGRQTUdUbE5BTWxfOGtHcXRRejN6WWktN2FmbjZTTmpsUENidjNEaTktTkVSbVQxRDNBZHNoM3ltLVVjTnUtWC1MdTBXX0EtWWM4NnJwQQ?oc=5</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1116,12 +1116,12 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>"Smarter and simpler": UAE speeds up VAT refunds for tourists shopping in Dubai - Tuko News</t>
+          <t>Dh5,000 fine a month: UAE firms have 5 days to appoint e-invoicing provider - Khaleej Times</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOR0ZWZkx0b2hxUzJfSlEwNEl4YWlSOEVreHVFZmEwMWxia2xYX1BxNThjczJ4bEk3S1lkRy1ZREZTV1FXNDZ2N29tcUxYVWxIZ3lZWkl4VHgtdUZ0QXYwcmFwMlVId19pX0lxWFpMT1hVVkxDZHIxR1NYemlyZ3Y2dG9Iczg3Q0tVcEtfVDlTVm9IQkxwMlQ1eEpRaUdBQmx5R0xQNXZ4QnotSHpYWnZYTlJYX3o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNTGtGYXoyUURCNlQzTzZldFhpUGJIb25mYjVQOXdsNXdDNVRQV1dZVW9EdFJ2aVNsRnQ4c1JsYjgzcWszU2JlbGNYa2p5SUl2UVptQnYyZ0hnQk9KM3BBS0VxNmY2d043bWEzb0ZPM3M1bks5RDFSQjlhNnNYMDRVMmU0SWFCQmZCU18wOWc4bG5yeVNIOE5Fazl4UU9sMjkxclROLVFvQ1l0ckFRaWhMRNIBuAFBVV95cUxNQjIyZmFMNm13T2dZMUpyOVplTWlrVTBEX3N2TS1iaGVQV2hSNFZXbkI4VW1DdDQ2ckcxSEtmRjA3YTA1Unc0dHY4WTBVRGNiRnlCN1RsRzFwQXl2bTJaaFhaYmptVDlQc0lkQ1RvNzViOW9nTGlxZUhnN21WcDBteXlHVm9mdXBqSXcyajhFdmYtZWt1MGlmamQwOEJkTUp6VDZsRkh5YnEyVjVGOHlmenRrb1psT1Vv?oc=5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>UAE launches paperless, AI-powered VAT refund app for tourists - Khaleej Times</t>
+          <t>UAE FTA urges e-Invoicing compliance as AED5,000 monthly penalty applies - Emirates 24|7</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNZWdmNWZuVEo5Uk9mUEQybHRrODZ4M1plWloxXy0wWDRtMlp0WDdlVzkzOEgzMHNxdm1kSXJZcWZSVklxX0pKV3dHSnhMOEs3aXFZYzUwSXdxa2JFcXphbnhmVG10cHJURUFaVkw0dHk5RHF3b0o0QklQQ1ZoNVE3UXRMNnhsbTJyUDdRbDBKTmlhVFdTSUVEN2RXc9IBowFBVV95cUxNbmFfQTNJbmpFSVhLcndEbHQxcGVqcnhzSEVnenJod09jelNLSHVSLVE4dVdtTHlHOFMtcmRjTVVnd2p5cU0ycEFEbWdHbVVoVWdGbVRvRUh5WGpGT0xQVWRaUklXdloySmd2QWRYNlV5UFlPYWhnRF9KM2tsWl9wek9RQ1ZuVVRWaXJkb3F4cHVCMkhfMDFOU0NGNTQtOFV4MGhv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQNFV2ZnJIZjdaTm1YS1RtRVN5UzZCZXNZcE9WOWlBV2U4d1BtQUg1SUNhcWJxWWRBRmZLVDl1SGNCbjhTdW1rRGFJUzhlX1dvQ2NkeldjNmdyNHNFLXAydHpUVG4yXzREQk1EN3l0cWpJZlo2RVBLQW5RZEFVMlQ5bXJ4eTBvSS1SVEtxd3RYUnppOUctcktBbTl3T2lOenVFcy1nN0VpaHk3QnQtZldlYzlIS3QxeTJCcDhwMW9xclRRVEtWNVZfZFdveF93UdIBzgFBVV95cUxQNFV2ZnJIZjdaTm1YS1RtRVN5UzZCZXNZcE9WOWlBV2U4d1BtQUg1SUNhcWJxWWRBRmZLVDl1SGNCbjhTdW1rRGFJUzhlX1dvQ2NkeldjNmdyNHNFLXAydHpUVG4yXzREQk1EN3l0cWpJZlo2RVBLQW5RZEFVMlQ5bXJ4eTBvSS1SVEtxd3RYUnppOUctcktBbTl3T2lOenVFcy1nN0VpaHk3QnQtZldlYzlIS3QxeTJCcDhwMW9xclRRVEtWNVZfZFdveF93UQ?oc=5</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>UAE Launches AI-Powered Tax Refund App For Tourists At Three Major Airports - Travel and Leisure Asia</t>
+          <t>DigiTax partners with Supy to help UAE restaurants adopt e-invoicing - Caterer Middle East</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNeXpZdm5uSHczcUh4UGJ1LU1kWUpJaVBKTFVrcVBBWlVrSlI4aWJzbGRTWHp0bkVQNWlMQ3dWUU44LUpqOTloZjZoN1JEeWwwSHg2YXk3Wm5xOEJTNklQb05UZHBUeUdETWxWWHlvT0dtVEVwODNwZWpFN1RPRzVkWFlYWk9BNExmU0pibXlJY1FFalQzbXVrUk9IMGZ1clhCSEdrTU55YkZ3dXBob2VzcXBsbC1qTm9OQS05d0ZTOWFySjjSAcMBQVVfeXFMTXl6WXZubkh3M3FIeFBidS1NZFlKSWlQSkxVa3FQQVpVa0pSOGlic2xkU1h6dG5FUDVpTEN3VlFOOC1Kajk5aGY2aDdSRHlsMEh4NmF5N1pucThCUzZJUG9OVGRwVHlHRE1sVlh5b09HbVRFcDgzcGVqRTdUT0c1ZFhZWFpPQTRMZlNKYm15SWNRRWpUM211a1JPSDBmdXJYQkhHa01OeWJGd3VwaG9lc3FwbGwtak5vTkEtOXdGUzlhcko4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQOU1EY2p6d1B0WW9WUFljUmF4dzdCVnVMNE50QjZ0QkJDeUFNYy1DLWl5bU5hdVphdmtOMmNuenVqVHNacTRTeFZqbUFvS3VFOGMzUlZ6VFFsZnJ4V0MxWGZLWkJiT295aWxaaUFjeS14LWlDeE5UYWliQW9nMFRBVWZkUEdHMlp1NWNTN3NadG9LNUwzck5Ja1F3LUlrN2Q3V2RZcEhKY05vejA?oc=5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,12 +1251,12 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>UAE: Claiming VAT Refunds For Tourists Just Got Simpler With New AI-Powered Digital Platform! - Curly Tales</t>
+          <t>UAE e-invoicing: Oct 30 provider deadline looms for firms with Dhs50m+ revenue - Gulf Business</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxORDJuVlViQjVHZ3JEMUxXV2NqVjBhbXVSWk1WWm1CMUVqU0RLX0JMNjctNnE1Q1FmSEhVZnNUcFFrLVBGQjJSWHF6UDJlVTJObFNhcDFRcnh3WFZMTEVycjZ3S2NEZnpqT180dFpHZ0VCeXgzdVd5QW5Yd0w3QUdHOXI5WE9NUzFPYlVYY0RTZ3NhU2kzWWRramVROTRQdmsxNk1zblRXY1ZOTVVnQlFicXNFTnRsWlYwWnBNd2Y3WV9EbFJlYi1UN2Z1dzlpSnfSAdQBQVVfeXFMTVJyVkVYR05PQldudW1QSzJsS0V5aW0yZVNyRmQ1YmhBaDhMVmtoNTJfSnZTdUV0amhlQ2lTa1pxbnpWRTA5aG9DaDhEdExWTDRrVmszb1gyTkNLY1RUMThXNEM2eXhKa2ZmUDNxbGM1YlVLQXl6c0MyaW5KQ2tQMGxMQ0dmM25iN3U3MUZKazN3X0lNeU83ZXJwTkE5REViLVZJZzJqcGVaLTJXWV9nWE9EVmJqSVJHV05XaXMtTkRjbTkzZml3bkNTdjFnYWVjU1E4SzY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNd1M0bzNJcTEybmx2M29pY01HRWxvUURNZmxjemd1WDByOGUzSDVmUW4xUnljZnRlQXZBYW1FdW5ubnd0N01wWTVpNjRDR2xzY0lWcGlDd2ZhLV9BNjZsOTJBME5jbTVoUkJUWjdYbVZjaGhoUktjWUYzNkdvRDNyMldoQXN0V3R2WGFOT0wwbkpSX1ZnTVE1YV8xdklwMlROQ2xiR01EU0xaNUlCYXV1TWFYT1FYUQ?oc=5</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>UAE Launches AI-Powered Tourist VAT Refund Platform Across Three Airports - Konsulteer</t>
+          <t>UAE e-invoicing rules: Key deadlines for businesses in 2026 and 2027 - Arabian Business</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOaTNXUlc5Yk5IdGN4RF9PeDN3Nkc3WnducVRwSEczbFlhb2dLXzlKNWFsdEh4VlQxZTRNRl9VQjhYZDgwWU51dmRjZVhYUFR1WFBKcWltSTZwcEp5N3ZYVkNRNWZVaTU3UXNBZzZqTVFrN2pMci1jZGhRemRGSnVRLTZsNW1Rc05Ic3NGd21nLU85VVJFLVR5MzZrOWI4Mkc2anZqb042c0xqUGc3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPMXU4Vm5ScFJWd2tINmI3WEI1X1pwRFU0R2NyYXFra1d1bXFFTWhiVExCdS16SVRNelZOSlB5SG5GaHZTZzhzendZZHV4aDc4WHMyZ2kzcTEwekZDNG0yenlUaWwzUEs4blp6bHlPYXRZMFZLQzZRbG5idHB0a3F0Sw?oc=5</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>UAE cuts tourist VAT refund time to one business day with new AI platform - Gulf Business</t>
+          <t>How tourists can claim UAE VAT refunds in one business day - Travels Dubai</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPZURXSjRhbWwwMzRkaWYyWlJSWkpSUl9nYllHVFJ0RnpDTHR4dGZJY2tlZzVGbEJuYWRjeFlXSm9fMDhDWTJwS2ViMTd2M1dKc2I1aUZmMTVGclB1eUhnRGV4SnlRZzJRWHhGYW80SFM0cWpCTjR5T29PMUNfU2l6MUN2RWlmdXVKTE5fVHkwNDZxVzdJSmdiUngtTlRzZHRqNHpNTkVSYy1Bb0JN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQUWpQaFlPcE8tQ3ZpWVhKZHBmTGlzVWRtcmdXOWdxcDlGcjZnSWsxa193SXhyQ3duMFphOGt5a1lFRFhveGRpVmlUQ1I4cjhmQTN1aXh5Nks1anFfV0Zua0JBaG44T1lNTWZlRGhtWFRJZkRVV2F3MGJ0RnloVDMtQWlnZGdrQTRBUEVnQUEwYkU0dlhoT2Fn?oc=5</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Federal Tax Authority launches world’s first-of-its-kind AI-powered digital platform for tourist tax refunds - Zawya</t>
+          <t>"Smarter and simpler": UAE speeds up VAT refunds for tourists shopping in Dubai - Tuko News</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxQV0NXYW5reU5Sb1FHRmNDT3dyaXphV2ZORlVZYXNhN1ZQV1FldnhlZGF4VTJpVVJ6c0k4MGRqZE13Rm95S0ZWWkpVQUdlNFpTdDA2cks5akhhZmNZNlFuVU8wVkVJMFhiRUVjNTg5d1dzb2htY05tM0xIb0RhS0dhZ1RaQzZrQ2Z6ZzJJTnlZd19vOTJsU09pamc1TWFqaGFiUFM3Z1JNSGlac0lFeDRrcFpIYWxLN3ZlVjdtc2drS01FRTl1eTdCM3FZdFd1ZU1jODNWYkZ2WHZzZk5USlNVcnlsTXRrcnhaUi1fbUhXWnR6U0FUc3lydXJwNDIyWWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOR0ZWZkx0b2hxUzJfSlEwNEl4YWlSOEVreHVFZmEwMWxia2xYX1BxNThjczJ4bEk3S1lkRy1ZREZTV1FXNDZ2N29tcUxYVWxIZ3lZWkl4VHgtdUZ0QXYwcmFwMlVId19pX0lxWFpMT1hVVkxDZHIxR1NYemlyZ3Y2dG9Iczg3Q0tVcEtfVDlTVm9IQkxwMlQ1eEpRaUdBQmx5R0xQNXZ4QnotSHpYWnZYTlJYX3o?oc=5</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>UAE Publishes Version 2.0 of E-Invoicing Guidelines - sharedserviceslink</t>
+          <t>UAE launches paperless, AI-powered VAT refund app for tourists - Khaleej Times</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPV1NkTHUycS0tOFh6TF9HVW4yU051Zk1zTExPWTVONTcxemN0WTVBajl3QkxVY3Bocno5N1BVbDFkUlZjQ214VEZQc1Y0eURfMHZzdTNyV0RuRmU0OXA4dU9MMTZhN19POUdvMXJRSld6UDZkbU9YbWNkaTVzeW9DNDNwX25zRGFKMGgwQlBfR3JzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNZWdmNWZuVEo5Uk9mUEQybHRrODZ4M1plWloxXy0wWDRtMlp0WDdlVzkzOEgzMHNxdm1kSXJZcWZSVklxX0pKV3dHSnhMOEs3aXFZYzUwSXdxa2JFcXphbnhmVG10cHJURUFaVkw0dHk5RHF3b0o0QklQQ1ZoNVE3UXRMNnhsbTJyUDdRbDBKTmlhVFdTSUVEN2RXc9IBowFBVV95cUxNbmFfQTNJbmpFSVhLcndEbHQxcGVqcnhzSEVnenJod09jelNLSHVSLVE4dVdtTHlHOFMtcmRjTVVnd2p5cU0ycEFEbWdHbVVoVWdGbVRvRUh5WGpGT0xQVWRaUklXdloySmd2QWRYNlV5UFlPYWhnRF9KM2tsWl9wek9RQ1ZuVVRWaXJkb3F4cHVCMkhfMDFOU0NGNTQtOFV4MGhv?oc=5</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>UAE's new AI platform to slash VAT refund time for tourists to one day - The National</t>
+          <t>UAE Launches AI-Powered Tax Refund App For Tourists At Three Major Airports - Travel and Leisure Asia</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQZVpMLWZ4cmVQdDlnSlZRRERKN0tJbVR5eGVfblhRam5IUGwtXzdIaWJqeWlSNEVNVGozWGpvMm5LSGQ0YXdlVl92YjRPNHhtZDFIQ2swNlRtdzRQeUtTVmE1d1ZfVF9vdXR3N1RvV3ZoLXlZdWFyTENheUtIa0lOTjZTcjUza3VWVmFLaXpEVm1kTkpVandrTE80a0dadG9IMlJsWUhyZHU4U0tMS3I0cVQ0RVM1aTUzWGF4U2pvQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNeXpZdm5uSHczcUh4UGJ1LU1kWUpJaVBKTFVrcVBBWlVrSlI4aWJzbGRTWHp0bkVQNWlMQ3dWUU44LUpqOTloZjZoN1JEeWwwSHg2YXk3Wm5xOEJTNklQb05UZHBUeUdETWxWWHlvT0dtVEVwODNwZWpFN1RPRzVkWFlYWk9BNExmU0pibXlJY1FFalQzbXVrUk9IMGZ1clhCSEdrTU55YkZ3dXBob2VzcXBsbC1qTm9OQS05d0ZTOWFySjjSAcMBQVVfeXFMTXl6WXZubkh3M3FIeFBidS1NZFlKSWlQSkxVa3FQQVpVa0pSOGlic2xkU1h6dG5FUDVpTEN3VlFOOC1Kajk5aGY2aDdSRHlsMEh4NmF5N1pucThCUzZJUG9OVGRwVHlHRE1sVlh5b09HbVRFcDgzcGVqRTdUT0c1ZFhZWFpPQTRMZlNKYm15SWNRRWpUM211a1JPSDBmdXJYQkhHa01OeWJGd3VwaG9lc3FwbGwtak5vTkEtOXdGUzlhcko4?oc=5</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>UAE announces major tax refund upgrade: Tourist VAT rules explained - Arabian Business</t>
+          <t>UAE: Claiming VAT Refunds For Tourists Just Got Simpler With New AI-Powered Digital Platform! - Curly Tales</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOOV9mdmlpRVVsSTdjRnA2bV9OSGUtNGlvNmgzTWVjSGJiZFkyYmpBQ1h1UE4zY2VGN3FFQ1M3N09ZQm4zc1lTNl8ybDNKTll4c1FweWZlNFBLMFI3aFRfSzAtaHJzVmxSajI4amM1OFBMRUlnWnBfbWZ2a0s1azBieWtybl9VRmVrRmd0VVI4T0tzNWZZbWdCNE5NR3BxZVR0TW1EZ3VCTlBHZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxORDJuVlViQjVHZ3JEMUxXV2NqVjBhbXVSWk1WWm1CMUVqU0RLX0JMNjctNnE1Q1FmSEhVZnNUcFFrLVBGQjJSWHF6UDJlVTJObFNhcDFRcnh3WFZMTEVycjZ3S2NEZnpqT180dFpHZ0VCeXgzdVd5QW5Yd0w3QUdHOXI5WE9NUzFPYlVYY0RTZ3NhU2kzWWRramVROTRQdmsxNk1zblRXY1ZOTVVnQlFicXNFTnRsWlYwWnBNd2Y3WV9EbFJlYi1UN2Z1dzlpSnfSAdQBQVVfeXFMTVJyVkVYR05PQldudW1QSzJsS0V5aW0yZVNyRmQ1YmhBaDhMVmtoNTJfSnZTdUV0amhlQ2lTa1pxbnpWRTA5aG9DaDhEdExWTDRrVmszb1gyTkNLY1RUMThXNEM2eXhKa2ZmUDNxbGM1YlVLQXl6c0MyaW5KQ2tQMGxMQ0dmM25iN3U3MUZKazN3X0lNeU83ZXJwTkE5REViLVZJZzJqcGVaLTJXWV9nWE9EVmJqSVJHV05XaXMtTkRjbTkzZml3bkNTdjFnYWVjU1E4SzY?oc=5</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>UAE launches AI platform to cut tourist VAT refunds to one business day — The National - UA.NEWS</t>
+          <t>UAE Launches AI-Powered Tourist VAT Refund Platform Across Three Airports - Konsulteer</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQYXdJZkJvX3ByM0lXS2ZtYjlHR0poREtsemlTaHdPWGExcVBhQzdNR3kyWmJMNHJsTnVYemRldHg2aG1jdlNidk5sV1JjcldzRF85dzh6ckpHeHdWVHp0SVdzeFZGNFlzdW04Q1dockJ1ajU2bnRFcmdwLUZfbE9iVm0tRE9jQklXM1Qzc2ppV2lDM19vUGUxLU9uc1ZJNm9TcTNlYnFnTzh2RVZyZUFEM0VVdHZWRFNKQmJsX1ZtQlc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOaTNXUlc5Yk5IdGN4RF9PeDN3Nkc3WnducVRwSEczbFlhb2dLXzlKNWFsdEh4VlQxZTRNRl9VQjhYZDgwWU51dmRjZVhYUFR1WFBKcWltSTZwcEp5N3ZYVkNRNWZVaTU3UXNBZzZqTVFrN2pMci1jZGhRemRGSnVRLTZsNW1Rc05Ic3NGd21nLU85VVJFLVR5MzZrOWI4Mkc2anZqb042c0xqUGc3?oc=5</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>UAE Federal Tax Authority Launches Digital VAT Refund Platform for Tourists - News and Statistics - IndexBox</t>
+          <t>UAE cuts tourist VAT refund time to one business day with new AI platform - Gulf Business</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOSm9HaWZSWEFFM3BNOW5acHZBT0luQWFnVEo3QUpJR1AwdUNMVjE0V3RXUXptLVVZR1VBN3doSnZlU1RNcU40UmJNVWpfQnVpY3NNRGRqNTM3WVFNRnB5X0g3SXFfbkl0Rk91MEtTWVBRejJDOElIcmxLSG1TcnNaRWdVbUdoS0QtMGVRX0NzSjJOSVJyV1luRVZsRW9ldl80c2VfUkNiempDdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPZURXSjRhbWwwMzRkaWYyWlJSWkpSUl9nYllHVFJ0RnpDTHR4dGZJY2tlZzVGbEJuYWRjeFlXSm9fMDhDWTJwS2ViMTd2M1dKc2I1aUZmMTVGclB1eUhnRGV4SnlRZzJRWHhGYW80SFM0cWpCTjR5T29PMUNfU2l6MUN2RWlmdXVKTE5fVHkwNDZxVzdJSmdiUngtTlRzZHRqNHpNTkVSYy1Bb0JN?oc=5</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>XYRA unveils an intuitive AI platform to transform UAE business accounting - Gulf News</t>
+          <t>Federal Tax Authority launches world’s first-of-its-kind AI-powered digital platform for tourist tax refunds - Zawya</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPeHRnSjFza2hMY1l3Q3p2dGtXYkRZRW5qTmFaZkJqTW1YZjU5Rzlva1pjTEJSMEg5MVlZd0pCdENvc2p4OXVGdWdBSEd6Q0gyWTFZS2JoUVVpaVVDa3hsYmNSaE1XWlZJWmZua3lOUVprakhMZFZmR1JsYjFTeDM5YWY2VGtLSmtCT3BOaS05aWRXV0k5NUJVanRpcFQ1MzJIdGVUcTd0cG55ZkpheGIxVjI3MlcwRHp0cmZOUEJPanVSUDNmWW1IUElMb1RYdExIOWFNd1lZcmU2X3hXSTYwVEhR0gH0AUFVX3lxTE9lZTBHQThBcUxrMHRBZkROUzQtaW9WMWVmaVhPdk9wYmtkZlYzVEJ0Z2FuWk1CVTFka0pZOTQxYlVMdzFXNVQxbWdIaURLWmY4RGNRM3FCaFRKbVF6akpqRmVabE9BX095Rk5tV0NZN3lRTm42bzNJR1dxUnJleklmd2E0bm9FUnVGTWxwUE05T2d4ZEVhUnBYVzNvazZHbWFWY29FSXVhU1NMTloweUlpdWZIYTl6b3BSaks4d2NrUFJQUzlqX2lzRFctMTF1ZnprRHZMMkNkRmFYbndEMl9YNHV0aXB0N0h1cU1YRHFPRE4zNWU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxQV0NXYW5reU5Sb1FHRmNDT3dyaXphV2ZORlVZYXNhN1ZQV1FldnhlZGF4VTJpVVJ6c0k4MGRqZE13Rm95S0ZWWkpVQUdlNFpTdDA2cks5akhhZmNZNlFuVU8wVkVJMFhiRUVjNTg5d1dzb2htY05tM0xIb0RhS0dhZ1RaQzZrQ2Z6ZzJJTnlZd19vOTJsU09pamc1TWFqaGFiUFM3Z1JNSGlac0lFeDRrcFpIYWxLN3ZlVjdtc2drS01FRTl1eTdCM3FZdFd1ZU1jODNWYkZ2WHZzZk5USlNVcnlsTXRrcnhaUi1fbUhXWnR6U0FUc3lydXJwNDIyWWc?oc=5</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1686,12 +1686,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1701,12 +1701,12 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>UAE tourist VAT refunds cut to one business day with new AI platform - Gulf News</t>
+          <t>UAE Publishes Version 2.0 of E-Invoicing Guidelines - sharedserviceslink</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPTHpETlBMdE1Kb2FWR0ZBdG5jRldvV1ZOWFpJYnMyVWhlQ1hTUE43dkV5UTJIWVA3eVFER0pKNXZHYTVXc3h4eVJ2R09YYVh3dEpkb2k3cXlyYWQyU3pPS0dvSjZhSkNmS1hpM0UwU0VXbEx6d2hydlh3SUJ4amkzQ3RlVGRtRTlqdGdjdW9rMVJkUG5PazRPdkZuY25mdHVoakZIZWFfcWNaLThEeXNyazVhTnVPckJZbXg40gHOAUFVX3lxTFBpcjZEUUktS3kzU1JHZzctTGFPTWZ2WG5PTGc0N21xLWoyS3gybHEzY0hMYU9XeGh2QUE0Z1NRSURaV0xhUkV6Y2VmbkpCR0VBRjR5c2l4SVpPYnBCQ28zTHNVN0k2aWhXcnpMYjFCaFJyUzQ3OUVJM0Q5YVBOS0JZbUV2ZXJVcS1xX2dnUGlYZ3NBaDVmREZyV3QxeTk3VnVUNDJfbG9fekhjX25MOEVhSERXSTk1a0x5THRXT3V2RmRtbkRXd0dTXzEzNWlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPV1NkTHUycS0tOFh6TF9HVW4yU051Zk1zTExPWTVONTcxemN0WTVBajl3QkxVY3Bocno5N1BVbDFkUlZjQ214VEZQc1Y0eURfMHZzdTNyV0RuRmU0OXA4dU9MMTZhN19POUdvMXJRSld6UDZkbU9YbWNkaTVzeW9DNDNwX25zRGFKMGgwQlBfR3JzQQ?oc=5</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1731,12 +1731,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1746,12 +1746,12 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>UAE e-invoicing deadline: Businesses face Dh5,000 monthly fines for delays - Gulf News</t>
+          <t>UAE's new AI platform to slash VAT refund time for tourists to one day - The National</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPWWVSUnR0QVRxaG1QTlhqa3NxcFNNQkdlNi1lYWVKRjFuOFRQMWNoNnY5Ni1CVWVNYWJjSEc3MVU0Q3h3eC0yQ0lJV2NRQTk1TWF3eThpcHFETEQ0OFg1SmJuYUVaZTVvZ3FHc3VpdW8zcEVtbTJJb1FHSFY5dWFOMk5SU3M5ZUpJNEk1OHQ3X1dxeFhLQ0tEbFRtcDR4dG04NS1aY2huV3BJVzlzeDFReDBKdmJmRjVnV3BkOWNQZ3bSAdMBQVVfeXFMTVFtR1VkanA4NWlBaDVrR1V2bDhlak5IUy16ODQtV24xTUVKdG5Sa0ZoeE42MlFWYjJuSmszT3JTSnd5ajJ1ZG1XQmd0M3hUWW5jczlsQ1hWQ3dNRFNxQUsxRkpfTm00WnBybTRpV3F6WXE4NXJmR3MzZDNOZzNqZzU3NmJKWjRVYzdoLXVGNFU2Tmh5Z3AtcVNUMTh0S0M4YThYVllGdW15MVdsZGM5cDFrS2hsV0JERUxzOXJhWkNEMnlydHhfazRucFhEMkUwVmUwOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQZVpMLWZ4cmVQdDlnSlZRRERKN0tJbVR5eGVfblhRam5IUGwtXzdIaWJqeWlSNEVNVGozWGpvMm5LSGQ0YXdlVl92YjRPNHhtZDFIQ2swNlRtdzRQeUtTVmE1d1ZfVF9vdXR3N1RvV3ZoLXlZdWFyTENheUtIa0lOTjZTcjUza3VWVmFLaXpEVm1kTkpVandrTE80a0dadG9IMlJsWUhyZHU4U0tMS3I0cVQ0RVM1aTUzWGF4U2pvQQ?oc=5</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>UAE VAT rules change staff expense claims: What businesses need to review - Gulf News</t>
+          <t>UAE announces major tax refund upgrade: Tourist VAT rules explained - Arabian Business</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPNjVZSlVOR1Bab1VubGlRNjZGeDNPWmVNSnRSNDlCXzk3bFk0U2dQTUt6dFlMVmY1QkpvWU1XMlVoQTN2MzluUVNxY01BYWtVb3JuYjFNU1dfQjl2X0dDTnJrXzd3eFFpanBCNGk1QS05LVAyVlliZUgzRFJhaHFKaTlsOTBMOExqLWtBUGZDaXFSZmVfZkRPQk9YSzF2VlNiUlJtbU9RWndXLUxjMjhoN1ZwYWYySDZHZkJRNGdTak3SAdMBQVVfeXFMTUhINEdZNjQybDJ5TjhWUkMwNDBmcENESVUxc214S044NTBva0JGVWNJMFFidVczdFVuN0U5d3VIT1dCczVFLW00LUczN080X0xVWmZTbVd2dkxEaWJBZkxuVHFuWjBoeWpDczhpVVJ2ZTVaY0R1dVVtN24tV3R0bU9WVm52M0lBeDQ0T2c3cEdBUjRjRHFkQTdiUl9HTmw2dmNDTk5BRkpjdVN0NlJaRVR6emc1Q2lpQUxocWx3SFFtRDFRZkI4cmMwLW5BTVhwUWNQbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOOV9mdmlpRVVsSTdjRnA2bV9OSGUtNGlvNmgzTWVjSGJiZFkyYmpBQ1h1UE4zY2VGN3FFQ1M3N09ZQm4zc1lTNl8ybDNKTll4c1FweWZlNFBLMFI3aFRfSzAtaHJzVmxSajI4amM1OFBMRUlnWnBfbWZ2a0s1azBieWtybl9VRmVrRmd0VVI4T0tzNWZZbWdCNE5NR3BxZVR0TW1EZ3VCTlBHZw?oc=5</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -1821,12 +1821,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>UAE e-invoicing deadline in 4 days: Who must comply to avoid Dh5,000 fines - Gulf News</t>
+          <t>UAE launches AI platform to cut tourist VAT refunds to one business day — The National - UA.NEWS</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNLWxHNTZNMkNZUTRHY3hWSFRld05JZm9FRzh3TlZsQzNCS2NqX3kwQjBvbFpjUXBCSG8xRmRLUFBhM25YYTVVNXNyQWFmYjdUTk9ndTZCRmY3dDVObUpsLW85bC1pZzUtWGM5UmR3d2hEckZDUDEzdXN2MEN3MXpFa1JaZWRDVGU5aGE3Ul9nVlZPN0FhVGRjSlctX2lnSHNyeDQ3Z2RFTEN6UmRZRXVuMkNBbGRrbFJfaGpZazZQT07SAdMBQVVfeXFMUEhrM2xRZk5Uc2Z2ZkRUV1p3bGpQSkEzaGpaQkdhZ1lrYld2LUMxd3ozdTh6WmxJVkJYNkJCeGxGOURPY2dsbU9RdmphOXpncm03bjZvSWRDeUp0Ykg5NmpOQjUyZ1MwS08xcTdzOXhnSFZGNklnbGxpTk44aldNOFJrNVNuS2trMkphb0xpOXN3ZU13Y0JmN0Q1ZlQtWTZscmNwa0RTbGg4M1M0cHd2R2NXTV9fRFZwQk5aNjMyUF90VXUwX2prR09OaklId0VYSFlHaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQYXdJZkJvX3ByM0lXS2ZtYjlHR0poREtsemlTaHdPWGExcVBhQzdNR3kyWmJMNHJsTnVYemRldHg2aG1jdlNidk5sV1JjcldzRF85dzh6ckpHeHdWVHp0SVdzeFZGNFlzdW04Q1dockJ1ajU2bnRFcmdwLUZfbE9iVm0tRE9jQklXM1Qzc2ppV2lDM19vUGUxLU9uc1ZJNm9TcTNlYnFnTzh2RVZyZUFEM0VVdHZWRFNKQmJsX1ZtQlc?oc=5</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Ezat Alnajm on Preparing Crypto Wealth for Greater Tax Transparency - Hubbis</t>
+          <t>UAE Federal Tax Authority Launches Digital VAT Refund Platform for Tourists - News and Statistics - IndexBox</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQRkVXSUFZWnYwTXRYTG5GZUtmN0pZLWx2anJoNTM1VERGZUVha1JZc01kMWxHek92SEVEbkgzeDgyZWh0RXY3VFhuYVJKcTlNeklhQlJvUVB1WXNnMVZ5WUFmY2pxYzNqblZRYkRBemxhdzktaWhwLVNBZFNqOE9RVGlsRm4zazVuVExuUGZtQ19JM2xFRHFldFdxbmN1Sjg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOSm9HaWZSWEFFM3BNOW5acHZBT0luQWFnVEo3QUpJR1AwdUNMVjE0V3RXUXptLVVZR1VBN3doSnZlU1RNcU40UmJNVWpfQnVpY3NNRGRqNTM3WVFNRnB5X0g3SXFfbkl0Rk91MEtTWVBRejJDOElIcmxLSG1TcnNaRWdVbUdoS0QtMGVRX0NzSjJOSVJyV1luRVZsRW9ldl80c2VfUkNiempDdw?oc=5</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Ministerial Decision No. 197 of 2026 - Crowe</t>
+          <t>XYRA unveils an intuitive AI platform to transform UAE business accounting - Gulf News</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOMFZaS3RKdnpEdVpQcUtlN1JJWlBuZmxxRkpnZHB4WXFpUGg1cHpjcHdKUzJlM0VTVExnRExWRkowZm5iek1yUHpaY3ZWamZfS3ZpM0tkSW9MTjV0YmxHOFhpeDltbkxENmZLamJkV1ZKMklZUjAySU1aZGVZSnRMamIxejJBdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPeHRnSjFza2hMY1l3Q3p2dGtXYkRZRW5qTmFaZkJqTW1YZjU5Rzlva1pjTEJSMEg5MVlZd0pCdENvc2p4OXVGdWdBSEd6Q0gyWTFZS2JoUVVpaVVDa3hsYmNSaE1XWlZJWmZua3lOUVprakhMZFZmR1JsYjFTeDM5YWY2VGtLSmtCT3BOaS05aWRXV0k5NUJVanRpcFQ1MzJIdGVUcTd0cG55ZkpheGIxVjI3MlcwRHp0cmZOUEJPanVSUDNmWW1IUElMb1RYdExIOWFNd1lZcmU2X3hXSTYwVEhR0gH0AUFVX3lxTE9lZTBHQThBcUxrMHRBZkROUzQtaW9WMWVmaVhPdk9wYmtkZlYzVEJ0Z2FuWk1CVTFka0pZOTQxYlVMdzFXNVQxbWdIaURLWmY4RGNRM3FCaFRKbVF6akpqRmVabE9BX095Rk5tV0NZN3lRTm42bzNJR1dxUnJleklmd2E0bm9FUnVGTWxwUE05T2d4ZEVhUnBYVzNvazZHbWFWY29FSXVhU1NMTloweUlpdWZIYTl6b3BSaks4d2NrUFJQUzlqX2lzRFctMTF1ZnprRHZMMkNkRmFYbndEMl9YNHV0aXB0N0h1cU1YRHFPRE4zNWU?oc=5</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Amendments to the UAE electronic invoicing system decision - Simmons &amp; Simmons</t>
+          <t>UAE tourist VAT refunds cut to one business day with new AI platform - Gulf News</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOUzJMUUdnR2Z0TjQ2eEMteTVMNHpOZndFbEh3T1hJaVQ5Z29HdXRlS3lTcXdRbkFFMnVRdFI5a0QzMzlQM2EzZnBDY1VDLXJUeFI5T1VtQnJ5UEFHTmU1bVA0bWJiMTZwTmhFR21sZzE0WEZReGRwMWRDalVDbm9kVWpVM0VfTmJHeThySXRwYjY0UzZXS1NhT0J2T0tGLVczYjk3Mno2TDZPeU5BbGM3VGR6SDJYR0wydkkxNUtYSzM1a19ocnhlNWQ3VS0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPTHpETlBMdE1Kb2FWR0ZBdG5jRldvV1ZOWFpJYnMyVWhlQ1hTUE43dkV5UTJIWVA3eVFER0pKNXZHYTVXc3h4eVJ2R09YYVh3dEpkb2k3cXlyYWQyU3pPS0dvSjZhSkNmS1hpM0UwU0VXbEx6d2hydlh3SUJ4amkzQ3RlVGRtRTlqdGdjdW9rMVJkUG5PazRPdkZuY25mdHVoakZIZWFfcWNaLThEeXNyazVhTnVPckJZbXg40gHOAUFVX3lxTFBpcjZEUUktS3kzU1JHZzctTGFPTWZ2WG5PTGc0N21xLWoyS3gybHEzY0hMYU9XeGh2QUE0Z1NRSURaV0xhUkV6Y2VmbkpCR0VBRjR5c2l4SVpPYnBCQ28zTHNVN0k2aWhXcnpMYjFCaFJyUzQ3OUVJM0Q5YVBOS0JZbUV2ZXJVcS1xX2dnUGlYZ3NBaDVmREZyV3QxeTk3VnVUNDJfbG9fekhjX25MOEVhSERXSTk1a0x5THRXT3V2RmRtbkRXd0dTXzEzNWlR?oc=5</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -1999,7 +1999,11 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>E-Invoicing</t>
@@ -2007,27 +2011,27 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>official</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Finance Amends Electronic Invoicing Regulations to Ease the Burden on Businesses</t>
+          <t>UAE e-invoicing deadline: Businesses face Dh5,000 monthly fines for delays - Gulf News</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Ministry of Finance — News</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>mof.gov.ae</t>
+          <t>news.google.com</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>https://mof.gov.ae/en/news/ministry-of-finance-amends-electronic-invoicing-regulations-to-ease-the-burden-on-businesses/</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPWWVSUnR0QVRxaG1QTlhqa3NxcFNNQkdlNi1lYWVKRjFuOFRQMWNoNnY5Ni1CVWVNYWJjSEc3MVU0Q3h3eC0yQ0lJV2NRQTk1TWF3eThpcHFETEQ0OFg1SmJuYUVaZTVvZ3FHc3VpdW8zcEVtbTJJb1FHSFY5dWFOMk5SU3M5ZUpJNEk1OHQ3X1dxeFhLQ0tEbFRtcDR4dG04NS1aY2huV3BJVzlzeDFReDBKdmJmRjVnV3BkOWNQZ3bSAdMBQVVfeXFMTVFtR1VkanA4NWlBaDVrR1V2bDhlak5IUy16ODQtV24xTUVKdG5Sa0ZoeE42MlFWYjJuSmszT3JTSnd5ajJ1ZG1XQmd0M3hUWW5jczlsQ1hWQ3dNRFNxQUsxRkpfTm00WnBybTRpV3F6WXE4NXJmR3MzZDNOZzNqZzU3NmJKWjRVYzdoLXVGNFU2Tmh5Z3AtcVNUMTh0S0M4YThYVllGdW15MVdsZGM5cDFrS2hsV0JERUxzOXJhWkNEMnlydHhfazRucFhEMkUwVmUwOA?oc=5</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2040,35 +2044,39 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>official</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>UAE Breaks into Global Top 10 in IMD’s 2026 Government Support Index</t>
+          <t>UAE VAT rules change staff expense claims: What businesses need to review - Gulf News</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Ministry of Finance — News</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>mof.gov.ae</t>
+          <t>news.google.com</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>https://mof.gov.ae/en/news/uae-breaks-into-global-top-10-in-imds-2026-government-support-index/</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPNjVZSlVOR1Bab1VubGlRNjZGeDNPWmVNSnRSNDlCXzk3bFk0U2dQTUt6dFlMVmY1QkpvWU1XMlVoQTN2MzluUVNxY01BYWtVb3JuYjFNU1dfQjl2X0dDTnJrXzd3eFFpanBCNGk1QS05LVAyVlliZUgzRFJhaHFKaTlsOTBMOExqLWtBUGZDaXFSZmVfZkRPQk9YSzF2VlNiUlJtbU9RWndXLUxjMjhoN1ZwYWYySDZHZkJRNGdTak3SAdMBQVVfeXFMTUhINEdZNjQybDJ5TjhWUkMwNDBmcENESVUxc214S044NTBva0JGVWNJMFFidVczdFVuN0U5d3VIT1dCczVFLW00LUczN080X0xVWmZTbVd2dkxEaWJBZkxuVHFuWjBoeWpDczhpVVJ2ZTVaY0R1dVVtN24tV3R0bU9WVm52M0lBeDQ0T2c3cEdBUjRjRHFkQTdiUl9HTmw2dmNDTk5BRkpjdVN0NlJaRVR6emc1Q2lpQUxocWx3SFFtRDFRZkI4cmMwLW5BTVhwUWNQbw?oc=5</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2081,35 +2089,39 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>IFRS / Reporting</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>official</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Finance convenes Financial Data Forum 2026 to boost efficiency in final account and financial statement preparation and reinforce the application of international accounting standards</t>
+          <t>UAE e-invoicing deadline in 4 days: Who must comply to avoid Dh5,000 fines - Gulf News</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Ministry of Finance — News</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>mof.gov.ae</t>
+          <t>news.google.com</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>https://mof.gov.ae/en/news/ministry-of-finance-convenes-financial-data-forum-2026-to-boost-efficiency-in-final-account-and-financial-statement-preparation-and-reinforce-the-application-of-international-accounting-standards/</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNLWxHNTZNMkNZUTRHY3hWSFRld05JZm9FRzh3TlZsQzNCS2NqX3kwQjBvbFpjUXBCSG8xRmRLUFBhM25YYTVVNXNyQWFmYjdUTk9ndTZCRmY3dDVObUpsLW85bC1pZzUtWGM5UmR3d2hEckZDUDEzdXN2MEN3MXpFa1JaZWRDVGU5aGE3Ul9nVlZPN0FhVGRjSlctX2lnSHNyeDQ3Z2RFTEN6UmRZRXVuMkNBbGRrbFJfaGpZazZQT07SAdMBQVVfeXFMUEhrM2xRZk5Uc2Z2ZkRUV1p3bGpQSkEzaGpaQkdhZ1lrYld2LUMxd3ozdTh6WmxJVkJYNkJCeGxGOURPY2dsbU9RdmphOXpncm03bjZvSWRDeUp0Ykg5NmpOQjUyZ1MwS08xcTdzOXhnSFZGNklnbGxpTk44aldNOFJrNVNuS2trMkphb0xpOXN3ZU13Y0JmN0Q1ZlQtWTZscmNwa0RTbGg4M1M0cHd2R2NXTV9fRFZwQk5aNjMyUF90VXUwX2prR09OaklId0VYSFlHaw?oc=5</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2119,12 +2131,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2139,12 +2151,12 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Foreign outflows in July were the lowest in the GCC - EnterpriseAM</t>
+          <t>Ezat Alnajm on Preparing Crypto Wealth for Greater Tax Transparency - Hubbis</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -2154,7 +2166,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE8tRko4Unh0QWI1ekpUTHJ3QmktT1dyWXd2S2REcHZIZVVvd2Rtdm1WSkUtQUtacjlnSGlLdWtIMk0tVVNxU1ZKTU1qSVdpc2NOUjBGWUh5STBrM0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQRkVXSUFZWnYwTXRYTG5GZUtmN0pZLWx2anJoNTM1VERGZUVha1JZc01kMWxHek92SEVEbkgzeDgyZWh0RXY3VFhuYVJKcTlNeklhQlJvUVB1WXNnMVZ5WUFmY2pxYzNqblZRYkRBemxhdzktaWhwLVNBZFNqOE9RVGlsRm4zazVuVExuUGZtQ19JM2xFRHFldFdxbmN1Sjg?oc=5</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2164,12 +2176,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2184,12 +2196,12 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>UAE extends small business tax relief until 2029 - Yahoo Finance</t>
+          <t>Ministerial Decision No. 197 of 2026 - Crowe</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -2199,7 +2211,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNM2FhblZZVW5LVzI2bmRYWFhadXJ5bGU2OU54U3UzTmpGWmlweXlYTVVSWHpXaXU5YnJLNlh0STNsNmhYdG9feTdsN2xKNWlNSGZRM3loRllITXB4U0ljUkpyYllpLU9jQUZVOVdab1Rocml1OWxsa1lKWE00Wk42QWZRejVCaTk4QllWdTJTMWxJd2RKbVZiWHo4UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOMFZaS3RKdnpEdVpQcUtlN1JJWlBuZmxxRkpnZHB4WXFpUGg1cHpjcHdKUzJlM0VTVExnRExWRkowZm5iek1yUHpaY3ZWamZfS3ZpM0tkSW9MTjV0YmxHOFhpeDltbkxENmZLamJkV1ZKMklZUjAySU1aZGVZSnRMamIxejJBdw?oc=5</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2209,17 +2221,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2229,12 +2241,12 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>UAE seizes 8.45m non-compliant tobacco and drink products in six-month tax drive - Gulf News</t>
+          <t>Amendments to the UAE electronic invoicing system decision - Simmons &amp; Simmons</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -2244,7 +2256,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOeXEwYUYyRVl3dzRiREtKU01zOTFJNXZCNVpNcE5wYTUxRUN3U1A0SkxudUUxYkI0WHUzUmZoelZBLUJSaUFFcno2WFc5bzNBR2FQZU4zSkFuMTNWbkcyMVNMdXc3dmplcVNLdDRsN2xDdng3ZFg2UnFiREgzZHIwUFlpUkhxdXdkeG0ySXJQS2Q2LWJJRGxrbWZMT3AxTU9KWWM1OS1qQ2FET0oyQjhhZFNXX3RDWklhU3VrdTM2aTRRcFIxdXlWOHJB0gHcAUFVX3lxTFA5OFBJbzlhcVVXbXNwNWtBamtpbFdwbVkxdHFtSTJXWk9TR3kxZ0F6UFVtQy1EYnpaZUM2Vmp1enVjeFJoSjR1ekpMenVHdEhaTlhGdmxKUzQwV1BsQnpiNXg0UDRpTndaTjE2RTJBNzFIbzNEZExXWlhmVnpYT2VTbmFsNldOZVlzX3BsaU5xUUplai13SEl2RUdpNG0tWTJOd1BCQkVaUVowX0NiZHF3VU1BLU5VcVpBb2RoRXVERGdaYmxhMmhEd3MxNVRoekNKQ3hZeEhyWkUwQUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOUzJMUUdnR2Z0TjQ2eEMteTVMNHpOZndFbEh3T1hJaVQ5Z29HdXRlS3lTcXdRbkFFMnVRdFI5a0QzMzlQM2EzZnBDY1VDLXJUeFI5T1VtQnJ5UEFHTmU1bVA0bWJiMTZwTmhFR21sZzE0WEZReGRwMWRDalVDbm9kVWpVM0VfTmJHeThySXRwYjY0UzZXS1NhT0J2T0tGLVczYjk3Mno2TDZPeU5BbGM3VGR6SDJYR0wydkkxNUtYSzM1a19ocnhlNWQ3VS0?oc=5</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2254,42 +2266,38 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>official</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>UAE Extends Small Business Relief for Corporate Tax Purposes Until 2029 - entARABI</t>
+          <t>Ministry of Finance Amends Electronic Invoicing Regulations to Ease the Burden on Businesses</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>Ministry of Finance — News</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>news.google.com</t>
+          <t>mof.gov.ae</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOV0NzYjBEMHBFM0dLeTRxdURMWjYtZUZ2OXpSTENyYVozcGpPWkVBb09JaU1pQjAtWEVTdlcyQ1VjbmNGc2NiT05jWFUxMTNFVzFJMHlHQlY3VmxDaU9XUVZwY21yS1ZFYldWckFZallwVDU3Y1ZzLVNKbndvMXVGckJFMnRWNUtNOTFzRlgzUDhMbHFpMEZsRk9XejN4S3F4cld0aTJPdw?oc=5</t>
+          <t>https://mof.gov.ae/en/news/ministry-of-finance-amends-electronic-invoicing-regulations-to-ease-the-burden-on-businesses/</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2299,42 +2307,38 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Transfer Pricing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>official</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Tax Insights: Canada introduces a simplified transfer pricing documentation regime - PwC</t>
+          <t>UAE Breaks into Global Top 10 in IMD’s 2026 Government Support Index</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>News — Big 4 UAE Tax Commentary</t>
+          <t>Ministry of Finance — News</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>news.google.com</t>
+          <t>mof.gov.ae</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOVm8yXzZQUVY4R2djbXBUdHQ0aFUyQnFaSHNxSkFCbTNxNmxSVTZVUHRxa1lvVnF2Nlk2bmhTQ2w4ejJaTVR2NUY4S3VsajBFTEV2dkRwbk9BbEh1MWtwczNVNHgtQm1yaFJwc2NlZldqM053NGhwbE1TLWR3eDNIQ3V2ZzhTQ2JmbVJlNlliMkRoalBfYzQ3WHdVaXR2R2MzNEw1dGRQNzFfRWxTWklzYkJNYVZKVjFMclFQQjIzMUU?oc=5</t>
+          <t>https://mof.gov.ae/en/news/uae-breaks-into-global-top-10-in-imds-2026-government-support-index/</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2344,42 +2348,38 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>IFRS / Reporting</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>official</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Canada launches public consultations on steel imports and imposes surtax on wood cabinets and vanities - EY</t>
+          <t>Ministry of Finance convenes Financial Data Forum 2026 to boost efficiency in final account and financial statement preparation and reinforce the application of international accounting standards</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>News — Big 4 UAE Tax Commentary</t>
+          <t>Ministry of Finance — News</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>news.google.com</t>
+          <t>mof.gov.ae</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNMy1qdEVRaXhDVUZ4c3FTNUlCS0F0SEhoRnQtRk5BTnB1d2VFSmZSUk95RmRSdEw4LUFBV1FwYTIwbTVLZHdqOEdkcDhRb29fWDc1cGN0ZFA3a0habW9iY0NWam9LZmtfa3c2NDlLZ3N1MVJYWWRwejlhM1ViSndzZg?oc=5</t>
+          <t>https://mof.gov.ae/en/news/ministry-of-finance-convenes-financial-data-forum-2026-to-boost-efficiency-in-final-account-and-financial-statement-preparation-and-reinforce-the-application-of-international-accounting-standards/</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2389,17 +2389,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>UAE extends Small Business Relief for corporate tax - Absolute Geeks</t>
+          <t>Foreign outflows in July were the lowest in the GCC - EnterpriseAM</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>News — FTA Announcements</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPWU10OExoZmlXRjdCamp5VHROMnNDb1dKN1I3NE85dTI4aU84VjVvczlyanRyWEw4OVBuOWpVa1NJZm9qQ2hSZl9YYlhxOGNEYXBCeDlGQVF1RUV1TWJlSGVmdnpHRktyS2ktV2IwQ0s3T3hZMzV4Ni03aGdvVTNHZFhEYThmRE5uclJqR1BKUF90MXktS2xEaXctR0RsLXphM0g0REdvWHY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE8tRko4Unh0QWI1ekpUTHJ3QmktT1dyWXd2S2REcHZIZVVvd2Rtdm1WSkUtQUtacjlnSGlLdWtIMk0tVVNxU1ZKTU1qSVdpc2NOUjBGWUh5STBrM0E?oc=5</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2434,12 +2434,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Spotify forecasts slower growth despite AI investment - Gulf Business</t>
+          <t>UAE extends small business tax relief until 2029 - Yahoo Finance</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>News — FTA Announcements</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNQUhDU0xPaGxHNTZZdDNmRFRsTndvQThIUkRVV0hyTkpVbWhFNXdsZ2hjUXFrNzByWEc1ZUdITm1FYkM2N3k5MW5paDBud1RfNGF4MXNIdlluaVktTVRfd0RlZzJpUmc0UlZ2WUlKU1VDTUdELXpoelU0Z2kteENFZjVfcWx5YmhLc21jS3J5VXVkeEZ3UXRV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNM2FhblZZVW5LVzI2bmRYWFhadXJ5bGU2OU54U3UzTmpGWmlweXlYTVVSWHpXaXU5YnJLNlh0STNsNmhYdG9feTdsN2xKNWlNSGZRM3loRllITXB4U0ljUkpyYllpLU9jQUZVOVdab1Rocml1OWxsa1lKWE00Wk42QWZRejVCaTk4QllWdTJTMWxJd2RKbVZiWHo4UQ?oc=5</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2479,17 +2479,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>UAE Sets Minimum Excise Price for E-Liquids - Vaping360</t>
+          <t>UAE seizes 8.45m non-compliant tobacco and drink products in six-month tax drive - Gulf News</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>News — FTA Announcements</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE9HS2ZoOFFrdlRtX3N4ZXM5UlpzLTFKc21Pdi1CVkhNYW1PNGozMDBVYVZ0VjlrUDNCMFRQRG1hOGpPNllSd0dpX0dhNm02a3drdmZneHpQOUhtUkxXWlFBcDlETkt0dF9xalFRMldrVWZMSXh5NHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOeXEwYUYyRVl3dzRiREtKU01zOTFJNXZCNVpNcE5wYTUxRUN3U1A0SkxudUUxYkI0WHUzUmZoelZBLUJSaUFFcno2WFc5bzNBR2FQZU4zSkFuMTNWbkcyMVNMdXc3dmplcVNLdDRsN2xDdng3ZFg2UnFiREgzZHIwUFlpUkhxdXdkeG0ySXJQS2Q2LWJJRGxrbWZMT3AxTU9KWWM1OS1qQ2FET0oyQjhhZFNXX3RDWklhU3VrdTM2aTRRcFIxdXlWOHJB0gHcAUFVX3lxTFA5OFBJbzlhcVVXbXNwNWtBamtpbFdwbVkxdHFtSTJXWk9TR3kxZ0F6UFVtQy1EYnpaZUM2Vmp1enVjeFJoSjR1ekpMenVHdEhaTlhGdmxKUzQwV1BsQnpiNXg0UDRpTndaTjE2RTJBNzFIbzNEZExXWlhmVnpYT2VTbmFsNldOZVlzX3BsaU5xUUplai13SEl2RUdpNG0tWTJOd1BCQkVaUVowX0NiZHF3VU1BLU5VcVpBb2RoRXVERGdaYmxhMmhEd3MxNVRoekNKQ3hZeEhyWkUwQUg?oc=5</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2524,17 +2524,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2544,12 +2544,12 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>E-Invoicing Readiness Checklist: How UAE Businesses Can Prepare Before the Deadline - NewsBreak: Local News &amp; Alerts</t>
+          <t>UAE Extends Small Business Relief for Corporate Tax Purposes Until 2029 - entARABI</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPQmFubHpKbnIzS2N1cVJkbFA5bDRWcUhzQ0lYazZ3Z0ZBazZKQzVoTjRxZXBrMFNNSGNXTGp4ZG1EZ0xTTGFwanZQZkxvbjA5UFQxYkNBLWF6bEtDSlB5UlcyNU9fc2E1VTRNMWtTYnRyOFRlTUxjRlVlcEVwRVdDb05OQlo4VC1GcUpqUkpmVzhsUmc0RGJrZlJWN0tCMXVQc0d5dTEtT055TFRDT3c5R2pUN1hpaEF3R21TOHo2d1pNZldNcUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOV0NzYjBEMHBFM0dLeTRxdURMWjYtZUZ2OXpSTENyYVozcGpPWkVBb09JaU1pQjAtWEVTdlcyQ1VjbmNGc2NiT05jWFUxMTNFVzFJMHlHQlY3VmxDaU9XUVZwY21yS1ZFYldWckFZallwVDU3Y1ZzLVNKbndvMXVGckJFMnRWNUtNOTFzRlgzUDhMbHFpMEZsRk9XejN4S3F4cld0aTJPdw?oc=5</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -2574,27 +2574,27 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Transfer Pricing</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>A jumpy July - EnterpriseAM</t>
+          <t>Tax Insights: Canada introduces a simplified transfer pricing documentation regime - PwC</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — Big 4 UAE Tax Commentary</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBCcFdtSjE1bW5pMlREMHVqWTYwcW1xajViLWZvTmU1MUk0MUZiX2pPay12Nm5RS0tzdmJjYU9VY2hjUi10enNsYk1qcEZqc3FQc3dEZE1CaTJRYTJvVWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOVm8yXzZQUVY4R2djbXBUdHQ0aFUyQnFaSHNxSkFCbTNxNmxSVTZVUHRxa1lvVnF2Nlk2bmhTQ2w4ejJaTVR2NUY4S3VsajBFTEV2dkRwbk9BbEh1MWtwczNVNHgtQm1yaFJwc2NlZldqM053NGhwbE1TLWR3eDNIQ3V2ZzhTQ2JmbVJlNlliMkRoalBfYzQ3WHdVaXR2R2MzNEw1dGRQNzFfRWxTWklzYkJNYVZKVjFMclFQQjIzMUU?oc=5</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -2629,17 +2629,17 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Another Hormuz workaround - EnterpriseAM</t>
+          <t>Canada launches public consultations on steel imports and imposes surtax on wood cabinets and vanities - EY</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — Big 4 UAE Tax Commentary</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5iUjRXRTlrdVBXOHUyRWlYc2ttOXdYaVktOE5ZU1YxMnRLcnlHeWRPdl9CQmRkR3Bqc21aeFlWMmdFcGdjanc3d2RNTnRGcWdKVGdxQTZmeC02clJoSXJJaGJlUUM5TW5pQjRORkVpRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNMy1qdEVRaXhDVUZ4c3FTNUlCS0F0SEhoRnQtRk5BTnB1d2VFSmZSUk95RmRSdEw4LUFBV1FwYTIwbTVLZHdqOEdkcDhRb29fWDc1cGN0ZFA3a0habW9iY0NWam9LZmtfa3c2NDlLZ3N1MVJYWWRwejlhM1ViSndzZg?oc=5</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -2664,12 +2664,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>UAE e-invoicing: How digital invoices will transform business - Khaleej Times</t>
+          <t>UAE extends Small Business Relief for corporate tax - Absolute Geeks</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — FTA Announcements</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQMjFwZTd6MkpqcXZKaEwxZV9fUlZWSEtSeVdIQXN6YXFPMURFMWZhOHc0NWFuWlRfd1ZNX2doQVBpbXBqRFBTOVNNcjVTYVpOcEozYmtoaWxDUHVoUFFNT1RBWEI3RzJybmFWejFNcEcxYXpybDBiUzRLUk85ajBkOHIydnBjOUV6NEVJUjZkQTNOQ0Fud1BjdGtUNVpwTmlTazdyNWZmaXRwTkthY1Nac1RPWU90T3lMemJJNHp5VdIBvwFBVV95cUxQMjFwZTd6MkpqcXZKaEwxZV9fUlZWSEtSeVdIQXN6YXFPMURFMWZhOHc0NWFuWlRfd1ZNX2doQVBpbXBqRFBTOVNNcjVTYVpOcEozYmtoaWxDUHVoUFFNT1RBWEI3RzJybmFWejFNcEcxYXpybDBiUzRLUk85ajBkOHIydnBjOUV6NEVJUjZkQTNOQ0Fud1BjdGtUNVpwTmlTazdyNWZmaXRwTkthY1Nac1RPWU90T3lMemJJNHp5VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPWU10OExoZmlXRjdCamp5VHROMnNDb1dKN1I3NE85dTI4aU84VjVvczlyanRyWEw4OVBuOWpVa1NJZm9qQ2hSZl9YYlhxOGNEYXBCeDlGQVF1RUV1TWJlSGVmdnpHRktyS2ktV2IwQ0s3T3hZMzV4Ni03aGdvVTNHZFhEYThmRE5uclJqR1BKUF90MXktS2xEaXctR0RsLXphM0g0REdvWHY?oc=5</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2724,12 +2724,12 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>More investments in Adnoc’s fleet, Indian IPOs, and Egypt’s North Coast - EnterpriseAM</t>
+          <t>Spotify forecasts slower growth despite AI investment - Gulf Business</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — FTA Announcements</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1RdV9pa3ZIMmpRWnFlcXRaeTRnSy1zZUp0enVScm1nc0hMX3UwTEdEOG9oQy00UUJiSUR4WENleElGQVVmLXh3ZE10b09nQWphT0IzNHNJb0h3Q0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNQUhDU0xPaGxHNTZZdDNmRFRsTndvQThIUkRVV0hyTkpVbWhFNXdsZ2hjUXFrNzByWEc1ZUdITm1FYkM2N3k5MW5paDBud1RfNGF4MXNIdlluaVktTVRfd0RlZzJpUmc0UlZ2WUlKU1VDTUdELXpoelU0Z2kteENFZjVfcWx5YmhLc21jS3J5VXVkeEZ3UXRV?oc=5</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2769,12 +2769,12 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>FTA Directive No. 5 of 2026 - Crowe</t>
+          <t>UAE Sets Minimum Excise Price for E-Liquids - Vaping360</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — FTA Announcements</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE40S0RnRzF2d1dBSmNHdkNNQXZQQmlOYWNOSk5OWnlVNUN3ZDB5UHBUV29RXzNvaF9pVFNQZ2FwTUdocGhxMXp1T3gxMUFycGNESFA1bXNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE9HS2ZoOFFrdlRtX3N4ZXM5UlpzLTFKc21Pdi1CVkhNYW1PNGozMDBVYVZ0VjlrUDNCMFRQRG1hOGpPNllSd0dpX0dhNm02a3drdmZneHpQOUhtUkxXWlFBcDlETkt0dF9xalFRMldrVWZMSXh5NHc?oc=5</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -2799,12 +2799,12 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Digital currency and VAT: New UAE rules for businesses to consider - thenationalnews.com</t>
+          <t>E-Invoicing Readiness Checklist: How UAE Businesses Can Prepare Before the Deadline - NewsBreak: Local News &amp; Alerts</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQamI1MElzOEtNS1ZjVWR3VGpjZjNUZjBXbjQwZkJIZ3AwOFVqckl0WWFQN2JpaEg5XzRTUTBVMDFOeVhMaUZxYW9GUnBFNW55WnhKd2ZKOVZoekRBWUNqQkp3dGFPZ2JQcWY5SjVlRUJuTURfcVN5aUNXVmthdUh4cHlJbFNHN3lyT1VTU2l2Nk92U09JZFh3eXp0c29jTlJNZW1VLTZBR2h5WmdBTjFuNGczZkZwdDY1QWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPQmFubHpKbnIzS2N1cVJkbFA5bDRWcUhzQ0lYazZ3Z0ZBazZKQzVoTjRxZXBrMFNNSGNXTGp4ZG1EZ0xTTGFwanZQZkxvbjA5UFQxYkNBLWF6bEtDSlB5UlcyNU9fc2E1VTRNMWtTYnRyOFRlTUxjRlVlcEVwRVdDb05OQlo4VC1GcUpqUkpmVzhsUmc0RGJrZlJWN0tCMXVQc0d5dTEtT055TFRDT3c5R2pUN1hpaEF3R21TOHo2d1pNZldNcUE?oc=5</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Air India turbulence injures passengers on Phuket-Delhi flight - Gulf Business</t>
+          <t>A jumpy July - EnterpriseAM</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOUk92b3hCQVZybGNndXNJOF9ZX0Z3TGl5NnRuXzE5NlBRb3czZXM2SkxXb3ZQSGNOdGo2a2U2b040ZVFDcFBqbzdvaFFZaVdBbFgwQkJOOEhDNzF6VXY1OU9Ca2t2Z1ZnQlhscXNXTVhDaWY3b2lvMUlEWFhkXzVxaDR3b191OUx2aTVKcEttYkFGTjRzRVpnbFJvLUZhYmNLTFJJNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBCcFdtSjE1bW5pMlREMHVqWTYwcW1xajViLWZvTmU1MUk0MUZiX2pPay12Nm5RS0tzdmJjYU9VY2hjUi10enNsYk1qcEZqc3FQc3dEZE1CaTJRYTJvVWc?oc=5</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>UAE Business: UAE extends small business relief for corporate tax until December 2029 - Gulf Daily News</t>
+          <t>Another Hormuz workaround - EnterpriseAM</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNVm43RXV5MWlfOTE5TjdqQjhtd3pzUnRIdmJycExNbXV6REpoRjQ5MlNiRENNemM5SG5VbUhJbnVXenhQXzFhRGgtNXE3QjRWWHhCcTJsZ0lfUW5ZTWNWcjdZQnZSSDM0VVdvVDY0ejBPMklPTUkzdTdXX090b1RQY21nbmdUQUtuZG42RHBxRWdCb05xNkdBT2xUVk1SNWN0cG1NbnhKNlBxSl96T3BzOU91cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5iUjRXRTlrdVBXOHUyRWlYc2ttOXdYaVktOE5ZU1YxMnRLcnlHeWRPdl9CQmRkR3Bqc21aeFlWMmdFcGdjanc3d2RNTnRGcWdKVGdxQTZmeC02clJoSXJJaGJlUUM5TW5pQjRORkVpRQ?oc=5</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -2934,12 +2934,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2949,12 +2949,12 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>UAE extends corporate tax relief for small businesses until 2029 - Khaleej Times</t>
+          <t>UAE e-invoicing: How digital invoices will transform business - Khaleej Times</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNMDNwUlhpclFxaFJkdkkzR0s5MVh4WHZOUDdfZzZtNTBFb2RIcklxMF91Tkp2NGRxRlZMM3BubEZGc0g5LXpsQUhHQy01eGcxTllzc1k1S1NqeFMtYXM4YlBmREttNlhsS0hmd2JXN0l2UjFEQ3B5M1pfRTVpOGw0Z1pPMTNHd0tHQ25ZNjNGZmVaZnhzZUJueE9sQ2dNNGVaUDVjTdIBrAFBVV95cUxNbWJjeHFtRU9DbExyNHRRY1NEUXB2WnZRZ1V2TlFhQ010T3RhSmptR2ItaDhxVnEta0NITUJyS3ppaGgyQ2FkclQwRFhCaWNnLUhNb21YaDVGLWZZNThic2hpN0MzNTI4cXI3RjYtLVUzN3VHanJUUHdYaEFRWUlvS2w5UVdja3pwd1Q4c2pXWHVPZ0xZVmFCcE43eWl1bG10N0s4UXdpVUhpU0tH?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQMjFwZTd6MkpqcXZKaEwxZV9fUlZWSEtSeVdIQXN6YXFPMURFMWZhOHc0NWFuWlRfd1ZNX2doQVBpbXBqRFBTOVNNcjVTYVpOcEozYmtoaWxDUHVoUFFNT1RBWEI3RzJybmFWejFNcEcxYXpybDBiUzRLUk85ajBkOHIydnBjOUV6NEVJUjZkQTNOQ0Fud1BjdGtUNVpwTmlTazdyNWZmaXRwTkthY1Nac1RPWU90T3lMemJJNHp5VdIBvwFBVV95cUxQMjFwZTd6MkpqcXZKaEwxZV9fUlZWSEtSeVdIQXN6YXFPMURFMWZhOHc0NWFuWlRfd1ZNX2doQVBpbXBqRFBTOVNNcjVTYVpOcEozYmtoaWxDUHVoUFFNT1RBWEI3RzJybmFWejFNcEcxYXpybDBiUzRLUk85ajBkOHIydnBjOUV6NEVJUjZkQTNOQ0Fud1BjdGtUNVpwTmlTazdyNWZmaXRwTkthY1Nac1RPWU90T3lMemJJNHp5VQ?oc=5</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -2979,12 +2979,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>UAE extends corporate tax relief for small businesses until 2029 - thenationalnews.com</t>
+          <t>More investments in Adnoc’s fleet, Indian IPOs, and Egypt’s North Coast - EnterpriseAM</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQOFMwcEtFYkFkbWxMRnBqX3Y1M2ZOcnJ4Q1FzTHg2b1NDYnU3dzVWMmMycVdhNzJSbTZhaTZ1bjRpN3RYcm9Gb3VIOUxydjN6anFTMU12SHNNcmt1YkhwSk1RVTV6Yk1yS0wtNm9PbVZLNkxmTVRNd3hEOW1xbXdnTlBiX0VJWWhINEw5MHc1eEk4UHhFZHFOZ04zcnZERDZhLXZJQ0VGWS15N080ZXBQYVhDMFU2al9wN1NlNXN2RnFaZEU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1RdV9pa3ZIMmpRWnFlcXRaeTRnSy1zZUp0enVScm1nc0hMX3UwTEdEOG9oQy00UUJiSUR4WENleElGQVVmLXh3ZE10b09nQWphT0IzNHNJb0h3Q0E?oc=5</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -3019,17 +3019,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>September 1 change: UAE announces new excise price rule for electronic smoking products - Gulf Business</t>
+          <t>FTA Directive No. 5 of 2026 - Crowe</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>News — FTA Announcements</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNMXNESjR5VDVIQ0Qwb0xKUk1xRlhaTmV2RjNfdVpGaDZZYk0wcjdSbC1RRHBUNkRRaGpNOS1mSjR1blVVRHJ6MzdLeUZXM1lMWURyX21CS25DZFN3engwRWZCOFFLUDJydEEwX0pSa1lLSlNqbVlhdk9pNmtvLUh1QzFubU9RVENUNEl3QVdLc2FkRUV6TGFjZmJwLUtiUVd5dlhjVW1SLU43WFI4eGNfZkJCTXBNaEQySVR3QjZuazA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE40S0RnRzF2d1dBSmNHdkNNQXZQQmlOYWNOSk5OWnlVNUN3ZDB5UHBUV29RXzNvaF9pVFNQZ2FwTUdocGhxMXp1T3gxMUFycGNESFA1bXNR?oc=5</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -3064,17 +3064,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>UAE small businesses claiming tax relief must still file corporate tax returns - Emirates 24|7</t>
+          <t>Digital currency and VAT: New UAE rules for businesses to consider - thenationalnews.com</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>News — FTA Announcements</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOLXJ6YVV3T2dXazExeU04V09UYlk3NmtYT2d3Z2t1X2RPckN0RjVQZE9oNTljdi1rUUlzTDlMalotZ1JWRS03TWVFWlVVS1hyMVlDUEsxYWQ3RWgtdTdUNzVaZjE5WlhVVUhJcjkyaDFVa28yeEN2ejAtVG43dnduV2NDa0k4czRLby1sU2w2ZHZTcGtPZmpiTjRYWXB2VUExMnhreUktUDBZSkZ4LUxZYW9TYXRJc2s0U1QyMtIB1wFBVV95cUxPNWVmQzRQOEJkZnBCZVFDblE2dkFlX1hGNWlnalJBVk5QREJoU0ZvMXZIM1JJYXdLb2lQZFNnejliekY3Y29nN0tLdTUxQ0h0SUFaSVlpOWhuX3dVaHdjX3NPM1pkd2xlVDRMT1VmTHJ4QV9PbmpWRmVHRFpHZ1lyUF9ZWEJTcFJ2LS1QX0hEa0Y3dnJ4S054S211cWRMWWlHVVd2V19wQnhGa2JVR1ZxSFVNVWJMejdESlFZSkxUMGYwQUlyQkpueDlwb2dJYnlqQnZGNklscw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQamI1MElzOEtNS1ZjVWR3VGpjZjNUZjBXbjQwZkJIZ3AwOFVqckl0WWFQN2JpaEg5XzRTUTBVMDFOeVhMaUZxYW9GUnBFNW55WnhKd2ZKOVZoekRBWUNqQkp3dGFPZ2JQcWY5SjVlRUJuTURfcVN5aUNXVmthdUh4cHlJbFNHN3lyT1VTU2l2Nk92U09JZFh3eXp0c29jTlJNZW1VLTZBR2h5WmdBTjFuNGczZkZwdDY1QWc?oc=5</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
@@ -3109,17 +3109,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3129,12 +3129,12 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>UAE releases registration requirements for domestic minimum top-up tax - kpmg.com</t>
+          <t>Air India turbulence injures passengers on Phuket-Delhi flight - Gulf Business</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>News — FTA Announcements</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPaGJWUy1MU0VZdmd3LTVPTmw0bDYtWlF5a3JCVkFwVnhJRUkxVkdEWUE4X1VZLXg0Tkg4YTlLWHhoOUJYVzJqR3lzUE5Pa1RpSWtjdkRDQ09UeDBoQ3Y2bGlLbkhzTXZ2WlNJeGFSLXNqRUZyRnBfNV9Mbk5UY25hdVZ6VWM2cWRYOEt4bUlnWV9QYkQtOWZudGJaV0ZJZDRVY2JGbTY1T1JTYVhyTGhEdlVuQzlzZkN6ZC1VRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOUk92b3hCQVZybGNndXNJOF9ZX0Z3TGl5NnRuXzE5NlBRb3czZXM2SkxXb3ZQSGNOdGo2a2U2b040ZVFDcFBqbzdvaFFZaVdBbFgwQkJOOEhDNzF6VXY1OU9Ca2t2Z1ZnQlhscXNXTVhDaWY3b2lvMUlEWFhkXzVxaDR3b191OUx2aTVKcEttYkFGTjRzRVpnbFJvLUZhYmNLTFJJNg?oc=5</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3154,17 +3154,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>UAE Digital Economy: Why Trust, Not Speed, Now Wins The Race - Menafn</t>
+          <t>UAE Business: UAE extends small business relief for corporate tax until December 2029 - Gulf Daily News</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNbi1OcWZwSTNNYjBRZkJWS1FodlVGTG5oZHB1T3Q2cGRqazRiZGQzeUtlOVB3VXlhNUM1TnhSdW1MVS1uSng1dGFmTlAzb3ZMNXlod0c5bWo2RkdOTW1idm9JQ3dQNTM5Z3FvZl96WlNuVVh4Mmx5NGFNWXBHVFZoWnUyQU9WT01idllWclJqTXE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNVm43RXV5MWlfOTE5TjdqQjhtd3pzUnRIdmJycExNbXV6REpoRjQ5MlNiRENNemM5SG5VbUhJbnVXenhQXzFhRGgtNXE3QjRWWHhCcTJsZ0lfUW5ZTWNWcjdZQnZSSDM0VVdvVDY0ejBPMklPTUkzdTdXX090b1RQY21nbmdUQUtuZG42RHBxRWdCb05xNkdBT2xUVk1SNWN0cG1NbnhKNlBxSl96T3BzOU91cw?oc=5</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
@@ -3199,7 +3199,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Finance sets e-cigarette liquid excise price - Sharjah24</t>
+          <t>UAE extends corporate tax relief for small businesses until 2029 - Khaleej Times</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBGY1BCNkVheXBxM3RBdWlPNXVULWVaaWdWM3RWWU9JSWI2T3JVMGlMdl94Ync5ekFqdGU1SzAxeEMwaUhJR1hTejhVTFo4blI2Y1d5QzZUaVgwUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNMDNwUlhpclFxaFJkdkkzR0s5MVh4WHZOUDdfZzZtNTBFb2RIcklxMF91Tkp2NGRxRlZMM3BubEZGc0g5LXpsQUhHQy01eGcxTllzc1k1S1NqeFMtYXM4YlBmREttNlhsS0hmd2JXN0l2UjFEQ3B5M1pfRTVpOGw0Z1pPMTNHd0tHQ25ZNjNGZmVaZnhzZUJueE9sQ2dNNGVaUDVjTdIBrAFBVV95cUxNbWJjeHFtRU9DbExyNHRRY1NEUXB2WnZRZ1V2TlFhQ010T3RhSmptR2ItaDhxVnEta0NITUJyS3ppaGgyQ2FkclQwRFhCaWNnLUhNb21YaDVGLWZZNThic2hpN0MzNTI4cXI3RjYtLVUzN3VHanJUUHdYaEFRWUlvS2w5UVdja3pwd1Q4c2pXWHVPZ0xZVmFCcE43eWl1bG10N0s4UXdpVUhpU0tH?oc=5</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -3244,17 +3244,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>CBUAE injects more liquidity into the banking system - EnterpriseAM</t>
+          <t>UAE extends corporate tax relief for small businesses until 2029 - thenationalnews.com</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPRVF2amFoSUlsRENGenUxcUlxRU9NeU9QWlJhUkExb1k0cExublF1YUdrM2dJc0FySm9zQmgyQUtKU092bkpYT1I1bUhaMkxGR2o2SFVnckhIR2d4RGQzOUJnb19tZERINThyZ0NrQ1A0WUttandLcmN0QUlUaTFVZ1djMnUxdEp4SmNGMjM1Zl9HX1k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQOFMwcEtFYkFkbWxMRnBqX3Y1M2ZOcnJ4Q1FzTHg2b1NDYnU3dzVWMmMycVdhNzJSbTZhaTZ1bjRpN3RYcm9Gb3VIOUxydjN6anFTMU12SHNNcmt1YkhwSk1RVTV6Yk1yS0wtNm9PbVZLNkxmTVRNd3hEOW1xbXdnTlBiX0VJWWhINEw5MHc1eEk4UHhFZHFOZ04zcnZERDZhLXZJQ0VGWS15N080ZXBQYVhDMFU2al9wN1NlNXN2RnFaZEU?oc=5</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>The Taxation Society partners with Tally Solutions to strengthen UAE's finance and tax professional community - khaleejtimes.com</t>
+          <t>September 1 change: UAE announces new excise price rule for electronic smoking products - Gulf Business</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — FTA Announcements</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNMXRpRGhpQXJvUkZhQU1IcTF6Z0JtLW16cTQ1d24zZWlwQTlPMHNCeG8tY0NLc1JGcXdjT2g5V01YM3hOVmtZYzBJeThiR3hhSDRpdGdwaDhsVC1WMDFTSWN0SWdhc3hiWTRSQmV0blZEZkowYWdoSU1BaUJ6Y01ZZ2ZrWlNRc2JtUllnc0huTF92aWdmbEp4bTRvRV9fN2xTU2dmMjdLSk43ZlFlcEtuWTBKQXdFTU5pMlRnWE55VFBwcTc0STRtcFluS3Ffek1oM2NRQ1dYemVkTktESkJRSVJ30gHqAUFVX3lxTE85ZnVhMjFKMWdhenV1YlFiRGtpVTBIdjRvLVNLRFBjTHBPUnVfeG5sUGxIcWVlSlhUTEVibFV2UXdWbEg5TGNmS3hBYnczSEctV3BBT2pZT3dpcDJUeGczWE9xQ1dweV9hc1hwQnhHQkFWUDRrb0FzV0tVdmZhZ0pLZC14YlVJZjBYQmcwbUZWeG55dnhpOFliT0wxYkQ0bzl1VEhiVUpQNjQ4TVN0bFhPRERROXB5NUZZQ0VRS08tY0VmSDdLRFQzMHZ0dEZtamJ5dmp1OGZ6SmNxQjZrck8wRWs2U1A0TFJZdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNMXNESjR5VDVIQ0Qwb0xKUk1xRlhaTmV2RjNfdVpGaDZZYk0wcjdSbC1RRHBUNkRRaGpNOS1mSjR1blVVRHJ6MzdLeUZXM1lMWURyX21CS25DZFN3engwRWZCOFFLUDJydEEwX0pSa1lLSlNqbVlhdk9pNmtvLUh1QzFubU9RVENUNEl3QVdLc2FkRUV6TGFjZmJwLUtiUVd5dlhjVW1SLU43WFI4eGNfZkJCTXBNaEQySVR3QjZuazA?oc=5</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3354,12 +3354,12 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>MoF extends Small Business Relief for corporate tax until end-2029 - Sharjah24</t>
+          <t>UAE small businesses claiming tax relief must still file corporate tax returns - Emirates 24|7</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — FTA Announcements</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFA4N01YTUZ2UGRGVWdDQ3JDM3JLYWJDanVuckdCLVhuQUdqUFo3clA1cGRoTUtubWNpQ0dTOUFSQk5jYzdGcVFYNkNpQjF4ckFVZ2pBc0FXM1Ffa0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOLXJ6YVV3T2dXazExeU04V09UYlk3NmtYT2d3Z2t1X2RPckN0RjVQZE9oNTljdi1rUUlzTDlMalotZ1JWRS03TWVFWlVVS1hyMVlDUEsxYWQ3RWgtdTdUNzVaZjE5WlhVVUhJcjkyaDFVa28yeEN2ejAtVG43dnduV2NDa0k4czRLby1sU2w2ZHZTcGtPZmpiTjRYWXB2VUExMnhreUktUDBZSkZ4LUxZYW9TYXRJc2s0U1QyMtIB1wFBVV95cUxPNWVmQzRQOEJkZnBCZVFDblE2dkFlX1hGNWlnalJBVk5QREJoU0ZvMXZIM1JJYXdLb2lQZFNnejliekY3Y29nN0tLdTUxQ0h0SUFaSVlpOWhuX3dVaHdjX3NPM1pkd2xlVDRMT1VmTHJ4QV9PbmpWRmVHRFpHZ1lyUF9ZWEJTcFJ2LS1QX0hEa0Y3dnJ4S054S211cWRMWWlHVVd2V19wQnhGa2JVR1ZxSFVNVWJMejdESlFZSkxUMGYwQUlyQkpueDlwb2dJYnlqQnZGNklscw?oc=5</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
@@ -3384,12 +3384,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Northern Emirates’ property markets cool off + Sidara locks in USD 1.35 bn in firepower - EnterpriseAM</t>
+          <t>UAE releases registration requirements for domestic minimum top-up tax - kpmg.com</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — FTA Announcements</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOMDUxZXd1MElSNXdaNDByLW9jbHFIenJCY21PRnhPMUx4YkdyZ1FMREVxenNWZWZUY2p3MHQ5V2xUQmswZ1RuV1g3Q3RHUzdvOFhvOGpST2diQWIwOXFBeXdzc1lYRl9FRDIxdjBjUVR3Y2VEcUdIWXB0amg4YW5qbklORzFMS3J4VUZGelkybDVZcXc0VHlNck4zTXdjR1N1UzZmSk9vSFFoMDJMVENKMFVlWEdvUTEwZFhiZmdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPaGJWUy1MU0VZdmd3LTVPTmw0bDYtWlF5a3JCVkFwVnhJRUkxVkdEWUE4X1VZLXg0Tkg4YTlLWHhoOUJYVzJqR3lzUE5Pa1RpSWtjdkRDQ09UeDBoQ3Y2bGlLbkhzTXZ2WlNJeGFSLXNqRUZyRnBfNV9Mbk5UY25hdVZ6VWM2cWRYOEt4bUlnWV9QYkQtOWZudGJaV0ZJZDRVY2JGbTY1T1JTYVhyTGhEdlVuQzlzZkN6ZC1VRQ?oc=5</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -3429,12 +3429,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>ClearTax urges UAE businesses to prioritise execution assurance as e-invoicing decisions gather pace - Gulf News</t>
+          <t>UAE Digital Economy: Why Trust, Not Speed, Now Wins The Race - Menafn</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPTG13TFpCRmpaaWU3ZGxsVEtqakxUUXhSc0ltWUZfOEUyWTcxWGhOZ2doazNZY1V2LWFnSlp0NHpHTXN4emN6TzFWbGlXT09xU0Q3X25BTmpBVVl0Nl9XMFdRUE9HMy1BU3BMRDFIZ1RITkw4d3BSanluZGFHal9CM3h5dDNtTlBtUG9LYXZZWkhILVZhdUpKTHhUd2lMWmVOdVJrREx4UUF4WjNvTW5hSmtBVjVyQVBpblVKa1hKbjhxRTNUVmpUMVpXOFFJSWx1NUZWUWFMYlY2ZjA2Nml6OGV6X2ZGcVhkQkQ00gH-AUFVX3lxTE12b1Q4Qjd0Rks3U1hqOC1GVTZ5RXRUOXB6eVdVd3RMTEV5Q1pRYVRrc19GaG1qY3FXRGhqMkN3N3c2emJyeTFWbEU2QkRSMHR5aWFzNlctUi1mdi1vamRHMHZoWFZlQlRCbEhrT3BLSXlsTXRfYjY4QjVHblFRU0JnZVhlam4xNEF6d0hQVUtmTHFoYnktSW5LS3dqU2VleEh4azlObnoyUTNPd2E0RWc4U0ZhMkRoc1J1c2R6VGJhc1lSYTF0cjhzdnY0Q0tvYk81YnY5UE5CdnBXZTVNQXE4UlZwMkFjbUREaEtRNlF2MWJYVFhaOTFJNTZRUlJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNbi1OcWZwSTNNYjBRZkJWS1FodlVGTG5oZHB1T3Q2cGRqazRiZGQzeUtlOVB3VXlhNUM1TnhSdW1MVS1uSng1dGFmTlAzb3ZMNXlod0c5bWo2RkdOTW1idm9JQ3dQNTM5Z3FvZl96WlNuVVh4Mmx5NGFNWXBHVFZoWnUyQU9WT01idllWclJqTXE?oc=5</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>UAE extends small business tax relief until 2029 - theaccountant-online.com</t>
+          <t>Ministry of Finance sets e-cigarette liquid excise price - Sharjah24</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOMTA1XzlxbnpmYjNMcU01VXV1RjdMOHFuMi1CSVNMYXlaNW9kb2ZMSXZXOEZ1dDlqbmRLR2hXQjNrMDdlaU4teDVRTG1CMmJsY0lDU3V0SWxRZE4tWXZXbV9pR2o5THFMREVyZ3VpY1pTYVhFeUJza1MwOWtVYXB1ckwxQlBRdVF6eURUUHlkblhUNnNoQ3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBGY1BCNkVheXBxM3RBdWlPNXVULWVaaWdWM3RWWU9JSWI2T3JVMGlMdl94Ync5ekFqdGU1SzAxeEMwaUhJR1hTejhVTFo4blI2Y1d5QzZUaVgwUQ?oc=5</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
@@ -3519,12 +3519,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Sovos Announces 2026 Partner of the Year Award Winners, Recognizing Excellence in Strategic Collaboration and Innovation - Business Wire</t>
+          <t>CBUAE injects more liquidity into the banking system - EnterpriseAM</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxQRzJIdmQ3VjZqenlUTldPal9HNXdxdTJibTJHWFBhMVBMTWcxbm0yeUhJYzVLd0Z3Yl9pdE1LQzREWm13dXE4ZG1abDFuRkZIdHhIcm4zYXVoOXZIS01KNW5xRU04SUVwMlRnZlBxb3BYQkJMQ01CeXhabEI5U1VfSlpad0ROaVNnTUVnUll2WFhwMkxUa2tidGRxTDlMRm93SlAxVkNoWW84Zk1oeFFoNVdnOWRBZERIZzNSdnVDMGpHZ0MzSXlxZ1JXc2hodEY0aXNoRkNBRldSOGdxSkowdmFoTEplTjBtOUVfeWFtNmpzeDZtR3J2bVk4UWthWFR5VjJRbEM2NA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPRVF2amFoSUlsRENGenUxcUlxRU9NeU9QWlJhUkExb1k0cExublF1YUdrM2dJc0FySm9zQmgyQUtKU092bkpYT1I1bUhaMkxGR2o2SFVnckhIR2d4RGQzOUJnb19tZERINThyZ0NrQ1A0WUttandLcmN0QUlUaTFVZ1djMnUxdEp4SmNGMjM1Zl9HX1k?oc=5</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>UAE E Invoicing Guidelines Updated to Version 1.1 - Crowe</t>
+          <t>The Taxation Society partners with Tally Solutions to strengthen UAE's finance and tax professional community - khaleejtimes.com</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQOGUxa2xtLVY1ejE0azVCMEZSa3lxNHZmajhUdzh5LTQ5NGRqVk5oenBzNmJUSk44X1B0elZ5aDI5YVl4VHpLb2RzdEFRYW9IVmR5dHpOaE1JbWVoNzdvQVpsR0xIalA1MHBaR1NNOVpVSHUyX2t4R0dIVmZiWHlXWg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNMXRpRGhpQXJvUkZhQU1IcTF6Z0JtLW16cTQ1d24zZWlwQTlPMHNCeG8tY0NLc1JGcXdjT2g5V01YM3hOVmtZYzBJeThiR3hhSDRpdGdwaDhsVC1WMDFTSWN0SWdhc3hiWTRSQmV0blZEZkowYWdoSU1BaUJ6Y01ZZ2ZrWlNRc2JtUllnc0huTF92aWdmbEp4bTRvRV9fN2xTU2dmMjdLSk43ZlFlcEtuWTBKQXdFTU5pMlRnWE55VFBwcTc0STRtcFluS3Ffek1oM2NRQ1dYemVkTktESkJRSVJ30gHqAUFVX3lxTE85ZnVhMjFKMWdhenV1YlFiRGtpVTBIdjRvLVNLRFBjTHBPUnVfeG5sUGxIcWVlSlhUTEVibFV2UXdWbEg5TGNmS3hBYnczSEctV3BBT2pZT3dpcDJUeGczWE9xQ1dweV9hc1hwQnhHQkFWUDRrb0FzV0tVdmZhZ0pLZC14YlVJZjBYQmcwbUZWeG55dnhpOFliT0wxYkQ0bzl1VEhiVUpQNjQ4TVN0bFhPRERROXB5NUZZQ0VRS08tY0VmSDdLRFQzMHZ0dEZtamJ5dmp1OGZ6SmNxQjZrck8wRWs2U1A0TFJZdw?oc=5</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
@@ -3609,12 +3609,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>VAT, E-Invoicing</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Congo Republic e-invoicing launched - vatcalc.com</t>
+          <t>MoF extends Small Business Relief for corporate tax until end-2029 - Sharjah24</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOLTlBQUhqTDJya1ZpUmx5Y0lPRlRHb0VpWW5GYWVBc1JkTGRFbFl0b3N5UGJSdEdXRmwxdld1RlhqSWVremtIU1pWSHNXb2ROejA2TzJYcF9RX29TQVN1akJ5d0cxWFplcmJPYUJTRDgzU2FzenRzMzJldUsyaE9rbzlVUmJMSEc5M1pzSGtR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFA4N01YTUZ2UGRGVWdDQ3JDM3JLYWJDanVuckdCLVhuQUdqUFo3clA1cGRoTUtubWNpQ0dTOUFSQk5jYzdGcVFYNkNpQjF4ckFVZ2pBc0FXM1Ffa0k?oc=5</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -3669,12 +3669,12 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Corporate Governance in the UAE - Crowe</t>
+          <t>Northern Emirates’ property markets cool off + Sidara locks in USD 1.35 bn in firepower - EnterpriseAM</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Transfer Pricing</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE4weWRYb0VETFpvMjdhUG9BbU5Wb2JXbzNkLVpxSC1VZHhwYjMwT0F2OFNvQkJNQTFkOG1OamVFZWU0NWpVN3hHb0lldkJWLV9GeThwSjdzNlpnQXp0VDdQbkpnSWFFU3lacVJOeXl3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOMDUxZXd1MElSNXdaNDByLW9jbHFIenJCY21PRnhPMUx4YkdyZ1FMREVxenNWZWZUY2p3MHQ5V2xUQmswZ1RuV1g3Q3RHUzdvOFhvOGpST2diQWIwOXFBeXdzc1lYRl9FRDIxdjBjUVR3Y2VEcUdIWXB0amg4YW5qbklORzFMS3J4VUZGelkybDVZcXc0VHlNck4zTXdjR1N1UzZmSk9vSFFoMDJMVENKMFVlWEdvUTEwZFhiZmdn?oc=5</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Shopping online in the UAE? Tourists can now claim tax refunds on Noon orders - The Global Filipino Magazine</t>
+          <t>ClearTax urges UAE businesses to prioritise execution assurance as e-invoicing decisions gather pace - Gulf News</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNa1BKRVpJRVZCZm5VNVp2d3h4Rl92ejg0aml0Qy1pTUotYTZ4ZHlaeURMcnRacE9Zc0J2TWt4VktTQWdFV3BlNXBzWmlfMXFEZFRiYWRIMmV3X3ItaWc0T3pzOG52THI4c1RQaDY1RWdNbXItTTUtdlFTS1d6SUpZTVlXM2lOTWtLWXF6TGNSRE9OWkJQSUs3UXFoSEtOa2NpNEJLeTFOektldFVUVHk4cFJCSE5Qdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPTG13TFpCRmpaaWU3ZGxsVEtqakxUUXhSc0ltWUZfOEUyWTcxWGhOZ2doazNZY1V2LWFnSlp0NHpHTXN4emN6TzFWbGlXT09xU0Q3X25BTmpBVVl0Nl9XMFdRUE9HMy1BU3BMRDFIZ1RITkw4d3BSanluZGFHal9CM3h5dDNtTlBtUG9LYXZZWkhILVZhdUpKTHhUd2lMWmVOdVJrREx4UUF4WjNvTW5hSmtBVjVyQVBpblVKa1hKbjhxRTNUVmpUMVpXOFFJSWx1NUZWUWFMYlY2ZjA2Nml6OGV6X2ZGcVhkQkQ00gH-AUFVX3lxTE12b1Q4Qjd0Rks3U1hqOC1GVTZ5RXRUOXB6eVdVd3RMTEV5Q1pRYVRrc19GaG1qY3FXRGhqMkN3N3c2emJyeTFWbEU2QkRSMHR5aWFzNlctUi1mdi1vamRHMHZoWFZlQlRCbEhrT3BLSXlsTXRfYjY4QjVHblFRU0JnZVhlam4xNEF6d0hQVUtmTHFoYnktSW5LS3dqU2VleEh4azlObnoyUTNPd2E0RWc4U0ZhMkRoc1J1c2R6VGJhc1lSYTF0cjhzdnY0Q0tvYk81YnY5UE5CdnBXZTVNQXE4UlZwMkFjbUREaEtRNlF2MWJYVFhaOTFJNTZRUlJn?oc=5</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
@@ -3744,12 +3744,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Number of retail outlets connected to Digital Tourist VAT Refund System reaches more than 19,300 - Big News Network.com</t>
+          <t>UAE extends small business tax relief until 2029 - theaccountant-online.com</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNUjRVVzdLOXJQTXpUZDhqeWlQNDAwVDV2ZmJqd3h4cW5ZbXc0cHEzZGJBSWlLOTk0ZlFFbXlVSThCUEtxcGFqUHYzSlRmeXF0bC1XQ1J3VVhKUUkzeVBfNTc4cmQwNmlRYldwUU01YXpmc0pxT0daNWRpRUwtM0N3MlBBR09rRldZZlA5bXVJOXVTcVZSeE5ldWRHSWhna0ZfTTNwZWEwODlFTXRRYnRhOVJVcHJ3dDRuSnZtQlBhc0NMa2dhSzk4b1lBWEx5Uk5Ld2RMaFdmNUY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOMTA1XzlxbnpmYjNMcU01VXV1RjdMOHFuMi1CSVNMYXlaNW9kb2ZMSXZXOEZ1dDlqbmRLR2hXQjNrMDdlaU4teDVRTG1CMmJsY0lDU3V0SWxRZE4tWXZXbV9pR2o5THFMREVyZ3VpY1pTYVhFeUJza1MwOWtVYXB1ckwxQlBRdVF6eURUUHlkblhUNnNoQ3c?oc=5</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>UAE tourists can claim VAT refunds at 19,340 stores and on Noon purchases - Gulf News</t>
+          <t>Sovos Announces 2026 Partner of the Year Award Winners, Recognizing Excellence in Strategic Collaboration and Innovation - Business Wire</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQeDRPcDE4QjJaSFU3Qm1wRGVaWXl6cjY2c3YyVDF3TmtqN1RYMkh0WDdoSm56QmlXU21xSllRQWt4WHNFU09vUWZpTEd3dVVMb0UxNy0yZG1ucUF6aXhIZ2dWVXpkVjVqa2hHUGN3VHNZWEticFZMXzNfb2NzaVpwOFFkOVAtNDhBY0xjSUo3bkh0WUg2ZEJ4Q0JDU05Td0FTLWlUWXNfN2JKeGJsTEg3NGFDMzNwT21JZTFGT0V30gHQAUFVX3lxTE9wdElvSG52YzNWWUt6WGJaRkp0LXpmVHpQTFV4WHczVkQtOUhOMWpqRzd2UjgyQjNOSWdMT3QwM1luZzdtNWhXdU91R2lqS0FKcG1hUGExZ1QxWG1SSUo2cWZSWll0bjdpQ2pBOXFjTUMxcjJma0RraGlVbjNjajZRM0h4OVZfM0FUQXNERTQzQm1TS29QVjdiQzM2T19naktoTXhfQ1pvNmx4U2IxVkkxUWF5QmZ4QUxmMXB2bFVvR2RVWm10bjE2SlNaRzJ2VEU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxQRzJIdmQ3VjZqenlUTldPal9HNXdxdTJibTJHWFBhMVBMTWcxbm0yeUhJYzVLd0Z3Yl9pdE1LQzREWm13dXE4ZG1abDFuRkZIdHhIcm4zYXVoOXZIS01KNW5xRU04SUVwMlRnZlBxb3BYQkJMQ01CeXhabEI5U1VfSlpad0ROaVNnTUVnUll2WFhwMkxUa2tidGRxTDlMRm93SlAxVkNoWW84Zk1oeFFoNVdnOWRBZERIZzNSdnVDMGpHZ0MzSXlxZ1JXc2hodEY0aXNoRkNBRldSOGdxSkowdmFoTEplTjBtOUVfeWFtNmpzeDZtR3J2bVk4UWthWFR5VjJRbEM2NA?oc=5</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
@@ -3834,12 +3834,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>Retail outlets linked to UAE's Digital Tourist VAT Refund System exceed 19,300 - Emirates 24|7</t>
+          <t>UAE E Invoicing Guidelines Updated to Version 1.1 - Crowe</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOcXRBMGsxX1Q5SkJXcEFwWnV3c0VVc19jUnRkWU5yMVlPelltaEhvOWNLcEJxYi1KUExWMVlmZE1FOExZYklsRHU4N3lQZGppMDRnYUFaRU1OWHdwaVpiWWowOENidVJjbDFPeTQyQklzOGM5bXhQbDJrRFg2TkR6bUplTzJNZzl2M3dJT2FEeHVTTVNtTml6UEdoZUFDcVRCZWFHMGg1ejZoSWI1UWFCLV9zREotcmF3V0HSAdQBQVVfeXFMT3Q0RFN0V3FRSlNWV20tMm5hY1N5VHBVWmxzdnZGVXIwZU92VTZVRDVUVkRZM0Q1U1ZNZzFRcFlEWTc2ckk0UjZhcEN4YmZIZndTd284ZDQ3Z2Z4OS1mVGFUX2RwRzgyMWViTjEyQ19wdUxucXEtZWtFRm5tOWpId1VYYlRmd1Rkc2tlb3Q3THR0THZxZWt3Q1ZyTGVvZ2hUUzZPeTBPSzlER3FXR0ZvUnJiWk5vdlpwYlYxdmZjZnNTVEQxM3hSY1pyTGV5Qkk2d2lrejQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQOGUxa2xtLVY1ejE0azVCMEZSa3lxNHZmajhUdzh5LTQ5NGRqVk5oenBzNmJUSk44X1B0elZ5aDI5YVl4VHpLb2RzdEFRYW9IVmR5dHpOaE1JbWVoNzdvQVpsR0xIalA1MHBaR1NNOVpVSHUyX2t4R0dIVmZiWHlXWg?oc=5</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
@@ -3879,12 +3879,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>VAT, E-Invoicing</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Indians, Russians, Turks top list of tourists claiming the most VAT refunds in UAE - khaleejtimes.com</t>
+          <t>Congo Republic e-invoicing launched - vatcalc.com</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPek9sY1dJUkpRblhiYnJDdDExOW1yREdXd1oyZ1Yxb0FnZlBYNTd3SUxGWnVMenlZVGlqRlIxLUszNk1Jd3BpcF9rVE9XLVF1OWdhY01fd0gteTJFRkVJLVREMjl4ZVRGZHJacUxJREpRN3UxdHFncGhITEQ0MnUzTkhKY2FSZnBnaFUzZDEyRnZOdG1hOWVFX2FLNG9Ca1lGekQzcllxd0FqTUhvTTRZM3MxcElQV0JaMWfSAcIBQVVfeXFMT2FPTEx4WGUzNUNhZWdBa1MzVU5GN1p3SkRwM0o5TWlqenhqVTNhR1Z0bThyN0laMS1tOUhfaG1qMmZpQi1pT3lTNEhKT2l3SklKZ1E3MXkyYVBrMnUwOTh1Y2RxSkFISUdlT1B6Qm1tTV9CUV9YM0xwcTJ2NzVmWUcxaFJ2YzhYeVBjZG1WSG9vcVc2N2tqRzNreHFwWVpaaUdncndzVEVLaE8zeHczU0Jvdl9FazU2NE1CNWZqQmZmekE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOLTlBQUhqTDJya1ZpUmx5Y0lPRlRHb0VpWW5GYWVBc1JkTGRFbFl0b3N5UGJSdEdXRmwxdld1RlhqSWVremtIU1pWSHNXb2ROejA2TzJYcF9RX29TQVN1akJ5d0cxWFplcmJPYUJTRDgzU2FzenRzMzJldUsyaE9rbzlVUmJMSEc5M1pzSGtR?oc=5</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Tourists can now claim VAT refunds at 19,300 retail outlets across the UAE - Gulf Business</t>
+          <t>Corporate Governance in the UAE - Crowe</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE Transfer Pricing</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQV2tyUkVhVzNVUlZ0QW9LdW5PWV9OTEVSN1FHU2c0Um9qbTRDNXFIdmZUaERGcDFPUkkyTVpzWXBQblJHb1VzVERybTh5WkIzcnRoRFo1ZVBicVRMQXpFZXB3VVJRQVZ6UDNNZDItT1RuTXcxYWxtSU1PaGlPNTFNUnpzLXBGX2QxSy1WVjU4alg4Q0dEWmY4WFZ6cEt1a1FZQXpRODFFN0xRT3VwSWFfNw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE4weWRYb0VETFpvMjdhUG9BbU5Wb2JXbzNkLVpxSC1VZHhwYjMwT0F2OFNvQkJNQTFkOG1OamVFZWU0NWpVN3hHb0lldkJWLV9GeThwSjdzNlpnQXp0VDdQbkpnSWFFU3lacVJOeXl3?oc=5</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
@@ -3969,12 +3969,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>UAE tourists can now claim VAT refunds on eligible Noon online shopping purchases - Arabian Business</t>
+          <t>Shopping online in the UAE? Tourists can now claim tax refunds on Noon orders - The Global Filipino Magazine</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNSk0xOTlEQk5DQm4tczlCUE1jZ1dmamdsaUQ2TUYwWnlNd2JHMjhhVXZVUF8wNGpSVUFRNXhvU01pY01FMlUwWEt0anFyS3Q3QS0wa3BjZE1YLWtkWkpYeUJxVmlaSUhQM0Z3Mk9odUFYenhNRnBZeUkyQ0doNWJ2VGUySGY2dG9kMnlJaWhuWEMzb25aWjA1VXZkLWRwelk1MXJjbjBrV2F1Z29KZTJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNa1BKRVpJRVZCZm5VNVp2d3h4Rl92ejg0aml0Qy1pTUotYTZ4ZHlaeURMcnRacE9Zc0J2TWt4VktTQWdFV3BlNXBzWmlfMXFEZFRiYWRIMmV3X3ItaWc0T3pzOG52THI4c1RQaDY1RWdNbXItTTUtdlFTS1d6SUpZTVlXM2lOTWtLWXF6TGNSRE9OWkJQSUs3UXFoSEtOa2NpNEJLeTFOektldFVUVHk4cFJCSE5Qdw?oc=5</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>FTA issues five binding VAT directives on tax transactions - kpmg.com</t>
+          <t>Number of retail outlets connected to Digital Tourist VAT Refund System reaches more than 19,300 - Big News Network.com</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQQXptRUZOQlpWYUZiNzd1QThPVDhlUGM3TF9PU3NKZjUyS2lucEZLUUFKZFpfZVhXLWxteTBKbU1OVEU1WXdPVlViT2ZBb2h5dmlHa0Z2bjd0SzMxa1p6TzF0ajhuVFVSaUpkczUxd1lzeGVCeDNwRnpPbXJVNVNGWHB4UTcwR2dCYTJoWTVSYkJGQmxRZE42cXNmOExtclgxR28tUUdYVFRzaE92?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNUjRVVzdLOXJQTXpUZDhqeWlQNDAwVDV2ZmJqd3h4cW5ZbXc0cHEzZGJBSWlLOTk0ZlFFbXlVSThCUEtxcGFqUHYzSlRmeXF0bC1XQ1J3VVhKUUkzeVBfNTc4cmQwNmlRYldwUU01YXpmc0pxT0daNWRpRUwtM0N3MlBBR09rRldZZlA5bXVJOXVTcVZSeE5ldWRHSWhna0ZfTTNwZWEwODlFTXRRYnRhOVJVcHJ3dDRuSnZtQlBhc0NMa2dhSzk4b1lBWEx5Uk5Ld2RMaFdmNUY?oc=5</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
@@ -4059,12 +4059,12 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -4074,12 +4074,12 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>UAE extends Corporate Tax Small Business Relief until end of 2029 - travelsdubai.com</t>
+          <t>UAE tourists can claim VAT refunds at 19,340 stores and on Noon purchases - Gulf News</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOYzFrN28yN3RDREhxYV9CVHl3UGU1NlpvSFJqaHJGWVpraVhEOEtqTnZVQk1OTjVjX1djWENocHdtYy1WY1dBSHZncjg3aGxWOXlwcFktaVVxYzBmZllLbzBaLUUxSEpyNW1HX3V5MG9YMWhTcjNfcnZxQ1JKRHZkMjlYSjlmUHk1SGFEYy0tYmlqWE96ajBqUnNSS19TUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQeDRPcDE4QjJaSFU3Qm1wRGVaWXl6cjY2c3YyVDF3TmtqN1RYMkh0WDdoSm56QmlXU21xSllRQWt4WHNFU09vUWZpTEd3dVVMb0UxNy0yZG1ucUF6aXhIZ2dWVXpkVjVqa2hHUGN3VHNZWEticFZMXzNfb2NzaVpwOFFkOVAtNDhBY0xjSUo3bkh0WUg2ZEJ4Q0JDU05Td0FTLWlUWXNfN2JKeGJsTEg3NGFDMzNwT21JZTFGT0V30gHQAUFVX3lxTE9wdElvSG52YzNWWUt6WGJaRkp0LXpmVHpQTFV4WHczVkQtOUhOMWpqRzd2UjgyQjNOSWdMT3QwM1luZzdtNWhXdU91R2lqS0FKcG1hUGExZ1QxWG1SSUo2cWZSWll0bjdpQ2pBOXFjTUMxcjJma0RraGlVbjNjajZRM0h4OVZfM0FUQXNERTQzQm1TS29QVjdiQzM2T19naktoTXhfQ1pvNmx4U2IxVkkxUWF5QmZ4QUxmMXB2bFVvR2RVWm10bjE2SlNaRzJ2VEU?oc=5</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>UAE seizes 3.58 million non-compliant excise goods - Gulf News</t>
+          <t>Retail outlets linked to UAE's Digital Tourist VAT Refund System exceed 19,300 - Emirates 24|7</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOOF9vUDk3UXlsY19FUWtOOEJ2V3Awam9fY09zeS1seXpTUUt2Y05TQlVUVjlwYlVuX2hRN3JBM095eTlqZ3pxWWx5ZWJzUzV1bGdCQ21JMzd1bjRIMGRMdHpiZWVOM1lmOVdtSXlicW4wYUNoYjMySjFTNl9OTnRvYWZycGdhODlTcU9sQUpwUEdJcnltNF9nSXpBWkpJbjF0VG1qeVJqTdIBugFBVV95cUxPMDVISGFVMTVqWFFiS0VMTmlzZzlyWXRVUl9BTjBGaWgtS21lN05BdlppYlVNQkNtYmZWaHRIczNlSWRmbXBBdG9zamlobjFhTFh6R2lYZFJ1RUtKWGZqOWpNd21LTmNxaUF1SjVIUm9UNjF6cmwxUGY2ZHFIVHBFdVJNMXcyeFp3dUZ2V1hpVmtnRmZOY29nLWNWQmxsQ0tHUzd0RjRyRUlZeW1adThtZEpPVl9KT1pFRUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOcXRBMGsxX1Q5SkJXcEFwWnV3c0VVc19jUnRkWU5yMVlPelltaEhvOWNLcEJxYi1KUExWMVlmZE1FOExZYklsRHU4N3lQZGppMDRnYUFaRU1OWHdwaVpiWWowOENidVJjbDFPeTQyQklzOGM5bXhQbDJrRFg2TkR6bUplTzJNZzl2M3dJT2FEeHVTTVNtTml6UEdoZUFDcVRCZWFHMGg1ejZoSWI1UWFCLV9zREotcmF3V0HSAdQBQVVfeXFMT3Q0RFN0V3FRSlNWV20tMm5hY1N5VHBVWmxzdnZGVXIwZU92VTZVRDVUVkRZM0Q1U1ZNZzFRcFlEWTc2ckk0UjZhcEN4YmZIZndTd284ZDQ3Z2Z4OS1mVGFUX2RwRzgyMWViTjEyQ19wdUxucXEtZWtFRm5tOWpId1VYYlRmd1Rkc2tlb3Q3THR0THZxZWt3Q1ZyTGVvZ2hUUzZPeTBPSzlER3FXR0ZvUnJiWk5vdlpwYlYxdmZjZnNTVEQxM3hSY1pyTGV5Qkk2d2lrejQ?oc=5</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>UAE Extends Small Business Relief for Corporate Tax to 2029 - tbreak.com</t>
+          <t>Indians, Russians, Turks top list of tourists claiming the most VAT refunds in UAE - khaleejtimes.com</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9icS1QSXhYc09ROHVJdzRtdXJTMEdLa0o5Mm5TZ3VxR002a3lTeFR5anZqRmNtcVEyQWxfQ050UFVOZnFBcFdwT1VoNGlVZU9xYkY2WkM5SlpSSnp6QkpHck5rTUxqOXNjNjM0UmFTQkFfOXZySFFON1pCSXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPek9sY1dJUkpRblhiYnJDdDExOW1yREdXd1oyZ1Yxb0FnZlBYNTd3SUxGWnVMenlZVGlqRlIxLUszNk1Jd3BpcF9rVE9XLVF1OWdhY01fd0gteTJFRkVJLVREMjl4ZVRGZHJacUxJREpRN3UxdHFncGhITEQ0MnUzTkhKY2FSZnBnaFUzZDEyRnZOdG1hOWVFX2FLNG9Ca1lGekQzcllxd0FqTUhvTTRZM3MxcElQV0JaMWfSAcIBQVVfeXFMT2FPTEx4WGUzNUNhZWdBa1MzVU5GN1p3SkRwM0o5TWlqenhqVTNhR1Z0bThyN0laMS1tOUhfaG1qMmZpQi1pT3lTNEhKT2l3SklKZ1E3MXkyYVBrMnUwOTh1Y2RxSkFISUdlT1B6Qm1tTV9CUV9YM0xwcTJ2NzVmWUcxaFJ2YzhYeVBjZG1WSG9vcVc2N2tqRzNreHFwWVpaaUdncndzVEVLaE8zeHczU0Jvdl9FazU2NE1CNWZqQmZmekE?oc=5</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr"/>
@@ -4194,12 +4194,12 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>UAE extends corporate tax relief for small businesses until end of 2029 - Gulf News</t>
+          <t>Tourists can now claim VAT refunds at 19,300 retail outlets across the UAE - Gulf Business</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNNEo4Tm9qN1dERmwzZ0tMR0ZOSUVQTkpOTTNiTDc1U2VaSTkyRkExekRzRjUzb2xrelYzV0oydU1qS2JCbHJXd1hxeWhPdmtUN1UtcXRCOHZpSXBxMlBMdFRKbDNxYlNFaVdwRXROTUVxWC1tZUpObDVIZzNVUDEzSUZpNkIxN3ctTDRNWU9xOUx6QXZieFdVV1hkNHhlcldHUzY5b21BZ1J2VTVhMlN2a1V5V1dJRkw1OTItdWo5Qzk5N2lPX1HSAdgBQVVfeXFMTmRQM08wYWhkelVySDhudHZWLWQyZ2lyUG9TNEJhWVV6ejAybDV6QXdvUFR5ZndxZldxWHVDMjRKVm1Ndm0yeE1HZHo1LXoyVFBzMkhuUDZESEw5RUFIaWlfNEdObjNxRlc4VFpOZVQ3RDhhellsdEpYN3pLVzl1d1Fva3R0RWpDb0d5cVN0Z3I3emowS2tNbkplWTh1Z2NvVkRMd0R3STNWV3hrUVFtd3hxdjQxWjI2ZU4wVE9JTzlsWVUwYXlPTmU4YWJmazMxQk93MHVHbGZE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQV2tyUkVhVzNVUlZ0QW9LdW5PWV9OTEVSN1FHU2c0Um9qbTRDNXFIdmZUaERGcDFPUkkyTVpzWXBQblJHb1VzVERybTh5WkIzcnRoRFo1ZVBicVRMQXpFZXB3VVJRQVZ6UDNNZDItT1RuTXcxYWxtSU1PaGlPNTFNUnpzLXBGX2QxSy1WVjU4alg4Q0dEWmY4WFZ6cEt1a1FZQXpRODFFN0xRT3VwSWFfNw?oc=5</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr"/>
@@ -4239,12 +4239,12 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Small businesses in UAE urged to file corporate tax returns before deadline, says FTA - khaleejtimes.com</t>
+          <t>UAE tourists can now claim VAT refunds on eligible Noon online shopping purchases - Arabian Business</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOWnJlYmRmRm4xdy0xZ0toMUNUbnhTd3A5UW1pVzhFeXhIM2txamo4NU5qYVYwZGlQcEYwLTJhelBkOEdHajRYSE5PRnZtdmxGWmc0R2JlUVk0eVc0aW53NzdlM08zeWFzTUNocU9UcnY3UTNhTHVzZHhjRXFPZ0ZMMHMyRExEcjFiVVhKVzMxYk9FSHUxdERQRnUyZlJLWXA0ZVHSAaoBQVVfeXFMT3BwVV9lZzBQRTFjWUNVNEFzaUlhOUJuTHByVVRhdjRTbjdpajdOTjRtc2hfOEotMWlSb0FvX1F3azI2czNjMHREWnRJbFptM0F5ZHJkWUFsMW5fMDBsNU1YODgzT2VkMWZacU51MzkxaHJ0S216TF9UR241SnM0OVo2eHlDM0F6V2VfbUt4elZfZVBub2pLNW5fazhqV1hNUnBzRmkxS0NUQVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNSk0xOTlEQk5DQm4tczlCUE1jZ1dmamdsaUQ2TUYwWnlNd2JHMjhhVXZVUF8wNGpSVUFRNXhvU01pY01FMlUwWEt0anFyS3Q3QS0wa3BjZE1YLWtkWkpYeUJxVmlaSUhQM0Z3Mk9odUFYenhNRnBZeUkyQ0doNWJ2VGUySGY2dG9kMnlJaWhuWEMzb25aWjA1VXZkLWRwelk1MXJjbjBrV2F1Z29KZTJ3?oc=5</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr"/>
@@ -4284,12 +4284,12 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>UAE extends Corporate Tax relief until 2029 for businesses earning up to $817,000 - Arabian Business</t>
+          <t>FTA issues five binding VAT directives on tax transactions - kpmg.com</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE5SM3FoRTVUSmJwTlpLbi1vOGFPM3RPcXpraXlCUG9iQlhuUUJ2MGRCczd6aDM0MFFNWS0yS2tNNVIxYjd2Y3AxWExhUnJNcHNXT3dLdGhyV2FBQUQwbmZ3YjRZc3NXTkNoLU5HTFRkTWRkSlZ6TEtHbg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQQXptRUZOQlpWYUZiNzd1QThPVDhlUGM3TF9PU3NKZjUyS2lucEZLUUFKZFpfZVhXLWxteTBKbU1OVEU1WXdPVlViT2ZBb2h5dmlHa0Z2bjd0SzMxa1p6TzF0ajhuVFVSaUpkczUxd1lzeGVCeDNwRnpPbXJVNVNGWHB4UTcwR2dCYTJoWTVSYkJGQmxRZE42cXNmOExtclgxR28tUUdYVFRzaE92?oc=5</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr"/>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Finance announces extension of small business relief for corporate tax purposes until 31 December 2029 - Zawya</t>
+          <t>UAE extends Corporate Tax Small Business Relief until end of 2029 - travelsdubai.com</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOWVAwdTI2R09XSWRHaFNWYkNGdUJsSTNnaGpRandNeklubW8zM2h3VkNIcmRiQTVrZUxlSnhydWtqUGVTRS1vYVVQWWJfY2swUzhYOFJrdHVCQTlvTk1LNVBfWjBPbHZxWVU5Q0xQVWFHbTlLYlE0ek1aWFhqaUF3dDlTY2p2T0dtV3gzSXhaWkdFdWFBejA5ZkhDSkVPanZUWDk0d1oxNlJOUkNxMER2M1oyc3Nla2NnUW9WYmFRS04zeGlCcjQ1YVNZT2ZraU5EN0h2ZWRDaklZTjFQUklLWmRGRVFkUjhKUjBybHA5UktLZHFiVnUtOFpuNmhSZ0o3YVV3eld3WQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOYzFrN28yN3RDREhxYV9CVHl3UGU1NlpvSFJqaHJGWVpraVhEOEtqTnZVQk1OTjVjX1djWENocHdtYy1WY1dBSHZncjg3aGxWOXlwcFktaVVxYzBmZllLbzBaLUUxSEpyNW1HX3V5MG9YMWhTcjNfcnZxQ1JKRHZkMjlYSjlmUHk1SGFEYy0tYmlqWE96ajBqUnNSS19TUQ?oc=5</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>FTA reminds small businesses to file corporate tax returns - Sharjah24</t>
+          <t>UAE seizes 3.58 million non-compliant excise goods - Gulf News</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5NZ1VTdFlkVERkd0pETmFiVUQzZzEySVNaeWFyV2N3MHdhSWZreEZnUDFCYXhiWGtCOVVxMFdWUzhDa3JCU1czenE3QzJzaG0tNU5iMkFmRFRsTUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOOF9vUDk3UXlsY19FUWtOOEJ2V3Awam9fY09zeS1seXpTUUt2Y05TQlVUVjlwYlVuX2hRN3JBM095eTlqZ3pxWWx5ZWJzUzV1bGdCQ21JMzd1bjRIMGRMdHpiZWVOM1lmOVdtSXlicW4wYUNoYjMySjFTNl9OTnRvYWZycGdhODlTcU9sQUpwUEdJcnltNF9nSXpBWkpJbjF0VG1qeVJqTdIBugFBVV95cUxPMDVISGFVMTVqWFFiS0VMTmlzZzlyWXRVUl9BTjBGaWgtS21lN05BdlppYlVNQkNtYmZWaHRIczNlSWRmbXBBdG9zamlobjFhTFh6R2lYZFJ1RUtKWGZqOWpNd21LTmNxaUF1SjVIUm9UNjF6cmwxUGY2ZHFIVHBFdVJNMXcyeFp3dUZ2V1hpVmtnRmZOY29nLWNWQmxsQ0tHUzd0RjRyRUlZeW1adThtZEpPVl9KT1pFRUE?oc=5</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr"/>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>UAE extends small business relief for corporate tax until December 2029 - TradeArabia</t>
+          <t>UAE Extends Small Business Relief for Corporate Tax to 2029 - tbreak.com</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOc3RJWW11LUNyUERIeHh0dTVRVFJySzBoWVB0N1RCdVNpTVpORW03RkVXaG1pdk5HbWJfTDUzYXRIellIdlo4dVBXcXpuZHNrQXZRMk5MMGF1UkpqbGRTbXZRekZTYkU3cHpsdmJHdTVRdFFxSE1aSzZxWW1rb0RuT1RNZzVOWG91OGVTcFZVUGFVLWRUY3JsRnEtYkR4WUJjWnp6NkljSUd2NExsdUYtVA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9icS1QSXhYc09ROHVJdzRtdXJTMEdLa0o5Mm5TZ3VxR002a3lTeFR5anZqRmNtcVEyQWxfQ050UFVOZnFBcFdwT1VoNGlVZU9xYkY2WkM5SlpSSnp6QkpHck5rTUxqOXNjNjM0UmFTQkFfOXZySFFON1pCSXc?oc=5</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr"/>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>UAE tax warning as thousands of businesses approach Corporate Tax deadline - Arabian Business</t>
+          <t>UAE extends corporate tax relief for small businesses until end of 2029 - Gulf News</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBGbVZOWkkxM2FaVGlfeENJVWJXYzN6SDdmNk9nOFBYWWJDV3N6eGxVcnBRRXc5cDY5Qy1xSnNBQzVHMXR3NGpacEVucjlTMFRSaHc0dG5aZXc1aUVwSXlrTXhFTGd3RWNMbzVpWmdEVUZuUC1N?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNNEo4Tm9qN1dERmwzZ0tMR0ZOSUVQTkpOTTNiTDc1U2VaSTkyRkExekRzRjUzb2xrelYzV0oydU1qS2JCbHJXd1hxeWhPdmtUN1UtcXRCOHZpSXBxMlBMdFRKbDNxYlNFaVdwRXROTUVxWC1tZUpObDVIZzNVUDEzSUZpNkIxN3ctTDRNWU9xOUx6QXZieFdVV1hkNHhlcldHUzY5b21BZ1J2VTVhMlN2a1V5V1dJRkw1OTItdWo5Qzk5N2lPX1HSAdgBQVVfeXFMTmRQM08wYWhkelVySDhudHZWLWQyZ2lyUG9TNEJhWVV6ejAybDV6QXdvUFR5ZndxZldxWHVDMjRKVm1Ndm0yeE1HZHo1LXoyVFBzMkhuUDZESEw5RUFIaWlfNEdObjNxRlc4VFpOZVQ3RDhhellsdEpYN3pLVzl1d1Fva3R0RWpDb0d5cVN0Z3I3emowS2tNbkplWTh1Z2NvVkRMd0R3STNWV3hrUVFtd3hxdjQxWjI2ZU4wVE9JTzlsWVUwYXlPTmU4YWJmazMxQk93MHVHbGZE?oc=5</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr"/>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>UAE reminds small businesses to file corporate tax returns even if no tax is due - Gulf News</t>
+          <t>Small businesses in UAE urged to file corporate tax returns before deadline, says FTA - khaleejtimes.com</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOTm96UlB4Q2xPRlcybWNBanAtYXhxQkg0eHVCNDBvZlZGTWNGNzlSekNuVWZCU1JvOWR4MWxLanJMZEsyRms3NnZDSU90RnZuTkhad3pLLU1XX2VWV215T21HMTBmbVF1X0hmakhwM1BYZVNUQXZEV3A1UmR0QkZxVlJ1VDV5dGVMMFJFSGRxckpYVkVMMmFNMFBBdE9MZnlFSjJ3MDFXNzg2UXd0SUthQlZrd1Zjdy1JTVFkMEZlU0VKc3lzQW84VDBGLXFfVF93SnfSAeQBQVVfeXFMUEpicHFURTEyaDByTG44RGZUZ2R0MGJwRmdpV0hydzNTdkVYd0lFZzNITm9ueldCQ0JUZjZ3dW1TZ0xCSHM1S3c5eXExQlZac3V6bGd5Q1EzWFljOVRrZkJWRV9XcnFQWHdzRHQzWDRiUFhHaXlKMldlZHp5YW9zMHh2emxiX0R3MXdva2NFZ2JwcnVBZk52dEh2UEhvTW9FYzlJQ2xWdWZPQmpteFpaWnNUV0lpUTRiT0hNRXdHQVg1Q1VibWZqVWdocjBVVHJtVVFUbVFBdjJoRndFUS1aMTc5SEVh?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOWnJlYmRmRm4xdy0xZ0toMUNUbnhTd3A5UW1pVzhFeXhIM2txamo4NU5qYVYwZGlQcEYwLTJhelBkOEdHajRYSE5PRnZtdmxGWmc0R2JlUVk0eVc0aW53NzdlM08zeWFzTUNocU9UcnY3UTNhTHVzZHhjRXFPZ0ZMMHMyRExEcjFiVVhKVzMxYk9FSHUxdERQRnUyZlJLWXA0ZVHSAaoBQVVfeXFMT3BwVV9lZzBQRTFjWUNVNEFzaUlhOUJuTHByVVRhdjRTbjdpajdOTjRtc2hfOEotMWlSb0FvX1F3azI2czNjMHREWnRJbFptM0F5ZHJkWUFsMW5fMDBsNU1YODgzT2VkMWZacU51MzkxaHJ0S216TF9UR241SnM0OVo2eHlDM0F6V2VfbUt4elZfZVBub2pLNW5fazhqV1hNUnBzRmkxS0NUQVE?oc=5</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr"/>
@@ -4554,12 +4554,12 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>Federal Tax Authority wins SAP Global Innovation Award - SAP News Center</t>
+          <t>UAE extends Corporate Tax relief until 2029 for businesses earning up to $817,000 - Arabian Business</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYWE1ODFVeGZ2UEVVd0IyYXY0ckdPdFp4blEzcm9pZTZ5dm1MUDlocTNzNnd4dTh3cVhQb0o2aHJ2Y2VjTndrd2d6N2t1eW9OTzVtQ2JrcXVwN2NidFd2WUViQlRleTVQQXNpV2VvOVkyMFRINHhnNXpsUWdOcDhDUk1TbkpTajRkcUFGblBfWXhRZVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE5SM3FoRTVUSmJwTlpLbi1vOGFPM3RPcXpraXlCUG9iQlhuUUJ2MGRCczd6aDM0MFFNWS0yS2tNNVIxYjd2Y3AxWExhUnJNcHNXT3dLdGhyV2FBQUQwbmZ3YjRZc3NXTkNoLU5HTFRkTWRkSlZ6TEtHbg?oc=5</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr"/>
@@ -4597,35 +4597,39 @@
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>official</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Finance Adopts “Aani” and “Jaywan” as New Payment Channels for Federal Service Fees and Fines</t>
+          <t>Ministry of Finance announces extension of small business relief for corporate tax purposes until 31 December 2029 - Zawya</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Ministry of Finance — News</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>mof.gov.ae</t>
+          <t>news.google.com</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>https://mof.gov.ae/en/news/ministry-of-finance-adopts-aani-and-jaywan-as-new-payment-channels-for-federal-service-fees-and-fines/</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOWVAwdTI2R09XSWRHaFNWYkNGdUJsSTNnaGpRandNeklubW8zM2h3VkNIcmRiQTVrZUxlSnhydWtqUGVTRS1vYVVQWWJfY2swUzhYOFJrdHVCQTlvTk1LNVBfWjBPbHZxWVU5Q0xQVWFHbTlLYlE0ek1aWFhqaUF3dDlTY2p2T0dtV3gzSXhaWkdFdWFBejA5ZkhDSkVPanZUWDk0d1oxNlJOUkNxMER2M1oyc3Nla2NnUW9WYmFRS04zeGlCcjQ1YVNZT2ZraU5EN0h2ZWRDaklZTjFQUklLWmRGRVFkUjhKUjBybHA5UktLZHFiVnUtOFpuNmhSZ0o3YVV3eld3WQ?oc=5</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr"/>
@@ -4638,35 +4642,39 @@
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>official</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Finance Announces Decision introduces a Minimum Excise Price for Liquids Used in Electronic Smoking Devices Effective 1 September 2026</t>
+          <t>FTA reminds small businesses to file corporate tax returns - Sharjah24</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Ministry of Finance — News</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>mof.gov.ae</t>
+          <t>news.google.com</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>https://mof.gov.ae/en/news/ministry-of-finance-announces-decision-introduces-a-minimum-excise-price-for-liquids-used-in-electronic-smoking-devices-effective-1-september-2026/</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5NZ1VTdFlkVERkd0pETmFiVUQzZzEySVNaeWFyV2N3MHdhSWZreEZnUDFCYXhiWGtCOVVxMFdWUzhDa3JCU1czenE3QzJzaG0tNU5iMkFmRFRsTUU?oc=5</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr"/>
@@ -4679,7 +4687,11 @@
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>Corporate Tax</t>
@@ -4687,32 +4699,290 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>official</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Finance Announces Extension of Small Business Relief for Corporate Tax Purposes until 31 December 2029</t>
+          <t>UAE extends small business relief for corporate tax until December 2029 - TradeArabia</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Ministry of Finance — News</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>mof.gov.ae</t>
+          <t>news.google.com</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>https://mof.gov.ae/en/news/ministry-of-finance-announces-extension-of-small-business-relief-for-corporate-tax-purposes-until-31-december-2029/</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOc3RJWW11LUNyUERIeHh0dTVRVFJySzBoWVB0N1RCdVNpTVpORW03RkVXaG1pdk5HbWJfTDUzYXRIellIdlo4dVBXcXpuZHNrQXZRMk5MMGF1UkpqbGRTbXZRekZTYkU3cHpsdmJHdTVRdFFxSE1aSzZxWW1rb0RuT1RNZzVOWG91OGVTcFZVUGFVLWRUY3JsRnEtYkR4WUJjWnp6NkljSUd2NExsdUYtVA?oc=5</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr"/>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Tax</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>UAE tax warning as thousands of businesses approach Corporate Tax deadline - Arabian Business</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE Corporate Tax</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBGbVZOWkkxM2FaVGlfeENJVWJXYzN6SDdmNk9nOFBYWWJDV3N6eGxVcnBRRXc5cDY5Qy1xSnNBQzVHMXR3NGpacEVucjlTMFRSaHc0dG5aZXc1aUVwSXlrTXhFTGd3RWNMbzVpWmdEVUZuUC1N?oc=5</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Tax</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>UAE reminds small businesses to file corporate tax returns even if no tax is due - Gulf News</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE Corporate Tax</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOTm96UlB4Q2xPRlcybWNBanAtYXhxQkg0eHVCNDBvZlZGTWNGNzlSekNuVWZCU1JvOWR4MWxLanJMZEsyRms3NnZDSU90RnZuTkhad3pLLU1XX2VWV215T21HMTBmbVF1X0hmakhwM1BYZVNUQXZEV3A1UmR0QkZxVlJ1VDV5dGVMMFJFSGRxckpYVkVMMmFNMFBBdE9MZnlFSjJ3MDFXNzg2UXd0SUthQlZrd1Zjdy1JTVFkMEZlU0VKc3lzQW84VDBGLXFfVF93SnfSAeQBQVVfeXFMUEpicHFURTEyaDByTG44RGZUZ2R0MGJwRmdpV0hydzNTdkVYd0lFZzNITm9ueldCQ0JUZjZ3dW1TZ0xCSHM1S3c5eXExQlZac3V6bGd5Q1EzWFljOVRrZkJWRV9XcnFQWHdzRHQzWDRiUFhHaXlKMldlZHp5YW9zMHh2emxiX0R3MXdva2NFZ2JwcnVBZk52dEh2UEhvTW9FYzlJQ2xWdWZPQmpteFpaWnNUV0lpUTRiT0hNRXdHQVg1Q1VibWZqVWdocjBVVHJtVVFUbVFBdjJoRndFUS1aMTc5SEVh?oc=5</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>Federal Tax Authority wins SAP Global Innovation Award - SAP News Center</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE Corporate Tax</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYWE1ODFVeGZ2UEVVd0IyYXY0ckdPdFp4blEzcm9pZTZ5dm1MUDlocTNzNnd4dTh3cVhQb0o2aHJ2Y2VjTndrd2d6N2t1eW9OTzVtQ2JrcXVwN2NidFd2WUViQlRleTVQQXNpV2VvOVkyMFRINHhnNXpsUWdOcDhDUk1TbkpTajRkcUFGblBfWXhRZVU?oc=5</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>official</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>Ministry of Finance Adopts “Aani” and “Jaywan” as New Payment Channels for Federal Service Fees and Fines</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Ministry of Finance — News</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>mof.gov.ae</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>https://mof.gov.ae/en/news/ministry-of-finance-adopts-aani-and-jaywan-as-new-payment-channels-for-federal-service-fees-and-fines/</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>official</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>Ministry of Finance Announces Decision introduces a Minimum Excise Price for Liquids Used in Electronic Smoking Devices Effective 1 September 2026</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Ministry of Finance — News</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>mof.gov.ae</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>https://mof.gov.ae/en/news/ministry-of-finance-announces-decision-introduces-a-minimum-excise-price-for-liquids-used-in-electronic-smoking-devices-effective-1-september-2026/</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr"/>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Tax</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>official</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>Ministry of Finance Announces Extension of Small Business Relief for Corporate Tax Purposes until 31 December 2029</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Ministry of Finance — News</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>mof.gov.ae</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>https://mof.gov.ae/en/news/ministry-of-finance-announces-extension-of-small-business-relief-for-corporate-tax-purposes-until-31-december-2029/</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/tax_updates_export.xlsx
+++ b/docs/tax_updates_export.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:K108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -511,12 +511,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Prefortune Technologies Announces Odoo UAE Peppol E-Invoicing - openPR.com</t>
+          <t>Dh5,000 fine for 1-day delay: UAE firms rush e-invoicing deadline - Khaleej Times</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQVG9nYjRRdy1xYVZ3cEU4ajVEd3dpaXJYNWNpWFB5eG5Ia054ejBUa0VkNVMwb1I4TUVQdkl3STFTcG9fMS1ObVRHTV91eng2SHBiVGtIZGRZVlRVOHAyVDVoLUJONTlDRDkyaTRocno5M0lwcVBfS283N1lEY0t5eWd0Rld6MzkybWktZEtqWXlaN0w4c2xzbzFzT1NiQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQQWhmSUVTODNEbHVMazVqOTdveVpnQVc1R0pTbzVlOFptck9OVlRzSXFjTmtnV2wzank2Mkw2NnM3dm5tRXVnSEpKVlpJeHBNejlmcHlza21QZlU3VDQtbFhFVHNUakg0NGhfRnJvVVBZdW9QZEhINUpZMy1qNVFuV0I1R29zS18xSTZIUzV0MnFPQnFQb3ozNmZSODFvUFpZX2RUR3d5UmFMZ1nSAasBQVVfeXFMUEFoZklFUzgzRGx1TGs1ajk3b3laZ0FXNUdKU281ZThabXJPTlZUc0lxY05rZ1dsM2p5NjJMNjZzN3ZubUV1Z0hKSlZaSXhwTXo5ZnB5c2ttUGZVN1Q0LWxYRVRzVGpINDRoX0Zyb1VQWXVvUGRISDVKWTMtajVRbldCNUdvc0tfMUk2SFM1dDJxT0JxUG96MzZmUjgxb1BaWV9kVEd3eVJhTGdZ?oc=5</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -556,14 +556,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>E-Invoicing</t>
@@ -576,7 +576,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>From readiness to implementation: 7 steps UAE SMEs should take for e-invoicing - Khaleej Times</t>
+          <t>UAE Passes 25,000 Peppol Participants - sharedserviceslink</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQUkNGMUtUUW55SjEwUnhUYjBycXVyOW9SS1Z0RGFVcTl3VWVMWlMxQ3E3WV95MWt4RUdoOHRQTmxDLXV4Yk1qMjdWUnJxSUNxVURUTWxrd2pWdDBBREZRZGNEVTZvSlB2Z0FuOFZFbGdKX05tT0tFeGx0SHVRQVdWaGE4UU1kdlhVYkZFQzF0R1lFOC0tNTBQTXBybUVLVFNHVEZyMnFwa1RVRUVUakExY0o5Wm80b2RJbFIxNW5TclZpNm1Hanh2RTJOdkF6d9IB1gFBVV95cUxOdTA0Q0pDMnBiTFpZbkcxRnFwZXg3OXdmU0ZQdzBQNEd5ODNtb1VyWndTM3NhMkpQRTJqVVRldEdubm45X1RxTTFGTHl3MWFmZENMZXlxXzRJTXBEOTQ1SENNUkZ5Sk5DZU1OUEljVjFVNWF1NTBwOHNJZE92UFQxZ3hPSEtObXJMcVFieGVBejZneGdiTzJfLURXQXIyM1FwbnJibGFMUG84RkFJZGVPbjZEanhkWTlFT0ljR1MyYnRyYmZKMkMtVGs5VzJOZTlXTm5YcTJB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE0ycm9haWtSX21lNk4yMkZESVBxVVFQTl96ajVERGZhUERTdS1faTZ5Ry02N3p0a0Znc0tnQVF5T2tHRjlYQzM5ZmZ4eVJDdWx1QzRDWFJTdzZubTdndlc0dmxtRkZQOEhoa19DWC05UjJMblZHTFNFVzR6WmhHSmc?oc=5</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -601,17 +601,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -621,12 +621,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>DP World appoints two independent directors to board - Gulf Business</t>
+          <t>Himachal Pradesh Makes Electronic Payment of VAT Mandatory for All Registered Dealers; Amends Rule 37A of HP VAT Rules, 2005 - A2Z Taxcorp LLP</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPX2QzdVpCMHdjWXN5M0ZHNEVvVEhGdFd1aEFHNnk1dXZ2ZWRKUHJLVG1pQ0hoTjVaRExrcXpyY2hTbkxFc3Z4aHgtMHB5ZHlValh4dGhNTjdvcnZzdzVDV3pKbUo2TW5HMGExa0hDcUZoSzctUUI5WDhIckx4N2tMVFo2WHpWUVp0NDIxQnNvV1hOX2NiTWZpdVJtelVFYW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQMWFMSHc1dFk0SXhSd2FsQWEzZk5vc2w2US12cEtZUkdjTWlsdWw3N2ZwbGw0Y2kzMnNGcnJvWUJrbFgtV1lHaHZnczNpUThZd1FJeEMtay1QR2s2R21STnk2aG54cGs2RUhRZFJ2eml3TFMxWTRDVzdCSFJEMFAxOTRra0JfS3dNeTBRT2xtWTFCNWpHM0U2QWtIYVp0MFdqYXpOYXJrZTUxWHZWN21Nbkp2elNhbWdtekI0TkktZEhOT1hIaXkxT2hDbkZvcFIyUTlTcVlBLWVwY1dwVUJV?oc=5</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -646,17 +646,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>FTA calls for compliance with e-Invoicing deadlines to avoid penalties - www.wam.ae</t>
+          <t>Federal Tax Authority holds second session at Al Barsha Majlis as part of Emirates Majalis initiative “Closer to Each Other” - Zawya</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPUDNQWVptSk1uTm9rVFI3ZVYwV3dRMVdXSmJxZVkxZlhBd2FEa1ZaNlJsQzcwaU9tcFNjbTJEWEs5UGJTNzhoWVEyeF90a1ZPcmVJM2RLUDJ3VHRMVU9qZ1ZBbEhPVTNDaklkSkNyVllwVEZ3UTE1N3ExZWNZZWhzQ2p0MkoyQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxOMWRFWVpfczR3aDdSTi1MMktYZXJraU5qdTAzWE1BSFA1UnF2RnJ5WWJ1V1hVVGZ3eTduZTFEdVFvWGQ2NENIbVdTeVhZQklVTzlkZkFUZGQweTBxOWMtc0toOG9ITjhzWVAyd1JfalJCcDhaV0RXYklVU24tYUxMcGRhTkd2ZTlmazdjbEVMLUItZEVYTVFqU3N0MExMTGVHbE5FQmQ0MkZGbF9nSHZXaGlMQTdyVnRsRF8xaEFVMEZRVExYQUd5dTRLNHlPWDVuVHRIS3Fjak0zV0pEZ29Yd2pmenlWVXY3OWFsSjlLM09KZnM0bjd3VERDSlNmQVVhWEY0dmFCcTk2UjBYUk5FdmZ2MA?oc=5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -691,17 +691,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -711,12 +711,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>UAE e-invoicing deadline: Businesses have until October 30 to meet first requirement - Gulf News</t>
+          <t>A new era begins for VAT input tax due diligence in the UAE - Consultancy-me.com</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQVlFDSEtCd1I4TTB1M2NIQlBtSUtHWEJGelF2aTctaVpIQzRtcTRDWkt5dkFwRFA3ZHVZc1N0RWF6UzYzMzd2TUJQdXZ3MGpFaE9IOUtrenFhLThTNjByTlpnQ0laeHJXMVpJZ25fcmxGUmRmb0ViRW1DRFJmV3M2elhTWllZM3M4TzNXS01SQjVldDVvTnFDbkdjaVlCcGV2VHAzSnFfS29ldVNRUVJEUU9iTnRqS1ZlemJZNEhhY3RvakY1RGNjd2VpR0R0Z9IB4AFBVV95cUxNSUF6V3NtcTJFd0tRQ1FQbTlxbmdwLXVCd3hlcE05amFITks4Z2RaT0I5Znp2UUN3UjNpbWlKVWNXQ2YydkpjUVBQaHdqZVFQM2tpM0xYWlV5bU1tN3QxbnpwRDhUVmliNmU3dnJ4Uk56ejRuaG1NSWNrRnZFc0gtYTJubVdSaUIxX2Q5TmRmWEZIMkFwTDc0UFpJSWo3TVhtTnBZRzl1RExGTWU5N2l3Y1FmRmd2RU9JUU9WY1dvaWZQdlZQWUpYbC1pY2VFemRJbUVPQ2tWb2cxenVHTFpRSw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPYnFTdmVUTW52ZWVOOHVISk5BaHJoMVVXZGd3cnpjZ1JySkJGRTRmWGxmU2FJX0pnSGNaeGJJREIxTGowWjhneDV2allRZ2dLU1dIVmdRWUd0X04tZ29Zc2JDUVJLUGNpZlU5X2JIUGNScXpyYmdMZURwWU1xa0VqMVNIbi1VQTh0RkJjZHFJdVI5T2ZZbzVJSTg0WHNWcUVpaURvWUF5T1jSAagBQVVfeXFMT2JxU3ZlVE1udmVlTjh1SEpOQWhyaDFVV2Rnd3J6Y2dSckpCRkU0ZlhsZlNhSV9KZ0hjWnhiSURCMUxqMFo4Z3g1dmpZUWdnS1NXSFZnUVlHdF9OLWdvWXNiQ1FSS1BjaWZVOV9iSFBjUnF6cmJnTGVEcFlNcWtFajFTSG4tVUE4dEZCY2RxSXVSOU9mWW81SUk4NFhzVnFFaWlEb1lBeU9Y?oc=5</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -736,17 +736,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>VAT, E-Invoicing</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -756,12 +756,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>MIDDLE EAST TAX ALERT | UAE | e-Invoicing Guidelines Version 2.0 - Alvarez &amp; Marsal</t>
+          <t>UAE electronic invoicing deadlines announced - Global VAT Compliance</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPeGtIWGRjTmV2SWU5UkpsektaSno5VVpYVGlpcmdUYW0zNW9lalJfeGk4Y0dacFNQaWZ1dWFpRkVmYTh2SWF5c3ExTW50eUxuNXRLblhLcl9xRWx4aWlYRm14eEFIMTM3UHJ5XzBZNktjRHFuNWFXbEVwWWhGdkhyTDNLbVJscWdXemU3RlhrcncyMHkzckRyV0wxdGRQY254Z1NXUHNfV1JhSkZ2b005WjVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPREZqVWFCZklDbHRZeXBpN29mbl9NSWQ2T2lfZjJqV3lzenV2WE1zWkFjOTRUMXJXRzdyRDNpSC12cDJoVUxSSHZWbG1EOEZUNVNHN1Y3czhCY0VOTzRDY3E2YWVZY3dVMFhUaHZNdnpUMG04YThMOVFJTGlRYW9RNGdKNThrOUVLRHJTbjRn?oc=5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -781,12 +781,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -796,17 +796,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Cyprus tax alerts - Deloitte</t>
+          <t>Why UK founders are moving their business to Dubai in 2026 - BusinessCloud</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>News — Big 4 UAE Tax Commentary</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPR3dMcm02YVpKS2NHZC1YZlJaV2VXZHJMYjNzVzRNa0NfSDNXaFhJcUNseDFYaUVRNVNpdmd5Rm1jbE04d2psTWRBMjZrOUxQQ19fOXdSeXF5cXpPN3NYRWxqMEJ0aFNGcWl4OTJfSU9mSnNxRXRXZHFxY3ZfaHJrNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNSk5QTTg0RVJHQ3Y3Y2h4d01nRW1QMF9iRGlZRnZkazR2LWszX0VkMHk1YlY0TkQ3bzNEX2pkazNROUZ1cTRNbWtXQ3FLbWZaV0xURTYwci1FTV9NaFF5RFY5WXRYY3kxeWRzTHlwZzRBZUNKMmI3bTBtV3dYblVGLUl0cmx6VnRweUxYT1Uxekk0SUk0eTZV?oc=5</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -826,32 +826,32 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>World Tax Rankings Middle East 2027 released: challenger firms surge in UAE - International Tax Review</t>
+          <t>Prefortune Technologies Announces Odoo UAE Peppol E-Invoicing - openPR.com</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>News — Big 4 UAE Tax Commentary</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQUWp5dVloOUQ4anZfTkR4NnJUYkZYdk1ZU2xDb1h6ZE5Wb3pzRzVxQklBNi1tTC1KWndLRlhpdVBaQmJzZ0FaRFVsNUQ3VXFDOWlRSGRMY3FHM0djMk9TRVQweThXS0lsSmxGN0xOT3V4ckZVNjRuTzVMOGJBSjN0Q1lwOTEtSXBwcm9zTTZUc1MxbVRpd2tRMlFjTE41b0EwTFRxSUg0TjlDTm93RU9WUDJFYm9sS3UtVm5XdWhmTVhndTF1dDdNZHUtWDB6Y2RpeFd5bnk3UzV4VHdwckNra1BoRWk3OVQxMjM5TWFaVkRlSjQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQVG9nYjRRdy1xYVZ3cEU4ajVEd3dpaXJYNWNpWFB5eG5Ia054ejBUa0VkNVMwb1I4TUVQdkl3STFTcG9fMS1ObVRHTV91eng2SHBiVGtIZGRZVlRVOHAyVDVoLUJONTlDRDkyaTRocno5M0lwcVBfS283N1lEY0t5eWd0Rld6MzkybWktZEtqWXlaN0w4c2xzbzFzT1NiQQ?oc=5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -871,32 +871,32 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Cross-border Tax Talks - PwC</t>
+          <t>From readiness to implementation: 7 steps UAE SMEs should take for e-invoicing - Khaleej Times</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>News — Big 4 UAE Tax Commentary</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNajMxUTZjZ2tOVUFvYThvdWY2RmE1UmFoV05XbTR1ak5FUXB5Z3FRV2RKdGtuVzZhR1Jva1lKQU5IUmVDMlo1dzNSQlc4TExYbkRudlZQT1haTXZWOGNmXzFPTF90c0luOFNrbWZxa0t5VElhM3NOY21CaS11UmFfVFdtVlRON1hRYjlDY2UxMFR2YVhBQno5Mk05NmJFel9DQXl2RXNsZWxhTTZxMmtycHJtNkdDWjNxX3Y2QU1TWTV5MEFTZFhJQw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQUkNGMUtUUW55SjEwUnhUYjBycXVyOW9SS1Z0RGFVcTl3VWVMWlMxQ3E3WV95MWt4RUdoOHRQTmxDLXV4Yk1qMjdWUnJxSUNxVURUTWxrd2pWdDBBREZRZGNEVTZvSlB2Z0FuOFZFbGdKX05tT0tFeGx0SHVRQVdWaGE4UU1kdlhVYkZFQzF0R1lFOC0tNTBQTXBybUVLVFNHVEZyMnFwa1RVRUVUakExY0o5Wm80b2RJbFIxNW5TclZpNm1Hanh2RTJOdkF6d9IB1gFBVV95cUxOdTA0Q0pDMnBiTFpZbkcxRnFwZXg3OXdmU0ZQdzBQNEd5ODNtb1VyWndTM3NhMkpQRTJqVVRldEdubm45X1RxTTFGTHl3MWFmZENMZXlxXzRJTXBEOTQ1SENNUkZ5Sk5DZU1OUEljVjFVNWF1NTBwOHNJZE92UFQxZ3hPSEtObXJMcVFieGVBejZneGdiTzJfLURXQXIyM1FwbnJibGFMUG84RkFJZGVPbjZEanhkWTlFT0ljR1MyYnRyYmZKMkMtVGs5VzJOZTlXTm5YcTJB?oc=5</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -916,14 +916,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Other</t>
@@ -936,12 +936,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Federal Tax Authority issues new guide on scope and registration for Top-Up Tax on multinational enterprises - برق الإمارات</t>
+          <t>DP World appoints two independent directors to board - Gulf Business</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>News — FTA Announcements</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQaFhsTDBvVWFWcHJNaWQxdFZoWnpxN0ExT0EtNENrZng3TTh4UFVleDhwOFd3Q05OY09UaXUxNS12YXljOUd3WXl6MWVUdlY5RXhWc3pEYVhBRDZPbjNhX2U4VjJLcUtncVFwMnBZUE55M1ZLLWxhMzFZQnNRYTFleGo3SDhFYWpmYTJ4dWg2dTEyNUkyT3JVQVZVa0JtcU5hdUNKZE52N25XdlNLckRWMThRQTRwQm5ZenFYUEFFYXVBeWhxMTlfNWFieFViR2FpSE84ZDVJcVR5VHhqbGVz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPX2QzdVpCMHdjWXN5M0ZHNEVvVEhGdFd1aEFHNnk1dXZ2ZWRKUHJLVG1pQ0hoTjVaRExrcXpyY2hTbkxFc3Z4aHgtMHB5ZHlValh4dGhNTjdvcnZzdzVDV3pKbUo2TW5HMGExa0hDcUZoSzctUUI5WDhIckx4N2tMVFo2WHpWUVp0NDIxQnNvV1hOX2NiTWZpdVJtelVFYW8?oc=5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -961,17 +961,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>APR, Korea's leading beauty company, showed an 11.8 billion won increase in operating profit in the - 매일경제</t>
+          <t>FTA calls for compliance with e-Invoicing deadlines to avoid penalties - www.wam.ae</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>News — IFRS Standards</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTFBtVnRiOXljUWlKOUtMcC0tQjNycVJxaGJMUTBPZXFwYkFPeHM1Q1R4eXhmNzZGMzhnbVFrNFNZSFAtMjRiYVB2TzNRVXJ2dW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPUDNQWVptSk1uTm9rVFI3ZVYwV3dRMVdXSmJxZVkxZlhBd2FEa1ZaNlJsQzcwaU9tcFNjbTJEWEs5UGJTNzhoWVEyeF90a1ZPcmVJM2RLUDJ3VHRMVU9qZ1ZBbEhPVTNDaklkSkNyVllwVEZ3UTE1N3ExZWNZZWhzQ2p0MkoyQQ?oc=5</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1006,17 +1006,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Ind AS 118: Big Changes to Financial Reporting Soon - TradingView</t>
+          <t>UAE e-invoicing deadline: Businesses have until October 30 to meet first requirement - Gulf News</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>News — IFRS Standards</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPa3pEaDB3Q21YU3FhSFQ0ekVZc1pwT00zQXFTbGE1MXkzX3NjazJ5TGZXelg4WnZocTlUZzVDMWp1aFlzNk4yMHIwMGR2d3dBUldzem5pY2xtLUVZckJJa1Rfc0c4MnJxX0YxckZIZWNNY09LVnh5RFVGMko0VEdrSXh2ZWlTdjdsQVlHTWotcGs2X0w0ZVRPbmNyVDdEc085SVNsYjJCR1NkR3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQVlFDSEtCd1I4TTB1M2NIQlBtSUtHWEJGelF2aTctaVpIQzRtcTRDWkt5dkFwRFA3ZHVZc1N0RWF6UzYzMzd2TUJQdXZ3MGpFaE9IOUtrenFhLThTNjByTlpnQ0laeHJXMVpJZ25fcmxGUmRmb0ViRW1DRFJmV3M2elhTWllZM3M4TzNXS01SQjVldDVvTnFDbkdjaVlCcGV2VHAzSnFfS29ldVNRUVJEUU9iTnRqS1ZlemJZNEhhY3RvakY1RGNjd2VpR0R0Z9IB4AFBVV95cUxNSUF6V3NtcTJFd0tRQ1FQbTlxbmdwLXVCd3hlcE05amFITks4Z2RaT0I5Znp2UUN3UjNpbWlKVWNXQ2YydkpjUVBQaHdqZVFQM2tpM0xYWlV5bU1tN3QxbnpwRDhUVmliNmU3dnJ4Uk56ejRuaG1NSWNrRnZFc0gtYTJubVdSaUIxX2Q5TmRmWEZIMkFwTDc0UFpJSWo3TVhtTnBZRzl1RExGTWU5N2l3Y1FmRmd2RU9JUU9WY1dvaWZQdlZQWUpYbC1pY2VFemRJbUVPQ2tWb2cxenVHTFpRSw?oc=5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1051,12 +1051,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>UAE Publishes Monthly Fine for Businesses that Miss e-Invoicing Deadline - Legit News</t>
+          <t>MIDDLE EAST TAX ALERT | UAE | e-Invoicing Guidelines Version 2.0 - Alvarez &amp; Marsal</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOcmtkbU5IdUxaZFVXUXVJWno3dERSaEJ2X0xKbGlCSi1rVUt1TDNNQUdiTkcwdEN6YlR6Y1FpeU10WWY2aGhWQ3gycGFOcGRQTUdUbE5BTWxfOGtHcXRRejN6WWktN2FmbjZTTmpsUENidjNEaTktTkVSbVQxRDNBZHNoM3ltLVVjTnUtWC1MdTBXX0EtWWM4NnJwQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPeGtIWGRjTmV2SWU5UkpsektaSno5VVpYVGlpcmdUYW0zNW9lalJfeGk4Y0dacFNQaWZ1dWFpRkVmYTh2SWF5c3ExTW50eUxuNXRLblhLcl9xRWx4aWlYRm14eEFIMTM3UHJ5XzBZNktjRHFuNWFXbEVwWWhGdkhyTDNLbVJscWdXemU3RlhrcncyMHkzckRyV0wxdGRQY254Z1NXUHNfV1JhSkZ2b005WjVR?oc=5</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1101,27 +1101,27 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Dh5,000 fine a month: UAE firms have 5 days to appoint e-invoicing provider - Khaleej Times</t>
+          <t>Cyprus tax alerts - Deloitte</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — Big 4 UAE Tax Commentary</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNTGtGYXoyUURCNlQzTzZldFhpUGJIb25mYjVQOXdsNXdDNVRQV1dZVW9EdFJ2aVNsRnQ4c1JsYjgzcWszU2JlbGNYa2p5SUl2UVptQnYyZ0hnQk9KM3BBS0VxNmY2d043bWEzb0ZPM3M1bks5RDFSQjlhNnNYMDRVMmU0SWFCQmZCU18wOWc4bG5yeVNIOE5Fazl4UU9sMjkxclROLVFvQ1l0ckFRaWhMRNIBuAFBVV95cUxNQjIyZmFMNm13T2dZMUpyOVplTWlrVTBEX3N2TS1iaGVQV2hSNFZXbkI4VW1DdDQ2ckcxSEtmRjA3YTA1Unc0dHY4WTBVRGNiRnlCN1RsRzFwQXl2bTJaaFhaYmptVDlQc0lkQ1RvNzViOW9nTGlxZUhnN21WcDBteXlHVm9mdXBqSXcyajhFdmYtZWt1MGlmamQwOEJkTUp6VDZsRkh5YnEyVjVGOHlmenRrb1psT1Vv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPR3dMcm02YVpKS2NHZC1YZlJaV2VXZHJMYjNzVzRNa0NfSDNXaFhJcUNseDFYaUVRNVNpdmd5Rm1jbE04d2psTWRBMjZrOUxQQ19fOXdSeXF5cXpPN3NYRWxqMEJ0aFNGcWl4OTJfSU9mSnNxRXRXZHFxY3ZfaHJrNA?oc=5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1146,27 +1146,27 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>UAE FTA urges e-Invoicing compliance as AED5,000 monthly penalty applies - Emirates 24|7</t>
+          <t>World Tax Rankings Middle East 2027 released: challenger firms surge in UAE - International Tax Review</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — Big 4 UAE Tax Commentary</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQNFV2ZnJIZjdaTm1YS1RtRVN5UzZCZXNZcE9WOWlBV2U4d1BtQUg1SUNhcWJxWWRBRmZLVDl1SGNCbjhTdW1rRGFJUzhlX1dvQ2NkeldjNmdyNHNFLXAydHpUVG4yXzREQk1EN3l0cWpJZlo2RVBLQW5RZEFVMlQ5bXJ4eTBvSS1SVEtxd3RYUnppOUctcktBbTl3T2lOenVFcy1nN0VpaHk3QnQtZldlYzlIS3QxeTJCcDhwMW9xclRRVEtWNVZfZFdveF93UdIBzgFBVV95cUxQNFV2ZnJIZjdaTm1YS1RtRVN5UzZCZXNZcE9WOWlBV2U4d1BtQUg1SUNhcWJxWWRBRmZLVDl1SGNCbjhTdW1rRGFJUzhlX1dvQ2NkeldjNmdyNHNFLXAydHpUVG4yXzREQk1EN3l0cWpJZlo2RVBLQW5RZEFVMlQ5bXJ4eTBvSS1SVEtxd3RYUnppOUctcktBbTl3T2lOenVFcy1nN0VpaHk3QnQtZldlYzlIS3QxeTJCcDhwMW9xclRRVEtWNVZfZFdveF93UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQUWp5dVloOUQ4anZfTkR4NnJUYkZYdk1ZU2xDb1h6ZE5Wb3pzRzVxQklBNi1tTC1KWndLRlhpdVBaQmJzZ0FaRFVsNUQ3VXFDOWlRSGRMY3FHM0djMk9TRVQweThXS0lsSmxGN0xOT3V4ckZVNjRuTzVMOGJBSjN0Q1lwOTEtSXBwcm9zTTZUc1MxbVRpd2tRMlFjTE41b0EwTFRxSUg0TjlDTm93RU9WUDJFYm9sS3UtVm5XdWhmTVhndTF1dDdNZHUtWDB6Y2RpeFd5bnk3UzV4VHdwckNra1BoRWk3OVQxMjM5TWFaVkRlSjQ?oc=5</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1191,27 +1191,27 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>DigiTax partners with Supy to help UAE restaurants adopt e-invoicing - Caterer Middle East</t>
+          <t>Cross-border Tax Talks - PwC</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — Big 4 UAE Tax Commentary</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQOU1EY2p6d1B0WW9WUFljUmF4dzdCVnVMNE50QjZ0QkJDeUFNYy1DLWl5bU5hdVphdmtOMmNuenVqVHNacTRTeFZqbUFvS3VFOGMzUlZ6VFFsZnJ4V0MxWGZLWkJiT295aWxaaUFjeS14LWlDeE5UYWliQW9nMFRBVWZkUEdHMlp1NWNTN3NadG9LNUwzck5Ja1F3LUlrN2Q3V2RZcEhKY05vejA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNajMxUTZjZ2tOVUFvYThvdWY2RmE1UmFoV05XbTR1ak5FUXB5Z3FRV2RKdGtuVzZhR1Jva1lKQU5IUmVDMlo1dzNSQlc4TExYbkRudlZQT1haTXZWOGNmXzFPTF90c0luOFNrbWZxa0t5VElhM3NOY21CaS11UmFfVFdtVlRON1hRYjlDY2UxMFR2YVhBQno5Mk05NmJFel9DQXl2RXNsZWxhTTZxMmtycHJtNkdDWjNxX3Y2QU1TWTV5MEFTZFhJQw?oc=5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,12 +1251,12 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>UAE e-invoicing: Oct 30 provider deadline looms for firms with Dhs50m+ revenue - Gulf Business</t>
+          <t>Federal Tax Authority issues new guide on scope and registration for Top-Up Tax on multinational enterprises - برق الإمارات</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — FTA Announcements</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNd1M0bzNJcTEybmx2M29pY01HRWxvUURNZmxjemd1WDByOGUzSDVmUW4xUnljZnRlQXZBYW1FdW5ubnd0N01wWTVpNjRDR2xzY0lWcGlDd2ZhLV9BNjZsOTJBME5jbTVoUkJUWjdYbVZjaGhoUktjWUYzNkdvRDNyMldoQXN0V3R2WGFOT0wwbkpSX1ZnTVE1YV8xdklwMlROQ2xiR01EU0xaNUlCYXV1TWFYT1FYUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQaFhsTDBvVWFWcHJNaWQxdFZoWnpxN0ExT0EtNENrZng3TTh4UFVleDhwOFd3Q05OY09UaXUxNS12YXljOUd3WXl6MWVUdlY5RXhWc3pEYVhBRDZPbjNhX2U4VjJLcUtncVFwMnBZUE55M1ZLLWxhMzFZQnNRYTFleGo3SDhFYWpmYTJ4dWg2dTEyNUkyT3JVQVZVa0JtcU5hdUNKZE52N25XdlNLckRWMThRQTRwQm5ZenFYUEFFYXVBeWhxMTlfNWFieFViR2FpSE84ZDVJcVR5VHhqbGVz?oc=5</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>UAE e-invoicing rules: Key deadlines for businesses in 2026 and 2027 - Arabian Business</t>
+          <t>APR, Korea's leading beauty company, showed an 11.8 billion won increase in operating profit in the - 매일경제</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — IFRS Standards</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPMXU4Vm5ScFJWd2tINmI3WEI1X1pwRFU0R2NyYXFra1d1bXFFTWhiVExCdS16SVRNelZOSlB5SG5GaHZTZzhzendZZHV4aDc4WHMyZ2kzcTEwekZDNG0yenlUaWwzUEs4blp6bHlPYXRZMFZLQzZRbG5idHB0a3F0Sw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTFBtVnRiOXljUWlKOUtMcC0tQjNycVJxaGJMUTBPZXFwYkFPeHM1Q1R4eXhmNzZGMzhnbVFrNFNZSFAtMjRiYVB2TzNRVXJ2dW8?oc=5</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1341,12 +1341,12 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>How tourists can claim UAE VAT refunds in one business day - Travels Dubai</t>
+          <t>Ind AS 118: Big Changes to Financial Reporting Soon - TradingView</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — IFRS Standards</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQUWpQaFlPcE8tQ3ZpWVhKZHBmTGlzVWRtcmdXOWdxcDlGcjZnSWsxa193SXhyQ3duMFphOGt5a1lFRFhveGRpVmlUQ1I4cjhmQTN1aXh5Nks1anFfV0Zua0JBaG44T1lNTWZlRGhtWFRJZkRVV2F3MGJ0RnloVDMtQWlnZGdrQTRBUEVnQUEwYkU0dlhoT2Fn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPa3pEaDB3Q21YU3FhSFQ0ekVZc1pwT00zQXFTbGE1MXkzX3NjazJ5TGZXelg4WnZocTlUZzVDMWp1aFlzNk4yMHIwMGR2d3dBUldzem5pY2xtLUVZckJJa1Rfc0c4MnJxX0YxckZIZWNNY09LVnh5RFVGMko0VEdrSXh2ZWlTdjdsQVlHTWotcGs2X0w0ZVRPbmNyVDdEc085SVNsYjJCR1NkR3M?oc=5</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>"Smarter and simpler": UAE speeds up VAT refunds for tourists shopping in Dubai - Tuko News</t>
+          <t>UAE Publishes Monthly Fine for Businesses that Miss e-Invoicing Deadline - Legit News</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOR0ZWZkx0b2hxUzJfSlEwNEl4YWlSOEVreHVFZmEwMWxia2xYX1BxNThjczJ4bEk3S1lkRy1ZREZTV1FXNDZ2N29tcUxYVWxIZ3lZWkl4VHgtdUZ0QXYwcmFwMlVId19pX0lxWFpMT1hVVkxDZHIxR1NYemlyZ3Y2dG9Iczg3Q0tVcEtfVDlTVm9IQkxwMlQ1eEpRaUdBQmx5R0xQNXZ4QnotSHpYWnZYTlJYX3o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOcmtkbU5IdUxaZFVXUXVJWno3dERSaEJ2X0xKbGlCSi1rVUt1TDNNQUdiTkcwdEN6YlR6Y1FpeU10WWY2aGhWQ3gycGFOcGRQTUdUbE5BTWxfOGtHcXRRejN6WWktN2FmbjZTTmpsUENidjNEaTktTkVSbVQxRDNBZHNoM3ltLVVjTnUtWC1MdTBXX0EtWWM4NnJwQQ?oc=5</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>UAE launches paperless, AI-powered VAT refund app for tourists - Khaleej Times</t>
+          <t>Dh5,000 fine a month: UAE firms have 5 days to appoint e-invoicing provider - Khaleej Times</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNZWdmNWZuVEo5Uk9mUEQybHRrODZ4M1plWloxXy0wWDRtMlp0WDdlVzkzOEgzMHNxdm1kSXJZcWZSVklxX0pKV3dHSnhMOEs3aXFZYzUwSXdxa2JFcXphbnhmVG10cHJURUFaVkw0dHk5RHF3b0o0QklQQ1ZoNVE3UXRMNnhsbTJyUDdRbDBKTmlhVFdTSUVEN2RXc9IBowFBVV95cUxNbmFfQTNJbmpFSVhLcndEbHQxcGVqcnhzSEVnenJod09jelNLSHVSLVE4dVdtTHlHOFMtcmRjTVVnd2p5cU0ycEFEbWdHbVVoVWdGbVRvRUh5WGpGT0xQVWRaUklXdloySmd2QWRYNlV5UFlPYWhnRF9KM2tsWl9wek9RQ1ZuVVRWaXJkb3F4cHVCMkhfMDFOU0NGNTQtOFV4MGhv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNTGtGYXoyUURCNlQzTzZldFhpUGJIb25mYjVQOXdsNXdDNVRQV1dZVW9EdFJ2aVNsRnQ4c1JsYjgzcWszU2JlbGNYa2p5SUl2UVptQnYyZ0hnQk9KM3BBS0VxNmY2d043bWEzb0ZPM3M1bks5RDFSQjlhNnNYMDRVMmU0SWFCQmZCU18wOWc4bG5yeVNIOE5Fazl4UU9sMjkxclROLVFvQ1l0ckFRaWhMRNIBuAFBVV95cUxNQjIyZmFMNm13T2dZMUpyOVplTWlrVTBEX3N2TS1iaGVQV2hSNFZXbkI4VW1DdDQ2ckcxSEtmRjA3YTA1Unc0dHY4WTBVRGNiRnlCN1RsRzFwQXl2bTJaaFhaYmptVDlQc0lkQ1RvNzViOW9nTGlxZUhnN21WcDBteXlHVm9mdXBqSXcyajhFdmYtZWt1MGlmamQwOEJkTUp6VDZsRkh5YnEyVjVGOHlmenRrb1psT1Vv?oc=5</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>UAE Launches AI-Powered Tax Refund App For Tourists At Three Major Airports - Travel and Leisure Asia</t>
+          <t>UAE FTA urges e-Invoicing compliance as AED5,000 monthly penalty applies - Emirates 24|7</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNeXpZdm5uSHczcUh4UGJ1LU1kWUpJaVBKTFVrcVBBWlVrSlI4aWJzbGRTWHp0bkVQNWlMQ3dWUU44LUpqOTloZjZoN1JEeWwwSHg2YXk3Wm5xOEJTNklQb05UZHBUeUdETWxWWHlvT0dtVEVwODNwZWpFN1RPRzVkWFlYWk9BNExmU0pibXlJY1FFalQzbXVrUk9IMGZ1clhCSEdrTU55YkZ3dXBob2VzcXBsbC1qTm9OQS05d0ZTOWFySjjSAcMBQVVfeXFMTXl6WXZubkh3M3FIeFBidS1NZFlKSWlQSkxVa3FQQVpVa0pSOGlic2xkU1h6dG5FUDVpTEN3VlFOOC1Kajk5aGY2aDdSRHlsMEh4NmF5N1pucThCUzZJUG9OVGRwVHlHRE1sVlh5b09HbVRFcDgzcGVqRTdUT0c1ZFhZWFpPQTRMZlNKYm15SWNRRWpUM211a1JPSDBmdXJYQkhHa01OeWJGd3VwaG9lc3FwbGwtak5vTkEtOXdGUzlhcko4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQNFV2ZnJIZjdaTm1YS1RtRVN5UzZCZXNZcE9WOWlBV2U4d1BtQUg1SUNhcWJxWWRBRmZLVDl1SGNCbjhTdW1rRGFJUzhlX1dvQ2NkeldjNmdyNHNFLXAydHpUVG4yXzREQk1EN3l0cWpJZlo2RVBLQW5RZEFVMlQ5bXJ4eTBvSS1SVEtxd3RYUnppOUctcktBbTl3T2lOenVFcy1nN0VpaHk3QnQtZldlYzlIS3QxeTJCcDhwMW9xclRRVEtWNVZfZFdveF93UdIBzgFBVV95cUxQNFV2ZnJIZjdaTm1YS1RtRVN5UzZCZXNZcE9WOWlBV2U4d1BtQUg1SUNhcWJxWWRBRmZLVDl1SGNCbjhTdW1rRGFJUzhlX1dvQ2NkeldjNmdyNHNFLXAydHpUVG4yXzREQk1EN3l0cWpJZlo2RVBLQW5RZEFVMlQ5bXJ4eTBvSS1SVEtxd3RYUnppOUctcktBbTl3T2lOenVFcy1nN0VpaHk3QnQtZldlYzlIS3QxeTJCcDhwMW9xclRRVEtWNVZfZFdveF93UQ?oc=5</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1521,12 +1521,12 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>UAE: Claiming VAT Refunds For Tourists Just Got Simpler With New AI-Powered Digital Platform! - Curly Tales</t>
+          <t>DigiTax partners with Supy to help UAE restaurants adopt e-invoicing - Caterer Middle East</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxORDJuVlViQjVHZ3JEMUxXV2NqVjBhbXVSWk1WWm1CMUVqU0RLX0JMNjctNnE1Q1FmSEhVZnNUcFFrLVBGQjJSWHF6UDJlVTJObFNhcDFRcnh3WFZMTEVycjZ3S2NEZnpqT180dFpHZ0VCeXgzdVd5QW5Yd0w3QUdHOXI5WE9NUzFPYlVYY0RTZ3NhU2kzWWRramVROTRQdmsxNk1zblRXY1ZOTVVnQlFicXNFTnRsWlYwWnBNd2Y3WV9EbFJlYi1UN2Z1dzlpSnfSAdQBQVVfeXFMTVJyVkVYR05PQldudW1QSzJsS0V5aW0yZVNyRmQ1YmhBaDhMVmtoNTJfSnZTdUV0amhlQ2lTa1pxbnpWRTA5aG9DaDhEdExWTDRrVmszb1gyTkNLY1RUMThXNEM2eXhKa2ZmUDNxbGM1YlVLQXl6c0MyaW5KQ2tQMGxMQ0dmM25iN3U3MUZKazN3X0lNeU83ZXJwTkE5REViLVZJZzJqcGVaLTJXWV9nWE9EVmJqSVJHV05XaXMtTkRjbTkzZml3bkNTdjFnYWVjU1E4SzY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQOU1EY2p6d1B0WW9WUFljUmF4dzdCVnVMNE50QjZ0QkJDeUFNYy1DLWl5bU5hdVphdmtOMmNuenVqVHNacTRTeFZqbUFvS3VFOGMzUlZ6VFFsZnJ4V0MxWGZLWkJiT295aWxaaUFjeS14LWlDeE5UYWliQW9nMFRBVWZkUEdHMlp1NWNTN3NadG9LNUwzck5Ja1F3LUlrN2Q3V2RZcEhKY05vejA?oc=5</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>UAE Launches AI-Powered Tourist VAT Refund Platform Across Three Airports - Konsulteer</t>
+          <t>UAE e-invoicing: Oct 30 provider deadline looms for firms with Dhs50m+ revenue - Gulf Business</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOaTNXUlc5Yk5IdGN4RF9PeDN3Nkc3WnducVRwSEczbFlhb2dLXzlKNWFsdEh4VlQxZTRNRl9VQjhYZDgwWU51dmRjZVhYUFR1WFBKcWltSTZwcEp5N3ZYVkNRNWZVaTU3UXNBZzZqTVFrN2pMci1jZGhRemRGSnVRLTZsNW1Rc05Ic3NGd21nLU85VVJFLVR5MzZrOWI4Mkc2anZqb042c0xqUGc3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNd1M0bzNJcTEybmx2M29pY01HRWxvUURNZmxjemd1WDByOGUzSDVmUW4xUnljZnRlQXZBYW1FdW5ubnd0N01wWTVpNjRDR2xzY0lWcGlDd2ZhLV9BNjZsOTJBME5jbTVoUkJUWjdYbVZjaGhoUktjWUYzNkdvRDNyMldoQXN0V3R2WGFOT0wwbkpSX1ZnTVE1YV8xdklwMlROQ2xiR01EU0xaNUlCYXV1TWFYT1FYUQ?oc=5</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>UAE cuts tourist VAT refund time to one business day with new AI platform - Gulf Business</t>
+          <t>UAE e-invoicing rules: Key deadlines for businesses in 2026 and 2027 - Arabian Business</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPZURXSjRhbWwwMzRkaWYyWlJSWkpSUl9nYllHVFJ0RnpDTHR4dGZJY2tlZzVGbEJuYWRjeFlXSm9fMDhDWTJwS2ViMTd2M1dKc2I1aUZmMTVGclB1eUhnRGV4SnlRZzJRWHhGYW80SFM0cWpCTjR5T29PMUNfU2l6MUN2RWlmdXVKTE5fVHkwNDZxVzdJSmdiUngtTlRzZHRqNHpNTkVSYy1Bb0JN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPMXU4Vm5ScFJWd2tINmI3WEI1X1pwRFU0R2NyYXFra1d1bXFFTWhiVExCdS16SVRNelZOSlB5SG5GaHZTZzhzendZZHV4aDc4WHMyZ2kzcTEwekZDNG0yenlUaWwzUEs4blp6bHlPYXRZMFZLQzZRbG5idHB0a3F0Sw?oc=5</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Federal Tax Authority launches world’s first-of-its-kind AI-powered digital platform for tourist tax refunds - Zawya</t>
+          <t>How tourists can claim UAE VAT refunds in one business day - Travels Dubai</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxQV0NXYW5reU5Sb1FHRmNDT3dyaXphV2ZORlVZYXNhN1ZQV1FldnhlZGF4VTJpVVJ6c0k4MGRqZE13Rm95S0ZWWkpVQUdlNFpTdDA2cks5akhhZmNZNlFuVU8wVkVJMFhiRUVjNTg5d1dzb2htY05tM0xIb0RhS0dhZ1RaQzZrQ2Z6ZzJJTnlZd19vOTJsU09pamc1TWFqaGFiUFM3Z1JNSGlac0lFeDRrcFpIYWxLN3ZlVjdtc2drS01FRTl1eTdCM3FZdFd1ZU1jODNWYkZ2WHZzZk5USlNVcnlsTXRrcnhaUi1fbUhXWnR6U0FUc3lydXJwNDIyWWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQUWpQaFlPcE8tQ3ZpWVhKZHBmTGlzVWRtcmdXOWdxcDlGcjZnSWsxa193SXhyQ3duMFphOGt5a1lFRFhveGRpVmlUQ1I4cjhmQTN1aXh5Nks1anFfV0Zua0JBaG44T1lNTWZlRGhtWFRJZkRVV2F3MGJ0RnloVDMtQWlnZGdrQTRBUEVnQUEwYkU0dlhoT2Fn?oc=5</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1686,12 +1686,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>UAE Publishes Version 2.0 of E-Invoicing Guidelines - sharedserviceslink</t>
+          <t>"Smarter and simpler": UAE speeds up VAT refunds for tourists shopping in Dubai - Tuko News</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPV1NkTHUycS0tOFh6TF9HVW4yU051Zk1zTExPWTVONTcxemN0WTVBajl3QkxVY3Bocno5N1BVbDFkUlZjQ214VEZQc1Y0eURfMHZzdTNyV0RuRmU0OXA4dU9MMTZhN19POUdvMXJRSld6UDZkbU9YbWNkaTVzeW9DNDNwX25zRGFKMGgwQlBfR3JzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOR0ZWZkx0b2hxUzJfSlEwNEl4YWlSOEVreHVFZmEwMWxia2xYX1BxNThjczJ4bEk3S1lkRy1ZREZTV1FXNDZ2N29tcUxYVWxIZ3lZWkl4VHgtdUZ0QXYwcmFwMlVId19pX0lxWFpMT1hVVkxDZHIxR1NYemlyZ3Y2dG9Iczg3Q0tVcEtfVDlTVm9IQkxwMlQ1eEpRaUdBQmx5R0xQNXZ4QnotSHpYWnZYTlJYX3o?oc=5</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>UAE's new AI platform to slash VAT refund time for tourists to one day - The National</t>
+          <t>UAE launches paperless, AI-powered VAT refund app for tourists - Khaleej Times</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQZVpMLWZ4cmVQdDlnSlZRRERKN0tJbVR5eGVfblhRam5IUGwtXzdIaWJqeWlSNEVNVGozWGpvMm5LSGQ0YXdlVl92YjRPNHhtZDFIQ2swNlRtdzRQeUtTVmE1d1ZfVF9vdXR3N1RvV3ZoLXlZdWFyTENheUtIa0lOTjZTcjUza3VWVmFLaXpEVm1kTkpVandrTE80a0dadG9IMlJsWUhyZHU4U0tMS3I0cVQ0RVM1aTUzWGF4U2pvQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNZWdmNWZuVEo5Uk9mUEQybHRrODZ4M1plWloxXy0wWDRtMlp0WDdlVzkzOEgzMHNxdm1kSXJZcWZSVklxX0pKV3dHSnhMOEs3aXFZYzUwSXdxa2JFcXphbnhmVG10cHJURUFaVkw0dHk5RHF3b0o0QklQQ1ZoNVE3UXRMNnhsbTJyUDdRbDBKTmlhVFdTSUVEN2RXc9IBowFBVV95cUxNbmFfQTNJbmpFSVhLcndEbHQxcGVqcnhzSEVnenJod09jelNLSHVSLVE4dVdtTHlHOFMtcmRjTVVnd2p5cU0ycEFEbWdHbVVoVWdGbVRvRUh5WGpGT0xQVWRaUklXdloySmd2QWRYNlV5UFlPYWhnRF9KM2tsWl9wek9RQ1ZuVVRWaXJkb3F4cHVCMkhfMDFOU0NGNTQtOFV4MGhv?oc=5</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -1776,12 +1776,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>UAE announces major tax refund upgrade: Tourist VAT rules explained - Arabian Business</t>
+          <t>UAE Launches AI-Powered Tax Refund App For Tourists At Three Major Airports - Travel and Leisure Asia</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOOV9mdmlpRVVsSTdjRnA2bV9OSGUtNGlvNmgzTWVjSGJiZFkyYmpBQ1h1UE4zY2VGN3FFQ1M3N09ZQm4zc1lTNl8ybDNKTll4c1FweWZlNFBLMFI3aFRfSzAtaHJzVmxSajI4amM1OFBMRUlnWnBfbWZ2a0s1azBieWtybl9VRmVrRmd0VVI4T0tzNWZZbWdCNE5NR3BxZVR0TW1EZ3VCTlBHZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNeXpZdm5uSHczcUh4UGJ1LU1kWUpJaVBKTFVrcVBBWlVrSlI4aWJzbGRTWHp0bkVQNWlMQ3dWUU44LUpqOTloZjZoN1JEeWwwSHg2YXk3Wm5xOEJTNklQb05UZHBUeUdETWxWWHlvT0dtVEVwODNwZWpFN1RPRzVkWFlYWk9BNExmU0pibXlJY1FFalQzbXVrUk9IMGZ1clhCSEdrTU55YkZ3dXBob2VzcXBsbC1qTm9OQS05d0ZTOWFySjjSAcMBQVVfeXFMTXl6WXZubkh3M3FIeFBidS1NZFlKSWlQSkxVa3FQQVpVa0pSOGlic2xkU1h6dG5FUDVpTEN3VlFOOC1Kajk5aGY2aDdSRHlsMEh4NmF5N1pucThCUzZJUG9OVGRwVHlHRE1sVlh5b09HbVRFcDgzcGVqRTdUT0c1ZFhZWFpPQTRMZlNKYm15SWNRRWpUM211a1JPSDBmdXJYQkhHa01OeWJGd3VwaG9lc3FwbGwtak5vTkEtOXdGUzlhcko4?oc=5</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>UAE launches AI platform to cut tourist VAT refunds to one business day — The National - UA.NEWS</t>
+          <t>UAE: Claiming VAT Refunds For Tourists Just Got Simpler With New AI-Powered Digital Platform! - Curly Tales</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQYXdJZkJvX3ByM0lXS2ZtYjlHR0poREtsemlTaHdPWGExcVBhQzdNR3kyWmJMNHJsTnVYemRldHg2aG1jdlNidk5sV1JjcldzRF85dzh6ckpHeHdWVHp0SVdzeFZGNFlzdW04Q1dockJ1ajU2bnRFcmdwLUZfbE9iVm0tRE9jQklXM1Qzc2ppV2lDM19vUGUxLU9uc1ZJNm9TcTNlYnFnTzh2RVZyZUFEM0VVdHZWRFNKQmJsX1ZtQlc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxORDJuVlViQjVHZ3JEMUxXV2NqVjBhbXVSWk1WWm1CMUVqU0RLX0JMNjctNnE1Q1FmSEhVZnNUcFFrLVBGQjJSWHF6UDJlVTJObFNhcDFRcnh3WFZMTEVycjZ3S2NEZnpqT180dFpHZ0VCeXgzdVd5QW5Yd0w3QUdHOXI5WE9NUzFPYlVYY0RTZ3NhU2kzWWRramVROTRQdmsxNk1zblRXY1ZOTVVnQlFicXNFTnRsWlYwWnBNd2Y3WV9EbFJlYi1UN2Z1dzlpSnfSAdQBQVVfeXFMTVJyVkVYR05PQldudW1QSzJsS0V5aW0yZVNyRmQ1YmhBaDhMVmtoNTJfSnZTdUV0amhlQ2lTa1pxbnpWRTA5aG9DaDhEdExWTDRrVmszb1gyTkNLY1RUMThXNEM2eXhKa2ZmUDNxbGM1YlVLQXl6c0MyaW5KQ2tQMGxMQ0dmM25iN3U3MUZKazN3X0lNeU83ZXJwTkE5REViLVZJZzJqcGVaLTJXWV9nWE9EVmJqSVJHV05XaXMtTkRjbTkzZml3bkNTdjFnYWVjU1E4SzY?oc=5</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>UAE Federal Tax Authority Launches Digital VAT Refund Platform for Tourists - News and Statistics - IndexBox</t>
+          <t>UAE Launches AI-Powered Tourist VAT Refund Platform Across Three Airports - Konsulteer</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOSm9HaWZSWEFFM3BNOW5acHZBT0luQWFnVEo3QUpJR1AwdUNMVjE0V3RXUXptLVVZR1VBN3doSnZlU1RNcU40UmJNVWpfQnVpY3NNRGRqNTM3WVFNRnB5X0g3SXFfbkl0Rk91MEtTWVBRejJDOElIcmxLSG1TcnNaRWdVbUdoS0QtMGVRX0NzSjJOSVJyV1luRVZsRW9ldl80c2VfUkNiempDdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOaTNXUlc5Yk5IdGN4RF9PeDN3Nkc3WnducVRwSEczbFlhb2dLXzlKNWFsdEh4VlQxZTRNRl9VQjhYZDgwWU51dmRjZVhYUFR1WFBKcWltSTZwcEp5N3ZYVkNRNWZVaTU3UXNBZzZqTVFrN2pMci1jZGhRemRGSnVRLTZsNW1Rc05Ic3NGd21nLU85VVJFLVR5MzZrOWI4Mkc2anZqb042c0xqUGc3?oc=5</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -1911,12 +1911,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1926,12 +1926,12 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>XYRA unveils an intuitive AI platform to transform UAE business accounting - Gulf News</t>
+          <t>UAE cuts tourist VAT refund time to one business day with new AI platform - Gulf Business</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPeHRnSjFza2hMY1l3Q3p2dGtXYkRZRW5qTmFaZkJqTW1YZjU5Rzlva1pjTEJSMEg5MVlZd0pCdENvc2p4OXVGdWdBSEd6Q0gyWTFZS2JoUVVpaVVDa3hsYmNSaE1XWlZJWmZua3lOUVprakhMZFZmR1JsYjFTeDM5YWY2VGtLSmtCT3BOaS05aWRXV0k5NUJVanRpcFQ1MzJIdGVUcTd0cG55ZkpheGIxVjI3MlcwRHp0cmZOUEJPanVSUDNmWW1IUElMb1RYdExIOWFNd1lZcmU2X3hXSTYwVEhR0gH0AUFVX3lxTE9lZTBHQThBcUxrMHRBZkROUzQtaW9WMWVmaVhPdk9wYmtkZlYzVEJ0Z2FuWk1CVTFka0pZOTQxYlVMdzFXNVQxbWdIaURLWmY4RGNRM3FCaFRKbVF6akpqRmVabE9BX095Rk5tV0NZN3lRTm42bzNJR1dxUnJleklmd2E0bm9FUnVGTWxwUE05T2d4ZEVhUnBYVzNvazZHbWFWY29FSXVhU1NMTloweUlpdWZIYTl6b3BSaks4d2NrUFJQUzlqX2lzRFctMTF1ZnprRHZMMkNkRmFYbndEMl9YNHV0aXB0N0h1cU1YRHFPRE4zNWU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPZURXSjRhbWwwMzRkaWYyWlJSWkpSUl9nYllHVFJ0RnpDTHR4dGZJY2tlZzVGbEJuYWRjeFlXSm9fMDhDWTJwS2ViMTd2M1dKc2I1aUZmMTVGclB1eUhnRGV4SnlRZzJRWHhGYW80SFM0cWpCTjR5T29PMUNfU2l6MUN2RWlmdXVKTE5fVHkwNDZxVzdJSmdiUngtTlRzZHRqNHpNTkVSYy1Bb0JN?oc=5</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1971,12 +1971,12 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>UAE tourist VAT refunds cut to one business day with new AI platform - Gulf News</t>
+          <t>Federal Tax Authority launches world’s first-of-its-kind AI-powered digital platform for tourist tax refunds - Zawya</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPTHpETlBMdE1Kb2FWR0ZBdG5jRldvV1ZOWFpJYnMyVWhlQ1hTUE43dkV5UTJIWVA3eVFER0pKNXZHYTVXc3h4eVJ2R09YYVh3dEpkb2k3cXlyYWQyU3pPS0dvSjZhSkNmS1hpM0UwU0VXbEx6d2hydlh3SUJ4amkzQ3RlVGRtRTlqdGdjdW9rMVJkUG5PazRPdkZuY25mdHVoakZIZWFfcWNaLThEeXNyazVhTnVPckJZbXg40gHOAUFVX3lxTFBpcjZEUUktS3kzU1JHZzctTGFPTWZ2WG5PTGc0N21xLWoyS3gybHEzY0hMYU9XeGh2QUE0Z1NRSURaV0xhUkV6Y2VmbkpCR0VBRjR5c2l4SVpPYnBCQ28zTHNVN0k2aWhXcnpMYjFCaFJyUzQ3OUVJM0Q5YVBOS0JZbUV2ZXJVcS1xX2dnUGlYZ3NBaDVmREZyV3QxeTk3VnVUNDJfbG9fekhjX25MOEVhSERXSTk1a0x5THRXT3V2RmRtbkRXd0dTXzEzNWlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxQV0NXYW5reU5Sb1FHRmNDT3dyaXphV2ZORlVZYXNhN1ZQV1FldnhlZGF4VTJpVVJ6c0k4MGRqZE13Rm95S0ZWWkpVQUdlNFpTdDA2cks5akhhZmNZNlFuVU8wVkVJMFhiRUVjNTg5d1dzb2htY05tM0xIb0RhS0dhZ1RaQzZrQ2Z6ZzJJTnlZd19vOTJsU09pamc1TWFqaGFiUFM3Z1JNSGlac0lFeDRrcFpIYWxLN3ZlVjdtc2drS01FRTl1eTdCM3FZdFd1ZU1jODNWYkZ2WHZzZk5USlNVcnlsTXRrcnhaUi1fbUhXWnR6U0FUc3lydXJwNDIyWWc?oc=5</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>UAE e-invoicing deadline: Businesses face Dh5,000 monthly fines for delays - Gulf News</t>
+          <t>UAE Publishes Version 2.0 of E-Invoicing Guidelines - sharedserviceslink</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPWWVSUnR0QVRxaG1QTlhqa3NxcFNNQkdlNi1lYWVKRjFuOFRQMWNoNnY5Ni1CVWVNYWJjSEc3MVU0Q3h3eC0yQ0lJV2NRQTk1TWF3eThpcHFETEQ0OFg1SmJuYUVaZTVvZ3FHc3VpdW8zcEVtbTJJb1FHSFY5dWFOMk5SU3M5ZUpJNEk1OHQ3X1dxeFhLQ0tEbFRtcDR4dG04NS1aY2huV3BJVzlzeDFReDBKdmJmRjVnV3BkOWNQZ3bSAdMBQVVfeXFMTVFtR1VkanA4NWlBaDVrR1V2bDhlak5IUy16ODQtV24xTUVKdG5Sa0ZoeE42MlFWYjJuSmszT3JTSnd5ajJ1ZG1XQmd0M3hUWW5jczlsQ1hWQ3dNRFNxQUsxRkpfTm00WnBybTRpV3F6WXE4NXJmR3MzZDNOZzNqZzU3NmJKWjRVYzdoLXVGNFU2Tmh5Z3AtcVNUMTh0S0M4YThYVllGdW15MVdsZGM5cDFrS2hsV0JERUxzOXJhWkNEMnlydHhfazRucFhEMkUwVmUwOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPV1NkTHUycS0tOFh6TF9HVW4yU051Zk1zTExPWTVONTcxemN0WTVBajl3QkxVY3Bocno5N1BVbDFkUlZjQ214VEZQc1Y0eURfMHZzdTNyV0RuRmU0OXA4dU9MMTZhN19POUdvMXJRSld6UDZkbU9YbWNkaTVzeW9DNDNwX25zRGFKMGgwQlBfR3JzQQ?oc=5</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>UAE VAT rules change staff expense claims: What businesses need to review - Gulf News</t>
+          <t>UAE's new AI platform to slash VAT refund time for tourists to one day - The National</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPNjVZSlVOR1Bab1VubGlRNjZGeDNPWmVNSnRSNDlCXzk3bFk0U2dQTUt6dFlMVmY1QkpvWU1XMlVoQTN2MzluUVNxY01BYWtVb3JuYjFNU1dfQjl2X0dDTnJrXzd3eFFpanBCNGk1QS05LVAyVlliZUgzRFJhaHFKaTlsOTBMOExqLWtBUGZDaXFSZmVfZkRPQk9YSzF2VlNiUlJtbU9RWndXLUxjMjhoN1ZwYWYySDZHZkJRNGdTak3SAdMBQVVfeXFMTUhINEdZNjQybDJ5TjhWUkMwNDBmcENESVUxc214S044NTBva0JGVWNJMFFidVczdFVuN0U5d3VIT1dCczVFLW00LUczN080X0xVWmZTbVd2dkxEaWJBZkxuVHFuWjBoeWpDczhpVVJ2ZTVaY0R1dVVtN24tV3R0bU9WVm52M0lBeDQ0T2c3cEdBUjRjRHFkQTdiUl9HTmw2dmNDTk5BRkpjdVN0NlJaRVR6emc1Q2lpQUxocWx3SFFtRDFRZkI4cmMwLW5BTVhwUWNQbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQZVpMLWZ4cmVQdDlnSlZRRERKN0tJbVR5eGVfblhRam5IUGwtXzdIaWJqeWlSNEVNVGozWGpvMm5LSGQ0YXdlVl92YjRPNHhtZDFIQ2swNlRtdzRQeUtTVmE1d1ZfVF9vdXR3N1RvV3ZoLXlZdWFyTENheUtIa0lOTjZTcjUza3VWVmFLaXpEVm1kTkpVandrTE80a0dadG9IMlJsWUhyZHU4U0tMS3I0cVQ0RVM1aTUzWGF4U2pvQQ?oc=5</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2091,12 +2091,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>UAE e-invoicing deadline in 4 days: Who must comply to avoid Dh5,000 fines - Gulf News</t>
+          <t>UAE announces major tax refund upgrade: Tourist VAT rules explained - Arabian Business</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNLWxHNTZNMkNZUTRHY3hWSFRld05JZm9FRzh3TlZsQzNCS2NqX3kwQjBvbFpjUXBCSG8xRmRLUFBhM25YYTVVNXNyQWFmYjdUTk9ndTZCRmY3dDVObUpsLW85bC1pZzUtWGM5UmR3d2hEckZDUDEzdXN2MEN3MXpFa1JaZWRDVGU5aGE3Ul9nVlZPN0FhVGRjSlctX2lnSHNyeDQ3Z2RFTEN6UmRZRXVuMkNBbGRrbFJfaGpZazZQT07SAdMBQVVfeXFMUEhrM2xRZk5Uc2Z2ZkRUV1p3bGpQSkEzaGpaQkdhZ1lrYld2LUMxd3ozdTh6WmxJVkJYNkJCeGxGOURPY2dsbU9RdmphOXpncm03bjZvSWRDeUp0Ykg5NmpOQjUyZ1MwS08xcTdzOXhnSFZGNklnbGxpTk44aldNOFJrNVNuS2trMkphb0xpOXN3ZU13Y0JmN0Q1ZlQtWTZscmNwa0RTbGg4M1M0cHd2R2NXTV9fRFZwQk5aNjMyUF90VXUwX2prR09OaklId0VYSFlHaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOOV9mdmlpRVVsSTdjRnA2bV9OSGUtNGlvNmgzTWVjSGJiZFkyYmpBQ1h1UE4zY2VGN3FFQ1M3N09ZQm4zc1lTNl8ybDNKTll4c1FweWZlNFBLMFI3aFRfSzAtaHJzVmxSajI4amM1OFBMRUlnWnBfbWZ2a0s1azBieWtybl9VRmVrRmd0VVI4T0tzNWZZbWdCNE5NR3BxZVR0TW1EZ3VCTlBHZw?oc=5</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2136,12 +2136,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Ezat Alnajm on Preparing Crypto Wealth for Greater Tax Transparency - Hubbis</t>
+          <t>UAE launches AI platform to cut tourist VAT refunds to one business day — The National - UA.NEWS</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQRkVXSUFZWnYwTXRYTG5GZUtmN0pZLWx2anJoNTM1VERGZUVha1JZc01kMWxHek92SEVEbkgzeDgyZWh0RXY3VFhuYVJKcTlNeklhQlJvUVB1WXNnMVZ5WUFmY2pxYzNqblZRYkRBemxhdzktaWhwLVNBZFNqOE9RVGlsRm4zazVuVExuUGZtQ19JM2xFRHFldFdxbmN1Sjg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQYXdJZkJvX3ByM0lXS2ZtYjlHR0poREtsemlTaHdPWGExcVBhQzdNR3kyWmJMNHJsTnVYemRldHg2aG1jdlNidk5sV1JjcldzRF85dzh6ckpHeHdWVHp0SVdzeFZGNFlzdW04Q1dockJ1ajU2bnRFcmdwLUZfbE9iVm0tRE9jQklXM1Qzc2ppV2lDM19vUGUxLU9uc1ZJNm9TcTNlYnFnTzh2RVZyZUFEM0VVdHZWRFNKQmJsX1ZtQlc?oc=5</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2196,12 +2196,12 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Ministerial Decision No. 197 of 2026 - Crowe</t>
+          <t>UAE Federal Tax Authority Launches Digital VAT Refund Platform for Tourists - News and Statistics - IndexBox</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOMFZaS3RKdnpEdVpQcUtlN1JJWlBuZmxxRkpnZHB4WXFpUGg1cHpjcHdKUzJlM0VTVExnRExWRkowZm5iek1yUHpaY3ZWamZfS3ZpM0tkSW9MTjV0YmxHOFhpeDltbkxENmZLamJkV1ZKMklZUjAySU1aZGVZSnRMamIxejJBdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOSm9HaWZSWEFFM3BNOW5acHZBT0luQWFnVEo3QUpJR1AwdUNMVjE0V3RXUXptLVVZR1VBN3doSnZlU1RNcU40UmJNVWpfQnVpY3NNRGRqNTM3WVFNRnB5X0g3SXFfbkl0Rk91MEtTWVBRejJDOElIcmxLSG1TcnNaRWdVbUdoS0QtMGVRX0NzSjJOSVJyV1luRVZsRW9ldl80c2VfUkNiempDdw?oc=5</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2226,12 +2226,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Amendments to the UAE electronic invoicing system decision - Simmons &amp; Simmons</t>
+          <t>XYRA unveils an intuitive AI platform to transform UAE business accounting - Gulf News</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOUzJMUUdnR2Z0TjQ2eEMteTVMNHpOZndFbEh3T1hJaVQ5Z29HdXRlS3lTcXdRbkFFMnVRdFI5a0QzMzlQM2EzZnBDY1VDLXJUeFI5T1VtQnJ5UEFHTmU1bVA0bWJiMTZwTmhFR21sZzE0WEZReGRwMWRDalVDbm9kVWpVM0VfTmJHeThySXRwYjY0UzZXS1NhT0J2T0tGLVczYjk3Mno2TDZPeU5BbGM3VGR6SDJYR0wydkkxNUtYSzM1a19ocnhlNWQ3VS0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPeHRnSjFza2hMY1l3Q3p2dGtXYkRZRW5qTmFaZkJqTW1YZjU5Rzlva1pjTEJSMEg5MVlZd0pCdENvc2p4OXVGdWdBSEd6Q0gyWTFZS2JoUVVpaVVDa3hsYmNSaE1XWlZJWmZua3lOUVprakhMZFZmR1JsYjFTeDM5YWY2VGtLSmtCT3BOaS05aWRXV0k5NUJVanRpcFQ1MzJIdGVUcTd0cG55ZkpheGIxVjI3MlcwRHp0cmZOUEJPanVSUDNmWW1IUElMb1RYdExIOWFNd1lZcmU2X3hXSTYwVEhR0gH0AUFVX3lxTE9lZTBHQThBcUxrMHRBZkROUzQtaW9WMWVmaVhPdk9wYmtkZlYzVEJ0Z2FuWk1CVTFka0pZOTQxYlVMdzFXNVQxbWdIaURLWmY4RGNRM3FCaFRKbVF6akpqRmVabE9BX095Rk5tV0NZN3lRTm42bzNJR1dxUnJleklmd2E0bm9FUnVGTWxwUE05T2d4ZEVhUnBYVzNvazZHbWFWY29FSXVhU1NMTloweUlpdWZIYTl6b3BSaks4d2NrUFJQUzlqX2lzRFctMTF1ZnprRHZMMkNkRmFYbndEMl9YNHV0aXB0N0h1cU1YRHFPRE4zNWU?oc=5</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2269,35 +2269,39 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>official</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Finance Amends Electronic Invoicing Regulations to Ease the Burden on Businesses</t>
+          <t>UAE tourist VAT refunds cut to one business day with new AI platform - Gulf News</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Ministry of Finance — News</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>mof.gov.ae</t>
+          <t>news.google.com</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://mof.gov.ae/en/news/ministry-of-finance-amends-electronic-invoicing-regulations-to-ease-the-burden-on-businesses/</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPTHpETlBMdE1Kb2FWR0ZBdG5jRldvV1ZOWFpJYnMyVWhlQ1hTUE43dkV5UTJIWVA3eVFER0pKNXZHYTVXc3h4eVJ2R09YYVh3dEpkb2k3cXlyYWQyU3pPS0dvSjZhSkNmS1hpM0UwU0VXbEx6d2hydlh3SUJ4amkzQ3RlVGRtRTlqdGdjdW9rMVJkUG5PazRPdkZuY25mdHVoakZIZWFfcWNaLThEeXNyazVhTnVPckJZbXg40gHOAUFVX3lxTFBpcjZEUUktS3kzU1JHZzctTGFPTWZ2WG5PTGc0N21xLWoyS3gybHEzY0hMYU9XeGh2QUE0Z1NRSURaV0xhUkV6Y2VmbkpCR0VBRjR5c2l4SVpPYnBCQ28zTHNVN0k2aWhXcnpMYjFCaFJyUzQ3OUVJM0Q5YVBOS0JZbUV2ZXJVcS1xX2dnUGlYZ3NBaDVmREZyV3QxeTk3VnVUNDJfbG9fekhjX25MOEVhSERXSTk1a0x5THRXT3V2RmRtbkRXd0dTXzEzNWlR?oc=5</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2310,35 +2314,39 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>official</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>UAE Breaks into Global Top 10 in IMD’s 2026 Government Support Index</t>
+          <t>UAE e-invoicing deadline: Businesses face Dh5,000 monthly fines for delays - Gulf News</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Ministry of Finance — News</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>mof.gov.ae</t>
+          <t>news.google.com</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>https://mof.gov.ae/en/news/uae-breaks-into-global-top-10-in-imds-2026-government-support-index/</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPWWVSUnR0QVRxaG1QTlhqa3NxcFNNQkdlNi1lYWVKRjFuOFRQMWNoNnY5Ni1CVWVNYWJjSEc3MVU0Q3h3eC0yQ0lJV2NRQTk1TWF3eThpcHFETEQ0OFg1SmJuYUVaZTVvZ3FHc3VpdW8zcEVtbTJJb1FHSFY5dWFOMk5SU3M5ZUpJNEk1OHQ3X1dxeFhLQ0tEbFRtcDR4dG04NS1aY2huV3BJVzlzeDFReDBKdmJmRjVnV3BkOWNQZ3bSAdMBQVVfeXFMTVFtR1VkanA4NWlBaDVrR1V2bDhlak5IUy16ODQtV24xTUVKdG5Sa0ZoeE42MlFWYjJuSmszT3JTSnd5ajJ1ZG1XQmd0M3hUWW5jczlsQ1hWQ3dNRFNxQUsxRkpfTm00WnBybTRpV3F6WXE4NXJmR3MzZDNOZzNqZzU3NmJKWjRVYzdoLXVGNFU2Tmh5Z3AtcVNUMTh0S0M4YThYVllGdW15MVdsZGM5cDFrS2hsV0JERUxzOXJhWkNEMnlydHhfazRucFhEMkUwVmUwOA?oc=5</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2351,35 +2359,39 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>IFRS / Reporting</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>official</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Finance convenes Financial Data Forum 2026 to boost efficiency in final account and financial statement preparation and reinforce the application of international accounting standards</t>
+          <t>UAE VAT rules change staff expense claims: What businesses need to review - Gulf News</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Ministry of Finance — News</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>mof.gov.ae</t>
+          <t>news.google.com</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://mof.gov.ae/en/news/ministry-of-finance-convenes-financial-data-forum-2026-to-boost-efficiency-in-final-account-and-financial-statement-preparation-and-reinforce-the-application-of-international-accounting-standards/</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPNjVZSlVOR1Bab1VubGlRNjZGeDNPWmVNSnRSNDlCXzk3bFk0U2dQTUt6dFlMVmY1QkpvWU1XMlVoQTN2MzluUVNxY01BYWtVb3JuYjFNU1dfQjl2X0dDTnJrXzd3eFFpanBCNGk1QS05LVAyVlliZUgzRFJhaHFKaTlsOTBMOExqLWtBUGZDaXFSZmVfZkRPQk9YSzF2VlNiUlJtbU9RWndXLUxjMjhoN1ZwYWYySDZHZkJRNGdTak3SAdMBQVVfeXFMTUhINEdZNjQybDJ5TjhWUkMwNDBmcENESVUxc214S044NTBva0JGVWNJMFFidVczdFVuN0U5d3VIT1dCczVFLW00LUczN080X0xVWmZTbVd2dkxEaWJBZkxuVHFuWjBoeWpDczhpVVJ2ZTVaY0R1dVVtN24tV3R0bU9WVm52M0lBeDQ0T2c3cEdBUjRjRHFkQTdiUl9HTmw2dmNDTk5BRkpjdVN0NlJaRVR6emc1Q2lpQUxocWx3SFFtRDFRZkI4cmMwLW5BTVhwUWNQbw?oc=5</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2389,17 +2401,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2409,12 +2421,12 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Foreign outflows in July were the lowest in the GCC - EnterpriseAM</t>
+          <t>UAE e-invoicing deadline in 4 days: Who must comply to avoid Dh5,000 fines - Gulf News</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -2424,7 +2436,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE8tRko4Unh0QWI1ekpUTHJ3QmktT1dyWXd2S2REcHZIZVVvd2Rtdm1WSkUtQUtacjlnSGlLdWtIMk0tVVNxU1ZKTU1qSVdpc2NOUjBGWUh5STBrM0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNLWxHNTZNMkNZUTRHY3hWSFRld05JZm9FRzh3TlZsQzNCS2NqX3kwQjBvbFpjUXBCSG8xRmRLUFBhM25YYTVVNXNyQWFmYjdUTk9ndTZCRmY3dDVObUpsLW85bC1pZzUtWGM5UmR3d2hEckZDUDEzdXN2MEN3MXpFa1JaZWRDVGU5aGE3Ul9nVlZPN0FhVGRjSlctX2lnSHNyeDQ3Z2RFTEN6UmRZRXVuMkNBbGRrbFJfaGpZazZQT07SAdMBQVVfeXFMUEhrM2xRZk5Uc2Z2ZkRUV1p3bGpQSkEzaGpaQkdhZ1lrYld2LUMxd3ozdTh6WmxJVkJYNkJCeGxGOURPY2dsbU9RdmphOXpncm03bjZvSWRDeUp0Ykg5NmpOQjUyZ1MwS08xcTdzOXhnSFZGNklnbGxpTk44aldNOFJrNVNuS2trMkphb0xpOXN3ZU13Y0JmN0Q1ZlQtWTZscmNwa0RTbGg4M1M0cHd2R2NXTV9fRFZwQk5aNjMyUF90VXUwX2prR09OaklId0VYSFlHaw?oc=5</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2434,12 +2446,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2454,12 +2466,12 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>UAE extends small business tax relief until 2029 - Yahoo Finance</t>
+          <t>Ezat Alnajm on Preparing Crypto Wealth for Greater Tax Transparency - Hubbis</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -2469,7 +2481,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNM2FhblZZVW5LVzI2bmRYWFhadXJ5bGU2OU54U3UzTmpGWmlweXlYTVVSWHpXaXU5YnJLNlh0STNsNmhYdG9feTdsN2xKNWlNSGZRM3loRllITXB4U0ljUkpyYllpLU9jQUZVOVdab1Rocml1OWxsa1lKWE00Wk42QWZRejVCaTk4QllWdTJTMWxJd2RKbVZiWHo4UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQRkVXSUFZWnYwTXRYTG5GZUtmN0pZLWx2anJoNTM1VERGZUVha1JZc01kMWxHek92SEVEbkgzeDgyZWh0RXY3VFhuYVJKcTlNeklhQlJvUVB1WXNnMVZ5WUFmY2pxYzNqblZRYkRBemxhdzktaWhwLVNBZFNqOE9RVGlsRm4zazVuVExuUGZtQ19JM2xFRHFldFdxbmN1Sjg?oc=5</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2479,12 +2491,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2499,12 +2511,12 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>UAE seizes 8.45m non-compliant tobacco and drink products in six-month tax drive - Gulf News</t>
+          <t>Ministerial Decision No. 197 of 2026 - Crowe</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -2514,7 +2526,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOeXEwYUYyRVl3dzRiREtKU01zOTFJNXZCNVpNcE5wYTUxRUN3U1A0SkxudUUxYkI0WHUzUmZoelZBLUJSaUFFcno2WFc5bzNBR2FQZU4zSkFuMTNWbkcyMVNMdXc3dmplcVNLdDRsN2xDdng3ZFg2UnFiREgzZHIwUFlpUkhxdXdkeG0ySXJQS2Q2LWJJRGxrbWZMT3AxTU9KWWM1OS1qQ2FET0oyQjhhZFNXX3RDWklhU3VrdTM2aTRRcFIxdXlWOHJB0gHcAUFVX3lxTFA5OFBJbzlhcVVXbXNwNWtBamtpbFdwbVkxdHFtSTJXWk9TR3kxZ0F6UFVtQy1EYnpaZUM2Vmp1enVjeFJoSjR1ekpMenVHdEhaTlhGdmxKUzQwV1BsQnpiNXg0UDRpTndaTjE2RTJBNzFIbzNEZExXWlhmVnpYT2VTbmFsNldOZVlzX3BsaU5xUUplai13SEl2RUdpNG0tWTJOd1BCQkVaUVowX0NiZHF3VU1BLU5VcVpBb2RoRXVERGdaYmxhMmhEd3MxNVRoekNKQ3hZeEhyWkUwQUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOMFZaS3RKdnpEdVpQcUtlN1JJWlBuZmxxRkpnZHB4WXFpUGg1cHpjcHdKUzJlM0VTVExnRExWRkowZm5iek1yUHpaY3ZWamZfS3ZpM0tkSW9MTjV0YmxHOFhpeDltbkxENmZLamJkV1ZKMklZUjAySU1aZGVZSnRMamIxejJBdw?oc=5</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2524,17 +2536,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2544,7 +2556,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>UAE Extends Small Business Relief for Corporate Tax Purposes Until 2029 - entARABI</t>
+          <t>Amendments to the UAE electronic invoicing system decision - Simmons &amp; Simmons</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2559,7 +2571,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOV0NzYjBEMHBFM0dLeTRxdURMWjYtZUZ2OXpSTENyYVozcGpPWkVBb09JaU1pQjAtWEVTdlcyQ1VjbmNGc2NiT05jWFUxMTNFVzFJMHlHQlY3VmxDaU9XUVZwY21yS1ZFYldWckFZallwVDU3Y1ZzLVNKbndvMXVGckJFMnRWNUtNOTFzRlgzUDhMbHFpMEZsRk9XejN4S3F4cld0aTJPdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOUzJMUUdnR2Z0TjQ2eEMteTVMNHpOZndFbEh3T1hJaVQ5Z29HdXRlS3lTcXdRbkFFMnVRdFI5a0QzMzlQM2EzZnBDY1VDLXJUeFI5T1VtQnJ5UEFHTmU1bVA0bWJiMTZwTmhFR21sZzE0WEZReGRwMWRDalVDbm9kVWpVM0VfTmJHeThySXRwYjY0UzZXS1NhT0J2T0tGLVczYjk3Mno2TDZPeU5BbGM3VGR6SDJYR0wydkkxNUtYSzM1a19ocnhlNWQ3VS0?oc=5</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -2569,42 +2581,38 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Transfer Pricing</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>official</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Tax Insights: Canada introduces a simplified transfer pricing documentation regime - PwC</t>
+          <t>Ministry of Finance Amends Electronic Invoicing Regulations to Ease the Burden on Businesses</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>News — Big 4 UAE Tax Commentary</t>
+          <t>Ministry of Finance — News</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>news.google.com</t>
+          <t>mof.gov.ae</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOVm8yXzZQUVY4R2djbXBUdHQ0aFUyQnFaSHNxSkFCbTNxNmxSVTZVUHRxa1lvVnF2Nlk2bmhTQ2w4ejJaTVR2NUY4S3VsajBFTEV2dkRwbk9BbEh1MWtwczNVNHgtQm1yaFJwc2NlZldqM053NGhwbE1TLWR3eDNIQ3V2ZzhTQ2JmbVJlNlliMkRoalBfYzQ3WHdVaXR2R2MzNEw1dGRQNzFfRWxTWklzYkJNYVZKVjFMclFQQjIzMUU?oc=5</t>
+          <t>https://mof.gov.ae/en/news/ministry-of-finance-amends-electronic-invoicing-regulations-to-ease-the-burden-on-businesses/</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -2614,14 +2622,10 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Other</t>
@@ -2629,27 +2633,27 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>official</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Canada launches public consultations on steel imports and imposes surtax on wood cabinets and vanities - EY</t>
+          <t>UAE Breaks into Global Top 10 in IMD’s 2026 Government Support Index</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>News — Big 4 UAE Tax Commentary</t>
+          <t>Ministry of Finance — News</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>news.google.com</t>
+          <t>mof.gov.ae</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNMy1qdEVRaXhDVUZ4c3FTNUlCS0F0SEhoRnQtRk5BTnB1d2VFSmZSUk95RmRSdEw4LUFBV1FwYTIwbTVLZHdqOEdkcDhRb29fWDc1cGN0ZFA3a0habW9iY0NWam9LZmtfa3c2NDlLZ3N1MVJYWWRwejlhM1ViSndzZg?oc=5</t>
+          <t>https://mof.gov.ae/en/news/uae-breaks-into-global-top-10-in-imds-2026-government-support-index/</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -2659,42 +2663,38 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>IFRS / Reporting</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>official</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>UAE extends Small Business Relief for corporate tax - Absolute Geeks</t>
+          <t>Ministry of Finance convenes Financial Data Forum 2026 to boost efficiency in final account and financial statement preparation and reinforce the application of international accounting standards</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>News — FTA Announcements</t>
+          <t>Ministry of Finance — News</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>news.google.com</t>
+          <t>mof.gov.ae</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPWU10OExoZmlXRjdCamp5VHROMnNDb1dKN1I3NE85dTI4aU84VjVvczlyanRyWEw4OVBuOWpVa1NJZm9qQ2hSZl9YYlhxOGNEYXBCeDlGQVF1RUV1TWJlSGVmdnpHRktyS2ktV2IwQ0s3T3hZMzV4Ni03aGdvVTNHZFhEYThmRE5uclJqR1BKUF90MXktS2xEaXctR0RsLXphM0g0REdvWHY?oc=5</t>
+          <t>https://mof.gov.ae/en/news/ministry-of-finance-convenes-financial-data-forum-2026-to-boost-efficiency-in-final-account-and-financial-statement-preparation-and-reinforce-the-application-of-international-accounting-standards/</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -2704,12 +2704,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2724,12 +2724,12 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Spotify forecasts slower growth despite AI investment - Gulf Business</t>
+          <t>Foreign outflows in July were the lowest in the GCC - EnterpriseAM</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>News — FTA Announcements</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNQUhDU0xPaGxHNTZZdDNmRFRsTndvQThIUkRVV0hyTkpVbWhFNXdsZ2hjUXFrNzByWEc1ZUdITm1FYkM2N3k5MW5paDBud1RfNGF4MXNIdlluaVktTVRfd0RlZzJpUmc0UlZ2WUlKU1VDTUdELXpoelU0Z2kteENFZjVfcWx5YmhLc21jS3J5VXVkeEZ3UXRV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE8tRko4Unh0QWI1ekpUTHJ3QmktT1dyWXd2S2REcHZIZVVvd2Rtdm1WSkUtQUtacjlnSGlLdWtIMk0tVVNxU1ZKTU1qSVdpc2NOUjBGWUh5STBrM0E?oc=5</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -2749,17 +2749,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2769,12 +2769,12 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>UAE Sets Minimum Excise Price for E-Liquids - Vaping360</t>
+          <t>UAE extends small business tax relief until 2029 - Yahoo Finance</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>News — FTA Announcements</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE9HS2ZoOFFrdlRtX3N4ZXM5UlpzLTFKc21Pdi1CVkhNYW1PNGozMDBVYVZ0VjlrUDNCMFRQRG1hOGpPNllSd0dpX0dhNm02a3drdmZneHpQOUhtUkxXWlFBcDlETkt0dF9xalFRMldrVWZMSXh5NHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNM2FhblZZVW5LVzI2bmRYWFhadXJ5bGU2OU54U3UzTmpGWmlweXlYTVVSWHpXaXU5YnJLNlh0STNsNmhYdG9feTdsN2xKNWlNSGZRM3loRllITXB4U0ljUkpyYllpLU9jQUZVOVdab1Rocml1OWxsa1lKWE00Wk42QWZRejVCaTk4QllWdTJTMWxJd2RKbVZiWHo4UQ?oc=5</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -2794,17 +2794,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>E-Invoicing Readiness Checklist: How UAE Businesses Can Prepare Before the Deadline - NewsBreak: Local News &amp; Alerts</t>
+          <t>UAE seizes 8.45m non-compliant tobacco and drink products in six-month tax drive - Gulf News</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPQmFubHpKbnIzS2N1cVJkbFA5bDRWcUhzQ0lYazZ3Z0ZBazZKQzVoTjRxZXBrMFNNSGNXTGp4ZG1EZ0xTTGFwanZQZkxvbjA5UFQxYkNBLWF6bEtDSlB5UlcyNU9fc2E1VTRNMWtTYnRyOFRlTUxjRlVlcEVwRVdDb05OQlo4VC1GcUpqUkpmVzhsUmc0RGJrZlJWN0tCMXVQc0d5dTEtT055TFRDT3c5R2pUN1hpaEF3R21TOHo2d1pNZldNcUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOeXEwYUYyRVl3dzRiREtKU01zOTFJNXZCNVpNcE5wYTUxRUN3U1A0SkxudUUxYkI0WHUzUmZoelZBLUJSaUFFcno2WFc5bzNBR2FQZU4zSkFuMTNWbkcyMVNMdXc3dmplcVNLdDRsN2xDdng3ZFg2UnFiREgzZHIwUFlpUkhxdXdkeG0ySXJQS2Q2LWJJRGxrbWZMT3AxTU9KWWM1OS1qQ2FET0oyQjhhZFNXX3RDWklhU3VrdTM2aTRRcFIxdXlWOHJB0gHcAUFVX3lxTFA5OFBJbzlhcVVXbXNwNWtBamtpbFdwbVkxdHFtSTJXWk9TR3kxZ0F6UFVtQy1EYnpaZUM2Vmp1enVjeFJoSjR1ekpMenVHdEhaTlhGdmxKUzQwV1BsQnpiNXg0UDRpTndaTjE2RTJBNzFIbzNEZExXWlhmVnpYT2VTbmFsNldOZVlzX3BsaU5xUUplai13SEl2RUdpNG0tWTJOd1BCQkVaUVowX0NiZHF3VU1BLU5VcVpBb2RoRXVERGdaYmxhMmhEd3MxNVRoekNKQ3hZeEhyWkUwQUg?oc=5</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -2839,17 +2839,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>A jumpy July - EnterpriseAM</t>
+          <t>UAE Extends Small Business Relief for Corporate Tax Purposes Until 2029 - entARABI</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBCcFdtSjE1bW5pMlREMHVqWTYwcW1xajViLWZvTmU1MUk0MUZiX2pPay12Nm5RS0tzdmJjYU9VY2hjUi10enNsYk1qcEZqc3FQc3dEZE1CaTJRYTJvVWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOV0NzYjBEMHBFM0dLeTRxdURMWjYtZUZ2OXpSTENyYVozcGpPWkVBb09JaU1pQjAtWEVTdlcyQ1VjbmNGc2NiT05jWFUxMTNFVzFJMHlHQlY3VmxDaU9XUVZwY21yS1ZFYldWckFZallwVDU3Y1ZzLVNKbndvMXVGckJFMnRWNUtNOTFzRlgzUDhMbHFpMEZsRk9XejN4S3F4cld0aTJPdw?oc=5</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -2894,22 +2894,22 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Transfer Pricing</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Another Hormuz workaround - EnterpriseAM</t>
+          <t>Tax Insights: Canada introduces a simplified transfer pricing documentation regime - PwC</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — Big 4 UAE Tax Commentary</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5iUjRXRTlrdVBXOHUyRWlYc2ttOXdYaVktOE5ZU1YxMnRLcnlHeWRPdl9CQmRkR3Bqc21aeFlWMmdFcGdjanc3d2RNTnRGcWdKVGdxQTZmeC02clJoSXJJaGJlUUM5TW5pQjRORkVpRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOVm8yXzZQUVY4R2djbXBUdHQ0aFUyQnFaSHNxSkFCbTNxNmxSVTZVUHRxa1lvVnF2Nlk2bmhTQ2w4ejJaTVR2NUY4S3VsajBFTEV2dkRwbk9BbEh1MWtwczNVNHgtQm1yaFJwc2NlZldqM053NGhwbE1TLWR3eDNIQ3V2ZzhTQ2JmbVJlNlliMkRoalBfYzQ3WHdVaXR2R2MzNEw1dGRQNzFfRWxTWklzYkJNYVZKVjFMclFQQjIzMUU?oc=5</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -2939,22 +2939,22 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>UAE e-invoicing: How digital invoices will transform business - Khaleej Times</t>
+          <t>Canada launches public consultations on steel imports and imposes surtax on wood cabinets and vanities - EY</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — Big 4 UAE Tax Commentary</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQMjFwZTd6MkpqcXZKaEwxZV9fUlZWSEtSeVdIQXN6YXFPMURFMWZhOHc0NWFuWlRfd1ZNX2doQVBpbXBqRFBTOVNNcjVTYVpOcEozYmtoaWxDUHVoUFFNT1RBWEI3RzJybmFWejFNcEcxYXpybDBiUzRLUk85ajBkOHIydnBjOUV6NEVJUjZkQTNOQ0Fud1BjdGtUNVpwTmlTazdyNWZmaXRwTkthY1Nac1RPWU90T3lMemJJNHp5VdIBvwFBVV95cUxQMjFwZTd6MkpqcXZKaEwxZV9fUlZWSEtSeVdIQXN6YXFPMURFMWZhOHc0NWFuWlRfd1ZNX2doQVBpbXBqRFBTOVNNcjVTYVpOcEozYmtoaWxDUHVoUFFNT1RBWEI3RzJybmFWejFNcEcxYXpybDBiUzRLUk85ajBkOHIydnBjOUV6NEVJUjZkQTNOQ0Fud1BjdGtUNVpwTmlTazdyNWZmaXRwTkthY1Nac1RPWU90T3lMemJJNHp5VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNMy1qdEVRaXhDVUZ4c3FTNUlCS0F0SEhoRnQtRk5BTnB1d2VFSmZSUk95RmRSdEw4LUFBV1FwYTIwbTVLZHdqOEdkcDhRb29fWDc1cGN0ZFA3a0habW9iY0NWam9LZmtfa3c2NDlLZ3N1MVJYWWRwejlhM1ViSndzZg?oc=5</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -2979,12 +2979,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>More investments in Adnoc’s fleet, Indian IPOs, and Egypt’s North Coast - EnterpriseAM</t>
+          <t>UAE extends Small Business Relief for corporate tax - Absolute Geeks</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — FTA Announcements</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1RdV9pa3ZIMmpRWnFlcXRaeTRnSy1zZUp0enVScm1nc0hMX3UwTEdEOG9oQy00UUJiSUR4WENleElGQVVmLXh3ZE10b09nQWphT0IzNHNJb0h3Q0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPWU10OExoZmlXRjdCamp5VHROMnNDb1dKN1I3NE85dTI4aU84VjVvczlyanRyWEw4OVBuOWpVa1NJZm9qQ2hSZl9YYlhxOGNEYXBCeDlGQVF1RUV1TWJlSGVmdnpHRktyS2ktV2IwQ0s3T3hZMzV4Ni03aGdvVTNHZFhEYThmRE5uclJqR1BKUF90MXktS2xEaXctR0RsLXphM0g0REdvWHY?oc=5</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>FTA Directive No. 5 of 2026 - Crowe</t>
+          <t>Spotify forecasts slower growth despite AI investment - Gulf Business</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — FTA Announcements</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE40S0RnRzF2d1dBSmNHdkNNQXZQQmlOYWNOSk5OWnlVNUN3ZDB5UHBUV29RXzNvaF9pVFNQZ2FwTUdocGhxMXp1T3gxMUFycGNESFA1bXNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNQUhDU0xPaGxHNTZZdDNmRFRsTndvQThIUkRVV0hyTkpVbWhFNXdsZ2hjUXFrNzByWEc1ZUdITm1FYkM2N3k5MW5paDBud1RfNGF4MXNIdlluaVktTVRfd0RlZzJpUmc0UlZ2WUlKU1VDTUdELXpoelU0Z2kteENFZjVfcWx5YmhLc21jS3J5VXVkeEZ3UXRV?oc=5</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Digital currency and VAT: New UAE rules for businesses to consider - thenationalnews.com</t>
+          <t>UAE Sets Minimum Excise Price for E-Liquids - Vaping360</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — FTA Announcements</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQamI1MElzOEtNS1ZjVWR3VGpjZjNUZjBXbjQwZkJIZ3AwOFVqckl0WWFQN2JpaEg5XzRTUTBVMDFOeVhMaUZxYW9GUnBFNW55WnhKd2ZKOVZoekRBWUNqQkp3dGFPZ2JQcWY5SjVlRUJuTURfcVN5aUNXVmthdUh4cHlJbFNHN3lyT1VTU2l2Nk92U09JZFh3eXp0c29jTlJNZW1VLTZBR2h5WmdBTjFuNGczZkZwdDY1QWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE9HS2ZoOFFrdlRtX3N4ZXM5UlpzLTFKc21Pdi1CVkhNYW1PNGozMDBVYVZ0VjlrUDNCMFRQRG1hOGpPNllSd0dpX0dhNm02a3drdmZneHpQOUhtUkxXWlFBcDlETkt0dF9xalFRMldrVWZMSXh5NHc?oc=5</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
@@ -3114,12 +3114,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3129,12 +3129,12 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Air India turbulence injures passengers on Phuket-Delhi flight - Gulf Business</t>
+          <t>E-Invoicing Readiness Checklist: How UAE Businesses Can Prepare Before the Deadline - NewsBreak: Local News &amp; Alerts</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOUk92b3hCQVZybGNndXNJOF9ZX0Z3TGl5NnRuXzE5NlBRb3czZXM2SkxXb3ZQSGNOdGo2a2U2b040ZVFDcFBqbzdvaFFZaVdBbFgwQkJOOEhDNzF6VXY1OU9Ca2t2Z1ZnQlhscXNXTVhDaWY3b2lvMUlEWFhkXzVxaDR3b191OUx2aTVKcEttYkFGTjRzRVpnbFJvLUZhYmNLTFJJNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPQmFubHpKbnIzS2N1cVJkbFA5bDRWcUhzQ0lYazZ3Z0ZBazZKQzVoTjRxZXBrMFNNSGNXTGp4ZG1EZ0xTTGFwanZQZkxvbjA5UFQxYkNBLWF6bEtDSlB5UlcyNU9fc2E1VTRNMWtTYnRyOFRlTUxjRlVlcEVwRVdDb05OQlo4VC1GcUpqUkpmVzhsUmc0RGJrZlJWN0tCMXVQc0d5dTEtT055TFRDT3c5R2pUN1hpaEF3R21TOHo2d1pNZldNcUE?oc=5</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3159,12 +3159,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>UAE Business: UAE extends small business relief for corporate tax until December 2029 - Gulf Daily News</t>
+          <t>A jumpy July - EnterpriseAM</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNVm43RXV5MWlfOTE5TjdqQjhtd3pzUnRIdmJycExNbXV6REpoRjQ5MlNiRENNemM5SG5VbUhJbnVXenhQXzFhRGgtNXE3QjRWWHhCcTJsZ0lfUW5ZTWNWcjdZQnZSSDM0VVdvVDY0ejBPMklPTUkzdTdXX090b1RQY21nbmdUQUtuZG42RHBxRWdCb05xNkdBT2xUVk1SNWN0cG1NbnhKNlBxSl96T3BzOU91cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBCcFdtSjE1bW5pMlREMHVqWTYwcW1xajViLWZvTmU1MUk0MUZiX2pPay12Nm5RS0tzdmJjYU9VY2hjUi10enNsYk1qcEZqc3FQc3dEZE1CaTJRYTJvVWc?oc=5</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
@@ -3204,12 +3204,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>UAE extends corporate tax relief for small businesses until 2029 - Khaleej Times</t>
+          <t>Another Hormuz workaround - EnterpriseAM</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNMDNwUlhpclFxaFJkdkkzR0s5MVh4WHZOUDdfZzZtNTBFb2RIcklxMF91Tkp2NGRxRlZMM3BubEZGc0g5LXpsQUhHQy01eGcxTllzc1k1S1NqeFMtYXM4YlBmREttNlhsS0hmd2JXN0l2UjFEQ3B5M1pfRTVpOGw0Z1pPMTNHd0tHQ25ZNjNGZmVaZnhzZUJueE9sQ2dNNGVaUDVjTdIBrAFBVV95cUxNbWJjeHFtRU9DbExyNHRRY1NEUXB2WnZRZ1V2TlFhQ010T3RhSmptR2ItaDhxVnEta0NITUJyS3ppaGgyQ2FkclQwRFhCaWNnLUhNb21YaDVGLWZZNThic2hpN0MzNTI4cXI3RjYtLVUzN3VHanJUUHdYaEFRWUlvS2w5UVdja3pwd1Q4c2pXWHVPZ0xZVmFCcE43eWl1bG10N0s4UXdpVUhpU0tH?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5iUjRXRTlrdVBXOHUyRWlYc2ttOXdYaVktOE5ZU1YxMnRLcnlHeWRPdl9CQmRkR3Bqc21aeFlWMmdFcGdjanc3d2RNTnRGcWdKVGdxQTZmeC02clJoSXJJaGJlUUM5TW5pQjRORkVpRQ?oc=5</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>UAE extends corporate tax relief for small businesses until 2029 - thenationalnews.com</t>
+          <t>UAE e-invoicing: How digital invoices will transform business - Khaleej Times</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQOFMwcEtFYkFkbWxMRnBqX3Y1M2ZOcnJ4Q1FzTHg2b1NDYnU3dzVWMmMycVdhNzJSbTZhaTZ1bjRpN3RYcm9Gb3VIOUxydjN6anFTMU12SHNNcmt1YkhwSk1RVTV6Yk1yS0wtNm9PbVZLNkxmTVRNd3hEOW1xbXdnTlBiX0VJWWhINEw5MHc1eEk4UHhFZHFOZ04zcnZERDZhLXZJQ0VGWS15N080ZXBQYVhDMFU2al9wN1NlNXN2RnFaZEU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQMjFwZTd6MkpqcXZKaEwxZV9fUlZWSEtSeVdIQXN6YXFPMURFMWZhOHc0NWFuWlRfd1ZNX2doQVBpbXBqRFBTOVNNcjVTYVpOcEozYmtoaWxDUHVoUFFNT1RBWEI3RzJybmFWejFNcEcxYXpybDBiUzRLUk85ajBkOHIydnBjOUV6NEVJUjZkQTNOQ0Fud1BjdGtUNVpwTmlTazdyNWZmaXRwTkthY1Nac1RPWU90T3lMemJJNHp5VdIBvwFBVV95cUxQMjFwZTd6MkpqcXZKaEwxZV9fUlZWSEtSeVdIQXN6YXFPMURFMWZhOHc0NWFuWlRfd1ZNX2doQVBpbXBqRFBTOVNNcjVTYVpOcEozYmtoaWxDUHVoUFFNT1RBWEI3RzJybmFWejFNcEcxYXpybDBiUzRLUk85ajBkOHIydnBjOUV6NEVJUjZkQTNOQ0Fud1BjdGtUNVpwTmlTazdyNWZmaXRwTkthY1Nac1RPWU90T3lMemJJNHp5VQ?oc=5</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
@@ -3289,17 +3289,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>September 1 change: UAE announces new excise price rule for electronic smoking products - Gulf Business</t>
+          <t>More investments in Adnoc’s fleet, Indian IPOs, and Egypt’s North Coast - EnterpriseAM</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>News — FTA Announcements</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNMXNESjR5VDVIQ0Qwb0xKUk1xRlhaTmV2RjNfdVpGaDZZYk0wcjdSbC1RRHBUNkRRaGpNOS1mSjR1blVVRHJ6MzdLeUZXM1lMWURyX21CS25DZFN3engwRWZCOFFLUDJydEEwX0pSa1lLSlNqbVlhdk9pNmtvLUh1QzFubU9RVENUNEl3QVdLc2FkRUV6TGFjZmJwLUtiUVd5dlhjVW1SLU43WFI4eGNfZkJCTXBNaEQySVR3QjZuazA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1RdV9pa3ZIMmpRWnFlcXRaeTRnSy1zZUp0enVScm1nc0hMX3UwTEdEOG9oQy00UUJiSUR4WENleElGQVVmLXh3ZE10b09nQWphT0IzNHNJb0h3Q0E?oc=5</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
@@ -3334,17 +3334,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3354,12 +3354,12 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>UAE small businesses claiming tax relief must still file corporate tax returns - Emirates 24|7</t>
+          <t>FTA Directive No. 5 of 2026 - Crowe</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>News — FTA Announcements</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOLXJ6YVV3T2dXazExeU04V09UYlk3NmtYT2d3Z2t1X2RPckN0RjVQZE9oNTljdi1rUUlzTDlMalotZ1JWRS03TWVFWlVVS1hyMVlDUEsxYWQ3RWgtdTdUNzVaZjE5WlhVVUhJcjkyaDFVa28yeEN2ejAtVG43dnduV2NDa0k4czRLby1sU2w2ZHZTcGtPZmpiTjRYWXB2VUExMnhreUktUDBZSkZ4LUxZYW9TYXRJc2s0U1QyMtIB1wFBVV95cUxPNWVmQzRQOEJkZnBCZVFDblE2dkFlX1hGNWlnalJBVk5QREJoU0ZvMXZIM1JJYXdLb2lQZFNnejliekY3Y29nN0tLdTUxQ0h0SUFaSVlpOWhuX3dVaHdjX3NPM1pkd2xlVDRMT1VmTHJ4QV9PbmpWRmVHRFpHZ1lyUF9ZWEJTcFJ2LS1QX0hEa0Y3dnJ4S054S211cWRMWWlHVVd2V19wQnhGa2JVR1ZxSFVNVWJMejdESlFZSkxUMGYwQUlyQkpueDlwb2dJYnlqQnZGNklscw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE40S0RnRzF2d1dBSmNHdkNNQXZQQmlOYWNOSk5OWnlVNUN3ZDB5UHBUV29RXzNvaF9pVFNQZ2FwTUdocGhxMXp1T3gxMUFycGNESFA1bXNR?oc=5</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
@@ -3379,17 +3379,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>UAE releases registration requirements for domestic minimum top-up tax - kpmg.com</t>
+          <t>Digital currency and VAT: New UAE rules for businesses to consider - thenationalnews.com</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>News — FTA Announcements</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPaGJWUy1MU0VZdmd3LTVPTmw0bDYtWlF5a3JCVkFwVnhJRUkxVkdEWUE4X1VZLXg0Tkg4YTlLWHhoOUJYVzJqR3lzUE5Pa1RpSWtjdkRDQ09UeDBoQ3Y2bGlLbkhzTXZ2WlNJeGFSLXNqRUZyRnBfNV9Mbk5UY25hdVZ6VWM2cWRYOEt4bUlnWV9QYkQtOWZudGJaV0ZJZDRVY2JGbTY1T1JTYVhyTGhEdlVuQzlzZkN6ZC1VRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQamI1MElzOEtNS1ZjVWR3VGpjZjNUZjBXbjQwZkJIZ3AwOFVqckl0WWFQN2JpaEg5XzRTUTBVMDFOeVhMaUZxYW9GUnBFNW55WnhKd2ZKOVZoekRBWUNqQkp3dGFPZ2JQcWY5SjVlRUJuTURfcVN5aUNXVmthdUh4cHlJbFNHN3lyT1VTU2l2Nk92U09JZFh3eXp0c29jTlJNZW1VLTZBR2h5WmdBTjFuNGczZkZwdDY1QWc?oc=5</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -3424,12 +3424,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3444,12 +3444,12 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>UAE Digital Economy: Why Trust, Not Speed, Now Wins The Race - Menafn</t>
+          <t>Air India turbulence injures passengers on Phuket-Delhi flight - Gulf Business</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNbi1OcWZwSTNNYjBRZkJWS1FodlVGTG5oZHB1T3Q2cGRqazRiZGQzeUtlOVB3VXlhNUM1TnhSdW1MVS1uSng1dGFmTlAzb3ZMNXlod0c5bWo2RkdOTW1idm9JQ3dQNTM5Z3FvZl96WlNuVVh4Mmx5NGFNWXBHVFZoWnUyQU9WT01idllWclJqTXE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOUk92b3hCQVZybGNndXNJOF9ZX0Z3TGl5NnRuXzE5NlBRb3czZXM2SkxXb3ZQSGNOdGo2a2U2b040ZVFDcFBqbzdvaFFZaVdBbFgwQkJOOEhDNzF6VXY1OU9Ca2t2Z1ZnQlhscXNXTVhDaWY3b2lvMUlEWFhkXzVxaDR3b191OUx2aTVKcEttYkFGTjRzRVpnbFJvLUZhYmNLTFJJNg?oc=5</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -3469,7 +3469,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Finance sets e-cigarette liquid excise price - Sharjah24</t>
+          <t>UAE Business: UAE extends small business relief for corporate tax until December 2029 - Gulf Daily News</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBGY1BCNkVheXBxM3RBdWlPNXVULWVaaWdWM3RWWU9JSWI2T3JVMGlMdl94Ync5ekFqdGU1SzAxeEMwaUhJR1hTejhVTFo4blI2Y1d5QzZUaVgwUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNVm43RXV5MWlfOTE5TjdqQjhtd3pzUnRIdmJycExNbXV6REpoRjQ5MlNiRENNemM5SG5VbUhJbnVXenhQXzFhRGgtNXE3QjRWWHhCcTJsZ0lfUW5ZTWNWcjdZQnZSSDM0VVdvVDY0ejBPMklPTUkzdTdXX090b1RQY21nbmdUQUtuZG42RHBxRWdCb05xNkdBT2xUVk1SNWN0cG1NbnhKNlBxSl96T3BzOU91cw?oc=5</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
@@ -3514,17 +3514,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3534,12 +3534,12 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>CBUAE injects more liquidity into the banking system - EnterpriseAM</t>
+          <t>UAE extends corporate tax relief for small businesses until 2029 - Khaleej Times</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPRVF2amFoSUlsRENGenUxcUlxRU9NeU9QWlJhUkExb1k0cExublF1YUdrM2dJc0FySm9zQmgyQUtKU092bkpYT1I1bUhaMkxGR2o2SFVnckhIR2d4RGQzOUJnb19tZERINThyZ0NrQ1A0WUttandLcmN0QUlUaTFVZ1djMnUxdEp4SmNGMjM1Zl9HX1k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNMDNwUlhpclFxaFJkdkkzR0s5MVh4WHZOUDdfZzZtNTBFb2RIcklxMF91Tkp2NGRxRlZMM3BubEZGc0g5LXpsQUhHQy01eGcxTllzc1k1S1NqeFMtYXM4YlBmREttNlhsS0hmd2JXN0l2UjFEQ3B5M1pfRTVpOGw0Z1pPMTNHd0tHQ25ZNjNGZmVaZnhzZUJueE9sQ2dNNGVaUDVjTdIBrAFBVV95cUxNbWJjeHFtRU9DbExyNHRRY1NEUXB2WnZRZ1V2TlFhQ010T3RhSmptR2ItaDhxVnEta0NITUJyS3ppaGgyQ2FkclQwRFhCaWNnLUhNb21YaDVGLWZZNThic2hpN0MzNTI4cXI3RjYtLVUzN3VHanJUUHdYaEFRWUlvS2w5UVdja3pwd1Q4c2pXWHVPZ0xZVmFCcE43eWl1bG10N0s4UXdpVUhpU0tH?oc=5</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
@@ -3559,17 +3559,17 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>The Taxation Society partners with Tally Solutions to strengthen UAE's finance and tax professional community - khaleejtimes.com</t>
+          <t>UAE extends corporate tax relief for small businesses until 2029 - thenationalnews.com</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNMXRpRGhpQXJvUkZhQU1IcTF6Z0JtLW16cTQ1d24zZWlwQTlPMHNCeG8tY0NLc1JGcXdjT2g5V01YM3hOVmtZYzBJeThiR3hhSDRpdGdwaDhsVC1WMDFTSWN0SWdhc3hiWTRSQmV0blZEZkowYWdoSU1BaUJ6Y01ZZ2ZrWlNRc2JtUllnc0huTF92aWdmbEp4bTRvRV9fN2xTU2dmMjdLSk43ZlFlcEtuWTBKQXdFTU5pMlRnWE55VFBwcTc0STRtcFluS3Ffek1oM2NRQ1dYemVkTktESkJRSVJ30gHqAUFVX3lxTE85ZnVhMjFKMWdhenV1YlFiRGtpVTBIdjRvLVNLRFBjTHBPUnVfeG5sUGxIcWVlSlhUTEVibFV2UXdWbEg5TGNmS3hBYnczSEctV3BBT2pZT3dpcDJUeGczWE9xQ1dweV9hc1hwQnhHQkFWUDRrb0FzV0tVdmZhZ0pLZC14YlVJZjBYQmcwbUZWeG55dnhpOFliT0wxYkQ0bzl1VEhiVUpQNjQ4TVN0bFhPRERROXB5NUZZQ0VRS08tY0VmSDdLRFQzMHZ0dEZtamJ5dmp1OGZ6SmNxQjZrck8wRWs2U1A0TFJZdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQOFMwcEtFYkFkbWxMRnBqX3Y1M2ZOcnJ4Q1FzTHg2b1NDYnU3dzVWMmMycVdhNzJSbTZhaTZ1bjRpN3RYcm9Gb3VIOUxydjN6anFTMU12SHNNcmt1YkhwSk1RVTV6Yk1yS0wtNm9PbVZLNkxmTVRNd3hEOW1xbXdnTlBiX0VJWWhINEw5MHc1eEk4UHhFZHFOZ04zcnZERDZhLXZJQ0VGWS15N080ZXBQYVhDMFU2al9wN1NlNXN2RnFaZEU?oc=5</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
@@ -3609,12 +3609,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>MoF extends Small Business Relief for corporate tax until end-2029 - Sharjah24</t>
+          <t>September 1 change: UAE announces new excise price rule for electronic smoking products - Gulf Business</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — FTA Announcements</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFA4N01YTUZ2UGRGVWdDQ3JDM3JLYWJDanVuckdCLVhuQUdqUFo3clA1cGRoTUtubWNpQ0dTOUFSQk5jYzdGcVFYNkNpQjF4ckFVZ2pBc0FXM1Ffa0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNMXNESjR5VDVIQ0Qwb0xKUk1xRlhaTmV2RjNfdVpGaDZZYk0wcjdSbC1RRHBUNkRRaGpNOS1mSjR1blVVRHJ6MzdLeUZXM1lMWURyX21CS25DZFN3engwRWZCOFFLUDJydEEwX0pSa1lLSlNqbVlhdk9pNmtvLUh1QzFubU9RVENUNEl3QVdLc2FkRUV6TGFjZmJwLUtiUVd5dlhjVW1SLU43WFI4eGNfZkJCTXBNaEQySVR3QjZuazA?oc=5</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
@@ -3654,12 +3654,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3669,12 +3669,12 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Northern Emirates’ property markets cool off + Sidara locks in USD 1.35 bn in firepower - EnterpriseAM</t>
+          <t>UAE small businesses claiming tax relief must still file corporate tax returns - Emirates 24|7</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — FTA Announcements</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOMDUxZXd1MElSNXdaNDByLW9jbHFIenJCY21PRnhPMUx4YkdyZ1FMREVxenNWZWZUY2p3MHQ5V2xUQmswZ1RuV1g3Q3RHUzdvOFhvOGpST2diQWIwOXFBeXdzc1lYRl9FRDIxdjBjUVR3Y2VEcUdIWXB0amg4YW5qbklORzFMS3J4VUZGelkybDVZcXc0VHlNck4zTXdjR1N1UzZmSk9vSFFoMDJMVENKMFVlWEdvUTEwZFhiZmdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOLXJ6YVV3T2dXazExeU04V09UYlk3NmtYT2d3Z2t1X2RPckN0RjVQZE9oNTljdi1rUUlzTDlMalotZ1JWRS03TWVFWlVVS1hyMVlDUEsxYWQ3RWgtdTdUNzVaZjE5WlhVVUhJcjkyaDFVa28yeEN2ejAtVG43dnduV2NDa0k4czRLby1sU2w2ZHZTcGtPZmpiTjRYWXB2VUExMnhreUktUDBZSkZ4LUxZYW9TYXRJc2s0U1QyMtIB1wFBVV95cUxPNWVmQzRQOEJkZnBCZVFDblE2dkFlX1hGNWlnalJBVk5QREJoU0ZvMXZIM1JJYXdLb2lQZFNnejliekY3Y29nN0tLdTUxQ0h0SUFaSVlpOWhuX3dVaHdjX3NPM1pkd2xlVDRMT1VmTHJ4QV9PbmpWRmVHRFpHZ1lyUF9ZWEJTcFJ2LS1QX0hEa0Y3dnJ4S054S211cWRMWWlHVVd2V19wQnhGa2JVR1ZxSFVNVWJMejdESlFZSkxUMGYwQUlyQkpueDlwb2dJYnlqQnZGNklscw?oc=5</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>ClearTax urges UAE businesses to prioritise execution assurance as e-invoicing decisions gather pace - Gulf News</t>
+          <t>UAE releases registration requirements for domestic minimum top-up tax - kpmg.com</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — FTA Announcements</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPTG13TFpCRmpaaWU3ZGxsVEtqakxUUXhSc0ltWUZfOEUyWTcxWGhOZ2doazNZY1V2LWFnSlp0NHpHTXN4emN6TzFWbGlXT09xU0Q3X25BTmpBVVl0Nl9XMFdRUE9HMy1BU3BMRDFIZ1RITkw4d3BSanluZGFHal9CM3h5dDNtTlBtUG9LYXZZWkhILVZhdUpKTHhUd2lMWmVOdVJrREx4UUF4WjNvTW5hSmtBVjVyQVBpblVKa1hKbjhxRTNUVmpUMVpXOFFJSWx1NUZWUWFMYlY2ZjA2Nml6OGV6X2ZGcVhkQkQ00gH-AUFVX3lxTE12b1Q4Qjd0Rks3U1hqOC1GVTZ5RXRUOXB6eVdVd3RMTEV5Q1pRYVRrc19GaG1qY3FXRGhqMkN3N3c2emJyeTFWbEU2QkRSMHR5aWFzNlctUi1mdi1vamRHMHZoWFZlQlRCbEhrT3BLSXlsTXRfYjY4QjVHblFRU0JnZVhlam4xNEF6d0hQVUtmTHFoYnktSW5LS3dqU2VleEh4azlObnoyUTNPd2E0RWc4U0ZhMkRoc1J1c2R6VGJhc1lSYTF0cjhzdnY0Q0tvYk81YnY5UE5CdnBXZTVNQXE4UlZwMkFjbUREaEtRNlF2MWJYVFhaOTFJNTZRUlJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPaGJWUy1MU0VZdmd3LTVPTmw0bDYtWlF5a3JCVkFwVnhJRUkxVkdEWUE4X1VZLXg0Tkg4YTlLWHhoOUJYVzJqR3lzUE5Pa1RpSWtjdkRDQ09UeDBoQ3Y2bGlLbkhzTXZ2WlNJeGFSLXNqRUZyRnBfNV9Mbk5UY25hdVZ6VWM2cWRYOEt4bUlnWV9QYkQtOWZudGJaV0ZJZDRVY2JGbTY1T1JTYVhyTGhEdlVuQzlzZkN6ZC1VRQ?oc=5</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>UAE extends small business tax relief until 2029 - theaccountant-online.com</t>
+          <t>UAE Digital Economy: Why Trust, Not Speed, Now Wins The Race - Menafn</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOMTA1XzlxbnpmYjNMcU01VXV1RjdMOHFuMi1CSVNMYXlaNW9kb2ZMSXZXOEZ1dDlqbmRLR2hXQjNrMDdlaU4teDVRTG1CMmJsY0lDU3V0SWxRZE4tWXZXbV9pR2o5THFMREVyZ3VpY1pTYVhFeUJza1MwOWtVYXB1ckwxQlBRdVF6eURUUHlkblhUNnNoQ3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNbi1OcWZwSTNNYjBRZkJWS1FodlVGTG5oZHB1T3Q2cGRqazRiZGQzeUtlOVB3VXlhNUM1TnhSdW1MVS1uSng1dGFmTlAzb3ZMNXlod0c5bWo2RkdOTW1idm9JQ3dQNTM5Z3FvZl96WlNuVVh4Mmx5NGFNWXBHVFZoWnUyQU9WT01idllWclJqTXE?oc=5</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Sovos Announces 2026 Partner of the Year Award Winners, Recognizing Excellence in Strategic Collaboration and Innovation - Business Wire</t>
+          <t>Ministry of Finance sets e-cigarette liquid excise price - Sharjah24</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxQRzJIdmQ3VjZqenlUTldPal9HNXdxdTJibTJHWFBhMVBMTWcxbm0yeUhJYzVLd0Z3Yl9pdE1LQzREWm13dXE4ZG1abDFuRkZIdHhIcm4zYXVoOXZIS01KNW5xRU04SUVwMlRnZlBxb3BYQkJMQ01CeXhabEI5U1VfSlpad0ROaVNnTUVnUll2WFhwMkxUa2tidGRxTDlMRm93SlAxVkNoWW84Zk1oeFFoNVdnOWRBZERIZzNSdnVDMGpHZ0MzSXlxZ1JXc2hodEY0aXNoRkNBRldSOGdxSkowdmFoTEplTjBtOUVfeWFtNmpzeDZtR3J2bVk4UWthWFR5VjJRbEM2NA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBGY1BCNkVheXBxM3RBdWlPNXVULWVaaWdWM3RWWU9JSWI2T3JVMGlMdl94Ync5ekFqdGU1SzAxeEMwaUhJR1hTejhVTFo4blI2Y1d5QzZUaVgwUQ?oc=5</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>UAE E Invoicing Guidelines Updated to Version 1.1 - Crowe</t>
+          <t>CBUAE injects more liquidity into the banking system - EnterpriseAM</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQOGUxa2xtLVY1ejE0azVCMEZSa3lxNHZmajhUdzh5LTQ5NGRqVk5oenBzNmJUSk44X1B0elZ5aDI5YVl4VHpLb2RzdEFRYW9IVmR5dHpOaE1JbWVoNzdvQVpsR0xIalA1MHBaR1NNOVpVSHUyX2t4R0dIVmZiWHlXWg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPRVF2amFoSUlsRENGenUxcUlxRU9NeU9QWlJhUkExb1k0cExublF1YUdrM2dJc0FySm9zQmgyQUtKU092bkpYT1I1bUhaMkxGR2o2SFVnckhIR2d4RGQzOUJnb19tZERINThyZ0NrQ1A0WUttandLcmN0QUlUaTFVZ1djMnUxdEp4SmNGMjM1Zl9HX1k?oc=5</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
@@ -3879,12 +3879,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>VAT, E-Invoicing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Congo Republic e-invoicing launched - vatcalc.com</t>
+          <t>The Taxation Society partners with Tally Solutions to strengthen UAE's finance and tax professional community - khaleejtimes.com</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOLTlBQUhqTDJya1ZpUmx5Y0lPRlRHb0VpWW5GYWVBc1JkTGRFbFl0b3N5UGJSdEdXRmwxdld1RlhqSWVremtIU1pWSHNXb2ROejA2TzJYcF9RX29TQVN1akJ5d0cxWFplcmJPYUJTRDgzU2FzenRzMzJldUsyaE9rbzlVUmJMSEc5M1pzSGtR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNMXRpRGhpQXJvUkZhQU1IcTF6Z0JtLW16cTQ1d24zZWlwQTlPMHNCeG8tY0NLc1JGcXdjT2g5V01YM3hOVmtZYzBJeThiR3hhSDRpdGdwaDhsVC1WMDFTSWN0SWdhc3hiWTRSQmV0blZEZkowYWdoSU1BaUJ6Y01ZZ2ZrWlNRc2JtUllnc0huTF92aWdmbEp4bTRvRV9fN2xTU2dmMjdLSk43ZlFlcEtuWTBKQXdFTU5pMlRnWE55VFBwcTc0STRtcFluS3Ffek1oM2NRQ1dYemVkTktESkJRSVJ30gHqAUFVX3lxTE85ZnVhMjFKMWdhenV1YlFiRGtpVTBIdjRvLVNLRFBjTHBPUnVfeG5sUGxIcWVlSlhUTEVibFV2UXdWbEg5TGNmS3hBYnczSEctV3BBT2pZT3dpcDJUeGczWE9xQ1dweV9hc1hwQnhHQkFWUDRrb0FzV0tVdmZhZ0pLZC14YlVJZjBYQmcwbUZWeG55dnhpOFliT0wxYkQ0bzl1VEhiVUpQNjQ4TVN0bFhPRERROXB5NUZZQ0VRS08tY0VmSDdLRFQzMHZ0dEZtamJ5dmp1OGZ6SmNxQjZrck8wRWs2U1A0TFJZdw?oc=5</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Corporate Governance in the UAE - Crowe</t>
+          <t>MoF extends Small Business Relief for corporate tax until end-2029 - Sharjah24</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Transfer Pricing</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE4weWRYb0VETFpvMjdhUG9BbU5Wb2JXbzNkLVpxSC1VZHhwYjMwT0F2OFNvQkJNQTFkOG1OamVFZWU0NWpVN3hHb0lldkJWLV9GeThwSjdzNlpnQXp0VDdQbkpnSWFFU3lacVJOeXl3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFA4N01YTUZ2UGRGVWdDQ3JDM3JLYWJDanVuckdCLVhuQUdqUFo3clA1cGRoTUtubWNpQ0dTOUFSQk5jYzdGcVFYNkNpQjF4ckFVZ2pBc0FXM1Ffa0k?oc=5</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Shopping online in the UAE? Tourists can now claim tax refunds on Noon orders - The Global Filipino Magazine</t>
+          <t>Northern Emirates’ property markets cool off + Sidara locks in USD 1.35 bn in firepower - EnterpriseAM</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNa1BKRVpJRVZCZm5VNVp2d3h4Rl92ejg0aml0Qy1pTUotYTZ4ZHlaeURMcnRacE9Zc0J2TWt4VktTQWdFV3BlNXBzWmlfMXFEZFRiYWRIMmV3X3ItaWc0T3pzOG52THI4c1RQaDY1RWdNbXItTTUtdlFTS1d6SUpZTVlXM2lOTWtLWXF6TGNSRE9OWkJQSUs3UXFoSEtOa2NpNEJLeTFOektldFVUVHk4cFJCSE5Qdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOMDUxZXd1MElSNXdaNDByLW9jbHFIenJCY21PRnhPMUx4YkdyZ1FMREVxenNWZWZUY2p3MHQ5V2xUQmswZ1RuV1g3Q3RHUzdvOFhvOGpST2diQWIwOXFBeXdzc1lYRl9FRDIxdjBjUVR3Y2VEcUdIWXB0amg4YW5qbklORzFMS3J4VUZGelkybDVZcXc0VHlNck4zTXdjR1N1UzZmSk9vSFFoMDJMVENKMFVlWEdvUTEwZFhiZmdn?oc=5</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
@@ -4014,12 +4014,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Number of retail outlets connected to Digital Tourist VAT Refund System reaches more than 19,300 - Big News Network.com</t>
+          <t>ClearTax urges UAE businesses to prioritise execution assurance as e-invoicing decisions gather pace - Gulf News</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNUjRVVzdLOXJQTXpUZDhqeWlQNDAwVDV2ZmJqd3h4cW5ZbXc0cHEzZGJBSWlLOTk0ZlFFbXlVSThCUEtxcGFqUHYzSlRmeXF0bC1XQ1J3VVhKUUkzeVBfNTc4cmQwNmlRYldwUU01YXpmc0pxT0daNWRpRUwtM0N3MlBBR09rRldZZlA5bXVJOXVTcVZSeE5ldWRHSWhna0ZfTTNwZWEwODlFTXRRYnRhOVJVcHJ3dDRuSnZtQlBhc0NMa2dhSzk4b1lBWEx5Uk5Ld2RMaFdmNUY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPTG13TFpCRmpaaWU3ZGxsVEtqakxUUXhSc0ltWUZfOEUyWTcxWGhOZ2doazNZY1V2LWFnSlp0NHpHTXN4emN6TzFWbGlXT09xU0Q3X25BTmpBVVl0Nl9XMFdRUE9HMy1BU3BMRDFIZ1RITkw4d3BSanluZGFHal9CM3h5dDNtTlBtUG9LYXZZWkhILVZhdUpKTHhUd2lMWmVOdVJrREx4UUF4WjNvTW5hSmtBVjVyQVBpblVKa1hKbjhxRTNUVmpUMVpXOFFJSWx1NUZWUWFMYlY2ZjA2Nml6OGV6X2ZGcVhkQkQ00gH-AUFVX3lxTE12b1Q4Qjd0Rks3U1hqOC1GVTZ5RXRUOXB6eVdVd3RMTEV5Q1pRYVRrc19GaG1qY3FXRGhqMkN3N3c2emJyeTFWbEU2QkRSMHR5aWFzNlctUi1mdi1vamRHMHZoWFZlQlRCbEhrT3BLSXlsTXRfYjY4QjVHblFRU0JnZVhlam4xNEF6d0hQVUtmTHFoYnktSW5LS3dqU2VleEh4azlObnoyUTNPd2E0RWc4U0ZhMkRoc1J1c2R6VGJhc1lSYTF0cjhzdnY0Q0tvYk81YnY5UE5CdnBXZTVNQXE4UlZwMkFjbUREaEtRNlF2MWJYVFhaOTFJNTZRUlJn?oc=5</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
@@ -4059,12 +4059,12 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -4074,12 +4074,12 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>UAE tourists can claim VAT refunds at 19,340 stores and on Noon purchases - Gulf News</t>
+          <t>UAE extends small business tax relief until 2029 - theaccountant-online.com</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQeDRPcDE4QjJaSFU3Qm1wRGVaWXl6cjY2c3YyVDF3TmtqN1RYMkh0WDdoSm56QmlXU21xSllRQWt4WHNFU09vUWZpTEd3dVVMb0UxNy0yZG1ucUF6aXhIZ2dWVXpkVjVqa2hHUGN3VHNZWEticFZMXzNfb2NzaVpwOFFkOVAtNDhBY0xjSUo3bkh0WUg2ZEJ4Q0JDU05Td0FTLWlUWXNfN2JKeGJsTEg3NGFDMzNwT21JZTFGT0V30gHQAUFVX3lxTE9wdElvSG52YzNWWUt6WGJaRkp0LXpmVHpQTFV4WHczVkQtOUhOMWpqRzd2UjgyQjNOSWdMT3QwM1luZzdtNWhXdU91R2lqS0FKcG1hUGExZ1QxWG1SSUo2cWZSWll0bjdpQ2pBOXFjTUMxcjJma0RraGlVbjNjajZRM0h4OVZfM0FUQXNERTQzQm1TS29QVjdiQzM2T19naktoTXhfQ1pvNmx4U2IxVkkxUWF5QmZ4QUxmMXB2bFVvR2RVWm10bjE2SlNaRzJ2VEU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOMTA1XzlxbnpmYjNMcU01VXV1RjdMOHFuMi1CSVNMYXlaNW9kb2ZMSXZXOEZ1dDlqbmRLR2hXQjNrMDdlaU4teDVRTG1CMmJsY0lDU3V0SWxRZE4tWXZXbV9pR2o5THFMREVyZ3VpY1pTYVhFeUJza1MwOWtVYXB1ckwxQlBRdVF6eURUUHlkblhUNnNoQ3c?oc=5</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Retail outlets linked to UAE's Digital Tourist VAT Refund System exceed 19,300 - Emirates 24|7</t>
+          <t>Sovos Announces 2026 Partner of the Year Award Winners, Recognizing Excellence in Strategic Collaboration and Innovation - Business Wire</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOcXRBMGsxX1Q5SkJXcEFwWnV3c0VVc19jUnRkWU5yMVlPelltaEhvOWNLcEJxYi1KUExWMVlmZE1FOExZYklsRHU4N3lQZGppMDRnYUFaRU1OWHdwaVpiWWowOENidVJjbDFPeTQyQklzOGM5bXhQbDJrRFg2TkR6bUplTzJNZzl2M3dJT2FEeHVTTVNtTml6UEdoZUFDcVRCZWFHMGg1ejZoSWI1UWFCLV9zREotcmF3V0HSAdQBQVVfeXFMT3Q0RFN0V3FRSlNWV20tMm5hY1N5VHBVWmxzdnZGVXIwZU92VTZVRDVUVkRZM0Q1U1ZNZzFRcFlEWTc2ckk0UjZhcEN4YmZIZndTd284ZDQ3Z2Z4OS1mVGFUX2RwRzgyMWViTjEyQ19wdUxucXEtZWtFRm5tOWpId1VYYlRmd1Rkc2tlb3Q3THR0THZxZWt3Q1ZyTGVvZ2hUUzZPeTBPSzlER3FXR0ZvUnJiWk5vdlpwYlYxdmZjZnNTVEQxM3hSY1pyTGV5Qkk2d2lrejQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxQRzJIdmQ3VjZqenlUTldPal9HNXdxdTJibTJHWFBhMVBMTWcxbm0yeUhJYzVLd0Z3Yl9pdE1LQzREWm13dXE4ZG1abDFuRkZIdHhIcm4zYXVoOXZIS01KNW5xRU04SUVwMlRnZlBxb3BYQkJMQ01CeXhabEI5U1VfSlpad0ROaVNnTUVnUll2WFhwMkxUa2tidGRxTDlMRm93SlAxVkNoWW84Zk1oeFFoNVdnOWRBZERIZzNSdnVDMGpHZ0MzSXlxZ1JXc2hodEY0aXNoRkNBRldSOGdxSkowdmFoTEplTjBtOUVfeWFtNmpzeDZtR3J2bVk4UWthWFR5VjJRbEM2NA?oc=5</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Indians, Russians, Turks top list of tourists claiming the most VAT refunds in UAE - khaleejtimes.com</t>
+          <t>UAE E Invoicing Guidelines Updated to Version 1.1 - Crowe</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPek9sY1dJUkpRblhiYnJDdDExOW1yREdXd1oyZ1Yxb0FnZlBYNTd3SUxGWnVMenlZVGlqRlIxLUszNk1Jd3BpcF9rVE9XLVF1OWdhY01fd0gteTJFRkVJLVREMjl4ZVRGZHJacUxJREpRN3UxdHFncGhITEQ0MnUzTkhKY2FSZnBnaFUzZDEyRnZOdG1hOWVFX2FLNG9Ca1lGekQzcllxd0FqTUhvTTRZM3MxcElQV0JaMWfSAcIBQVVfeXFMT2FPTEx4WGUzNUNhZWdBa1MzVU5GN1p3SkRwM0o5TWlqenhqVTNhR1Z0bThyN0laMS1tOUhfaG1qMmZpQi1pT3lTNEhKT2l3SklKZ1E3MXkyYVBrMnUwOTh1Y2RxSkFISUdlT1B6Qm1tTV9CUV9YM0xwcTJ2NzVmWUcxaFJ2YzhYeVBjZG1WSG9vcVc2N2tqRzNreHFwWVpaaUdncndzVEVLaE8zeHczU0Jvdl9FazU2NE1CNWZqQmZmekE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQOGUxa2xtLVY1ejE0azVCMEZSa3lxNHZmajhUdzh5LTQ5NGRqVk5oenBzNmJUSk44X1B0elZ5aDI5YVl4VHpLb2RzdEFRYW9IVmR5dHpOaE1JbWVoNzdvQVpsR0xIalA1MHBaR1NNOVpVSHUyX2t4R0dIVmZiWHlXWg?oc=5</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr"/>
@@ -4194,12 +4194,12 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>VAT, E-Invoicing</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>Tourists can now claim VAT refunds at 19,300 retail outlets across the UAE - Gulf Business</t>
+          <t>Congo Republic e-invoicing launched - vatcalc.com</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQV2tyUkVhVzNVUlZ0QW9LdW5PWV9OTEVSN1FHU2c0Um9qbTRDNXFIdmZUaERGcDFPUkkyTVpzWXBQblJHb1VzVERybTh5WkIzcnRoRFo1ZVBicVRMQXpFZXB3VVJRQVZ6UDNNZDItT1RuTXcxYWxtSU1PaGlPNTFNUnpzLXBGX2QxSy1WVjU4alg4Q0dEWmY4WFZ6cEt1a1FZQXpRODFFN0xRT3VwSWFfNw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOLTlBQUhqTDJya1ZpUmx5Y0lPRlRHb0VpWW5GYWVBc1JkTGRFbFl0b3N5UGJSdEdXRmwxdld1RlhqSWVremtIU1pWSHNXb2ROejA2TzJYcF9RX29TQVN1akJ5d0cxWFplcmJPYUJTRDgzU2FzenRzMzJldUsyaE9rbzlVUmJMSEc5M1pzSGtR?oc=5</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr"/>
@@ -4239,12 +4239,12 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>UAE tourists can now claim VAT refunds on eligible Noon online shopping purchases - Arabian Business</t>
+          <t>Corporate Governance in the UAE - Crowe</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE Transfer Pricing</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNSk0xOTlEQk5DQm4tczlCUE1jZ1dmamdsaUQ2TUYwWnlNd2JHMjhhVXZVUF8wNGpSVUFRNXhvU01pY01FMlUwWEt0anFyS3Q3QS0wa3BjZE1YLWtkWkpYeUJxVmlaSUhQM0Z3Mk9odUFYenhNRnBZeUkyQ0doNWJ2VGUySGY2dG9kMnlJaWhuWEMzb25aWjA1VXZkLWRwelk1MXJjbjBrV2F1Z29KZTJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE4weWRYb0VETFpvMjdhUG9BbU5Wb2JXbzNkLVpxSC1VZHhwYjMwT0F2OFNvQkJNQTFkOG1OamVFZWU0NWpVN3hHb0lldkJWLV9GeThwSjdzNlpnQXp0VDdQbkpnSWFFU3lacVJOeXl3?oc=5</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr"/>
@@ -4284,12 +4284,12 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>FTA issues five binding VAT directives on tax transactions - kpmg.com</t>
+          <t>Shopping online in the UAE? Tourists can now claim tax refunds on Noon orders - The Global Filipino Magazine</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQQXptRUZOQlpWYUZiNzd1QThPVDhlUGM3TF9PU3NKZjUyS2lucEZLUUFKZFpfZVhXLWxteTBKbU1OVEU1WXdPVlViT2ZBb2h5dmlHa0Z2bjd0SzMxa1p6TzF0ajhuVFVSaUpkczUxd1lzeGVCeDNwRnpPbXJVNVNGWHB4UTcwR2dCYTJoWTVSYkJGQmxRZE42cXNmOExtclgxR28tUUdYVFRzaE92?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNa1BKRVpJRVZCZm5VNVp2d3h4Rl92ejg0aml0Qy1pTUotYTZ4ZHlaeURMcnRacE9Zc0J2TWt4VktTQWdFV3BlNXBzWmlfMXFEZFRiYWRIMmV3X3ItaWc0T3pzOG52THI4c1RQaDY1RWdNbXItTTUtdlFTS1d6SUpZTVlXM2lOTWtLWXF6TGNSRE9OWkJQSUs3UXFoSEtOa2NpNEJLeTFOektldFVUVHk4cFJCSE5Qdw?oc=5</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr"/>
@@ -4329,12 +4329,12 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>UAE extends Corporate Tax Small Business Relief until end of 2029 - travelsdubai.com</t>
+          <t>Number of retail outlets connected to Digital Tourist VAT Refund System reaches more than 19,300 - Big News Network.com</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOYzFrN28yN3RDREhxYV9CVHl3UGU1NlpvSFJqaHJGWVpraVhEOEtqTnZVQk1OTjVjX1djWENocHdtYy1WY1dBSHZncjg3aGxWOXlwcFktaVVxYzBmZllLbzBaLUUxSEpyNW1HX3V5MG9YMWhTcjNfcnZxQ1JKRHZkMjlYSjlmUHk1SGFEYy0tYmlqWE96ajBqUnNSS19TUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNUjRVVzdLOXJQTXpUZDhqeWlQNDAwVDV2ZmJqd3h4cW5ZbXc0cHEzZGJBSWlLOTk0ZlFFbXlVSThCUEtxcGFqUHYzSlRmeXF0bC1XQ1J3VVhKUUkzeVBfNTc4cmQwNmlRYldwUU01YXpmc0pxT0daNWRpRUwtM0N3MlBBR09rRldZZlA5bXVJOXVTcVZSeE5ldWRHSWhna0ZfTTNwZWEwODlFTXRRYnRhOVJVcHJ3dDRuSnZtQlBhc0NMa2dhSzk4b1lBWEx5Uk5Ld2RMaFdmNUY?oc=5</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr"/>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>UAE seizes 3.58 million non-compliant excise goods - Gulf News</t>
+          <t>UAE tourists can claim VAT refunds at 19,340 stores and on Noon purchases - Gulf News</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOOF9vUDk3UXlsY19FUWtOOEJ2V3Awam9fY09zeS1seXpTUUt2Y05TQlVUVjlwYlVuX2hRN3JBM095eTlqZ3pxWWx5ZWJzUzV1bGdCQ21JMzd1bjRIMGRMdHpiZWVOM1lmOVdtSXlicW4wYUNoYjMySjFTNl9OTnRvYWZycGdhODlTcU9sQUpwUEdJcnltNF9nSXpBWkpJbjF0VG1qeVJqTdIBugFBVV95cUxPMDVISGFVMTVqWFFiS0VMTmlzZzlyWXRVUl9BTjBGaWgtS21lN05BdlppYlVNQkNtYmZWaHRIczNlSWRmbXBBdG9zamlobjFhTFh6R2lYZFJ1RUtKWGZqOWpNd21LTmNxaUF1SjVIUm9UNjF6cmwxUGY2ZHFIVHBFdVJNMXcyeFp3dUZ2V1hpVmtnRmZOY29nLWNWQmxsQ0tHUzd0RjRyRUlZeW1adThtZEpPVl9KT1pFRUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQeDRPcDE4QjJaSFU3Qm1wRGVaWXl6cjY2c3YyVDF3TmtqN1RYMkh0WDdoSm56QmlXU21xSllRQWt4WHNFU09vUWZpTEd3dVVMb0UxNy0yZG1ucUF6aXhIZ2dWVXpkVjVqa2hHUGN3VHNZWEticFZMXzNfb2NzaVpwOFFkOVAtNDhBY0xjSUo3bkh0WUg2ZEJ4Q0JDU05Td0FTLWlUWXNfN2JKeGJsTEg3NGFDMzNwT21JZTFGT0V30gHQAUFVX3lxTE9wdElvSG52YzNWWUt6WGJaRkp0LXpmVHpQTFV4WHczVkQtOUhOMWpqRzd2UjgyQjNOSWdMT3QwM1luZzdtNWhXdU91R2lqS0FKcG1hUGExZ1QxWG1SSUo2cWZSWll0bjdpQ2pBOXFjTUMxcjJma0RraGlVbjNjajZRM0h4OVZfM0FUQXNERTQzQm1TS29QVjdiQzM2T19naktoTXhfQ1pvNmx4U2IxVkkxUWF5QmZ4QUxmMXB2bFVvR2RVWm10bjE2SlNaRzJ2VEU?oc=5</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr"/>
@@ -4419,12 +4419,12 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>UAE Extends Small Business Relief for Corporate Tax to 2029 - tbreak.com</t>
+          <t>Retail outlets linked to UAE's Digital Tourist VAT Refund System exceed 19,300 - Emirates 24|7</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9icS1QSXhYc09ROHVJdzRtdXJTMEdLa0o5Mm5TZ3VxR002a3lTeFR5anZqRmNtcVEyQWxfQ050UFVOZnFBcFdwT1VoNGlVZU9xYkY2WkM5SlpSSnp6QkpHck5rTUxqOXNjNjM0UmFTQkFfOXZySFFON1pCSXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOcXRBMGsxX1Q5SkJXcEFwWnV3c0VVc19jUnRkWU5yMVlPelltaEhvOWNLcEJxYi1KUExWMVlmZE1FOExZYklsRHU4N3lQZGppMDRnYUFaRU1OWHdwaVpiWWowOENidVJjbDFPeTQyQklzOGM5bXhQbDJrRFg2TkR6bUplTzJNZzl2M3dJT2FEeHVTTVNtTml6UEdoZUFDcVRCZWFHMGg1ejZoSWI1UWFCLV9zREotcmF3V0HSAdQBQVVfeXFMT3Q0RFN0V3FRSlNWV20tMm5hY1N5VHBVWmxzdnZGVXIwZU92VTZVRDVUVkRZM0Q1U1ZNZzFRcFlEWTc2ckk0UjZhcEN4YmZIZndTd284ZDQ3Z2Z4OS1mVGFUX2RwRzgyMWViTjEyQ19wdUxucXEtZWtFRm5tOWpId1VYYlRmd1Rkc2tlb3Q3THR0THZxZWt3Q1ZyTGVvZ2hUUzZPeTBPSzlER3FXR0ZvUnJiWk5vdlpwYlYxdmZjZnNTVEQxM3hSY1pyTGV5Qkk2d2lrejQ?oc=5</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr"/>
@@ -4464,12 +4464,12 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>UAE extends corporate tax relief for small businesses until end of 2029 - Gulf News</t>
+          <t>Indians, Russians, Turks top list of tourists claiming the most VAT refunds in UAE - khaleejtimes.com</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNNEo4Tm9qN1dERmwzZ0tMR0ZOSUVQTkpOTTNiTDc1U2VaSTkyRkExekRzRjUzb2xrelYzV0oydU1qS2JCbHJXd1hxeWhPdmtUN1UtcXRCOHZpSXBxMlBMdFRKbDNxYlNFaVdwRXROTUVxWC1tZUpObDVIZzNVUDEzSUZpNkIxN3ctTDRNWU9xOUx6QXZieFdVV1hkNHhlcldHUzY5b21BZ1J2VTVhMlN2a1V5V1dJRkw1OTItdWo5Qzk5N2lPX1HSAdgBQVVfeXFMTmRQM08wYWhkelVySDhudHZWLWQyZ2lyUG9TNEJhWVV6ejAybDV6QXdvUFR5ZndxZldxWHVDMjRKVm1Ndm0yeE1HZHo1LXoyVFBzMkhuUDZESEw5RUFIaWlfNEdObjNxRlc4VFpOZVQ3RDhhellsdEpYN3pLVzl1d1Fva3R0RWpDb0d5cVN0Z3I3emowS2tNbkplWTh1Z2NvVkRMd0R3STNWV3hrUVFtd3hxdjQxWjI2ZU4wVE9JTzlsWVUwYXlPTmU4YWJmazMxQk93MHVHbGZE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPek9sY1dJUkpRblhiYnJDdDExOW1yREdXd1oyZ1Yxb0FnZlBYNTd3SUxGWnVMenlZVGlqRlIxLUszNk1Jd3BpcF9rVE9XLVF1OWdhY01fd0gteTJFRkVJLVREMjl4ZVRGZHJacUxJREpRN3UxdHFncGhITEQ0MnUzTkhKY2FSZnBnaFUzZDEyRnZOdG1hOWVFX2FLNG9Ca1lGekQzcllxd0FqTUhvTTRZM3MxcElQV0JaMWfSAcIBQVVfeXFMT2FPTEx4WGUzNUNhZWdBa1MzVU5GN1p3SkRwM0o5TWlqenhqVTNhR1Z0bThyN0laMS1tOUhfaG1qMmZpQi1pT3lTNEhKT2l3SklKZ1E3MXkyYVBrMnUwOTh1Y2RxSkFISUdlT1B6Qm1tTV9CUV9YM0xwcTJ2NzVmWUcxaFJ2YzhYeVBjZG1WSG9vcVc2N2tqRzNreHFwWVpaaUdncndzVEVLaE8zeHczU0Jvdl9FazU2NE1CNWZqQmZmekE?oc=5</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr"/>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>Small businesses in UAE urged to file corporate tax returns before deadline, says FTA - khaleejtimes.com</t>
+          <t>Tourists can now claim VAT refunds at 19,300 retail outlets across the UAE - Gulf Business</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOWnJlYmRmRm4xdy0xZ0toMUNUbnhTd3A5UW1pVzhFeXhIM2txamo4NU5qYVYwZGlQcEYwLTJhelBkOEdHajRYSE5PRnZtdmxGWmc0R2JlUVk0eVc0aW53NzdlM08zeWFzTUNocU9UcnY3UTNhTHVzZHhjRXFPZ0ZMMHMyRExEcjFiVVhKVzMxYk9FSHUxdERQRnUyZlJLWXA0ZVHSAaoBQVVfeXFMT3BwVV9lZzBQRTFjWUNVNEFzaUlhOUJuTHByVVRhdjRTbjdpajdOTjRtc2hfOEotMWlSb0FvX1F3azI2czNjMHREWnRJbFptM0F5ZHJkWUFsMW5fMDBsNU1YODgzT2VkMWZacU51MzkxaHJ0S216TF9UR241SnM0OVo2eHlDM0F6V2VfbUt4elZfZVBub2pLNW5fazhqV1hNUnBzRmkxS0NUQVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQV2tyUkVhVzNVUlZ0QW9LdW5PWV9OTEVSN1FHU2c0Um9qbTRDNXFIdmZUaERGcDFPUkkyTVpzWXBQblJHb1VzVERybTh5WkIzcnRoRFo1ZVBicVRMQXpFZXB3VVJRQVZ6UDNNZDItT1RuTXcxYWxtSU1PaGlPNTFNUnpzLXBGX2QxSy1WVjU4alg4Q0dEWmY4WFZ6cEt1a1FZQXpRODFFN0xRT3VwSWFfNw?oc=5</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr"/>
@@ -4554,12 +4554,12 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>UAE extends Corporate Tax relief until 2029 for businesses earning up to $817,000 - Arabian Business</t>
+          <t>UAE tourists can now claim VAT refunds on eligible Noon online shopping purchases - Arabian Business</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE5SM3FoRTVUSmJwTlpLbi1vOGFPM3RPcXpraXlCUG9iQlhuUUJ2MGRCczd6aDM0MFFNWS0yS2tNNVIxYjd2Y3AxWExhUnJNcHNXT3dLdGhyV2FBQUQwbmZ3YjRZc3NXTkNoLU5HTFRkTWRkSlZ6TEtHbg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNSk0xOTlEQk5DQm4tczlCUE1jZ1dmamdsaUQ2TUYwWnlNd2JHMjhhVXZVUF8wNGpSVUFRNXhvU01pY01FMlUwWEt0anFyS3Q3QS0wa3BjZE1YLWtkWkpYeUJxVmlaSUhQM0Z3Mk9odUFYenhNRnBZeUkyQ0doNWJ2VGUySGY2dG9kMnlJaWhuWEMzb25aWjA1VXZkLWRwelk1MXJjbjBrV2F1Z29KZTJ3?oc=5</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr"/>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Finance announces extension of small business relief for corporate tax purposes until 31 December 2029 - Zawya</t>
+          <t>FTA issues five binding VAT directives on tax transactions - kpmg.com</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOWVAwdTI2R09XSWRHaFNWYkNGdUJsSTNnaGpRandNeklubW8zM2h3VkNIcmRiQTVrZUxlSnhydWtqUGVTRS1vYVVQWWJfY2swUzhYOFJrdHVCQTlvTk1LNVBfWjBPbHZxWVU5Q0xQVWFHbTlLYlE0ek1aWFhqaUF3dDlTY2p2T0dtV3gzSXhaWkdFdWFBejA5ZkhDSkVPanZUWDk0d1oxNlJOUkNxMER2M1oyc3Nla2NnUW9WYmFRS04zeGlCcjQ1YVNZT2ZraU5EN0h2ZWRDaklZTjFQUklLWmRGRVFkUjhKUjBybHA5UktLZHFiVnUtOFpuNmhSZ0o3YVV3eld3WQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQQXptRUZOQlpWYUZiNzd1QThPVDhlUGM3TF9PU3NKZjUyS2lucEZLUUFKZFpfZVhXLWxteTBKbU1OVEU1WXdPVlViT2ZBb2h5dmlHa0Z2bjd0SzMxa1p6TzF0ajhuVFVSaUpkczUxd1lzeGVCeDNwRnpPbXJVNVNGWHB4UTcwR2dCYTJoWTVSYkJGQmxRZE42cXNmOExtclgxR28tUUdYVFRzaE92?oc=5</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr"/>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>FTA reminds small businesses to file corporate tax returns - Sharjah24</t>
+          <t>UAE extends Corporate Tax Small Business Relief until end of 2029 - travelsdubai.com</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5NZ1VTdFlkVERkd0pETmFiVUQzZzEySVNaeWFyV2N3MHdhSWZreEZnUDFCYXhiWGtCOVVxMFdWUzhDa3JCU1czenE3QzJzaG0tNU5iMkFmRFRsTUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOYzFrN28yN3RDREhxYV9CVHl3UGU1NlpvSFJqaHJGWVpraVhEOEtqTnZVQk1OTjVjX1djWENocHdtYy1WY1dBSHZncjg3aGxWOXlwcFktaVVxYzBmZllLbzBaLUUxSEpyNW1HX3V5MG9YMWhTcjNfcnZxQ1JKRHZkMjlYSjlmUHk1SGFEYy0tYmlqWE96ajBqUnNSS19TUQ?oc=5</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr"/>
@@ -4689,12 +4689,12 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>UAE extends small business relief for corporate tax until December 2029 - TradeArabia</t>
+          <t>UAE seizes 3.58 million non-compliant excise goods - Gulf News</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOc3RJWW11LUNyUERIeHh0dTVRVFJySzBoWVB0N1RCdVNpTVpORW03RkVXaG1pdk5HbWJfTDUzYXRIellIdlo4dVBXcXpuZHNrQXZRMk5MMGF1UkpqbGRTbXZRekZTYkU3cHpsdmJHdTVRdFFxSE1aSzZxWW1rb0RuT1RNZzVOWG91OGVTcFZVUGFVLWRUY3JsRnEtYkR4WUJjWnp6NkljSUd2NExsdUYtVA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOOF9vUDk3UXlsY19FUWtOOEJ2V3Awam9fY09zeS1seXpTUUt2Y05TQlVUVjlwYlVuX2hRN3JBM095eTlqZ3pxWWx5ZWJzUzV1bGdCQ21JMzd1bjRIMGRMdHpiZWVOM1lmOVdtSXlicW4wYUNoYjMySjFTNl9OTnRvYWZycGdhODlTcU9sQUpwUEdJcnltNF9nSXpBWkpJbjF0VG1qeVJqTdIBugFBVV95cUxPMDVISGFVMTVqWFFiS0VMTmlzZzlyWXRVUl9BTjBGaWgtS21lN05BdlppYlVNQkNtYmZWaHRIczNlSWRmbXBBdG9zamlobjFhTFh6R2lYZFJ1RUtKWGZqOWpNd21LTmNxaUF1SjVIUm9UNjF6cmwxUGY2ZHFIVHBFdVJNMXcyeFp3dUZ2V1hpVmtnRmZOY29nLWNWQmxsQ0tHUzd0RjRyRUlZeW1adThtZEpPVl9KT1pFRUE?oc=5</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr"/>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>UAE tax warning as thousands of businesses approach Corporate Tax deadline - Arabian Business</t>
+          <t>UAE Extends Small Business Relief for Corporate Tax to 2029 - tbreak.com</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBGbVZOWkkxM2FaVGlfeENJVWJXYzN6SDdmNk9nOFBYWWJDV3N6eGxVcnBRRXc5cDY5Qy1xSnNBQzVHMXR3NGpacEVucjlTMFRSaHc0dG5aZXc1aUVwSXlrTXhFTGd3RWNMbzVpWmdEVUZuUC1N?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9icS1QSXhYc09ROHVJdzRtdXJTMEdLa0o5Mm5TZ3VxR002a3lTeFR5anZqRmNtcVEyQWxfQ050UFVOZnFBcFdwT1VoNGlVZU9xYkY2WkM5SlpSSnp6QkpHck5rTUxqOXNjNjM0UmFTQkFfOXZySFFON1pCSXc?oc=5</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr"/>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>UAE reminds small businesses to file corporate tax returns even if no tax is due - Gulf News</t>
+          <t>UAE extends corporate tax relief for small businesses until end of 2029 - Gulf News</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOTm96UlB4Q2xPRlcybWNBanAtYXhxQkg0eHVCNDBvZlZGTWNGNzlSekNuVWZCU1JvOWR4MWxLanJMZEsyRms3NnZDSU90RnZuTkhad3pLLU1XX2VWV215T21HMTBmbVF1X0hmakhwM1BYZVNUQXZEV3A1UmR0QkZxVlJ1VDV5dGVMMFJFSGRxckpYVkVMMmFNMFBBdE9MZnlFSjJ3MDFXNzg2UXd0SUthQlZrd1Zjdy1JTVFkMEZlU0VKc3lzQW84VDBGLXFfVF93SnfSAeQBQVVfeXFMUEpicHFURTEyaDByTG44RGZUZ2R0MGJwRmdpV0hydzNTdkVYd0lFZzNITm9ueldCQ0JUZjZ3dW1TZ0xCSHM1S3c5eXExQlZac3V6bGd5Q1EzWFljOVRrZkJWRV9XcnFQWHdzRHQzWDRiUFhHaXlKMldlZHp5YW9zMHh2emxiX0R3MXdva2NFZ2JwcnVBZk52dEh2UEhvTW9FYzlJQ2xWdWZPQmpteFpaWnNUV0lpUTRiT0hNRXdHQVg1Q1VibWZqVWdocjBVVHJtVVFUbVFBdjJoRndFUS1aMTc5SEVh?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNNEo4Tm9qN1dERmwzZ0tMR0ZOSUVQTkpOTTNiTDc1U2VaSTkyRkExekRzRjUzb2xrelYzV0oydU1qS2JCbHJXd1hxeWhPdmtUN1UtcXRCOHZpSXBxMlBMdFRKbDNxYlNFaVdwRXROTUVxWC1tZUpObDVIZzNVUDEzSUZpNkIxN3ctTDRNWU9xOUx6QXZieFdVV1hkNHhlcldHUzY5b21BZ1J2VTVhMlN2a1V5V1dJRkw1OTItdWo5Qzk5N2lPX1HSAdgBQVVfeXFMTmRQM08wYWhkelVySDhudHZWLWQyZ2lyUG9TNEJhWVV6ejAybDV6QXdvUFR5ZndxZldxWHVDMjRKVm1Ndm0yeE1HZHo1LXoyVFBzMkhuUDZESEw5RUFIaWlfNEdObjNxRlc4VFpOZVQ3RDhhellsdEpYN3pLVzl1d1Fva3R0RWpDb0d5cVN0Z3I3emowS2tNbkplWTh1Z2NvVkRMd0R3STNWV3hrUVFtd3hxdjQxWjI2ZU4wVE9JTzlsWVUwYXlPTmU4YWJmazMxQk93MHVHbGZE?oc=5</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr"/>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>Federal Tax Authority wins SAP Global Innovation Award - SAP News Center</t>
+          <t>Small businesses in UAE urged to file corporate tax returns before deadline, says FTA - khaleejtimes.com</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYWE1ODFVeGZ2UEVVd0IyYXY0ckdPdFp4blEzcm9pZTZ5dm1MUDlocTNzNnd4dTh3cVhQb0o2aHJ2Y2VjTndrd2d6N2t1eW9OTzVtQ2JrcXVwN2NidFd2WUViQlRleTVQQXNpV2VvOVkyMFRINHhnNXpsUWdOcDhDUk1TbkpTajRkcUFGblBfWXhRZVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOWnJlYmRmRm4xdy0xZ0toMUNUbnhTd3A5UW1pVzhFeXhIM2txamo4NU5qYVYwZGlQcEYwLTJhelBkOEdHajRYSE5PRnZtdmxGWmc0R2JlUVk0eVc0aW53NzdlM08zeWFzTUNocU9UcnY3UTNhTHVzZHhjRXFPZ0ZMMHMyRExEcjFiVVhKVzMxYk9FSHUxdERQRnUyZlJLWXA0ZVHSAaoBQVVfeXFMT3BwVV9lZzBQRTFjWUNVNEFzaUlhOUJuTHByVVRhdjRTbjdpajdOTjRtc2hfOEotMWlSb0FvX1F3azI2czNjMHREWnRJbFptM0F5ZHJkWUFsMW5fMDBsNU1YODgzT2VkMWZacU51MzkxaHJ0S216TF9UR241SnM0OVo2eHlDM0F6V2VfbUt4elZfZVBub2pLNW5fazhqV1hNUnBzRmkxS0NUQVE?oc=5</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr"/>
@@ -4867,35 +4867,39 @@
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>official</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Finance Adopts “Aani” and “Jaywan” as New Payment Channels for Federal Service Fees and Fines</t>
+          <t>UAE extends Corporate Tax relief until 2029 for businesses earning up to $817,000 - Arabian Business</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Ministry of Finance — News</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>mof.gov.ae</t>
+          <t>news.google.com</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>https://mof.gov.ae/en/news/ministry-of-finance-adopts-aani-and-jaywan-as-new-payment-channels-for-federal-service-fees-and-fines/</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE5SM3FoRTVUSmJwTlpLbi1vOGFPM3RPcXpraXlCUG9iQlhuUUJ2MGRCczd6aDM0MFFNWS0yS2tNNVIxYjd2Y3AxWExhUnJNcHNXT3dLdGhyV2FBQUQwbmZ3YjRZc3NXTkNoLU5HTFRkTWRkSlZ6TEtHbg?oc=5</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr"/>
@@ -4908,35 +4912,39 @@
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>official</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Finance Announces Decision introduces a Minimum Excise Price for Liquids Used in Electronic Smoking Devices Effective 1 September 2026</t>
+          <t>Ministry of Finance announces extension of small business relief for corporate tax purposes until 31 December 2029 - Zawya</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Ministry of Finance — News</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>mof.gov.ae</t>
+          <t>news.google.com</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>https://mof.gov.ae/en/news/ministry-of-finance-announces-decision-introduces-a-minimum-excise-price-for-liquids-used-in-electronic-smoking-devices-effective-1-september-2026/</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOWVAwdTI2R09XSWRHaFNWYkNGdUJsSTNnaGpRandNeklubW8zM2h3VkNIcmRiQTVrZUxlSnhydWtqUGVTRS1vYVVQWWJfY2swUzhYOFJrdHVCQTlvTk1LNVBfWjBPbHZxWVU5Q0xQVWFHbTlLYlE0ek1aWFhqaUF3dDlTY2p2T0dtV3gzSXhaWkdFdWFBejA5ZkhDSkVPanZUWDk0d1oxNlJOUkNxMER2M1oyc3Nla2NnUW9WYmFRS04zeGlCcjQ1YVNZT2ZraU5EN0h2ZWRDaklZTjFQUklLWmRGRVFkUjhKUjBybHA5UktLZHFiVnUtOFpuNmhSZ0o3YVV3eld3WQ?oc=5</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr"/>
@@ -4949,7 +4957,11 @@
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>Corporate Tax</t>
@@ -4957,32 +4969,335 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>official</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Finance Announces Extension of Small Business Relief for Corporate Tax Purposes until 31 December 2029</t>
+          <t>FTA reminds small businesses to file corporate tax returns - Sharjah24</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Ministry of Finance — News</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>mof.gov.ae</t>
+          <t>news.google.com</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>https://mof.gov.ae/en/news/ministry-of-finance-announces-extension-of-small-business-relief-for-corporate-tax-purposes-until-31-december-2029/</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5NZ1VTdFlkVERkd0pETmFiVUQzZzEySVNaeWFyV2N3MHdhSWZreEZnUDFCYXhiWGtCOVVxMFdWUzhDa3JCU1czenE3QzJzaG0tNU5iMkFmRFRsTUU?oc=5</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr"/>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Tax</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>UAE extends small business relief for corporate tax until December 2029 - TradeArabia</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE Corporate Tax</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOc3RJWW11LUNyUERIeHh0dTVRVFJySzBoWVB0N1RCdVNpTVpORW03RkVXaG1pdk5HbWJfTDUzYXRIellIdlo4dVBXcXpuZHNrQXZRMk5MMGF1UkpqbGRTbXZRekZTYkU3cHpsdmJHdTVRdFFxSE1aSzZxWW1rb0RuT1RNZzVOWG91OGVTcFZVUGFVLWRUY3JsRnEtYkR4WUJjWnp6NkljSUd2NExsdUYtVA?oc=5</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Tax</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>UAE tax warning as thousands of businesses approach Corporate Tax deadline - Arabian Business</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE Corporate Tax</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBGbVZOWkkxM2FaVGlfeENJVWJXYzN6SDdmNk9nOFBYWWJDV3N6eGxVcnBRRXc5cDY5Qy1xSnNBQzVHMXR3NGpacEVucjlTMFRSaHc0dG5aZXc1aUVwSXlrTXhFTGd3RWNMbzVpWmdEVUZuUC1N?oc=5</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Tax</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>UAE reminds small businesses to file corporate tax returns even if no tax is due - Gulf News</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE Corporate Tax</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOTm96UlB4Q2xPRlcybWNBanAtYXhxQkg0eHVCNDBvZlZGTWNGNzlSekNuVWZCU1JvOWR4MWxLanJMZEsyRms3NnZDSU90RnZuTkhad3pLLU1XX2VWV215T21HMTBmbVF1X0hmakhwM1BYZVNUQXZEV3A1UmR0QkZxVlJ1VDV5dGVMMFJFSGRxckpYVkVMMmFNMFBBdE9MZnlFSjJ3MDFXNzg2UXd0SUthQlZrd1Zjdy1JTVFkMEZlU0VKc3lzQW84VDBGLXFfVF93SnfSAeQBQVVfeXFMUEpicHFURTEyaDByTG44RGZUZ2R0MGJwRmdpV0hydzNTdkVYd0lFZzNITm9ueldCQ0JUZjZ3dW1TZ0xCSHM1S3c5eXExQlZac3V6bGd5Q1EzWFljOVRrZkJWRV9XcnFQWHdzRHQzWDRiUFhHaXlKMldlZHp5YW9zMHh2emxiX0R3MXdva2NFZ2JwcnVBZk52dEh2UEhvTW9FYzlJQ2xWdWZPQmpteFpaWnNUV0lpUTRiT0hNRXdHQVg1Q1VibWZqVWdocjBVVHJtVVFUbVFBdjJoRndFUS1aMTc5SEVh?oc=5</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>Federal Tax Authority wins SAP Global Innovation Award - SAP News Center</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE Corporate Tax</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYWE1ODFVeGZ2UEVVd0IyYXY0ckdPdFp4blEzcm9pZTZ5dm1MUDlocTNzNnd4dTh3cVhQb0o2aHJ2Y2VjTndrd2d6N2t1eW9OTzVtQ2JrcXVwN2NidFd2WUViQlRleTVQQXNpV2VvOVkyMFRINHhnNXpsUWdOcDhDUk1TbkpTajRkcUFGblBfWXhRZVU?oc=5</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr"/>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>official</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>Ministry of Finance Adopts “Aani” and “Jaywan” as New Payment Channels for Federal Service Fees and Fines</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Ministry of Finance — News</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>mof.gov.ae</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>https://mof.gov.ae/en/news/ministry-of-finance-adopts-aani-and-jaywan-as-new-payment-channels-for-federal-service-fees-and-fines/</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr"/>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>official</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>Ministry of Finance Announces Decision introduces a Minimum Excise Price for Liquids Used in Electronic Smoking Devices Effective 1 September 2026</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Ministry of Finance — News</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>mof.gov.ae</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>https://mof.gov.ae/en/news/ministry-of-finance-announces-decision-introduces-a-minimum-excise-price-for-liquids-used-in-electronic-smoking-devices-effective-1-september-2026/</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr"/>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Tax</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>official</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>Ministry of Finance Announces Extension of Small Business Relief for Corporate Tax Purposes until 31 December 2029</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Ministry of Finance — News</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>mof.gov.ae</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>https://mof.gov.ae/en/news/ministry-of-finance-announces-extension-of-small-business-relief-for-corporate-tax-purposes-until-31-december-2029/</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/tax_updates_export.xlsx
+++ b/docs/tax_updates_export.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K108"/>
+  <dimension ref="A1:K113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -511,12 +511,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Dh5,000 fine for 1-day delay: UAE firms rush e-invoicing deadline - Khaleej Times</t>
+          <t>MoF announces updated administrative penalties related to the UAE eInvoicing system to enhance clarity and support business compliance - Zawya</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQQWhmSUVTODNEbHVMazVqOTdveVpnQVc1R0pTbzVlOFptck9OVlRzSXFjTmtnV2wzank2Mkw2NnM3dm5tRXVnSEpKVlpJeHBNejlmcHlza21QZlU3VDQtbFhFVHNUakg0NGhfRnJvVVBZdW9QZEhINUpZMy1qNVFuV0I1R29zS18xSTZIUzV0MnFPQnFQb3ozNmZSODFvUFpZX2RUR3d5UmFMZ1nSAasBQVVfeXFMUEFoZklFUzgzRGx1TGs1ajk3b3laZ0FXNUdKU281ZThabXJPTlZUc0lxY05rZ1dsM2p5NjJMNjZzN3ZubUV1Z0hKSlZaSXhwTXo5ZnB5c2ttUGZVN1Q0LWxYRVRzVGpINDRoX0Zyb1VQWXVvUGRISDVKWTMtajVRbldCNUdvc0tfMUk2SFM1dDJxT0JxUG96MzZmUjgxb1BaWV9kVEd3eVJhTGdZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxQdVpPVGZGSlI3MDZ3VXJTTzcyaWt2S1hTVktic3VjQ2VMeng0dTNFcFNhdS05TjkxZXg5TzNXVTNibUUtTFZpQi1BcUcyZzNKYlJFX2ZuOEt1X2pDTDlWWEh1bjJfYnZkSUZoMTNCNnlmYVBmSWpIT3NXRmt1TWx0c1FaQ3liYlhDZHNxSGQyUzk1V1JWWnlLbXlTVlYwSlJsVnlEVGE1Q2R5SEFqRGpDc0RUaV9PdzU0NGh4dThSaGthQVc5c1hZRjZtU0hpOUtua0lmam9udmFTZ3NkSWdRb3FlaHFmOXc1cW40YnptdXBDWHNoQlk1Q1VUdTNhclI3SjRzLWVxRHlZek1oZFpWX0k0TWU2c21XWERfRk4xRXBEcUk?oc=5</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -556,17 +556,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -576,12 +576,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>UAE Passes 25,000 Peppol Participants - sharedserviceslink</t>
+          <t>UAE streamlines VAT refunds for citizens building new homes as satisfaction hits 93% - Arabian Business</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE0ycm9haWtSX21lNk4yMkZESVBxVVFQTl96ajVERGZhUERTdS1faTZ5Ry02N3p0a0Znc0tnQVF5T2tHRjlYQzM5ZmZ4eVJDdWx1QzRDWFJTdzZubTdndlc0dmxtRkZQOEhoa19DWC05UjJMblZHTFNFVzR6WmhHSmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOWXYyQ1QtaHVtZXZZV205VDVQZTdGdUhZOUZOZE1STjVYdWdlMl9RNGV5ZUZtVFIyczQ4V0F0aEFCOTVGUXdKYU55amNBOWJmR2U2dnVRdnlydmdlZ1Z4TzF2TXJtOHJlMlFJaExFRzBLOWZ6SXpTczdudC10UkFxTzE1VC1oaDZEVFJmZ2dmdVdkMzk0T28zOGIxaExoN1g4b1lURGZiaGd0elNTVnZGbzVCazhKVEhhOURqdDdadng?oc=5</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -601,17 +601,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Himachal Pradesh Makes Electronic Payment of VAT Mandatory for All Registered Dealers; Amends Rule 37A of HP VAT Rules, 2005 - A2Z Taxcorp LLP</t>
+          <t>Federal Tax Authority holds Customer Council session in Dubai - Zawya</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQMWFMSHc1dFk0SXhSd2FsQWEzZk5vc2w2US12cEtZUkdjTWlsdWw3N2ZwbGw0Y2kzMnNGcnJvWUJrbFgtV1lHaHZnczNpUThZd1FJeEMtay1QR2s2R21STnk2aG54cGs2RUhRZFJ2eml3TFMxWTRDVzdCSFJEMFAxOTRra0JfS3dNeTBRT2xtWTFCNWpHM0U2QWtIYVp0MFdqYXpOYXJrZTUxWHZWN21Nbkp2elNhbWdtekI0TkktZEhOT1hIaXkxT2hDbkZvcFIyUTlTcVlBLWVwY1dwVUJV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNdzRGRGJMMHQwUGtsN1lORlVoeGhnWjRXT2djTzNDWUpzOUNjaWpSa2c2YjBGVzhvZm1qSW9lYjNVZWQtdGMzYVMxTlNxQ1FPckdEV2ppREZhbWlzNGlJd0tqeEVyTXdHVkVmby1Yajd3REF1MkVkenoybDNwbC1KR1pURFhBTGdDRXpaM2RLYl9Fb25CSzlhS2FDZWdORUJGTWpQWDd3aTBSdHF1YTBUNDU3Um5Lc0VFZWhQRk1uSnNyQQ?oc=5</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -646,12 +646,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Federal Tax Authority holds second session at Al Barsha Majlis as part of Emirates Majalis initiative “Closer to Each Other” - Zawya</t>
+          <t>UAE top-up tax deadline nears for multinationals with $800 million revenue - Arabian Business</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxOMWRFWVpfczR3aDdSTi1MMktYZXJraU5qdTAzWE1BSFA1UnF2RnJ5WWJ1V1hVVGZ3eTduZTFEdVFvWGQ2NENIbVdTeVhZQklVTzlkZkFUZGQweTBxOWMtc0toOG9ITjhzWVAyd1JfalJCcDhaV0RXYklVU24tYUxMcGRhTkd2ZTlmazdjbEVMLUItZEVYTVFqU3N0MExMTGVHbE5FQmQ0MkZGbF9nSHZXaGlMQTdyVnRsRF8xaEFVMEZRVExYQUd5dTRLNHlPWDVuVHRIS3Fjak0zV0pEZ29Yd2pmenlWVXY3OWFsSjlLM09KZnM0bjd3VERDSlNmQVVhWEY0dmFCcTk2UjBYUk5FdmZ2MA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQTFZnWXNReHhfaFJQbkIxNlJHOHQxYlUzX3J4d0xaQ0lqWTc2Rk9MeUJodEF6eEtjMmRzcEJDcmtoTGUzanRyX0kwTE1ycWZ5ZS1Uc0lNeHphTjdXeXU3YnpWdGNIVEk1cEUzYkJLMUxESE9xdHpLa0RJUVpQTWNvZlVna1lUa29SUXFsUlQxRnZDdkF0WnJnQnZCeHExOURzWlpRMGVMVjJuN0JLUkpKNTRQZw?oc=5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -691,17 +691,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -711,12 +711,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>A new era begins for VAT input tax due diligence in the UAE - Consultancy-me.com</t>
+          <t>The UAE’s foreign-ownership reform - The Arab Weekly</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPYnFTdmVUTW52ZWVOOHVISk5BaHJoMVVXZGd3cnpjZ1JySkJGRTRmWGxmU2FJX0pnSGNaeGJJREIxTGowWjhneDV2allRZ2dLU1dIVmdRWUd0X04tZ29Zc2JDUVJLUGNpZlU5X2JIUGNScXpyYmdMZURwWU1xa0VqMVNIbi1VQTh0RkJjZHFJdVI5T2ZZbzVJSTg0WHNWcUVpaURvWUF5T1jSAagBQVVfeXFMT2JxU3ZlVE1udmVlTjh1SEpOQWhyaDFVV2Rnd3J6Y2dSckpCRkU0ZlhsZlNhSV9KZ0hjWnhiSURCMUxqMFo4Z3g1dmpZUWdnS1NXSFZnUVlHdF9OLWdvWXNiQ1FSS1BjaWZVOV9iSFBjUnF6cmJnTGVEcFlNcWtFajFTSG4tVUE4dEZCY2RxSXVSOU9mWW81SUk4NFhzVnFFaWlEb1lBeU9Y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE5yZlA5ekZTR2g0VFBqdklkcHlpYWFtODd3QWZ1dEowY0tpbE42NDJ6Y2ZNRTFjMkpYUkhXWFVyck1YUnRnMkhsUFNObWtaaXc5Q3BDVVZzZTV4NFBWWlJOR1lHbGg3dw?oc=5</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -746,7 +746,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>VAT, E-Invoicing</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -756,12 +756,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>UAE electronic invoicing deadlines announced - Global VAT Compliance</t>
+          <t>Dh5,000 fine for 1-day delay: UAE firms rush e-invoicing deadline - Khaleej Times</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPREZqVWFCZklDbHRZeXBpN29mbl9NSWQ2T2lfZjJqV3lzenV2WE1zWkFjOTRUMXJXRzdyRDNpSC12cDJoVUxSSHZWbG1EOEZUNVNHN1Y3czhCY0VOTzRDY3E2YWVZY3dVMFhUaHZNdnpUMG04YThMOVFJTGlRYW9RNGdKNThrOUVLRHJTbjRn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQQWhmSUVTODNEbHVMazVqOTdveVpnQVc1R0pTbzVlOFptck9OVlRzSXFjTmtnV2wzank2Mkw2NnM3dm5tRXVnSEpKVlpJeHBNejlmcHlza21QZlU3VDQtbFhFVHNUakg0NGhfRnJvVVBZdW9QZEhINUpZMy1qNVFuV0I1R29zS18xSTZIUzV0MnFPQnFQb3ozNmZSODFvUFpZX2RUR3d5UmFMZ1nSAasBQVVfeXFMUEFoZklFUzgzRGx1TGs1ajk3b3laZ0FXNUdKU281ZThabXJPTlZUc0lxY05rZ1dsM2p5NjJMNjZzN3ZubUV1Z0hKSlZaSXhwTXo5ZnB5c2ttUGZVN1Q0LWxYRVRzVGpINDRoX0Zyb1VQWXVvUGRISDVKWTMtajVRbldCNUdvc0tfMUk2SFM1dDJxT0JxUG96MzZmUjgxb1BaWV9kVEd3eVJhTGdZ?oc=5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -786,12 +786,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Why UK founders are moving their business to Dubai in 2026 - BusinessCloud</t>
+          <t>UAE Passes 25,000 Peppol Participants - sharedserviceslink</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNSk5QTTg0RVJHQ3Y3Y2h4d01nRW1QMF9iRGlZRnZkazR2LWszX0VkMHk1YlY0TkQ3bzNEX2pkazNROUZ1cTRNbWtXQ3FLbWZaV0xURTYwci1FTV9NaFF5RFY5WXRYY3kxeWRzTHlwZzRBZUNKMmI3bTBtV3dYblVGLUl0cmx6VnRweUxYT1Uxekk0SUk0eTZV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE0ycm9haWtSX21lNk4yMkZESVBxVVFQTl96ajVERGZhUERTdS1faTZ5Ry02N3p0a0Znc0tnQVF5T2tHRjlYQzM5ZmZ4eVJDdWx1QzRDWFJTdzZubTdndlc0dmxtRkZQOEhoa19DWC05UjJMblZHTFNFVzR6WmhHSmc?oc=5</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -826,17 +826,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Prefortune Technologies Announces Odoo UAE Peppol E-Invoicing - openPR.com</t>
+          <t>Himachal Pradesh Makes Electronic Payment of VAT Mandatory for All Registered Dealers; Amends Rule 37A of HP VAT Rules, 2005 - A2Z Taxcorp LLP</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQVG9nYjRRdy1xYVZ3cEU4ajVEd3dpaXJYNWNpWFB5eG5Ia054ejBUa0VkNVMwb1I4TUVQdkl3STFTcG9fMS1ObVRHTV91eng2SHBiVGtIZGRZVlRVOHAyVDVoLUJONTlDRDkyaTRocno5M0lwcVBfS283N1lEY0t5eWd0Rld6MzkybWktZEtqWXlaN0w4c2xzbzFzT1NiQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQMWFMSHc1dFk0SXhSd2FsQWEzZk5vc2w2US12cEtZUkdjTWlsdWw3N2ZwbGw0Y2kzMnNGcnJvWUJrbFgtV1lHaHZnczNpUThZd1FJeEMtay1QR2s2R21STnk2aG54cGs2RUhRZFJ2eml3TFMxWTRDVzdCSFJEMFAxOTRra0JfS3dNeTBRT2xtWTFCNWpHM0U2QWtIYVp0MFdqYXpOYXJrZTUxWHZWN21Nbkp2elNhbWdtekI0TkktZEhOT1hIaXkxT2hDbkZvcFIyUTlTcVlBLWVwY1dwVUJV?oc=5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -871,17 +871,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>From readiness to implementation: 7 steps UAE SMEs should take for e-invoicing - Khaleej Times</t>
+          <t>Federal Tax Authority holds second session at Al Barsha Majlis as part of Emirates Majalis initiative “Closer to Each Other” - Zawya</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQUkNGMUtUUW55SjEwUnhUYjBycXVyOW9SS1Z0RGFVcTl3VWVMWlMxQ3E3WV95MWt4RUdoOHRQTmxDLXV4Yk1qMjdWUnJxSUNxVURUTWxrd2pWdDBBREZRZGNEVTZvSlB2Z0FuOFZFbGdKX05tT0tFeGx0SHVRQVdWaGE4UU1kdlhVYkZFQzF0R1lFOC0tNTBQTXBybUVLVFNHVEZyMnFwa1RVRUVUakExY0o5Wm80b2RJbFIxNW5TclZpNm1Hanh2RTJOdkF6d9IB1gFBVV95cUxOdTA0Q0pDMnBiTFpZbkcxRnFwZXg3OXdmU0ZQdzBQNEd5ODNtb1VyWndTM3NhMkpQRTJqVVRldEdubm45X1RxTTFGTHl3MWFmZENMZXlxXzRJTXBEOTQ1SENNUkZ5Sk5DZU1OUEljVjFVNWF1NTBwOHNJZE92UFQxZ3hPSEtObXJMcVFieGVBejZneGdiTzJfLURXQXIyM1FwbnJibGFMUG84RkFJZGVPbjZEanhkWTlFT0ljR1MyYnRyYmZKMkMtVGs5VzJOZTlXTm5YcTJB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxOMWRFWVpfczR3aDdSTi1MMktYZXJraU5qdTAzWE1BSFA1UnF2RnJ5WWJ1V1hVVGZ3eTduZTFEdVFvWGQ2NENIbVdTeVhZQklVTzlkZkFUZGQweTBxOWMtc0toOG9ITjhzWVAyd1JfalJCcDhaV0RXYklVU24tYUxMcGRhTkd2ZTlmazdjbEVMLUItZEVYTVFqU3N0MExMTGVHbE5FQmQ0MkZGbF9nSHZXaGlMQTdyVnRsRF8xaEFVMEZRVExYQUd5dTRLNHlPWDVuVHRIS3Fjak0zV0pEZ29Yd2pmenlWVXY3OWFsSjlLM09KZnM0bjd3VERDSlNmQVVhWEY0dmFCcTk2UjBYUk5FdmZ2MA?oc=5</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -916,17 +916,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -936,12 +936,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>DP World appoints two independent directors to board - Gulf Business</t>
+          <t>A new era begins for VAT input tax due diligence in the UAE - Consultancy-me.com</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPX2QzdVpCMHdjWXN5M0ZHNEVvVEhGdFd1aEFHNnk1dXZ2ZWRKUHJLVG1pQ0hoTjVaRExrcXpyY2hTbkxFc3Z4aHgtMHB5ZHlValh4dGhNTjdvcnZzdzVDV3pKbUo2TW5HMGExa0hDcUZoSzctUUI5WDhIckx4N2tMVFo2WHpWUVp0NDIxQnNvV1hOX2NiTWZpdVJtelVFYW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPYnFTdmVUTW52ZWVOOHVISk5BaHJoMVVXZGd3cnpjZ1JySkJGRTRmWGxmU2FJX0pnSGNaeGJJREIxTGowWjhneDV2allRZ2dLU1dIVmdRWUd0X04tZ29Zc2JDUVJLUGNpZlU5X2JIUGNScXpyYmdMZURwWU1xa0VqMVNIbi1VQTh0RkJjZHFJdVI5T2ZZbzVJSTg0WHNWcUVpaURvWUF5T1jSAagBQVVfeXFMT2JxU3ZlVE1udmVlTjh1SEpOQWhyaDFVV2Rnd3J6Y2dSckpCRkU0ZlhsZlNhSV9KZ0hjWnhiSURCMUxqMFo4Z3g1dmpZUWdnS1NXSFZnUVlHdF9OLWdvWXNiQ1FSS1BjaWZVOV9iSFBjUnF6cmJnTGVEcFlNcWtFajFTSG4tVUE4dEZCY2RxSXVSOU9mWW81SUk4NFhzVnFFaWlEb1lBeU9Y?oc=5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -961,17 +961,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>VAT, E-Invoicing</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>FTA calls for compliance with e-Invoicing deadlines to avoid penalties - www.wam.ae</t>
+          <t>UAE electronic invoicing deadlines announced - Global VAT Compliance</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPUDNQWVptSk1uTm9rVFI3ZVYwV3dRMVdXSmJxZVkxZlhBd2FEa1ZaNlJsQzcwaU9tcFNjbTJEWEs5UGJTNzhoWVEyeF90a1ZPcmVJM2RLUDJ3VHRMVU9qZ1ZBbEhPVTNDaklkSkNyVllwVEZ3UTE1N3ExZWNZZWhzQ2p0MkoyQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPREZqVWFCZklDbHRZeXBpN29mbl9NSWQ2T2lfZjJqV3lzenV2WE1zWkFjOTRUMXJXRzdyRDNpSC12cDJoVUxSSHZWbG1EOEZUNVNHN1Y3czhCY0VOTzRDY3E2YWVZY3dVMFhUaHZNdnpUMG04YThMOVFJTGlRYW9RNGdKNThrOUVLRHJTbjRn?oc=5</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1006,17 +1006,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>UAE e-invoicing deadline: Businesses have until October 30 to meet first requirement - Gulf News</t>
+          <t>Why UK founders are moving their business to Dubai in 2026 - BusinessCloud</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQVlFDSEtCd1I4TTB1M2NIQlBtSUtHWEJGelF2aTctaVpIQzRtcTRDWkt5dkFwRFA3ZHVZc1N0RWF6UzYzMzd2TUJQdXZ3MGpFaE9IOUtrenFhLThTNjByTlpnQ0laeHJXMVpJZ25fcmxGUmRmb0ViRW1DRFJmV3M2elhTWllZM3M4TzNXS01SQjVldDVvTnFDbkdjaVlCcGV2VHAzSnFfS29ldVNRUVJEUU9iTnRqS1ZlemJZNEhhY3RvakY1RGNjd2VpR0R0Z9IB4AFBVV95cUxNSUF6V3NtcTJFd0tRQ1FQbTlxbmdwLXVCd3hlcE05amFITks4Z2RaT0I5Znp2UUN3UjNpbWlKVWNXQ2YydkpjUVBQaHdqZVFQM2tpM0xYWlV5bU1tN3QxbnpwRDhUVmliNmU3dnJ4Uk56ejRuaG1NSWNrRnZFc0gtYTJubVdSaUIxX2Q5TmRmWEZIMkFwTDc0UFpJSWo3TVhtTnBZRzl1RExGTWU5N2l3Y1FmRmd2RU9JUU9WY1dvaWZQdlZQWUpYbC1pY2VFemRJbUVPQ2tWb2cxenVHTFpRSw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNSk5QTTg0RVJHQ3Y3Y2h4d01nRW1QMF9iRGlZRnZkazR2LWszX0VkMHk1YlY0TkQ3bzNEX2pkazNROUZ1cTRNbWtXQ3FLbWZaV0xURTYwci1FTV9NaFF5RFY5WXRYY3kxeWRzTHlwZzRBZUNKMmI3bTBtV3dYblVGLUl0cmx6VnRweUxYT1Uxekk0SUk0eTZV?oc=5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>MIDDLE EAST TAX ALERT | UAE | e-Invoicing Guidelines Version 2.0 - Alvarez &amp; Marsal</t>
+          <t>Prefortune Technologies Announces Odoo UAE Peppol E-Invoicing - openPR.com</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPeGtIWGRjTmV2SWU5UkpsektaSno5VVpYVGlpcmdUYW0zNW9lalJfeGk4Y0dacFNQaWZ1dWFpRkVmYTh2SWF5c3ExTW50eUxuNXRLblhLcl9xRWx4aWlYRm14eEFIMTM3UHJ5XzBZNktjRHFuNWFXbEVwWWhGdkhyTDNLbVJscWdXemU3RlhrcncyMHkzckRyV0wxdGRQY254Z1NXUHNfV1JhSkZ2b005WjVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQVG9nYjRRdy1xYVZ3cEU4ajVEd3dpaXJYNWNpWFB5eG5Ia054ejBUa0VkNVMwb1I4TUVQdkl3STFTcG9fMS1ObVRHTV91eng2SHBiVGtIZGRZVlRVOHAyVDVoLUJONTlDRDkyaTRocno5M0lwcVBfS283N1lEY0t5eWd0Rld6MzkybWktZEtqWXlaN0w4c2xzbzFzT1NiQQ?oc=5</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1096,32 +1096,32 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Cyprus tax alerts - Deloitte</t>
+          <t>From readiness to implementation: 7 steps UAE SMEs should take for e-invoicing - Khaleej Times</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>News — Big 4 UAE Tax Commentary</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPR3dMcm02YVpKS2NHZC1YZlJaV2VXZHJMYjNzVzRNa0NfSDNXaFhJcUNseDFYaUVRNVNpdmd5Rm1jbE04d2psTWRBMjZrOUxQQ19fOXdSeXF5cXpPN3NYRWxqMEJ0aFNGcWl4OTJfSU9mSnNxRXRXZHFxY3ZfaHJrNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQUkNGMUtUUW55SjEwUnhUYjBycXVyOW9SS1Z0RGFVcTl3VWVMWlMxQ3E3WV95MWt4RUdoOHRQTmxDLXV4Yk1qMjdWUnJxSUNxVURUTWxrd2pWdDBBREZRZGNEVTZvSlB2Z0FuOFZFbGdKX05tT0tFeGx0SHVRQVdWaGE4UU1kdlhVYkZFQzF0R1lFOC0tNTBQTXBybUVLVFNHVEZyMnFwa1RVRUVUakExY0o5Wm80b2RJbFIxNW5TclZpNm1Hanh2RTJOdkF6d9IB1gFBVV95cUxOdTA0Q0pDMnBiTFpZbkcxRnFwZXg3OXdmU0ZQdzBQNEd5ODNtb1VyWndTM3NhMkpQRTJqVVRldEdubm45X1RxTTFGTHl3MWFmZENMZXlxXzRJTXBEOTQ1SENNUkZ5Sk5DZU1OUEljVjFVNWF1NTBwOHNJZE92UFQxZ3hPSEtObXJMcVFieGVBejZneGdiTzJfLURXQXIyM1FwbnJibGFMUG84RkFJZGVPbjZEanhkWTlFT0ljR1MyYnRyYmZKMkMtVGs5VzJOZTlXTm5YcTJB?oc=5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1141,14 +1141,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Other</t>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>World Tax Rankings Middle East 2027 released: challenger firms surge in UAE - International Tax Review</t>
+          <t>DP World appoints two independent directors to board - Gulf Business</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>News — Big 4 UAE Tax Commentary</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQUWp5dVloOUQ4anZfTkR4NnJUYkZYdk1ZU2xDb1h6ZE5Wb3pzRzVxQklBNi1tTC1KWndLRlhpdVBaQmJzZ0FaRFVsNUQ3VXFDOWlRSGRMY3FHM0djMk9TRVQweThXS0lsSmxGN0xOT3V4ckZVNjRuTzVMOGJBSjN0Q1lwOTEtSXBwcm9zTTZUc1MxbVRpd2tRMlFjTE41b0EwTFRxSUg0TjlDTm93RU9WUDJFYm9sS3UtVm5XdWhmTVhndTF1dDdNZHUtWDB6Y2RpeFd5bnk3UzV4VHdwckNra1BoRWk3OVQxMjM5TWFaVkRlSjQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPX2QzdVpCMHdjWXN5M0ZHNEVvVEhGdFd1aEFHNnk1dXZ2ZWRKUHJLVG1pQ0hoTjVaRExrcXpyY2hTbkxFc3Z4aHgtMHB5ZHlValh4dGhNTjdvcnZzdzVDV3pKbUo2TW5HMGExa0hDcUZoSzctUUI5WDhIckx4N2tMVFo2WHpWUVp0NDIxQnNvV1hOX2NiTWZpdVJtelVFYW8?oc=5</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1186,32 +1186,32 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Cross-border Tax Talks - PwC</t>
+          <t>FTA calls for compliance with e-Invoicing deadlines to avoid penalties - www.wam.ae</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>News — Big 4 UAE Tax Commentary</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNajMxUTZjZ2tOVUFvYThvdWY2RmE1UmFoV05XbTR1ak5FUXB5Z3FRV2RKdGtuVzZhR1Jva1lKQU5IUmVDMlo1dzNSQlc4TExYbkRudlZQT1haTXZWOGNmXzFPTF90c0luOFNrbWZxa0t5VElhM3NOY21CaS11UmFfVFdtVlRON1hRYjlDY2UxMFR2YVhBQno5Mk05NmJFel9DQXl2RXNsZWxhTTZxMmtycHJtNkdDWjNxX3Y2QU1TWTV5MEFTZFhJQw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPUDNQWVptSk1uTm9rVFI3ZVYwV3dRMVdXSmJxZVkxZlhBd2FEa1ZaNlJsQzcwaU9tcFNjbTJEWEs5UGJTNzhoWVEyeF90a1ZPcmVJM2RLUDJ3VHRMVU9qZ1ZBbEhPVTNDaklkSkNyVllwVEZ3UTE1N3ExZWNZZWhzQ2p0MkoyQQ?oc=5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1231,17 +1231,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,12 +1251,12 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Federal Tax Authority issues new guide on scope and registration for Top-Up Tax on multinational enterprises - برق الإمارات</t>
+          <t>UAE e-invoicing deadline: Businesses have until October 30 to meet first requirement - Gulf News</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>News — FTA Announcements</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQaFhsTDBvVWFWcHJNaWQxdFZoWnpxN0ExT0EtNENrZng3TTh4UFVleDhwOFd3Q05OY09UaXUxNS12YXljOUd3WXl6MWVUdlY5RXhWc3pEYVhBRDZPbjNhX2U4VjJLcUtncVFwMnBZUE55M1ZLLWxhMzFZQnNRYTFleGo3SDhFYWpmYTJ4dWg2dTEyNUkyT3JVQVZVa0JtcU5hdUNKZE52N25XdlNLckRWMThRQTRwQm5ZenFYUEFFYXVBeWhxMTlfNWFieFViR2FpSE84ZDVJcVR5VHhqbGVz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQVlFDSEtCd1I4TTB1M2NIQlBtSUtHWEJGelF2aTctaVpIQzRtcTRDWkt5dkFwRFA3ZHVZc1N0RWF6UzYzMzd2TUJQdXZ3MGpFaE9IOUtrenFhLThTNjByTlpnQ0laeHJXMVpJZ25fcmxGUmRmb0ViRW1DRFJmV3M2elhTWllZM3M4TzNXS01SQjVldDVvTnFDbkdjaVlCcGV2VHAzSnFfS29ldVNRUVJEUU9iTnRqS1ZlemJZNEhhY3RvakY1RGNjd2VpR0R0Z9IB4AFBVV95cUxNSUF6V3NtcTJFd0tRQ1FQbTlxbmdwLXVCd3hlcE05amFITks4Z2RaT0I5Znp2UUN3UjNpbWlKVWNXQ2YydkpjUVBQaHdqZVFQM2tpM0xYWlV5bU1tN3QxbnpwRDhUVmliNmU3dnJ4Uk56ejRuaG1NSWNrRnZFc0gtYTJubVdSaUIxX2Q5TmRmWEZIMkFwTDc0UFpJSWo3TVhtTnBZRzl1RExGTWU5N2l3Y1FmRmd2RU9JUU9WY1dvaWZQdlZQWUpYbC1pY2VFemRJbUVPQ2tWb2cxenVHTFpRSw?oc=5</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1276,17 +1276,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>APR, Korea's leading beauty company, showed an 11.8 billion won increase in operating profit in the - 매일경제</t>
+          <t>MIDDLE EAST TAX ALERT | UAE | e-Invoicing Guidelines Version 2.0 - Alvarez &amp; Marsal</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>News — IFRS Standards</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTFBtVnRiOXljUWlKOUtMcC0tQjNycVJxaGJMUTBPZXFwYkFPeHM1Q1R4eXhmNzZGMzhnbVFrNFNZSFAtMjRiYVB2TzNRVXJ2dW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPeGtIWGRjTmV2SWU5UkpsektaSno5VVpYVGlpcmdUYW0zNW9lalJfeGk4Y0dacFNQaWZ1dWFpRkVmYTh2SWF5c3ExTW50eUxuNXRLblhLcl9xRWx4aWlYRm14eEFIMTM3UHJ5XzBZNktjRHFuNWFXbEVwWWhGdkhyTDNLbVJscWdXemU3RlhrcncyMHkzckRyV0wxdGRQY254Z1NXUHNfV1JhSkZ2b005WjVR?oc=5</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1336,17 +1336,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Ind AS 118: Big Changes to Financial Reporting Soon - TradingView</t>
+          <t>Cyprus tax alerts - Deloitte</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>News — IFRS Standards</t>
+          <t>News — Big 4 UAE Tax Commentary</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPa3pEaDB3Q21YU3FhSFQ0ekVZc1pwT00zQXFTbGE1MXkzX3NjazJ5TGZXelg4WnZocTlUZzVDMWp1aFlzNk4yMHIwMGR2d3dBUldzem5pY2xtLUVZckJJa1Rfc0c4MnJxX0YxckZIZWNNY09LVnh5RFVGMko0VEdrSXh2ZWlTdjdsQVlHTWotcGs2X0w0ZVRPbmNyVDdEc085SVNsYjJCR1NkR3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPR3dMcm02YVpKS2NHZC1YZlJaV2VXZHJMYjNzVzRNa0NfSDNXaFhJcUNseDFYaUVRNVNpdmd5Rm1jbE04d2psTWRBMjZrOUxQQ19fOXdSeXF5cXpPN3NYRWxqMEJ0aFNGcWl4OTJfSU9mSnNxRXRXZHFxY3ZfaHJrNA?oc=5</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1371,27 +1371,27 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>UAE Publishes Monthly Fine for Businesses that Miss e-Invoicing Deadline - Legit News</t>
+          <t>World Tax Rankings Middle East 2027 released: challenger firms surge in UAE - International Tax Review</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — Big 4 UAE Tax Commentary</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOcmtkbU5IdUxaZFVXUXVJWno3dERSaEJ2X0xKbGlCSi1rVUt1TDNNQUdiTkcwdEN6YlR6Y1FpeU10WWY2aGhWQ3gycGFOcGRQTUdUbE5BTWxfOGtHcXRRejN6WWktN2FmbjZTTmpsUENidjNEaTktTkVSbVQxRDNBZHNoM3ltLVVjTnUtWC1MdTBXX0EtWWM4NnJwQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQUWp5dVloOUQ4anZfTkR4NnJUYkZYdk1ZU2xDb1h6ZE5Wb3pzRzVxQklBNi1tTC1KWndLRlhpdVBaQmJzZ0FaRFVsNUQ3VXFDOWlRSGRMY3FHM0djMk9TRVQweThXS0lsSmxGN0xOT3V4ckZVNjRuTzVMOGJBSjN0Q1lwOTEtSXBwcm9zTTZUc1MxbVRpd2tRMlFjTE41b0EwTFRxSUg0TjlDTm93RU9WUDJFYm9sS3UtVm5XdWhmTVhndTF1dDdNZHUtWDB6Y2RpeFd5bnk3UzV4VHdwckNra1BoRWk3OVQxMjM5TWFaVkRlSjQ?oc=5</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1416,27 +1416,27 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Dh5,000 fine a month: UAE firms have 5 days to appoint e-invoicing provider - Khaleej Times</t>
+          <t>Cross-border Tax Talks - PwC</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — Big 4 UAE Tax Commentary</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNTGtGYXoyUURCNlQzTzZldFhpUGJIb25mYjVQOXdsNXdDNVRQV1dZVW9EdFJ2aVNsRnQ4c1JsYjgzcWszU2JlbGNYa2p5SUl2UVptQnYyZ0hnQk9KM3BBS0VxNmY2d043bWEzb0ZPM3M1bks5RDFSQjlhNnNYMDRVMmU0SWFCQmZCU18wOWc4bG5yeVNIOE5Fazl4UU9sMjkxclROLVFvQ1l0ckFRaWhMRNIBuAFBVV95cUxNQjIyZmFMNm13T2dZMUpyOVplTWlrVTBEX3N2TS1iaGVQV2hSNFZXbkI4VW1DdDQ2ckcxSEtmRjA3YTA1Unc0dHY4WTBVRGNiRnlCN1RsRzFwQXl2bTJaaFhaYmptVDlQc0lkQ1RvNzViOW9nTGlxZUhnN21WcDBteXlHVm9mdXBqSXcyajhFdmYtZWt1MGlmamQwOEJkTUp6VDZsRkh5YnEyVjVGOHlmenRrb1psT1Vv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNajMxUTZjZ2tOVUFvYThvdWY2RmE1UmFoV05XbTR1ak5FUXB5Z3FRV2RKdGtuVzZhR1Jva1lKQU5IUmVDMlo1dzNSQlc4TExYbkRudlZQT1haTXZWOGNmXzFPTF90c0luOFNrbWZxa0t5VElhM3NOY21CaS11UmFfVFdtVlRON1hRYjlDY2UxMFR2YVhBQno5Mk05NmJFel9DQXl2RXNsZWxhTTZxMmtycHJtNkdDWjNxX3Y2QU1TWTV5MEFTZFhJQw?oc=5</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>UAE FTA urges e-Invoicing compliance as AED5,000 monthly penalty applies - Emirates 24|7</t>
+          <t>Federal Tax Authority issues new guide on scope and registration for Top-Up Tax on multinational enterprises - برق الإمارات</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — FTA Announcements</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQNFV2ZnJIZjdaTm1YS1RtRVN5UzZCZXNZcE9WOWlBV2U4d1BtQUg1SUNhcWJxWWRBRmZLVDl1SGNCbjhTdW1rRGFJUzhlX1dvQ2NkeldjNmdyNHNFLXAydHpUVG4yXzREQk1EN3l0cWpJZlo2RVBLQW5RZEFVMlQ5bXJ4eTBvSS1SVEtxd3RYUnppOUctcktBbTl3T2lOenVFcy1nN0VpaHk3QnQtZldlYzlIS3QxeTJCcDhwMW9xclRRVEtWNVZfZFdveF93UdIBzgFBVV95cUxQNFV2ZnJIZjdaTm1YS1RtRVN5UzZCZXNZcE9WOWlBV2U4d1BtQUg1SUNhcWJxWWRBRmZLVDl1SGNCbjhTdW1rRGFJUzhlX1dvQ2NkeldjNmdyNHNFLXAydHpUVG4yXzREQk1EN3l0cWpJZlo2RVBLQW5RZEFVMlQ5bXJ4eTBvSS1SVEtxd3RYUnppOUctcktBbTl3T2lOenVFcy1nN0VpaHk3QnQtZldlYzlIS3QxeTJCcDhwMW9xclRRVEtWNVZfZFdveF93UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQaFhsTDBvVWFWcHJNaWQxdFZoWnpxN0ExT0EtNENrZng3TTh4UFVleDhwOFd3Q05OY09UaXUxNS12YXljOUd3WXl6MWVUdlY5RXhWc3pEYVhBRDZPbjNhX2U4VjJLcUtncVFwMnBZUE55M1ZLLWxhMzFZQnNRYTFleGo3SDhFYWpmYTJ4dWg2dTEyNUkyT3JVQVZVa0JtcU5hdUNKZE52N25XdlNLckRWMThRQTRwQm5ZenFYUEFFYXVBeWhxMTlfNWFieFViR2FpSE84ZDVJcVR5VHhqbGVz?oc=5</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1521,12 +1521,12 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>DigiTax partners with Supy to help UAE restaurants adopt e-invoicing - Caterer Middle East</t>
+          <t>APR, Korea's leading beauty company, showed an 11.8 billion won increase in operating profit in the - 매일경제</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — IFRS Standards</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQOU1EY2p6d1B0WW9WUFljUmF4dzdCVnVMNE50QjZ0QkJDeUFNYy1DLWl5bU5hdVphdmtOMmNuenVqVHNacTRTeFZqbUFvS3VFOGMzUlZ6VFFsZnJ4V0MxWGZLWkJiT295aWxaaUFjeS14LWlDeE5UYWliQW9nMFRBVWZkUEdHMlp1NWNTN3NadG9LNUwzck5Ja1F3LUlrN2Q3V2RZcEhKY05vejA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTFBtVnRiOXljUWlKOUtMcC0tQjNycVJxaGJMUTBPZXFwYkFPeHM1Q1R4eXhmNzZGMzhnbVFrNFNZSFAtMjRiYVB2TzNRVXJ2dW8?oc=5</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>UAE e-invoicing: Oct 30 provider deadline looms for firms with Dhs50m+ revenue - Gulf Business</t>
+          <t>Ind AS 118: Big Changes to Financial Reporting Soon - TradingView</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — IFRS Standards</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNd1M0bzNJcTEybmx2M29pY01HRWxvUURNZmxjemd1WDByOGUzSDVmUW4xUnljZnRlQXZBYW1FdW5ubnd0N01wWTVpNjRDR2xzY0lWcGlDd2ZhLV9BNjZsOTJBME5jbTVoUkJUWjdYbVZjaGhoUktjWUYzNkdvRDNyMldoQXN0V3R2WGFOT0wwbkpSX1ZnTVE1YV8xdklwMlROQ2xiR01EU0xaNUlCYXV1TWFYT1FYUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPa3pEaDB3Q21YU3FhSFQ0ekVZc1pwT00zQXFTbGE1MXkzX3NjazJ5TGZXelg4WnZocTlUZzVDMWp1aFlzNk4yMHIwMGR2d3dBUldzem5pY2xtLUVZckJJa1Rfc0c4MnJxX0YxckZIZWNNY09LVnh5RFVGMko0VEdrSXh2ZWlTdjdsQVlHTWotcGs2X0w0ZVRPbmNyVDdEc085SVNsYjJCR1NkR3M?oc=5</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>UAE e-invoicing rules: Key deadlines for businesses in 2026 and 2027 - Arabian Business</t>
+          <t>UAE Publishes Monthly Fine for Businesses that Miss e-Invoicing Deadline - Legit News</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPMXU4Vm5ScFJWd2tINmI3WEI1X1pwRFU0R2NyYXFra1d1bXFFTWhiVExCdS16SVRNelZOSlB5SG5GaHZTZzhzendZZHV4aDc4WHMyZ2kzcTEwekZDNG0yenlUaWwzUEs4blp6bHlPYXRZMFZLQzZRbG5idHB0a3F0Sw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOcmtkbU5IdUxaZFVXUXVJWno3dERSaEJ2X0xKbGlCSi1rVUt1TDNNQUdiTkcwdEN6YlR6Y1FpeU10WWY2aGhWQ3gycGFOcGRQTUdUbE5BTWxfOGtHcXRRejN6WWktN2FmbjZTTmpsUENidjNEaTktTkVSbVQxRDNBZHNoM3ltLVVjTnUtWC1MdTBXX0EtWWM4NnJwQQ?oc=5</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>How tourists can claim UAE VAT refunds in one business day - Travels Dubai</t>
+          <t>Dh5,000 fine a month: UAE firms have 5 days to appoint e-invoicing provider - Khaleej Times</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQUWpQaFlPcE8tQ3ZpWVhKZHBmTGlzVWRtcmdXOWdxcDlGcjZnSWsxa193SXhyQ3duMFphOGt5a1lFRFhveGRpVmlUQ1I4cjhmQTN1aXh5Nks1anFfV0Zua0JBaG44T1lNTWZlRGhtWFRJZkRVV2F3MGJ0RnloVDMtQWlnZGdrQTRBUEVnQUEwYkU0dlhoT2Fn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNTGtGYXoyUURCNlQzTzZldFhpUGJIb25mYjVQOXdsNXdDNVRQV1dZVW9EdFJ2aVNsRnQ4c1JsYjgzcWszU2JlbGNYa2p5SUl2UVptQnYyZ0hnQk9KM3BBS0VxNmY2d043bWEzb0ZPM3M1bks5RDFSQjlhNnNYMDRVMmU0SWFCQmZCU18wOWc4bG5yeVNIOE5Fazl4UU9sMjkxclROLVFvQ1l0ckFRaWhMRNIBuAFBVV95cUxNQjIyZmFMNm13T2dZMUpyOVplTWlrVTBEX3N2TS1iaGVQV2hSNFZXbkI4VW1DdDQ2ckcxSEtmRjA3YTA1Unc0dHY4WTBVRGNiRnlCN1RsRzFwQXl2bTJaaFhaYmptVDlQc0lkQ1RvNzViOW9nTGlxZUhnN21WcDBteXlHVm9mdXBqSXcyajhFdmYtZWt1MGlmamQwOEJkTUp6VDZsRkh5YnEyVjVGOHlmenRrb1psT1Vv?oc=5</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1686,12 +1686,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1701,12 +1701,12 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>"Smarter and simpler": UAE speeds up VAT refunds for tourists shopping in Dubai - Tuko News</t>
+          <t>UAE FTA urges e-Invoicing compliance as AED5,000 monthly penalty applies - Emirates 24|7</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOR0ZWZkx0b2hxUzJfSlEwNEl4YWlSOEVreHVFZmEwMWxia2xYX1BxNThjczJ4bEk3S1lkRy1ZREZTV1FXNDZ2N29tcUxYVWxIZ3lZWkl4VHgtdUZ0QXYwcmFwMlVId19pX0lxWFpMT1hVVkxDZHIxR1NYemlyZ3Y2dG9Iczg3Q0tVcEtfVDlTVm9IQkxwMlQ1eEpRaUdBQmx5R0xQNXZ4QnotSHpYWnZYTlJYX3o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQNFV2ZnJIZjdaTm1YS1RtRVN5UzZCZXNZcE9WOWlBV2U4d1BtQUg1SUNhcWJxWWRBRmZLVDl1SGNCbjhTdW1rRGFJUzhlX1dvQ2NkeldjNmdyNHNFLXAydHpUVG4yXzREQk1EN3l0cWpJZlo2RVBLQW5RZEFVMlQ5bXJ4eTBvSS1SVEtxd3RYUnppOUctcktBbTl3T2lOenVFcy1nN0VpaHk3QnQtZldlYzlIS3QxeTJCcDhwMW9xclRRVEtWNVZfZFdveF93UdIBzgFBVV95cUxQNFV2ZnJIZjdaTm1YS1RtRVN5UzZCZXNZcE9WOWlBV2U4d1BtQUg1SUNhcWJxWWRBRmZLVDl1SGNCbjhTdW1rRGFJUzhlX1dvQ2NkeldjNmdyNHNFLXAydHpUVG4yXzREQk1EN3l0cWpJZlo2RVBLQW5RZEFVMlQ5bXJ4eTBvSS1SVEtxd3RYUnppOUctcktBbTl3T2lOenVFcy1nN0VpaHk3QnQtZldlYzlIS3QxeTJCcDhwMW9xclRRVEtWNVZfZFdveF93UQ?oc=5</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1746,12 +1746,12 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>UAE launches paperless, AI-powered VAT refund app for tourists - Khaleej Times</t>
+          <t>DigiTax partners with Supy to help UAE restaurants adopt e-invoicing - Caterer Middle East</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNZWdmNWZuVEo5Uk9mUEQybHRrODZ4M1plWloxXy0wWDRtMlp0WDdlVzkzOEgzMHNxdm1kSXJZcWZSVklxX0pKV3dHSnhMOEs3aXFZYzUwSXdxa2JFcXphbnhmVG10cHJURUFaVkw0dHk5RHF3b0o0QklQQ1ZoNVE3UXRMNnhsbTJyUDdRbDBKTmlhVFdTSUVEN2RXc9IBowFBVV95cUxNbmFfQTNJbmpFSVhLcndEbHQxcGVqcnhzSEVnenJod09jelNLSHVSLVE4dVdtTHlHOFMtcmRjTVVnd2p5cU0ycEFEbWdHbVVoVWdGbVRvRUh5WGpGT0xQVWRaUklXdloySmd2QWRYNlV5UFlPYWhnRF9KM2tsWl9wek9RQ1ZuVVRWaXJkb3F4cHVCMkhfMDFOU0NGNTQtOFV4MGhv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQOU1EY2p6d1B0WW9WUFljUmF4dzdCVnVMNE50QjZ0QkJDeUFNYy1DLWl5bU5hdVphdmtOMmNuenVqVHNacTRTeFZqbUFvS3VFOGMzUlZ6VFFsZnJ4V0MxWGZLWkJiT295aWxaaUFjeS14LWlDeE5UYWliQW9nMFRBVWZkUEdHMlp1NWNTN3NadG9LNUwzck5Ja1F3LUlrN2Q3V2RZcEhKY05vejA?oc=5</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -1776,12 +1776,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>UAE Launches AI-Powered Tax Refund App For Tourists At Three Major Airports - Travel and Leisure Asia</t>
+          <t>UAE e-invoicing: Oct 30 provider deadline looms for firms with Dhs50m+ revenue - Gulf Business</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNeXpZdm5uSHczcUh4UGJ1LU1kWUpJaVBKTFVrcVBBWlVrSlI4aWJzbGRTWHp0bkVQNWlMQ3dWUU44LUpqOTloZjZoN1JEeWwwSHg2YXk3Wm5xOEJTNklQb05UZHBUeUdETWxWWHlvT0dtVEVwODNwZWpFN1RPRzVkWFlYWk9BNExmU0pibXlJY1FFalQzbXVrUk9IMGZ1clhCSEdrTU55YkZ3dXBob2VzcXBsbC1qTm9OQS05d0ZTOWFySjjSAcMBQVVfeXFMTXl6WXZubkh3M3FIeFBidS1NZFlKSWlQSkxVa3FQQVpVa0pSOGlic2xkU1h6dG5FUDVpTEN3VlFOOC1Kajk5aGY2aDdSRHlsMEh4NmF5N1pucThCUzZJUG9OVGRwVHlHRE1sVlh5b09HbVRFcDgzcGVqRTdUT0c1ZFhZWFpPQTRMZlNKYm15SWNRRWpUM211a1JPSDBmdXJYQkhHa01OeWJGd3VwaG9lc3FwbGwtak5vTkEtOXdGUzlhcko4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNd1M0bzNJcTEybmx2M29pY01HRWxvUURNZmxjemd1WDByOGUzSDVmUW4xUnljZnRlQXZBYW1FdW5ubnd0N01wWTVpNjRDR2xzY0lWcGlDd2ZhLV9BNjZsOTJBME5jbTVoUkJUWjdYbVZjaGhoUktjWUYzNkdvRDNyMldoQXN0V3R2WGFOT0wwbkpSX1ZnTVE1YV8xdklwMlROQ2xiR01EU0xaNUlCYXV1TWFYT1FYUQ?oc=5</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -1821,12 +1821,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>UAE: Claiming VAT Refunds For Tourists Just Got Simpler With New AI-Powered Digital Platform! - Curly Tales</t>
+          <t>UAE e-invoicing rules: Key deadlines for businesses in 2026 and 2027 - Arabian Business</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxORDJuVlViQjVHZ3JEMUxXV2NqVjBhbXVSWk1WWm1CMUVqU0RLX0JMNjctNnE1Q1FmSEhVZnNUcFFrLVBGQjJSWHF6UDJlVTJObFNhcDFRcnh3WFZMTEVycjZ3S2NEZnpqT180dFpHZ0VCeXgzdVd5QW5Yd0w3QUdHOXI5WE9NUzFPYlVYY0RTZ3NhU2kzWWRramVROTRQdmsxNk1zblRXY1ZOTVVnQlFicXNFTnRsWlYwWnBNd2Y3WV9EbFJlYi1UN2Z1dzlpSnfSAdQBQVVfeXFMTVJyVkVYR05PQldudW1QSzJsS0V5aW0yZVNyRmQ1YmhBaDhMVmtoNTJfSnZTdUV0amhlQ2lTa1pxbnpWRTA5aG9DaDhEdExWTDRrVmszb1gyTkNLY1RUMThXNEM2eXhKa2ZmUDNxbGM1YlVLQXl6c0MyaW5KQ2tQMGxMQ0dmM25iN3U3MUZKazN3X0lNeU83ZXJwTkE5REViLVZJZzJqcGVaLTJXWV9nWE9EVmJqSVJHV05XaXMtTkRjbTkzZml3bkNTdjFnYWVjU1E4SzY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPMXU4Vm5ScFJWd2tINmI3WEI1X1pwRFU0R2NyYXFra1d1bXFFTWhiVExCdS16SVRNelZOSlB5SG5GaHZTZzhzendZZHV4aDc4WHMyZ2kzcTEwekZDNG0yenlUaWwzUEs4blp6bHlPYXRZMFZLQzZRbG5idHB0a3F0Sw?oc=5</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>UAE Launches AI-Powered Tourist VAT Refund Platform Across Three Airports - Konsulteer</t>
+          <t>How tourists can claim UAE VAT refunds in one business day - Travels Dubai</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOaTNXUlc5Yk5IdGN4RF9PeDN3Nkc3WnducVRwSEczbFlhb2dLXzlKNWFsdEh4VlQxZTRNRl9VQjhYZDgwWU51dmRjZVhYUFR1WFBKcWltSTZwcEp5N3ZYVkNRNWZVaTU3UXNBZzZqTVFrN2pMci1jZGhRemRGSnVRLTZsNW1Rc05Ic3NGd21nLU85VVJFLVR5MzZrOWI4Mkc2anZqb042c0xqUGc3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQUWpQaFlPcE8tQ3ZpWVhKZHBmTGlzVWRtcmdXOWdxcDlGcjZnSWsxa193SXhyQ3duMFphOGt5a1lFRFhveGRpVmlUQ1I4cjhmQTN1aXh5Nks1anFfV0Zua0JBaG44T1lNTWZlRGhtWFRJZkRVV2F3MGJ0RnloVDMtQWlnZGdrQTRBUEVnQUEwYkU0dlhoT2Fn?oc=5</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>UAE cuts tourist VAT refund time to one business day with new AI platform - Gulf Business</t>
+          <t>"Smarter and simpler": UAE speeds up VAT refunds for tourists shopping in Dubai - Tuko News</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPZURXSjRhbWwwMzRkaWYyWlJSWkpSUl9nYllHVFJ0RnpDTHR4dGZJY2tlZzVGbEJuYWRjeFlXSm9fMDhDWTJwS2ViMTd2M1dKc2I1aUZmMTVGclB1eUhnRGV4SnlRZzJRWHhGYW80SFM0cWpCTjR5T29PMUNfU2l6MUN2RWlmdXVKTE5fVHkwNDZxVzdJSmdiUngtTlRzZHRqNHpNTkVSYy1Bb0JN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOR0ZWZkx0b2hxUzJfSlEwNEl4YWlSOEVreHVFZmEwMWxia2xYX1BxNThjczJ4bEk3S1lkRy1ZREZTV1FXNDZ2N29tcUxYVWxIZ3lZWkl4VHgtdUZ0QXYwcmFwMlVId19pX0lxWFpMT1hVVkxDZHIxR1NYemlyZ3Y2dG9Iczg3Q0tVcEtfVDlTVm9IQkxwMlQ1eEpRaUdBQmx5R0xQNXZ4QnotSHpYWnZYTlJYX3o?oc=5</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Federal Tax Authority launches world’s first-of-its-kind AI-powered digital platform for tourist tax refunds - Zawya</t>
+          <t>UAE launches paperless, AI-powered VAT refund app for tourists - Khaleej Times</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxQV0NXYW5reU5Sb1FHRmNDT3dyaXphV2ZORlVZYXNhN1ZQV1FldnhlZGF4VTJpVVJ6c0k4MGRqZE13Rm95S0ZWWkpVQUdlNFpTdDA2cks5akhhZmNZNlFuVU8wVkVJMFhiRUVjNTg5d1dzb2htY05tM0xIb0RhS0dhZ1RaQzZrQ2Z6ZzJJTnlZd19vOTJsU09pamc1TWFqaGFiUFM3Z1JNSGlac0lFeDRrcFpIYWxLN3ZlVjdtc2drS01FRTl1eTdCM3FZdFd1ZU1jODNWYkZ2WHZzZk5USlNVcnlsTXRrcnhaUi1fbUhXWnR6U0FUc3lydXJwNDIyWWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNZWdmNWZuVEo5Uk9mUEQybHRrODZ4M1plWloxXy0wWDRtMlp0WDdlVzkzOEgzMHNxdm1kSXJZcWZSVklxX0pKV3dHSnhMOEs3aXFZYzUwSXdxa2JFcXphbnhmVG10cHJURUFaVkw0dHk5RHF3b0o0QklQQ1ZoNVE3UXRMNnhsbTJyUDdRbDBKTmlhVFdTSUVEN2RXc9IBowFBVV95cUxNbmFfQTNJbmpFSVhLcndEbHQxcGVqcnhzSEVnenJod09jelNLSHVSLVE4dVdtTHlHOFMtcmRjTVVnd2p5cU0ycEFEbWdHbVVoVWdGbVRvRUh5WGpGT0xQVWRaUklXdloySmd2QWRYNlV5UFlPYWhnRF9KM2tsWl9wek9RQ1ZuVVRWaXJkb3F4cHVCMkhfMDFOU0NGNTQtOFV4MGhv?oc=5</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2001,12 +2001,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>UAE Publishes Version 2.0 of E-Invoicing Guidelines - sharedserviceslink</t>
+          <t>UAE Launches AI-Powered Tax Refund App For Tourists At Three Major Airports - Travel and Leisure Asia</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPV1NkTHUycS0tOFh6TF9HVW4yU051Zk1zTExPWTVONTcxemN0WTVBajl3QkxVY3Bocno5N1BVbDFkUlZjQ214VEZQc1Y0eURfMHZzdTNyV0RuRmU0OXA4dU9MMTZhN19POUdvMXJRSld6UDZkbU9YbWNkaTVzeW9DNDNwX25zRGFKMGgwQlBfR3JzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNeXpZdm5uSHczcUh4UGJ1LU1kWUpJaVBKTFVrcVBBWlVrSlI4aWJzbGRTWHp0bkVQNWlMQ3dWUU44LUpqOTloZjZoN1JEeWwwSHg2YXk3Wm5xOEJTNklQb05UZHBUeUdETWxWWHlvT0dtVEVwODNwZWpFN1RPRzVkWFlYWk9BNExmU0pibXlJY1FFalQzbXVrUk9IMGZ1clhCSEdrTU55YkZ3dXBob2VzcXBsbC1qTm9OQS05d0ZTOWFySjjSAcMBQVVfeXFMTXl6WXZubkh3M3FIeFBidS1NZFlKSWlQSkxVa3FQQVpVa0pSOGlic2xkU1h6dG5FUDVpTEN3VlFOOC1Kajk5aGY2aDdSRHlsMEh4NmF5N1pucThCUzZJUG9OVGRwVHlHRE1sVlh5b09HbVRFcDgzcGVqRTdUT0c1ZFhZWFpPQTRMZlNKYm15SWNRRWpUM211a1JPSDBmdXJYQkhHa01OeWJGd3VwaG9lc3FwbGwtak5vTkEtOXdGUzlhcko4?oc=5</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>UAE's new AI platform to slash VAT refund time for tourists to one day - The National</t>
+          <t>UAE: Claiming VAT Refunds For Tourists Just Got Simpler With New AI-Powered Digital Platform! - Curly Tales</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQZVpMLWZ4cmVQdDlnSlZRRERKN0tJbVR5eGVfblhRam5IUGwtXzdIaWJqeWlSNEVNVGozWGpvMm5LSGQ0YXdlVl92YjRPNHhtZDFIQ2swNlRtdzRQeUtTVmE1d1ZfVF9vdXR3N1RvV3ZoLXlZdWFyTENheUtIa0lOTjZTcjUza3VWVmFLaXpEVm1kTkpVandrTE80a0dadG9IMlJsWUhyZHU4U0tMS3I0cVQ0RVM1aTUzWGF4U2pvQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxORDJuVlViQjVHZ3JEMUxXV2NqVjBhbXVSWk1WWm1CMUVqU0RLX0JMNjctNnE1Q1FmSEhVZnNUcFFrLVBGQjJSWHF6UDJlVTJObFNhcDFRcnh3WFZMTEVycjZ3S2NEZnpqT180dFpHZ0VCeXgzdVd5QW5Yd0w3QUdHOXI5WE9NUzFPYlVYY0RTZ3NhU2kzWWRramVROTRQdmsxNk1zblRXY1ZOTVVnQlFicXNFTnRsWlYwWnBNd2Y3WV9EbFJlYi1UN2Z1dzlpSnfSAdQBQVVfeXFMTVJyVkVYR05PQldudW1QSzJsS0V5aW0yZVNyRmQ1YmhBaDhMVmtoNTJfSnZTdUV0amhlQ2lTa1pxbnpWRTA5aG9DaDhEdExWTDRrVmszb1gyTkNLY1RUMThXNEM2eXhKa2ZmUDNxbGM1YlVLQXl6c0MyaW5KQ2tQMGxMQ0dmM25iN3U3MUZKazN3X0lNeU83ZXJwTkE5REViLVZJZzJqcGVaLTJXWV9nWE9EVmJqSVJHV05XaXMtTkRjbTkzZml3bkNTdjFnYWVjU1E4SzY?oc=5</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>UAE announces major tax refund upgrade: Tourist VAT rules explained - Arabian Business</t>
+          <t>UAE Launches AI-Powered Tourist VAT Refund Platform Across Three Airports - Konsulteer</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOOV9mdmlpRVVsSTdjRnA2bV9OSGUtNGlvNmgzTWVjSGJiZFkyYmpBQ1h1UE4zY2VGN3FFQ1M3N09ZQm4zc1lTNl8ybDNKTll4c1FweWZlNFBLMFI3aFRfSzAtaHJzVmxSajI4amM1OFBMRUlnWnBfbWZ2a0s1azBieWtybl9VRmVrRmd0VVI4T0tzNWZZbWdCNE5NR3BxZVR0TW1EZ3VCTlBHZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOaTNXUlc5Yk5IdGN4RF9PeDN3Nkc3WnducVRwSEczbFlhb2dLXzlKNWFsdEh4VlQxZTRNRl9VQjhYZDgwWU51dmRjZVhYUFR1WFBKcWltSTZwcEp5N3ZYVkNRNWZVaTU3UXNBZzZqTVFrN2pMci1jZGhRemRGSnVRLTZsNW1Rc05Ic3NGd21nLU85VVJFLVR5MzZrOWI4Mkc2anZqb042c0xqUGc3?oc=5</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>UAE launches AI platform to cut tourist VAT refunds to one business day — The National - UA.NEWS</t>
+          <t>UAE cuts tourist VAT refund time to one business day with new AI platform - Gulf Business</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQYXdJZkJvX3ByM0lXS2ZtYjlHR0poREtsemlTaHdPWGExcVBhQzdNR3kyWmJMNHJsTnVYemRldHg2aG1jdlNidk5sV1JjcldzRF85dzh6ckpHeHdWVHp0SVdzeFZGNFlzdW04Q1dockJ1ajU2bnRFcmdwLUZfbE9iVm0tRE9jQklXM1Qzc2ppV2lDM19vUGUxLU9uc1ZJNm9TcTNlYnFnTzh2RVZyZUFEM0VVdHZWRFNKQmJsX1ZtQlc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPZURXSjRhbWwwMzRkaWYyWlJSWkpSUl9nYllHVFJ0RnpDTHR4dGZJY2tlZzVGbEJuYWRjeFlXSm9fMDhDWTJwS2ViMTd2M1dKc2I1aUZmMTVGclB1eUhnRGV4SnlRZzJRWHhGYW80SFM0cWpCTjR5T29PMUNfU2l6MUN2RWlmdXVKTE5fVHkwNDZxVzdJSmdiUngtTlRzZHRqNHpNTkVSYy1Bb0JN?oc=5</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>UAE Federal Tax Authority Launches Digital VAT Refund Platform for Tourists - News and Statistics - IndexBox</t>
+          <t>Federal Tax Authority launches world’s first-of-its-kind AI-powered digital platform for tourist tax refunds - Zawya</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOSm9HaWZSWEFFM3BNOW5acHZBT0luQWFnVEo3QUpJR1AwdUNMVjE0V3RXUXptLVVZR1VBN3doSnZlU1RNcU40UmJNVWpfQnVpY3NNRGRqNTM3WVFNRnB5X0g3SXFfbkl0Rk91MEtTWVBRejJDOElIcmxLSG1TcnNaRWdVbUdoS0QtMGVRX0NzSjJOSVJyV1luRVZsRW9ldl80c2VfUkNiempDdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxQV0NXYW5reU5Sb1FHRmNDT3dyaXphV2ZORlVZYXNhN1ZQV1FldnhlZGF4VTJpVVJ6c0k4MGRqZE13Rm95S0ZWWkpVQUdlNFpTdDA2cks5akhhZmNZNlFuVU8wVkVJMFhiRUVjNTg5d1dzb2htY05tM0xIb0RhS0dhZ1RaQzZrQ2Z6ZzJJTnlZd19vOTJsU09pamc1TWFqaGFiUFM3Z1JNSGlac0lFeDRrcFpIYWxLN3ZlVjdtc2drS01FRTl1eTdCM3FZdFd1ZU1jODNWYkZ2WHZzZk5USlNVcnlsTXRrcnhaUi1fbUhXWnR6U0FUc3lydXJwNDIyWWc?oc=5</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2226,12 +2226,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>XYRA unveils an intuitive AI platform to transform UAE business accounting - Gulf News</t>
+          <t>UAE Publishes Version 2.0 of E-Invoicing Guidelines - sharedserviceslink</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPeHRnSjFza2hMY1l3Q3p2dGtXYkRZRW5qTmFaZkJqTW1YZjU5Rzlva1pjTEJSMEg5MVlZd0pCdENvc2p4OXVGdWdBSEd6Q0gyWTFZS2JoUVVpaVVDa3hsYmNSaE1XWlZJWmZua3lOUVprakhMZFZmR1JsYjFTeDM5YWY2VGtLSmtCT3BOaS05aWRXV0k5NUJVanRpcFQ1MzJIdGVUcTd0cG55ZkpheGIxVjI3MlcwRHp0cmZOUEJPanVSUDNmWW1IUElMb1RYdExIOWFNd1lZcmU2X3hXSTYwVEhR0gH0AUFVX3lxTE9lZTBHQThBcUxrMHRBZkROUzQtaW9WMWVmaVhPdk9wYmtkZlYzVEJ0Z2FuWk1CVTFka0pZOTQxYlVMdzFXNVQxbWdIaURLWmY4RGNRM3FCaFRKbVF6akpqRmVabE9BX095Rk5tV0NZN3lRTm42bzNJR1dxUnJleklmd2E0bm9FUnVGTWxwUE05T2d4ZEVhUnBYVzNvazZHbWFWY29FSXVhU1NMTloweUlpdWZIYTl6b3BSaks4d2NrUFJQUzlqX2lzRFctMTF1ZnprRHZMMkNkRmFYbndEMl9YNHV0aXB0N0h1cU1YRHFPRE4zNWU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPV1NkTHUycS0tOFh6TF9HVW4yU051Zk1zTExPWTVONTcxemN0WTVBajl3QkxVY3Bocno5N1BVbDFkUlZjQ214VEZQc1Y0eURfMHZzdTNyV0RuRmU0OXA4dU9MMTZhN19POUdvMXJRSld6UDZkbU9YbWNkaTVzeW9DNDNwX25zRGFKMGgwQlBfR3JzQQ?oc=5</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2286,12 +2286,12 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>UAE tourist VAT refunds cut to one business day with new AI platform - Gulf News</t>
+          <t>UAE's new AI platform to slash VAT refund time for tourists to one day - The National</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPTHpETlBMdE1Kb2FWR0ZBdG5jRldvV1ZOWFpJYnMyVWhlQ1hTUE43dkV5UTJIWVA3eVFER0pKNXZHYTVXc3h4eVJ2R09YYVh3dEpkb2k3cXlyYWQyU3pPS0dvSjZhSkNmS1hpM0UwU0VXbEx6d2hydlh3SUJ4amkzQ3RlVGRtRTlqdGdjdW9rMVJkUG5PazRPdkZuY25mdHVoakZIZWFfcWNaLThEeXNyazVhTnVPckJZbXg40gHOAUFVX3lxTFBpcjZEUUktS3kzU1JHZzctTGFPTWZ2WG5PTGc0N21xLWoyS3gybHEzY0hMYU9XeGh2QUE0Z1NRSURaV0xhUkV6Y2VmbkpCR0VBRjR5c2l4SVpPYnBCQ28zTHNVN0k2aWhXcnpMYjFCaFJyUzQ3OUVJM0Q5YVBOS0JZbUV2ZXJVcS1xX2dnUGlYZ3NBaDVmREZyV3QxeTk3VnVUNDJfbG9fekhjX25MOEVhSERXSTk1a0x5THRXT3V2RmRtbkRXd0dTXzEzNWlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQZVpMLWZ4cmVQdDlnSlZRRERKN0tJbVR5eGVfblhRam5IUGwtXzdIaWJqeWlSNEVNVGozWGpvMm5LSGQ0YXdlVl92YjRPNHhtZDFIQ2swNlRtdzRQeUtTVmE1d1ZfVF9vdXR3N1RvV3ZoLXlZdWFyTENheUtIa0lOTjZTcjUza3VWVmFLaXpEVm1kTkpVandrTE80a0dadG9IMlJsWUhyZHU4U0tMS3I0cVQ0RVM1aTUzWGF4U2pvQQ?oc=5</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2316,12 +2316,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>UAE e-invoicing deadline: Businesses face Dh5,000 monthly fines for delays - Gulf News</t>
+          <t>UAE announces major tax refund upgrade: Tourist VAT rules explained - Arabian Business</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPWWVSUnR0QVRxaG1QTlhqa3NxcFNNQkdlNi1lYWVKRjFuOFRQMWNoNnY5Ni1CVWVNYWJjSEc3MVU0Q3h3eC0yQ0lJV2NRQTk1TWF3eThpcHFETEQ0OFg1SmJuYUVaZTVvZ3FHc3VpdW8zcEVtbTJJb1FHSFY5dWFOMk5SU3M5ZUpJNEk1OHQ3X1dxeFhLQ0tEbFRtcDR4dG04NS1aY2huV3BJVzlzeDFReDBKdmJmRjVnV3BkOWNQZ3bSAdMBQVVfeXFMTVFtR1VkanA4NWlBaDVrR1V2bDhlak5IUy16ODQtV24xTUVKdG5Sa0ZoeE42MlFWYjJuSmszT3JTSnd5ajJ1ZG1XQmd0M3hUWW5jczlsQ1hWQ3dNRFNxQUsxRkpfTm00WnBybTRpV3F6WXE4NXJmR3MzZDNOZzNqZzU3NmJKWjRVYzdoLXVGNFU2Tmh5Z3AtcVNUMTh0S0M4YThYVllGdW15MVdsZGM5cDFrS2hsV0JERUxzOXJhWkNEMnlydHhfazRucFhEMkUwVmUwOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOOV9mdmlpRVVsSTdjRnA2bV9OSGUtNGlvNmgzTWVjSGJiZFkyYmpBQ1h1UE4zY2VGN3FFQ1M3N09ZQm4zc1lTNl8ybDNKTll4c1FweWZlNFBLMFI3aFRfSzAtaHJzVmxSajI4amM1OFBMRUlnWnBfbWZ2a0s1azBieWtybl9VRmVrRmd0VVI4T0tzNWZZbWdCNE5NR3BxZVR0TW1EZ3VCTlBHZw?oc=5</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>UAE VAT rules change staff expense claims: What businesses need to review - Gulf News</t>
+          <t>UAE launches AI platform to cut tourist VAT refunds to one business day — The National - UA.NEWS</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPNjVZSlVOR1Bab1VubGlRNjZGeDNPWmVNSnRSNDlCXzk3bFk0U2dQTUt6dFlMVmY1QkpvWU1XMlVoQTN2MzluUVNxY01BYWtVb3JuYjFNU1dfQjl2X0dDTnJrXzd3eFFpanBCNGk1QS05LVAyVlliZUgzRFJhaHFKaTlsOTBMOExqLWtBUGZDaXFSZmVfZkRPQk9YSzF2VlNiUlJtbU9RWndXLUxjMjhoN1ZwYWYySDZHZkJRNGdTak3SAdMBQVVfeXFMTUhINEdZNjQybDJ5TjhWUkMwNDBmcENESVUxc214S044NTBva0JGVWNJMFFidVczdFVuN0U5d3VIT1dCczVFLW00LUczN080X0xVWmZTbVd2dkxEaWJBZkxuVHFuWjBoeWpDczhpVVJ2ZTVaY0R1dVVtN24tV3R0bU9WVm52M0lBeDQ0T2c3cEdBUjRjRHFkQTdiUl9HTmw2dmNDTk5BRkpjdVN0NlJaRVR6emc1Q2lpQUxocWx3SFFtRDFRZkI4cmMwLW5BTVhwUWNQbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQYXdJZkJvX3ByM0lXS2ZtYjlHR0poREtsemlTaHdPWGExcVBhQzdNR3kyWmJMNHJsTnVYemRldHg2aG1jdlNidk5sV1JjcldzRF85dzh6ckpHeHdWVHp0SVdzeFZGNFlzdW04Q1dockJ1ajU2bnRFcmdwLUZfbE9iVm0tRE9jQklXM1Qzc2ppV2lDM19vUGUxLU9uc1ZJNm9TcTNlYnFnTzh2RVZyZUFEM0VVdHZWRFNKQmJsX1ZtQlc?oc=5</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>UAE e-invoicing deadline in 4 days: Who must comply to avoid Dh5,000 fines - Gulf News</t>
+          <t>UAE Federal Tax Authority Launches Digital VAT Refund Platform for Tourists - News and Statistics - IndexBox</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNLWxHNTZNMkNZUTRHY3hWSFRld05JZm9FRzh3TlZsQzNCS2NqX3kwQjBvbFpjUXBCSG8xRmRLUFBhM25YYTVVNXNyQWFmYjdUTk9ndTZCRmY3dDVObUpsLW85bC1pZzUtWGM5UmR3d2hEckZDUDEzdXN2MEN3MXpFa1JaZWRDVGU5aGE3Ul9nVlZPN0FhVGRjSlctX2lnSHNyeDQ3Z2RFTEN6UmRZRXVuMkNBbGRrbFJfaGpZazZQT07SAdMBQVVfeXFMUEhrM2xRZk5Uc2Z2ZkRUV1p3bGpQSkEzaGpaQkdhZ1lrYld2LUMxd3ozdTh6WmxJVkJYNkJCeGxGOURPY2dsbU9RdmphOXpncm03bjZvSWRDeUp0Ykg5NmpOQjUyZ1MwS08xcTdzOXhnSFZGNklnbGxpTk44aldNOFJrNVNuS2trMkphb0xpOXN3ZU13Y0JmN0Q1ZlQtWTZscmNwa0RTbGg4M1M0cHd2R2NXTV9fRFZwQk5aNjMyUF90VXUwX2prR09OaklId0VYSFlHaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOSm9HaWZSWEFFM3BNOW5acHZBT0luQWFnVEo3QUpJR1AwdUNMVjE0V3RXUXptLVVZR1VBN3doSnZlU1RNcU40UmJNVWpfQnVpY3NNRGRqNTM3WVFNRnB5X0g3SXFfbkl0Rk91MEtTWVBRejJDOElIcmxLSG1TcnNaRWdVbUdoS0QtMGVRX0NzSjJOSVJyV1luRVZsRW9ldl80c2VfUkNiempDdw?oc=5</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Ezat Alnajm on Preparing Crypto Wealth for Greater Tax Transparency - Hubbis</t>
+          <t>XYRA unveils an intuitive AI platform to transform UAE business accounting - Gulf News</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQRkVXSUFZWnYwTXRYTG5GZUtmN0pZLWx2anJoNTM1VERGZUVha1JZc01kMWxHek92SEVEbkgzeDgyZWh0RXY3VFhuYVJKcTlNeklhQlJvUVB1WXNnMVZ5WUFmY2pxYzNqblZRYkRBemxhdzktaWhwLVNBZFNqOE9RVGlsRm4zazVuVExuUGZtQ19JM2xFRHFldFdxbmN1Sjg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPeHRnSjFza2hMY1l3Q3p2dGtXYkRZRW5qTmFaZkJqTW1YZjU5Rzlva1pjTEJSMEg5MVlZd0pCdENvc2p4OXVGdWdBSEd6Q0gyWTFZS2JoUVVpaVVDa3hsYmNSaE1XWlZJWmZua3lOUVprakhMZFZmR1JsYjFTeDM5YWY2VGtLSmtCT3BOaS05aWRXV0k5NUJVanRpcFQ1MzJIdGVUcTd0cG55ZkpheGIxVjI3MlcwRHp0cmZOUEJPanVSUDNmWW1IUElMb1RYdExIOWFNd1lZcmU2X3hXSTYwVEhR0gH0AUFVX3lxTE9lZTBHQThBcUxrMHRBZkROUzQtaW9WMWVmaVhPdk9wYmtkZlYzVEJ0Z2FuWk1CVTFka0pZOTQxYlVMdzFXNVQxbWdIaURLWmY4RGNRM3FCaFRKbVF6akpqRmVabE9BX095Rk5tV0NZN3lRTm42bzNJR1dxUnJleklmd2E0bm9FUnVGTWxwUE05T2d4ZEVhUnBYVzNvazZHbWFWY29FSXVhU1NMTloweUlpdWZIYTl6b3BSaks4d2NrUFJQUzlqX2lzRFctMTF1ZnprRHZMMkNkRmFYbndEMl9YNHV0aXB0N0h1cU1YRHFPRE4zNWU?oc=5</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Ministerial Decision No. 197 of 2026 - Crowe</t>
+          <t>UAE tourist VAT refunds cut to one business day with new AI platform - Gulf News</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOMFZaS3RKdnpEdVpQcUtlN1JJWlBuZmxxRkpnZHB4WXFpUGg1cHpjcHdKUzJlM0VTVExnRExWRkowZm5iek1yUHpaY3ZWamZfS3ZpM0tkSW9MTjV0YmxHOFhpeDltbkxENmZLamJkV1ZKMklZUjAySU1aZGVZSnRMamIxejJBdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPTHpETlBMdE1Kb2FWR0ZBdG5jRldvV1ZOWFpJYnMyVWhlQ1hTUE43dkV5UTJIWVA3eVFER0pKNXZHYTVXc3h4eVJ2R09YYVh3dEpkb2k3cXlyYWQyU3pPS0dvSjZhSkNmS1hpM0UwU0VXbEx6d2hydlh3SUJ4amkzQ3RlVGRtRTlqdGdjdW9rMVJkUG5PazRPdkZuY25mdHVoakZIZWFfcWNaLThEeXNyazVhTnVPckJZbXg40gHOAUFVX3lxTFBpcjZEUUktS3kzU1JHZzctTGFPTWZ2WG5PTGc0N21xLWoyS3gybHEzY0hMYU9XeGh2QUE0Z1NRSURaV0xhUkV6Y2VmbkpCR0VBRjR5c2l4SVpPYnBCQ28zTHNVN0k2aWhXcnpMYjFCaFJyUzQ3OUVJM0Q5YVBOS0JZbUV2ZXJVcS1xX2dnUGlYZ3NBaDVmREZyV3QxeTk3VnVUNDJfbG9fekhjX25MOEVhSERXSTk1a0x5THRXT3V2RmRtbkRXd0dTXzEzNWlR?oc=5</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Amendments to the UAE electronic invoicing system decision - Simmons &amp; Simmons</t>
+          <t>UAE e-invoicing deadline: Businesses face Dh5,000 monthly fines for delays - Gulf News</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOUzJMUUdnR2Z0TjQ2eEMteTVMNHpOZndFbEh3T1hJaVQ5Z29HdXRlS3lTcXdRbkFFMnVRdFI5a0QzMzlQM2EzZnBDY1VDLXJUeFI5T1VtQnJ5UEFHTmU1bVA0bWJiMTZwTmhFR21sZzE0WEZReGRwMWRDalVDbm9kVWpVM0VfTmJHeThySXRwYjY0UzZXS1NhT0J2T0tGLVczYjk3Mno2TDZPeU5BbGM3VGR6SDJYR0wydkkxNUtYSzM1a19ocnhlNWQ3VS0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPWWVSUnR0QVRxaG1QTlhqa3NxcFNNQkdlNi1lYWVKRjFuOFRQMWNoNnY5Ni1CVWVNYWJjSEc3MVU0Q3h3eC0yQ0lJV2NRQTk1TWF3eThpcHFETEQ0OFg1SmJuYUVaZTVvZ3FHc3VpdW8zcEVtbTJJb1FHSFY5dWFOMk5SU3M5ZUpJNEk1OHQ3X1dxeFhLQ0tEbFRtcDR4dG04NS1aY2huV3BJVzlzeDFReDBKdmJmRjVnV3BkOWNQZ3bSAdMBQVVfeXFMTVFtR1VkanA4NWlBaDVrR1V2bDhlak5IUy16ODQtV24xTUVKdG5Sa0ZoeE42MlFWYjJuSmszT3JTSnd5ajJ1ZG1XQmd0M3hUWW5jczlsQ1hWQ3dNRFNxQUsxRkpfTm00WnBybTRpV3F6WXE4NXJmR3MzZDNOZzNqZzU3NmJKWjRVYzdoLXVGNFU2Tmh5Z3AtcVNUMTh0S0M4YThYVllGdW15MVdsZGM5cDFrS2hsV0JERUxzOXJhWkNEMnlydHhfazRucFhEMkUwVmUwOA?oc=5</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -2584,35 +2584,39 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>official</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Finance Amends Electronic Invoicing Regulations to Ease the Burden on Businesses</t>
+          <t>UAE VAT rules change staff expense claims: What businesses need to review - Gulf News</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Ministry of Finance — News</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>mof.gov.ae</t>
+          <t>news.google.com</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>https://mof.gov.ae/en/news/ministry-of-finance-amends-electronic-invoicing-regulations-to-ease-the-burden-on-businesses/</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPNjVZSlVOR1Bab1VubGlRNjZGeDNPWmVNSnRSNDlCXzk3bFk0U2dQTUt6dFlMVmY1QkpvWU1XMlVoQTN2MzluUVNxY01BYWtVb3JuYjFNU1dfQjl2X0dDTnJrXzd3eFFpanBCNGk1QS05LVAyVlliZUgzRFJhaHFKaTlsOTBMOExqLWtBUGZDaXFSZmVfZkRPQk9YSzF2VlNiUlJtbU9RWndXLUxjMjhoN1ZwYWYySDZHZkJRNGdTak3SAdMBQVVfeXFMTUhINEdZNjQybDJ5TjhWUkMwNDBmcENESVUxc214S044NTBva0JGVWNJMFFidVczdFVuN0U5d3VIT1dCczVFLW00LUczN080X0xVWmZTbVd2dkxEaWJBZkxuVHFuWjBoeWpDczhpVVJ2ZTVaY0R1dVVtN24tV3R0bU9WVm52M0lBeDQ0T2c3cEdBUjRjRHFkQTdiUl9HTmw2dmNDTk5BRkpjdVN0NlJaRVR6emc1Q2lpQUxocWx3SFFtRDFRZkI4cmMwLW5BTVhwUWNQbw?oc=5</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -2625,35 +2629,39 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>official</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>UAE Breaks into Global Top 10 in IMD’s 2026 Government Support Index</t>
+          <t>UAE e-invoicing deadline in 4 days: Who must comply to avoid Dh5,000 fines - Gulf News</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Ministry of Finance — News</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>mof.gov.ae</t>
+          <t>news.google.com</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>https://mof.gov.ae/en/news/uae-breaks-into-global-top-10-in-imds-2026-government-support-index/</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNLWxHNTZNMkNZUTRHY3hWSFRld05JZm9FRzh3TlZsQzNCS2NqX3kwQjBvbFpjUXBCSG8xRmRLUFBhM25YYTVVNXNyQWFmYjdUTk9ndTZCRmY3dDVObUpsLW85bC1pZzUtWGM5UmR3d2hEckZDUDEzdXN2MEN3MXpFa1JaZWRDVGU5aGE3Ul9nVlZPN0FhVGRjSlctX2lnSHNyeDQ3Z2RFTEN6UmRZRXVuMkNBbGRrbFJfaGpZazZQT07SAdMBQVVfeXFMUEhrM2xRZk5Uc2Z2ZkRUV1p3bGpQSkEzaGpaQkdhZ1lrYld2LUMxd3ozdTh6WmxJVkJYNkJCeGxGOURPY2dsbU9RdmphOXpncm03bjZvSWRDeUp0Ykg5NmpOQjUyZ1MwS08xcTdzOXhnSFZGNklnbGxpTk44aldNOFJrNVNuS2trMkphb0xpOXN3ZU13Y0JmN0Q1ZlQtWTZscmNwa0RTbGg4M1M0cHd2R2NXTV9fRFZwQk5aNjMyUF90VXUwX2prR09OaklId0VYSFlHaw?oc=5</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -2666,35 +2674,39 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>IFRS / Reporting</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>official</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Finance convenes Financial Data Forum 2026 to boost efficiency in final account and financial statement preparation and reinforce the application of international accounting standards</t>
+          <t>Ezat Alnajm on Preparing Crypto Wealth for Greater Tax Transparency - Hubbis</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Ministry of Finance — News</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>mof.gov.ae</t>
+          <t>news.google.com</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>https://mof.gov.ae/en/news/ministry-of-finance-convenes-financial-data-forum-2026-to-boost-efficiency-in-final-account-and-financial-statement-preparation-and-reinforce-the-application-of-international-accounting-standards/</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQRkVXSUFZWnYwTXRYTG5GZUtmN0pZLWx2anJoNTM1VERGZUVha1JZc01kMWxHek92SEVEbkgzeDgyZWh0RXY3VFhuYVJKcTlNeklhQlJvUVB1WXNnMVZ5WUFmY2pxYzNqblZRYkRBemxhdzktaWhwLVNBZFNqOE9RVGlsRm4zazVuVExuUGZtQ19JM2xFRHFldFdxbmN1Sjg?oc=5</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -2704,12 +2716,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2724,12 +2736,12 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Foreign outflows in July were the lowest in the GCC - EnterpriseAM</t>
+          <t>Ministerial Decision No. 197 of 2026 - Crowe</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -2739,7 +2751,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE8tRko4Unh0QWI1ekpUTHJ3QmktT1dyWXd2S2REcHZIZVVvd2Rtdm1WSkUtQUtacjlnSGlLdWtIMk0tVVNxU1ZKTU1qSVdpc2NOUjBGWUh5STBrM0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOMFZaS3RKdnpEdVpQcUtlN1JJWlBuZmxxRkpnZHB4WXFpUGg1cHpjcHdKUzJlM0VTVExnRExWRkowZm5iek1yUHpaY3ZWamZfS3ZpM0tkSW9MTjV0YmxHOFhpeDltbkxENmZLamJkV1ZKMklZUjAySU1aZGVZSnRMamIxejJBdw?oc=5</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -2749,17 +2761,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2769,12 +2781,12 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>UAE extends small business tax relief until 2029 - Yahoo Finance</t>
+          <t>Amendments to the UAE electronic invoicing system decision - Simmons &amp; Simmons</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -2784,7 +2796,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNM2FhblZZVW5LVzI2bmRYWFhadXJ5bGU2OU54U3UzTmpGWmlweXlYTVVSWHpXaXU5YnJLNlh0STNsNmhYdG9feTdsN2xKNWlNSGZRM3loRllITXB4U0ljUkpyYllpLU9jQUZVOVdab1Rocml1OWxsa1lKWE00Wk42QWZRejVCaTk4QllWdTJTMWxJd2RKbVZiWHo4UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOUzJMUUdnR2Z0TjQ2eEMteTVMNHpOZndFbEh3T1hJaVQ5Z29HdXRlS3lTcXdRbkFFMnVRdFI5a0QzMzlQM2EzZnBDY1VDLXJUeFI5T1VtQnJ5UEFHTmU1bVA0bWJiMTZwTmhFR21sZzE0WEZReGRwMWRDalVDbm9kVWpVM0VfTmJHeThySXRwYjY0UzZXS1NhT0J2T0tGLVczYjk3Mno2TDZPeU5BbGM3VGR6SDJYR0wydkkxNUtYSzM1a19ocnhlNWQ3VS0?oc=5</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -2794,42 +2806,38 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>official</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>UAE seizes 8.45m non-compliant tobacco and drink products in six-month tax drive - Gulf News</t>
+          <t>Ministry of Finance Amends Electronic Invoicing Regulations to Ease the Burden on Businesses</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>Ministry of Finance — News</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>news.google.com</t>
+          <t>mof.gov.ae</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOeXEwYUYyRVl3dzRiREtKU01zOTFJNXZCNVpNcE5wYTUxRUN3U1A0SkxudUUxYkI0WHUzUmZoelZBLUJSaUFFcno2WFc5bzNBR2FQZU4zSkFuMTNWbkcyMVNMdXc3dmplcVNLdDRsN2xDdng3ZFg2UnFiREgzZHIwUFlpUkhxdXdkeG0ySXJQS2Q2LWJJRGxrbWZMT3AxTU9KWWM1OS1qQ2FET0oyQjhhZFNXX3RDWklhU3VrdTM2aTRRcFIxdXlWOHJB0gHcAUFVX3lxTFA5OFBJbzlhcVVXbXNwNWtBamtpbFdwbVkxdHFtSTJXWk9TR3kxZ0F6UFVtQy1EYnpaZUM2Vmp1enVjeFJoSjR1ekpMenVHdEhaTlhGdmxKUzQwV1BsQnpiNXg0UDRpTndaTjE2RTJBNzFIbzNEZExXWlhmVnpYT2VTbmFsNldOZVlzX3BsaU5xUUplai13SEl2RUdpNG0tWTJOd1BCQkVaUVowX0NiZHF3VU1BLU5VcVpBb2RoRXVERGdaYmxhMmhEd3MxNVRoekNKQ3hZeEhyWkUwQUg?oc=5</t>
+          <t>https://mof.gov.ae/en/news/ministry-of-finance-amends-electronic-invoicing-regulations-to-ease-the-burden-on-businesses/</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -2839,42 +2847,38 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>official</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>UAE Extends Small Business Relief for Corporate Tax Purposes Until 2029 - entARABI</t>
+          <t>UAE Breaks into Global Top 10 in IMD’s 2026 Government Support Index</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>Ministry of Finance — News</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>news.google.com</t>
+          <t>mof.gov.ae</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOV0NzYjBEMHBFM0dLeTRxdURMWjYtZUZ2OXpSTENyYVozcGpPWkVBb09JaU1pQjAtWEVTdlcyQ1VjbmNGc2NiT05jWFUxMTNFVzFJMHlHQlY3VmxDaU9XUVZwY21yS1ZFYldWckFZallwVDU3Y1ZzLVNKbndvMXVGckJFMnRWNUtNOTFzRlgzUDhMbHFpMEZsRk9XejN4S3F4cld0aTJPdw?oc=5</t>
+          <t>https://mof.gov.ae/en/news/uae-breaks-into-global-top-10-in-imds-2026-government-support-index/</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -2884,42 +2888,38 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Transfer Pricing</t>
+          <t>IFRS / Reporting</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>official</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Tax Insights: Canada introduces a simplified transfer pricing documentation regime - PwC</t>
+          <t>Ministry of Finance convenes Financial Data Forum 2026 to boost efficiency in final account and financial statement preparation and reinforce the application of international accounting standards</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>News — Big 4 UAE Tax Commentary</t>
+          <t>Ministry of Finance — News</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>news.google.com</t>
+          <t>mof.gov.ae</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOVm8yXzZQUVY4R2djbXBUdHQ0aFUyQnFaSHNxSkFCbTNxNmxSVTZVUHRxa1lvVnF2Nlk2bmhTQ2w4ejJaTVR2NUY4S3VsajBFTEV2dkRwbk9BbEh1MWtwczNVNHgtQm1yaFJwc2NlZldqM053NGhwbE1TLWR3eDNIQ3V2ZzhTQ2JmbVJlNlliMkRoalBfYzQ3WHdVaXR2R2MzNEw1dGRQNzFfRWxTWklzYkJNYVZKVjFMclFQQjIzMUU?oc=5</t>
+          <t>https://mof.gov.ae/en/news/ministry-of-finance-convenes-financial-data-forum-2026-to-boost-efficiency-in-final-account-and-financial-statement-preparation-and-reinforce-the-application-of-international-accounting-standards/</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -2929,12 +2929,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -2944,17 +2944,17 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Canada launches public consultations on steel imports and imposes surtax on wood cabinets and vanities - EY</t>
+          <t>Foreign outflows in July were the lowest in the GCC - EnterpriseAM</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>News — Big 4 UAE Tax Commentary</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNMy1qdEVRaXhDVUZ4c3FTNUlCS0F0SEhoRnQtRk5BTnB1d2VFSmZSUk95RmRSdEw4LUFBV1FwYTIwbTVLZHdqOEdkcDhRb29fWDc1cGN0ZFA3a0habW9iY0NWam9LZmtfa3c2NDlLZ3N1MVJYWWRwejlhM1ViSndzZg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE8tRko4Unh0QWI1ekpUTHJ3QmktT1dyWXd2S2REcHZIZVVvd2Rtdm1WSkUtQUtacjlnSGlLdWtIMk0tVVNxU1ZKTU1qSVdpc2NOUjBGWUh5STBrM0E?oc=5</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -2974,7 +2974,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>UAE extends Small Business Relief for corporate tax - Absolute Geeks</t>
+          <t>UAE extends small business tax relief until 2029 - Yahoo Finance</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>News — FTA Announcements</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPWU10OExoZmlXRjdCamp5VHROMnNDb1dKN1I3NE85dTI4aU84VjVvczlyanRyWEw4OVBuOWpVa1NJZm9qQ2hSZl9YYlhxOGNEYXBCeDlGQVF1RUV1TWJlSGVmdnpHRktyS2ktV2IwQ0s3T3hZMzV4Ni03aGdvVTNHZFhEYThmRE5uclJqR1BKUF90MXktS2xEaXctR0RsLXphM0g0REdvWHY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNM2FhblZZVW5LVzI2bmRYWFhadXJ5bGU2OU54U3UzTmpGWmlweXlYTVVSWHpXaXU5YnJLNlh0STNsNmhYdG9feTdsN2xKNWlNSGZRM3loRllITXB4U0ljUkpyYllpLU9jQUZVOVdab1Rocml1OWxsa1lKWE00Wk42QWZRejVCaTk4QllWdTJTMWxJd2RKbVZiWHo4UQ?oc=5</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -3019,14 +3019,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>Other</t>
@@ -3039,12 +3039,12 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Spotify forecasts slower growth despite AI investment - Gulf Business</t>
+          <t>UAE seizes 8.45m non-compliant tobacco and drink products in six-month tax drive - Gulf News</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>News — FTA Announcements</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNQUhDU0xPaGxHNTZZdDNmRFRsTndvQThIUkRVV0hyTkpVbWhFNXdsZ2hjUXFrNzByWEc1ZUdITm1FYkM2N3k5MW5paDBud1RfNGF4MXNIdlluaVktTVRfd0RlZzJpUmc0UlZ2WUlKU1VDTUdELXpoelU0Z2kteENFZjVfcWx5YmhLc21jS3J5VXVkeEZ3UXRV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOeXEwYUYyRVl3dzRiREtKU01zOTFJNXZCNVpNcE5wYTUxRUN3U1A0SkxudUUxYkI0WHUzUmZoelZBLUJSaUFFcno2WFc5bzNBR2FQZU4zSkFuMTNWbkcyMVNMdXc3dmplcVNLdDRsN2xDdng3ZFg2UnFiREgzZHIwUFlpUkhxdXdkeG0ySXJQS2Q2LWJJRGxrbWZMT3AxTU9KWWM1OS1qQ2FET0oyQjhhZFNXX3RDWklhU3VrdTM2aTRRcFIxdXlWOHJB0gHcAUFVX3lxTFA5OFBJbzlhcVVXbXNwNWtBamtpbFdwbVkxdHFtSTJXWk9TR3kxZ0F6UFVtQy1EYnpaZUM2Vmp1enVjeFJoSjR1ekpMenVHdEhaTlhGdmxKUzQwV1BsQnpiNXg0UDRpTndaTjE2RTJBNzFIbzNEZExXWlhmVnpYT2VTbmFsNldOZVlzX3BsaU5xUUplai13SEl2RUdpNG0tWTJOd1BCQkVaUVowX0NiZHF3VU1BLU5VcVpBb2RoRXVERGdaYmxhMmhEd3MxNVRoekNKQ3hZeEhyWkUwQUg?oc=5</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -3064,17 +3064,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>UAE Sets Minimum Excise Price for E-Liquids - Vaping360</t>
+          <t>UAE Extends Small Business Relief for Corporate Tax Purposes Until 2029 - entARABI</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>News — FTA Announcements</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE9HS2ZoOFFrdlRtX3N4ZXM5UlpzLTFKc21Pdi1CVkhNYW1PNGozMDBVYVZ0VjlrUDNCMFRQRG1hOGpPNllSd0dpX0dhNm02a3drdmZneHpQOUhtUkxXWlFBcDlETkt0dF9xalFRMldrVWZMSXh5NHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOV0NzYjBEMHBFM0dLeTRxdURMWjYtZUZ2OXpSTENyYVozcGpPWkVBb09JaU1pQjAtWEVTdlcyQ1VjbmNGc2NiT05jWFUxMTNFVzFJMHlHQlY3VmxDaU9XUVZwY21yS1ZFYldWckFZallwVDU3Y1ZzLVNKbndvMXVGckJFMnRWNUtNOTFzRlgzUDhMbHFpMEZsRk9XejN4S3F4cld0aTJPdw?oc=5</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
@@ -3114,27 +3114,27 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>Transfer Pricing</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>E-Invoicing Readiness Checklist: How UAE Businesses Can Prepare Before the Deadline - NewsBreak: Local News &amp; Alerts</t>
+          <t>Tax Insights: Canada introduces a simplified transfer pricing documentation regime - PwC</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — Big 4 UAE Tax Commentary</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPQmFubHpKbnIzS2N1cVJkbFA5bDRWcUhzQ0lYazZ3Z0ZBazZKQzVoTjRxZXBrMFNNSGNXTGp4ZG1EZ0xTTGFwanZQZkxvbjA5UFQxYkNBLWF6bEtDSlB5UlcyNU9fc2E1VTRNMWtTYnRyOFRlTUxjRlVlcEVwRVdDb05OQlo4VC1GcUpqUkpmVzhsUmc0RGJrZlJWN0tCMXVQc0d5dTEtT055TFRDT3c5R2pUN1hpaEF3R21TOHo2d1pNZldNcUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOVm8yXzZQUVY4R2djbXBUdHQ0aFUyQnFaSHNxSkFCbTNxNmxSVTZVUHRxa1lvVnF2Nlk2bmhTQ2w4ejJaTVR2NUY4S3VsajBFTEV2dkRwbk9BbEh1MWtwczNVNHgtQm1yaFJwc2NlZldqM053NGhwbE1TLWR3eDNIQ3V2ZzhTQ2JmbVJlNlliMkRoalBfYzQ3WHdVaXR2R2MzNEw1dGRQNzFfRWxTWklzYkJNYVZKVjFMclFQQjIzMUU?oc=5</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3169,17 +3169,17 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>A jumpy July - EnterpriseAM</t>
+          <t>Canada launches public consultations on steel imports and imposes surtax on wood cabinets and vanities - EY</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — Big 4 UAE Tax Commentary</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBCcFdtSjE1bW5pMlREMHVqWTYwcW1xajViLWZvTmU1MUk0MUZiX2pPay12Nm5RS0tzdmJjYU9VY2hjUi10enNsYk1qcEZqc3FQc3dEZE1CaTJRYTJvVWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNMy1qdEVRaXhDVUZ4c3FTNUlCS0F0SEhoRnQtRk5BTnB1d2VFSmZSUk95RmRSdEw4LUFBV1FwYTIwbTVLZHdqOEdkcDhRb29fWDc1cGN0ZFA3a0habW9iY0NWam9LZmtfa3c2NDlLZ3N1MVJYWWRwejlhM1ViSndzZg?oc=5</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
@@ -3204,12 +3204,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Another Hormuz workaround - EnterpriseAM</t>
+          <t>UAE extends Small Business Relief for corporate tax - Absolute Geeks</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — FTA Announcements</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5iUjRXRTlrdVBXOHUyRWlYc2ttOXdYaVktOE5ZU1YxMnRLcnlHeWRPdl9CQmRkR3Bqc21aeFlWMmdFcGdjanc3d2RNTnRGcWdKVGdxQTZmeC02clJoSXJJaGJlUUM5TW5pQjRORkVpRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPWU10OExoZmlXRjdCamp5VHROMnNDb1dKN1I3NE85dTI4aU84VjVvczlyanRyWEw4OVBuOWpVa1NJZm9qQ2hSZl9YYlhxOGNEYXBCeDlGQVF1RUV1TWJlSGVmdnpHRktyS2ktV2IwQ0s3T3hZMzV4Ni03aGdvVTNHZFhEYThmRE5uclJqR1BKUF90MXktS2xEaXctR0RsLXphM0g0REdvWHY?oc=5</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>UAE e-invoicing: How digital invoices will transform business - Khaleej Times</t>
+          <t>Spotify forecasts slower growth despite AI investment - Gulf Business</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — FTA Announcements</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQMjFwZTd6MkpqcXZKaEwxZV9fUlZWSEtSeVdIQXN6YXFPMURFMWZhOHc0NWFuWlRfd1ZNX2doQVBpbXBqRFBTOVNNcjVTYVpOcEozYmtoaWxDUHVoUFFNT1RBWEI3RzJybmFWejFNcEcxYXpybDBiUzRLUk85ajBkOHIydnBjOUV6NEVJUjZkQTNOQ0Fud1BjdGtUNVpwTmlTazdyNWZmaXRwTkthY1Nac1RPWU90T3lMemJJNHp5VdIBvwFBVV95cUxQMjFwZTd6MkpqcXZKaEwxZV9fUlZWSEtSeVdIQXN6YXFPMURFMWZhOHc0NWFuWlRfd1ZNX2doQVBpbXBqRFBTOVNNcjVTYVpOcEozYmtoaWxDUHVoUFFNT1RBWEI3RzJybmFWejFNcEcxYXpybDBiUzRLUk85ajBkOHIydnBjOUV6NEVJUjZkQTNOQ0Fud1BjdGtUNVpwTmlTazdyNWZmaXRwTkthY1Nac1RPWU90T3lMemJJNHp5VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNQUhDU0xPaGxHNTZZdDNmRFRsTndvQThIUkRVV0hyTkpVbWhFNXdsZ2hjUXFrNzByWEc1ZUdITm1FYkM2N3k5MW5paDBud1RfNGF4MXNIdlluaVktTVRfd0RlZzJpUmc0UlZ2WUlKU1VDTUdELXpoelU0Z2kteENFZjVfcWx5YmhLc21jS3J5VXVkeEZ3UXRV?oc=5</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>More investments in Adnoc’s fleet, Indian IPOs, and Egypt’s North Coast - EnterpriseAM</t>
+          <t>UAE Sets Minimum Excise Price for E-Liquids - Vaping360</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — FTA Announcements</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1RdV9pa3ZIMmpRWnFlcXRaeTRnSy1zZUp0enVScm1nc0hMX3UwTEdEOG9oQy00UUJiSUR4WENleElGQVVmLXh3ZE10b09nQWphT0IzNHNJb0h3Q0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE9HS2ZoOFFrdlRtX3N4ZXM5UlpzLTFKc21Pdi1CVkhNYW1PNGozMDBVYVZ0VjlrUDNCMFRQRG1hOGpPNllSd0dpX0dhNm02a3drdmZneHpQOUhtUkxXWlFBcDlETkt0dF9xalFRMldrVWZMSXh5NHc?oc=5</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
@@ -3339,12 +3339,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3354,12 +3354,12 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>FTA Directive No. 5 of 2026 - Crowe</t>
+          <t>E-Invoicing Readiness Checklist: How UAE Businesses Can Prepare Before the Deadline - NewsBreak: Local News &amp; Alerts</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE40S0RnRzF2d1dBSmNHdkNNQXZQQmlOYWNOSk5OWnlVNUN3ZDB5UHBUV29RXzNvaF9pVFNQZ2FwTUdocGhxMXp1T3gxMUFycGNESFA1bXNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPQmFubHpKbnIzS2N1cVJkbFA5bDRWcUhzQ0lYazZ3Z0ZBazZKQzVoTjRxZXBrMFNNSGNXTGp4ZG1EZ0xTTGFwanZQZkxvbjA5UFQxYkNBLWF6bEtDSlB5UlcyNU9fc2E1VTRNMWtTYnRyOFRlTUxjRlVlcEVwRVdDb05OQlo4VC1GcUpqUkpmVzhsUmc0RGJrZlJWN0tCMXVQc0d5dTEtT055TFRDT3c5R2pUN1hpaEF3R21TOHo2d1pNZldNcUE?oc=5</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
@@ -3384,12 +3384,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Digital currency and VAT: New UAE rules for businesses to consider - thenationalnews.com</t>
+          <t>A jumpy July - EnterpriseAM</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQamI1MElzOEtNS1ZjVWR3VGpjZjNUZjBXbjQwZkJIZ3AwOFVqckl0WWFQN2JpaEg5XzRTUTBVMDFOeVhMaUZxYW9GUnBFNW55WnhKd2ZKOVZoekRBWUNqQkp3dGFPZ2JQcWY5SjVlRUJuTURfcVN5aUNXVmthdUh4cHlJbFNHN3lyT1VTU2l2Nk92U09JZFh3eXp0c29jTlJNZW1VLTZBR2h5WmdBTjFuNGczZkZwdDY1QWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBCcFdtSjE1bW5pMlREMHVqWTYwcW1xajViLWZvTmU1MUk0MUZiX2pPay12Nm5RS0tzdmJjYU9VY2hjUi10enNsYk1qcEZqc3FQc3dEZE1CaTJRYTJvVWc?oc=5</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3444,12 +3444,12 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Air India turbulence injures passengers on Phuket-Delhi flight - Gulf Business</t>
+          <t>Another Hormuz workaround - EnterpriseAM</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOUk92b3hCQVZybGNndXNJOF9ZX0Z3TGl5NnRuXzE5NlBRb3czZXM2SkxXb3ZQSGNOdGo2a2U2b040ZVFDcFBqbzdvaFFZaVdBbFgwQkJOOEhDNzF6VXY1OU9Ca2t2Z1ZnQlhscXNXTVhDaWY3b2lvMUlEWFhkXzVxaDR3b191OUx2aTVKcEttYkFGTjRzRVpnbFJvLUZhYmNLTFJJNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5iUjRXRTlrdVBXOHUyRWlYc2ttOXdYaVktOE5ZU1YxMnRLcnlHeWRPdl9CQmRkR3Bqc21aeFlWMmdFcGdjanc3d2RNTnRGcWdKVGdxQTZmeC02clJoSXJJaGJlUUM5TW5pQjRORkVpRQ?oc=5</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>UAE Business: UAE extends small business relief for corporate tax until December 2029 - Gulf Daily News</t>
+          <t>UAE e-invoicing: How digital invoices will transform business - Khaleej Times</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNVm43RXV5MWlfOTE5TjdqQjhtd3pzUnRIdmJycExNbXV6REpoRjQ5MlNiRENNemM5SG5VbUhJbnVXenhQXzFhRGgtNXE3QjRWWHhCcTJsZ0lfUW5ZTWNWcjdZQnZSSDM0VVdvVDY0ejBPMklPTUkzdTdXX090b1RQY21nbmdUQUtuZG42RHBxRWdCb05xNkdBT2xUVk1SNWN0cG1NbnhKNlBxSl96T3BzOU91cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQMjFwZTd6MkpqcXZKaEwxZV9fUlZWSEtSeVdIQXN6YXFPMURFMWZhOHc0NWFuWlRfd1ZNX2doQVBpbXBqRFBTOVNNcjVTYVpOcEozYmtoaWxDUHVoUFFNT1RBWEI3RzJybmFWejFNcEcxYXpybDBiUzRLUk85ajBkOHIydnBjOUV6NEVJUjZkQTNOQ0Fud1BjdGtUNVpwTmlTazdyNWZmaXRwTkthY1Nac1RPWU90T3lMemJJNHp5VdIBvwFBVV95cUxQMjFwZTd6MkpqcXZKaEwxZV9fUlZWSEtSeVdIQXN6YXFPMURFMWZhOHc0NWFuWlRfd1ZNX2doQVBpbXBqRFBTOVNNcjVTYVpOcEozYmtoaWxDUHVoUFFNT1RBWEI3RzJybmFWejFNcEcxYXpybDBiUzRLUk85ajBkOHIydnBjOUV6NEVJUjZkQTNOQ0Fud1BjdGtUNVpwTmlTazdyNWZmaXRwTkthY1Nac1RPWU90T3lMemJJNHp5VQ?oc=5</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
@@ -3519,12 +3519,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3534,12 +3534,12 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>UAE extends corporate tax relief for small businesses until 2029 - Khaleej Times</t>
+          <t>More investments in Adnoc’s fleet, Indian IPOs, and Egypt’s North Coast - EnterpriseAM</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNMDNwUlhpclFxaFJkdkkzR0s5MVh4WHZOUDdfZzZtNTBFb2RIcklxMF91Tkp2NGRxRlZMM3BubEZGc0g5LXpsQUhHQy01eGcxTllzc1k1S1NqeFMtYXM4YlBmREttNlhsS0hmd2JXN0l2UjFEQ3B5M1pfRTVpOGw0Z1pPMTNHd0tHQ25ZNjNGZmVaZnhzZUJueE9sQ2dNNGVaUDVjTdIBrAFBVV95cUxNbWJjeHFtRU9DbExyNHRRY1NEUXB2WnZRZ1V2TlFhQ010T3RhSmptR2ItaDhxVnEta0NITUJyS3ppaGgyQ2FkclQwRFhCaWNnLUhNb21YaDVGLWZZNThic2hpN0MzNTI4cXI3RjYtLVUzN3VHanJUUHdYaEFRWUlvS2w5UVdja3pwd1Q4c2pXWHVPZ0xZVmFCcE43eWl1bG10N0s4UXdpVUhpU0tH?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1RdV9pa3ZIMmpRWnFlcXRaeTRnSy1zZUp0enVScm1nc0hMX3UwTEdEOG9oQy00UUJiSUR4WENleElGQVVmLXh3ZE10b09nQWphT0IzNHNJb0h3Q0E?oc=5</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
@@ -3564,12 +3564,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>UAE extends corporate tax relief for small businesses until 2029 - thenationalnews.com</t>
+          <t>FTA Directive No. 5 of 2026 - Crowe</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQOFMwcEtFYkFkbWxMRnBqX3Y1M2ZOcnJ4Q1FzTHg2b1NDYnU3dzVWMmMycVdhNzJSbTZhaTZ1bjRpN3RYcm9Gb3VIOUxydjN6anFTMU12SHNNcmt1YkhwSk1RVTV6Yk1yS0wtNm9PbVZLNkxmTVRNd3hEOW1xbXdnTlBiX0VJWWhINEw5MHc1eEk4UHhFZHFOZ04zcnZERDZhLXZJQ0VGWS15N080ZXBQYVhDMFU2al9wN1NlNXN2RnFaZEU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE40S0RnRzF2d1dBSmNHdkNNQXZQQmlOYWNOSk5OWnlVNUN3ZDB5UHBUV29RXzNvaF9pVFNQZ2FwTUdocGhxMXp1T3gxMUFycGNESFA1bXNR?oc=5</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
@@ -3604,12 +3604,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>September 1 change: UAE announces new excise price rule for electronic smoking products - Gulf Business</t>
+          <t>Digital currency and VAT: New UAE rules for businesses to consider - thenationalnews.com</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>News — FTA Announcements</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNMXNESjR5VDVIQ0Qwb0xKUk1xRlhaTmV2RjNfdVpGaDZZYk0wcjdSbC1RRHBUNkRRaGpNOS1mSjR1blVVRHJ6MzdLeUZXM1lMWURyX21CS25DZFN3engwRWZCOFFLUDJydEEwX0pSa1lLSlNqbVlhdk9pNmtvLUh1QzFubU9RVENUNEl3QVdLc2FkRUV6TGFjZmJwLUtiUVd5dlhjVW1SLU43WFI4eGNfZkJCTXBNaEQySVR3QjZuazA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQamI1MElzOEtNS1ZjVWR3VGpjZjNUZjBXbjQwZkJIZ3AwOFVqckl0WWFQN2JpaEg5XzRTUTBVMDFOeVhMaUZxYW9GUnBFNW55WnhKd2ZKOVZoekRBWUNqQkp3dGFPZ2JQcWY5SjVlRUJuTURfcVN5aUNXVmthdUh4cHlJbFNHN3lyT1VTU2l2Nk92U09JZFh3eXp0c29jTlJNZW1VLTZBR2h5WmdBTjFuNGczZkZwdDY1QWc?oc=5</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
@@ -3649,17 +3649,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3669,12 +3669,12 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>UAE small businesses claiming tax relief must still file corporate tax returns - Emirates 24|7</t>
+          <t>Air India turbulence injures passengers on Phuket-Delhi flight - Gulf Business</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>News — FTA Announcements</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOLXJ6YVV3T2dXazExeU04V09UYlk3NmtYT2d3Z2t1X2RPckN0RjVQZE9oNTljdi1rUUlzTDlMalotZ1JWRS03TWVFWlVVS1hyMVlDUEsxYWQ3RWgtdTdUNzVaZjE5WlhVVUhJcjkyaDFVa28yeEN2ejAtVG43dnduV2NDa0k4czRLby1sU2w2ZHZTcGtPZmpiTjRYWXB2VUExMnhreUktUDBZSkZ4LUxZYW9TYXRJc2s0U1QyMtIB1wFBVV95cUxPNWVmQzRQOEJkZnBCZVFDblE2dkFlX1hGNWlnalJBVk5QREJoU0ZvMXZIM1JJYXdLb2lQZFNnejliekY3Y29nN0tLdTUxQ0h0SUFaSVlpOWhuX3dVaHdjX3NPM1pkd2xlVDRMT1VmTHJ4QV9PbmpWRmVHRFpHZ1lyUF9ZWEJTcFJ2LS1QX0hEa0Y3dnJ4S054S211cWRMWWlHVVd2V19wQnhGa2JVR1ZxSFVNVWJMejdESlFZSkxUMGYwQUlyQkpueDlwb2dJYnlqQnZGNklscw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOUk92b3hCQVZybGNndXNJOF9ZX0Z3TGl5NnRuXzE5NlBRb3czZXM2SkxXb3ZQSGNOdGo2a2U2b040ZVFDcFBqbzdvaFFZaVdBbFgwQkJOOEhDNzF6VXY1OU9Ca2t2Z1ZnQlhscXNXTVhDaWY3b2lvMUlEWFhkXzVxaDR3b191OUx2aTVKcEttYkFGTjRzRVpnbFJvLUZhYmNLTFJJNg?oc=5</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
@@ -3694,12 +3694,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>UAE releases registration requirements for domestic minimum top-up tax - kpmg.com</t>
+          <t>UAE Business: UAE extends small business relief for corporate tax until December 2029 - Gulf Daily News</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>News — FTA Announcements</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPaGJWUy1MU0VZdmd3LTVPTmw0bDYtWlF5a3JCVkFwVnhJRUkxVkdEWUE4X1VZLXg0Tkg4YTlLWHhoOUJYVzJqR3lzUE5Pa1RpSWtjdkRDQ09UeDBoQ3Y2bGlLbkhzTXZ2WlNJeGFSLXNqRUZyRnBfNV9Mbk5UY25hdVZ6VWM2cWRYOEt4bUlnWV9QYkQtOWZudGJaV0ZJZDRVY2JGbTY1T1JTYVhyTGhEdlVuQzlzZkN6ZC1VRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNVm43RXV5MWlfOTE5TjdqQjhtd3pzUnRIdmJycExNbXV6REpoRjQ5MlNiRENNemM5SG5VbUhJbnVXenhQXzFhRGgtNXE3QjRWWHhCcTJsZ0lfUW5ZTWNWcjdZQnZSSDM0VVdvVDY0ejBPMklPTUkzdTdXX090b1RQY21nbmdUQUtuZG42RHBxRWdCb05xNkdBT2xUVk1SNWN0cG1NbnhKNlBxSl96T3BzOU91cw?oc=5</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
@@ -3739,17 +3739,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>UAE Digital Economy: Why Trust, Not Speed, Now Wins The Race - Menafn</t>
+          <t>UAE extends corporate tax relief for small businesses until 2029 - Khaleej Times</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNbi1OcWZwSTNNYjBRZkJWS1FodlVGTG5oZHB1T3Q2cGRqazRiZGQzeUtlOVB3VXlhNUM1TnhSdW1MVS1uSng1dGFmTlAzb3ZMNXlod0c5bWo2RkdOTW1idm9JQ3dQNTM5Z3FvZl96WlNuVVh4Mmx5NGFNWXBHVFZoWnUyQU9WT01idllWclJqTXE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNMDNwUlhpclFxaFJkdkkzR0s5MVh4WHZOUDdfZzZtNTBFb2RIcklxMF91Tkp2NGRxRlZMM3BubEZGc0g5LXpsQUhHQy01eGcxTllzc1k1S1NqeFMtYXM4YlBmREttNlhsS0hmd2JXN0l2UjFEQ3B5M1pfRTVpOGw0Z1pPMTNHd0tHQ25ZNjNGZmVaZnhzZUJueE9sQ2dNNGVaUDVjTdIBrAFBVV95cUxNbWJjeHFtRU9DbExyNHRRY1NEUXB2WnZRZ1V2TlFhQ010T3RhSmptR2ItaDhxVnEta0NITUJyS3ppaGgyQ2FkclQwRFhCaWNnLUhNb21YaDVGLWZZNThic2hpN0MzNTI4cXI3RjYtLVUzN3VHanJUUHdYaEFRWUlvS2w5UVdja3pwd1Q4c2pXWHVPZ0xZVmFCcE43eWl1bG10N0s4UXdpVUhpU0tH?oc=5</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -3784,7 +3784,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Finance sets e-cigarette liquid excise price - Sharjah24</t>
+          <t>UAE extends corporate tax relief for small businesses until 2029 - thenationalnews.com</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBGY1BCNkVheXBxM3RBdWlPNXVULWVaaWdWM3RWWU9JSWI2T3JVMGlMdl94Ync5ekFqdGU1SzAxeEMwaUhJR1hTejhVTFo4blI2Y1d5QzZUaVgwUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQOFMwcEtFYkFkbWxMRnBqX3Y1M2ZOcnJ4Q1FzTHg2b1NDYnU3dzVWMmMycVdhNzJSbTZhaTZ1bjRpN3RYcm9Gb3VIOUxydjN6anFTMU12SHNNcmt1YkhwSk1RVTV6Yk1yS0wtNm9PbVZLNkxmTVRNd3hEOW1xbXdnTlBiX0VJWWhINEw5MHc1eEk4UHhFZHFOZ04zcnZERDZhLXZJQ0VGWS15N080ZXBQYVhDMFU2al9wN1NlNXN2RnFaZEU?oc=5</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
@@ -3834,12 +3834,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>CBUAE injects more liquidity into the banking system - EnterpriseAM</t>
+          <t>September 1 change: UAE announces new excise price rule for electronic smoking products - Gulf Business</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — FTA Announcements</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPRVF2amFoSUlsRENGenUxcUlxRU9NeU9QWlJhUkExb1k0cExublF1YUdrM2dJc0FySm9zQmgyQUtKU092bkpYT1I1bUhaMkxGR2o2SFVnckhIR2d4RGQzOUJnb19tZERINThyZ0NrQ1A0WUttandLcmN0QUlUaTFVZ1djMnUxdEp4SmNGMjM1Zl9HX1k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNMXNESjR5VDVIQ0Qwb0xKUk1xRlhaTmV2RjNfdVpGaDZZYk0wcjdSbC1RRHBUNkRRaGpNOS1mSjR1blVVRHJ6MzdLeUZXM1lMWURyX21CS25DZFN3engwRWZCOFFLUDJydEEwX0pSa1lLSlNqbVlhdk9pNmtvLUh1QzFubU9RVENUNEl3QVdLc2FkRUV6TGFjZmJwLUtiUVd5dlhjVW1SLU43WFI4eGNfZkJCTXBNaEQySVR3QjZuazA?oc=5</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
@@ -3879,12 +3879,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>The Taxation Society partners with Tally Solutions to strengthen UAE's finance and tax professional community - khaleejtimes.com</t>
+          <t>UAE small businesses claiming tax relief must still file corporate tax returns - Emirates 24|7</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — FTA Announcements</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNMXRpRGhpQXJvUkZhQU1IcTF6Z0JtLW16cTQ1d24zZWlwQTlPMHNCeG8tY0NLc1JGcXdjT2g5V01YM3hOVmtZYzBJeThiR3hhSDRpdGdwaDhsVC1WMDFTSWN0SWdhc3hiWTRSQmV0blZEZkowYWdoSU1BaUJ6Y01ZZ2ZrWlNRc2JtUllnc0huTF92aWdmbEp4bTRvRV9fN2xTU2dmMjdLSk43ZlFlcEtuWTBKQXdFTU5pMlRnWE55VFBwcTc0STRtcFluS3Ffek1oM2NRQ1dYemVkTktESkJRSVJ30gHqAUFVX3lxTE85ZnVhMjFKMWdhenV1YlFiRGtpVTBIdjRvLVNLRFBjTHBPUnVfeG5sUGxIcWVlSlhUTEVibFV2UXdWbEg5TGNmS3hBYnczSEctV3BBT2pZT3dpcDJUeGczWE9xQ1dweV9hc1hwQnhHQkFWUDRrb0FzV0tVdmZhZ0pLZC14YlVJZjBYQmcwbUZWeG55dnhpOFliT0wxYkQ0bzl1VEhiVUpQNjQ4TVN0bFhPRERROXB5NUZZQ0VRS08tY0VmSDdLRFQzMHZ0dEZtamJ5dmp1OGZ6SmNxQjZrck8wRWs2U1A0TFJZdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOLXJ6YVV3T2dXazExeU04V09UYlk3NmtYT2d3Z2t1X2RPckN0RjVQZE9oNTljdi1rUUlzTDlMalotZ1JWRS03TWVFWlVVS1hyMVlDUEsxYWQ3RWgtdTdUNzVaZjE5WlhVVUhJcjkyaDFVa28yeEN2ejAtVG43dnduV2NDa0k4czRLby1sU2w2ZHZTcGtPZmpiTjRYWXB2VUExMnhreUktUDBZSkZ4LUxZYW9TYXRJc2s0U1QyMtIB1wFBVV95cUxPNWVmQzRQOEJkZnBCZVFDblE2dkFlX1hGNWlnalJBVk5QREJoU0ZvMXZIM1JJYXdLb2lQZFNnejliekY3Y29nN0tLdTUxQ0h0SUFaSVlpOWhuX3dVaHdjX3NPM1pkd2xlVDRMT1VmTHJ4QV9PbmpWRmVHRFpHZ1lyUF9ZWEJTcFJ2LS1QX0hEa0Y3dnJ4S054S211cWRMWWlHVVd2V19wQnhGa2JVR1ZxSFVNVWJMejdESlFZSkxUMGYwQUlyQkpueDlwb2dJYnlqQnZGNklscw?oc=5</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>MoF extends Small Business Relief for corporate tax until end-2029 - Sharjah24</t>
+          <t>UAE releases registration requirements for domestic minimum top-up tax - kpmg.com</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>News — UAE E-Invoicing</t>
+          <t>News — FTA Announcements</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFA4N01YTUZ2UGRGVWdDQ3JDM3JLYWJDanVuckdCLVhuQUdqUFo3clA1cGRoTUtubWNpQ0dTOUFSQk5jYzdGcVFYNkNpQjF4ckFVZ2pBc0FXM1Ffa0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPaGJWUy1MU0VZdmd3LTVPTmw0bDYtWlF5a3JCVkFwVnhJRUkxVkdEWUE4X1VZLXg0Tkg4YTlLWHhoOUJYVzJqR3lzUE5Pa1RpSWtjdkRDQ09UeDBoQ3Y2bGlLbkhzTXZ2WlNJeGFSLXNqRUZyRnBfNV9Mbk5UY25hdVZ6VWM2cWRYOEt4bUlnWV9QYkQtOWZudGJaV0ZJZDRVY2JGbTY1T1JTYVhyTGhEdlVuQzlzZkN6ZC1VRQ?oc=5</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Northern Emirates’ property markets cool off + Sidara locks in USD 1.35 bn in firepower - EnterpriseAM</t>
+          <t>UAE Digital Economy: Why Trust, Not Speed, Now Wins The Race - Menafn</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOMDUxZXd1MElSNXdaNDByLW9jbHFIenJCY21PRnhPMUx4YkdyZ1FMREVxenNWZWZUY2p3MHQ5V2xUQmswZ1RuV1g3Q3RHUzdvOFhvOGpST2diQWIwOXFBeXdzc1lYRl9FRDIxdjBjUVR3Y2VEcUdIWXB0amg4YW5qbklORzFMS3J4VUZGelkybDVZcXc0VHlNck4zTXdjR1N1UzZmSk9vSFFoMDJMVENKMFVlWEdvUTEwZFhiZmdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNbi1OcWZwSTNNYjBRZkJWS1FodlVGTG5oZHB1T3Q2cGRqazRiZGQzeUtlOVB3VXlhNUM1TnhSdW1MVS1uSng1dGFmTlAzb3ZMNXlod0c5bWo2RkdOTW1idm9JQ3dQNTM5Z3FvZl96WlNuVVh4Mmx5NGFNWXBHVFZoWnUyQU9WT01idllWclJqTXE?oc=5</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
@@ -4014,12 +4014,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>E-Invoicing</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>ClearTax urges UAE businesses to prioritise execution assurance as e-invoicing decisions gather pace - Gulf News</t>
+          <t>Ministry of Finance sets e-cigarette liquid excise price - Sharjah24</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPTG13TFpCRmpaaWU3ZGxsVEtqakxUUXhSc0ltWUZfOEUyWTcxWGhOZ2doazNZY1V2LWFnSlp0NHpHTXN4emN6TzFWbGlXT09xU0Q3X25BTmpBVVl0Nl9XMFdRUE9HMy1BU3BMRDFIZ1RITkw4d3BSanluZGFHal9CM3h5dDNtTlBtUG9LYXZZWkhILVZhdUpKTHhUd2lMWmVOdVJrREx4UUF4WjNvTW5hSmtBVjVyQVBpblVKa1hKbjhxRTNUVmpUMVpXOFFJSWx1NUZWUWFMYlY2ZjA2Nml6OGV6X2ZGcVhkQkQ00gH-AUFVX3lxTE12b1Q4Qjd0Rks3U1hqOC1GVTZ5RXRUOXB6eVdVd3RMTEV5Q1pRYVRrc19GaG1qY3FXRGhqMkN3N3c2emJyeTFWbEU2QkRSMHR5aWFzNlctUi1mdi1vamRHMHZoWFZlQlRCbEhrT3BLSXlsTXRfYjY4QjVHblFRU0JnZVhlam4xNEF6d0hQVUtmTHFoYnktSW5LS3dqU2VleEh4azlObnoyUTNPd2E0RWc4U0ZhMkRoc1J1c2R6VGJhc1lSYTF0cjhzdnY0Q0tvYk81YnY5UE5CdnBXZTVNQXE4UlZwMkFjbUREaEtRNlF2MWJYVFhaOTFJNTZRUlJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBGY1BCNkVheXBxM3RBdWlPNXVULWVaaWdWM3RWWU9JSWI2T3JVMGlMdl94Ync5ekFqdGU1SzAxeEMwaUhJR1hTejhVTFo4blI2Y1d5QzZUaVgwUQ?oc=5</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>UAE extends small business tax relief until 2029 - theaccountant-online.com</t>
+          <t>CBUAE injects more liquidity into the banking system - EnterpriseAM</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOMTA1XzlxbnpmYjNMcU01VXV1RjdMOHFuMi1CSVNMYXlaNW9kb2ZMSXZXOEZ1dDlqbmRLR2hXQjNrMDdlaU4teDVRTG1CMmJsY0lDU3V0SWxRZE4tWXZXbV9pR2o5THFMREVyZ3VpY1pTYVhFeUJza1MwOWtVYXB1ckwxQlBRdVF6eURUUHlkblhUNnNoQ3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPRVF2amFoSUlsRENGenUxcUlxRU9NeU9QWlJhUkExb1k0cExublF1YUdrM2dJc0FySm9zQmgyQUtKU092bkpYT1I1bUhaMkxGR2o2SFVnckhIR2d4RGQzOUJnb19tZERINThyZ0NrQ1A0WUttandLcmN0QUlUaTFVZ1djMnUxdEp4SmNGMjM1Zl9HX1k?oc=5</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Sovos Announces 2026 Partner of the Year Award Winners, Recognizing Excellence in Strategic Collaboration and Innovation - Business Wire</t>
+          <t>The Taxation Society partners with Tally Solutions to strengthen UAE's finance and tax professional community - khaleejtimes.com</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxQRzJIdmQ3VjZqenlUTldPal9HNXdxdTJibTJHWFBhMVBMTWcxbm0yeUhJYzVLd0Z3Yl9pdE1LQzREWm13dXE4ZG1abDFuRkZIdHhIcm4zYXVoOXZIS01KNW5xRU04SUVwMlRnZlBxb3BYQkJMQ01CeXhabEI5U1VfSlpad0ROaVNnTUVnUll2WFhwMkxUa2tidGRxTDlMRm93SlAxVkNoWW84Zk1oeFFoNVdnOWRBZERIZzNSdnVDMGpHZ0MzSXlxZ1JXc2hodEY0aXNoRkNBRldSOGdxSkowdmFoTEplTjBtOUVfeWFtNmpzeDZtR3J2bVk4UWthWFR5VjJRbEM2NA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNMXRpRGhpQXJvUkZhQU1IcTF6Z0JtLW16cTQ1d24zZWlwQTlPMHNCeG8tY0NLc1JGcXdjT2g5V01YM3hOVmtZYzBJeThiR3hhSDRpdGdwaDhsVC1WMDFTSWN0SWdhc3hiWTRSQmV0blZEZkowYWdoSU1BaUJ6Y01ZZ2ZrWlNRc2JtUllnc0huTF92aWdmbEp4bTRvRV9fN2xTU2dmMjdLSk43ZlFlcEtuWTBKQXdFTU5pMlRnWE55VFBwcTc0STRtcFluS3Ffek1oM2NRQ1dYemVkTktESkJRSVJ30gHqAUFVX3lxTE85ZnVhMjFKMWdhenV1YlFiRGtpVTBIdjRvLVNLRFBjTHBPUnVfeG5sUGxIcWVlSlhUTEVibFV2UXdWbEg5TGNmS3hBYnczSEctV3BBT2pZT3dpcDJUeGczWE9xQ1dweV9hc1hwQnhHQkFWUDRrb0FzV0tVdmZhZ0pLZC14YlVJZjBYQmcwbUZWeG55dnhpOFliT0wxYkQ0bzl1VEhiVUpQNjQ4TVN0bFhPRERROXB5NUZZQ0VRS08tY0VmSDdLRFQzMHZ0dEZtamJ5dmp1OGZ6SmNxQjZrck8wRWs2U1A0TFJZdw?oc=5</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>UAE E Invoicing Guidelines Updated to Version 1.1 - Crowe</t>
+          <t>MoF extends Small Business Relief for corporate tax until end-2029 - Sharjah24</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQOGUxa2xtLVY1ejE0azVCMEZSa3lxNHZmajhUdzh5LTQ5NGRqVk5oenBzNmJUSk44X1B0elZ5aDI5YVl4VHpLb2RzdEFRYW9IVmR5dHpOaE1JbWVoNzdvQVpsR0xIalA1MHBaR1NNOVpVSHUyX2t4R0dIVmZiWHlXWg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFA4N01YTUZ2UGRGVWdDQ3JDM3JLYWJDanVuckdCLVhuQUdqUFo3clA1cGRoTUtubWNpQ0dTOUFSQk5jYzdGcVFYNkNpQjF4ckFVZ2pBc0FXM1Ffa0k?oc=5</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr"/>
@@ -4194,12 +4194,12 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>VAT, E-Invoicing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>Congo Republic e-invoicing launched - vatcalc.com</t>
+          <t>Northern Emirates’ property markets cool off + Sidara locks in USD 1.35 bn in firepower - EnterpriseAM</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOLTlBQUhqTDJya1ZpUmx5Y0lPRlRHb0VpWW5GYWVBc1JkTGRFbFl0b3N5UGJSdEdXRmwxdld1RlhqSWVremtIU1pWSHNXb2ROejA2TzJYcF9RX29TQVN1akJ5d0cxWFplcmJPYUJTRDgzU2FzenRzMzJldUsyaE9rbzlVUmJMSEc5M1pzSGtR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOMDUxZXd1MElSNXdaNDByLW9jbHFIenJCY21PRnhPMUx4YkdyZ1FMREVxenNWZWZUY2p3MHQ5V2xUQmswZ1RuV1g3Q3RHUzdvOFhvOGpST2diQWIwOXFBeXdzc1lYRl9FRDIxdjBjUVR3Y2VEcUdIWXB0amg4YW5qbklORzFMS3J4VUZGelkybDVZcXc0VHlNck4zTXdjR1N1UzZmSk9vSFFoMDJMVENKMFVlWEdvUTEwZFhiZmdn?oc=5</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr"/>
@@ -4239,12 +4239,12 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-Invoicing</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Corporate Governance in the UAE - Crowe</t>
+          <t>ClearTax urges UAE businesses to prioritise execution assurance as e-invoicing decisions gather pace - Gulf News</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Transfer Pricing</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE4weWRYb0VETFpvMjdhUG9BbU5Wb2JXbzNkLVpxSC1VZHhwYjMwT0F2OFNvQkJNQTFkOG1OamVFZWU0NWpVN3hHb0lldkJWLV9GeThwSjdzNlpnQXp0VDdQbkpnSWFFU3lacVJOeXl3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPTG13TFpCRmpaaWU3ZGxsVEtqakxUUXhSc0ltWUZfOEUyWTcxWGhOZ2doazNZY1V2LWFnSlp0NHpHTXN4emN6TzFWbGlXT09xU0Q3X25BTmpBVVl0Nl9XMFdRUE9HMy1BU3BMRDFIZ1RITkw4d3BSanluZGFHal9CM3h5dDNtTlBtUG9LYXZZWkhILVZhdUpKTHhUd2lMWmVOdVJrREx4UUF4WjNvTW5hSmtBVjVyQVBpblVKa1hKbjhxRTNUVmpUMVpXOFFJSWx1NUZWUWFMYlY2ZjA2Nml6OGV6X2ZGcVhkQkQ00gH-AUFVX3lxTE12b1Q4Qjd0Rks3U1hqOC1GVTZ5RXRUOXB6eVdVd3RMTEV5Q1pRYVRrc19GaG1qY3FXRGhqMkN3N3c2emJyeTFWbEU2QkRSMHR5aWFzNlctUi1mdi1vamRHMHZoWFZlQlRCbEhrT3BLSXlsTXRfYjY4QjVHblFRU0JnZVhlam4xNEF6d0hQVUtmTHFoYnktSW5LS3dqU2VleEh4azlObnoyUTNPd2E0RWc4U0ZhMkRoc1J1c2R6VGJhc1lSYTF0cjhzdnY0Q0tvYk81YnY5UE5CdnBXZTVNQXE4UlZwMkFjbUREaEtRNlF2MWJYVFhaOTFJNTZRUlJn?oc=5</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr"/>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>Shopping online in the UAE? Tourists can now claim tax refunds on Noon orders - The Global Filipino Magazine</t>
+          <t>UAE extends small business tax relief until 2029 - theaccountant-online.com</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNa1BKRVpJRVZCZm5VNVp2d3h4Rl92ejg0aml0Qy1pTUotYTZ4ZHlaeURMcnRacE9Zc0J2TWt4VktTQWdFV3BlNXBzWmlfMXFEZFRiYWRIMmV3X3ItaWc0T3pzOG52THI4c1RQaDY1RWdNbXItTTUtdlFTS1d6SUpZTVlXM2lOTWtLWXF6TGNSRE9OWkJQSUs3UXFoSEtOa2NpNEJLeTFOektldFVUVHk4cFJCSE5Qdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOMTA1XzlxbnpmYjNMcU01VXV1RjdMOHFuMi1CSVNMYXlaNW9kb2ZMSXZXOEZ1dDlqbmRLR2hXQjNrMDdlaU4teDVRTG1CMmJsY0lDU3V0SWxRZE4tWXZXbV9pR2o5THFMREVyZ3VpY1pTYVhFeUJza1MwOWtVYXB1ckwxQlBRdVF6eURUUHlkblhUNnNoQ3c?oc=5</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr"/>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>Number of retail outlets connected to Digital Tourist VAT Refund System reaches more than 19,300 - Big News Network.com</t>
+          <t>Sovos Announces 2026 Partner of the Year Award Winners, Recognizing Excellence in Strategic Collaboration and Innovation - Business Wire</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNUjRVVzdLOXJQTXpUZDhqeWlQNDAwVDV2ZmJqd3h4cW5ZbXc0cHEzZGJBSWlLOTk0ZlFFbXlVSThCUEtxcGFqUHYzSlRmeXF0bC1XQ1J3VVhKUUkzeVBfNTc4cmQwNmlRYldwUU01YXpmc0pxT0daNWRpRUwtM0N3MlBBR09rRldZZlA5bXVJOXVTcVZSeE5ldWRHSWhna0ZfTTNwZWEwODlFTXRRYnRhOVJVcHJ3dDRuSnZtQlBhc0NMa2dhSzk4b1lBWEx5Uk5Ld2RMaFdmNUY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxQRzJIdmQ3VjZqenlUTldPal9HNXdxdTJibTJHWFBhMVBMTWcxbm0yeUhJYzVLd0Z3Yl9pdE1LQzREWm13dXE4ZG1abDFuRkZIdHhIcm4zYXVoOXZIS01KNW5xRU04SUVwMlRnZlBxb3BYQkJMQ01CeXhabEI5U1VfSlpad0ROaVNnTUVnUll2WFhwMkxUa2tidGRxTDlMRm93SlAxVkNoWW84Zk1oeFFoNVdnOWRBZERIZzNSdnVDMGpHZ0MzSXlxZ1JXc2hodEY0aXNoRkNBRldSOGdxSkowdmFoTEplTjBtOUVfeWFtNmpzeDZtR3J2bVk4UWthWFR5VjJRbEM2NA?oc=5</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>UAE tourists can claim VAT refunds at 19,340 stores and on Noon purchases - Gulf News</t>
+          <t>UAE E Invoicing Guidelines Updated to Version 1.1 - Crowe</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQeDRPcDE4QjJaSFU3Qm1wRGVaWXl6cjY2c3YyVDF3TmtqN1RYMkh0WDdoSm56QmlXU21xSllRQWt4WHNFU09vUWZpTEd3dVVMb0UxNy0yZG1ucUF6aXhIZ2dWVXpkVjVqa2hHUGN3VHNZWEticFZMXzNfb2NzaVpwOFFkOVAtNDhBY0xjSUo3bkh0WUg2ZEJ4Q0JDU05Td0FTLWlUWXNfN2JKeGJsTEg3NGFDMzNwT21JZTFGT0V30gHQAUFVX3lxTE9wdElvSG52YzNWWUt6WGJaRkp0LXpmVHpQTFV4WHczVkQtOUhOMWpqRzd2UjgyQjNOSWdMT3QwM1luZzdtNWhXdU91R2lqS0FKcG1hUGExZ1QxWG1SSUo2cWZSWll0bjdpQ2pBOXFjTUMxcjJma0RraGlVbjNjajZRM0h4OVZfM0FUQXNERTQzQm1TS29QVjdiQzM2T19naktoTXhfQ1pvNmx4U2IxVkkxUWF5QmZ4QUxmMXB2bFVvR2RVWm10bjE2SlNaRzJ2VEU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQOGUxa2xtLVY1ejE0azVCMEZSa3lxNHZmajhUdzh5LTQ5NGRqVk5oenBzNmJUSk44X1B0elZ5aDI5YVl4VHpLb2RzdEFRYW9IVmR5dHpOaE1JbWVoNzdvQVpsR0xIalA1MHBaR1NNOVpVSHUyX2t4R0dIVmZiWHlXWg?oc=5</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr"/>
@@ -4419,12 +4419,12 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>VAT, E-Invoicing</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>Retail outlets linked to UAE's Digital Tourist VAT Refund System exceed 19,300 - Emirates 24|7</t>
+          <t>Congo Republic e-invoicing launched - vatcalc.com</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE E-Invoicing</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOcXRBMGsxX1Q5SkJXcEFwWnV3c0VVc19jUnRkWU5yMVlPelltaEhvOWNLcEJxYi1KUExWMVlmZE1FOExZYklsRHU4N3lQZGppMDRnYUFaRU1OWHdwaVpiWWowOENidVJjbDFPeTQyQklzOGM5bXhQbDJrRFg2TkR6bUplTzJNZzl2M3dJT2FEeHVTTVNtTml6UEdoZUFDcVRCZWFHMGg1ejZoSWI1UWFCLV9zREotcmF3V0HSAdQBQVVfeXFMT3Q0RFN0V3FRSlNWV20tMm5hY1N5VHBVWmxzdnZGVXIwZU92VTZVRDVUVkRZM0Q1U1ZNZzFRcFlEWTc2ckk0UjZhcEN4YmZIZndTd284ZDQ3Z2Z4OS1mVGFUX2RwRzgyMWViTjEyQ19wdUxucXEtZWtFRm5tOWpId1VYYlRmd1Rkc2tlb3Q3THR0THZxZWt3Q1ZyTGVvZ2hUUzZPeTBPSzlER3FXR0ZvUnJiWk5vdlpwYlYxdmZjZnNTVEQxM3hSY1pyTGV5Qkk2d2lrejQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOLTlBQUhqTDJya1ZpUmx5Y0lPRlRHb0VpWW5GYWVBc1JkTGRFbFl0b3N5UGJSdEdXRmwxdld1RlhqSWVremtIU1pWSHNXb2ROejA2TzJYcF9RX29TQVN1akJ5d0cxWFplcmJPYUJTRDgzU2FzenRzMzJldUsyaE9rbzlVUmJMSEc5M1pzSGtR?oc=5</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr"/>
@@ -4464,12 +4464,12 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>Indians, Russians, Turks top list of tourists claiming the most VAT refunds in UAE - khaleejtimes.com</t>
+          <t>Corporate Governance in the UAE - Crowe</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>News — UAE VAT</t>
+          <t>News — UAE Transfer Pricing</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPek9sY1dJUkpRblhiYnJDdDExOW1yREdXd1oyZ1Yxb0FnZlBYNTd3SUxGWnVMenlZVGlqRlIxLUszNk1Jd3BpcF9rVE9XLVF1OWdhY01fd0gteTJFRkVJLVREMjl4ZVRGZHJacUxJREpRN3UxdHFncGhITEQ0MnUzTkhKY2FSZnBnaFUzZDEyRnZOdG1hOWVFX2FLNG9Ca1lGekQzcllxd0FqTUhvTTRZM3MxcElQV0JaMWfSAcIBQVVfeXFMT2FPTEx4WGUzNUNhZWdBa1MzVU5GN1p3SkRwM0o5TWlqenhqVTNhR1Z0bThyN0laMS1tOUhfaG1qMmZpQi1pT3lTNEhKT2l3SklKZ1E3MXkyYVBrMnUwOTh1Y2RxSkFISUdlT1B6Qm1tTV9CUV9YM0xwcTJ2NzVmWUcxaFJ2YzhYeVBjZG1WSG9vcVc2N2tqRzNreHFwWVpaaUdncndzVEVLaE8zeHczU0Jvdl9FazU2NE1CNWZqQmZmekE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE4weWRYb0VETFpvMjdhUG9BbU5Wb2JXbzNkLVpxSC1VZHhwYjMwT0F2OFNvQkJNQTFkOG1OamVFZWU0NWpVN3hHb0lldkJWLV9GeThwSjdzNlpnQXp0VDdQbkpnSWFFU3lacVJOeXl3?oc=5</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr"/>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>Tourists can now claim VAT refunds at 19,300 retail outlets across the UAE - Gulf Business</t>
+          <t>Shopping online in the UAE? Tourists can now claim tax refunds on Noon orders - The Global Filipino Magazine</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQV2tyUkVhVzNVUlZ0QW9LdW5PWV9OTEVSN1FHU2c0Um9qbTRDNXFIdmZUaERGcDFPUkkyTVpzWXBQblJHb1VzVERybTh5WkIzcnRoRFo1ZVBicVRMQXpFZXB3VVJRQVZ6UDNNZDItT1RuTXcxYWxtSU1PaGlPNTFNUnpzLXBGX2QxSy1WVjU4alg4Q0dEWmY4WFZ6cEt1a1FZQXpRODFFN0xRT3VwSWFfNw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNa1BKRVpJRVZCZm5VNVp2d3h4Rl92ejg0aml0Qy1pTUotYTZ4ZHlaeURMcnRacE9Zc0J2TWt4VktTQWdFV3BlNXBzWmlfMXFEZFRiYWRIMmV3X3ItaWc0T3pzOG52THI4c1RQaDY1RWdNbXItTTUtdlFTS1d6SUpZTVlXM2lOTWtLWXF6TGNSRE9OWkJQSUs3UXFoSEtOa2NpNEJLeTFOektldFVUVHk4cFJCSE5Qdw?oc=5</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr"/>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>UAE tourists can now claim VAT refunds on eligible Noon online shopping purchases - Arabian Business</t>
+          <t>Number of retail outlets connected to Digital Tourist VAT Refund System reaches more than 19,300 - Big News Network.com</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNSk0xOTlEQk5DQm4tczlCUE1jZ1dmamdsaUQ2TUYwWnlNd2JHMjhhVXZVUF8wNGpSVUFRNXhvU01pY01FMlUwWEt0anFyS3Q3QS0wa3BjZE1YLWtkWkpYeUJxVmlaSUhQM0Z3Mk9odUFYenhNRnBZeUkyQ0doNWJ2VGUySGY2dG9kMnlJaWhuWEMzb25aWjA1VXZkLWRwelk1MXJjbjBrV2F1Z29KZTJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNUjRVVzdLOXJQTXpUZDhqeWlQNDAwVDV2ZmJqd3h4cW5ZbXc0cHEzZGJBSWlLOTk0ZlFFbXlVSThCUEtxcGFqUHYzSlRmeXF0bC1XQ1J3VVhKUUkzeVBfNTc4cmQwNmlRYldwUU01YXpmc0pxT0daNWRpRUwtM0N3MlBBR09rRldZZlA5bXVJOXVTcVZSeE5ldWRHSWhna0ZfTTNwZWEwODlFTXRRYnRhOVJVcHJ3dDRuSnZtQlBhc0NMa2dhSzk4b1lBWEx5Uk5Ld2RMaFdmNUY?oc=5</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr"/>
@@ -4614,7 +4614,7 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>FTA issues five binding VAT directives on tax transactions - kpmg.com</t>
+          <t>UAE tourists can claim VAT refunds at 19,340 stores and on Noon purchases - Gulf News</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQQXptRUZOQlpWYUZiNzd1QThPVDhlUGM3TF9PU3NKZjUyS2lucEZLUUFKZFpfZVhXLWxteTBKbU1OVEU1WXdPVlViT2ZBb2h5dmlHa0Z2bjd0SzMxa1p6TzF0ajhuVFVSaUpkczUxd1lzeGVCeDNwRnpPbXJVNVNGWHB4UTcwR2dCYTJoWTVSYkJGQmxRZE42cXNmOExtclgxR28tUUdYVFRzaE92?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQeDRPcDE4QjJaSFU3Qm1wRGVaWXl6cjY2c3YyVDF3TmtqN1RYMkh0WDdoSm56QmlXU21xSllRQWt4WHNFU09vUWZpTEd3dVVMb0UxNy0yZG1ucUF6aXhIZ2dWVXpkVjVqa2hHUGN3VHNZWEticFZMXzNfb2NzaVpwOFFkOVAtNDhBY0xjSUo3bkh0WUg2ZEJ4Q0JDU05Td0FTLWlUWXNfN2JKeGJsTEg3NGFDMzNwT21JZTFGT0V30gHQAUFVX3lxTE9wdElvSG52YzNWWUt6WGJaRkp0LXpmVHpQTFV4WHczVkQtOUhOMWpqRzd2UjgyQjNOSWdMT3QwM1luZzdtNWhXdU91R2lqS0FKcG1hUGExZ1QxWG1SSUo2cWZSWll0bjdpQ2pBOXFjTUMxcjJma0RraGlVbjNjajZRM0h4OVZfM0FUQXNERTQzQm1TS29QVjdiQzM2T19naktoTXhfQ1pvNmx4U2IxVkkxUWF5QmZ4QUxmMXB2bFVvR2RVWm10bjE2SlNaRzJ2VEU?oc=5</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr"/>
@@ -4644,12 +4644,12 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>UAE extends Corporate Tax Small Business Relief until end of 2029 - travelsdubai.com</t>
+          <t>Retail outlets linked to UAE's Digital Tourist VAT Refund System exceed 19,300 - Emirates 24|7</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOYzFrN28yN3RDREhxYV9CVHl3UGU1NlpvSFJqaHJGWVpraVhEOEtqTnZVQk1OTjVjX1djWENocHdtYy1WY1dBSHZncjg3aGxWOXlwcFktaVVxYzBmZllLbzBaLUUxSEpyNW1HX3V5MG9YMWhTcjNfcnZxQ1JKRHZkMjlYSjlmUHk1SGFEYy0tYmlqWE96ajBqUnNSS19TUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOcXRBMGsxX1Q5SkJXcEFwWnV3c0VVc19jUnRkWU5yMVlPelltaEhvOWNLcEJxYi1KUExWMVlmZE1FOExZYklsRHU4N3lQZGppMDRnYUFaRU1OWHdwaVpiWWowOENidVJjbDFPeTQyQklzOGM5bXhQbDJrRFg2TkR6bUplTzJNZzl2M3dJT2FEeHVTTVNtTml6UEdoZUFDcVRCZWFHMGg1ejZoSWI1UWFCLV9zREotcmF3V0HSAdQBQVVfeXFMT3Q0RFN0V3FRSlNWV20tMm5hY1N5VHBVWmxzdnZGVXIwZU92VTZVRDVUVkRZM0Q1U1ZNZzFRcFlEWTc2ckk0UjZhcEN4YmZIZndTd284ZDQ3Z2Z4OS1mVGFUX2RwRzgyMWViTjEyQ19wdUxucXEtZWtFRm5tOWpId1VYYlRmd1Rkc2tlb3Q3THR0THZxZWt3Q1ZyTGVvZ2hUUzZPeTBPSzlER3FXR0ZvUnJiWk5vdlpwYlYxdmZjZnNTVEQxM3hSY1pyTGV5Qkk2d2lrejQ?oc=5</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr"/>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -4704,12 +4704,12 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>UAE seizes 3.58 million non-compliant excise goods - Gulf News</t>
+          <t>Indians, Russians, Turks top list of tourists claiming the most VAT refunds in UAE - khaleejtimes.com</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOOF9vUDk3UXlsY19FUWtOOEJ2V3Awam9fY09zeS1seXpTUUt2Y05TQlVUVjlwYlVuX2hRN3JBM095eTlqZ3pxWWx5ZWJzUzV1bGdCQ21JMzd1bjRIMGRMdHpiZWVOM1lmOVdtSXlicW4wYUNoYjMySjFTNl9OTnRvYWZycGdhODlTcU9sQUpwUEdJcnltNF9nSXpBWkpJbjF0VG1qeVJqTdIBugFBVV95cUxPMDVISGFVMTVqWFFiS0VMTmlzZzlyWXRVUl9BTjBGaWgtS21lN05BdlppYlVNQkNtYmZWaHRIczNlSWRmbXBBdG9zamlobjFhTFh6R2lYZFJ1RUtKWGZqOWpNd21LTmNxaUF1SjVIUm9UNjF6cmwxUGY2ZHFIVHBFdVJNMXcyeFp3dUZ2V1hpVmtnRmZOY29nLWNWQmxsQ0tHUzd0RjRyRUlZeW1adThtZEpPVl9KT1pFRUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPek9sY1dJUkpRblhiYnJDdDExOW1yREdXd1oyZ1Yxb0FnZlBYNTd3SUxGWnVMenlZVGlqRlIxLUszNk1Jd3BpcF9rVE9XLVF1OWdhY01fd0gteTJFRkVJLVREMjl4ZVRGZHJacUxJREpRN3UxdHFncGhITEQ0MnUzTkhKY2FSZnBnaFUzZDEyRnZOdG1hOWVFX2FLNG9Ca1lGekQzcllxd0FqTUhvTTRZM3MxcElQV0JaMWfSAcIBQVVfeXFMT2FPTEx4WGUzNUNhZWdBa1MzVU5GN1p3SkRwM0o5TWlqenhqVTNhR1Z0bThyN0laMS1tOUhfaG1qMmZpQi1pT3lTNEhKT2l3SklKZ1E3MXkyYVBrMnUwOTh1Y2RxSkFISUdlT1B6Qm1tTV9CUV9YM0xwcTJ2NzVmWUcxaFJ2YzhYeVBjZG1WSG9vcVc2N2tqRzNreHFwWVpaaUdncndzVEVLaE8zeHczU0Jvdl9FazU2NE1CNWZqQmZmekE?oc=5</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr"/>
@@ -4734,12 +4734,12 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>UAE Extends Small Business Relief for Corporate Tax to 2029 - tbreak.com</t>
+          <t>Tourists can now claim VAT refunds at 19,300 retail outlets across the UAE - Gulf Business</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9icS1QSXhYc09ROHVJdzRtdXJTMEdLa0o5Mm5TZ3VxR002a3lTeFR5anZqRmNtcVEyQWxfQ050UFVOZnFBcFdwT1VoNGlVZU9xYkY2WkM5SlpSSnp6QkpHck5rTUxqOXNjNjM0UmFTQkFfOXZySFFON1pCSXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQV2tyUkVhVzNVUlZ0QW9LdW5PWV9OTEVSN1FHU2c0Um9qbTRDNXFIdmZUaERGcDFPUkkyTVpzWXBQblJHb1VzVERybTh5WkIzcnRoRFo1ZVBicVRMQXpFZXB3VVJRQVZ6UDNNZDItT1RuTXcxYWxtSU1PaGlPNTFNUnpzLXBGX2QxSy1WVjU4alg4Q0dEWmY4WFZ6cEt1a1FZQXpRODFFN0xRT3VwSWFfNw?oc=5</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr"/>
@@ -4779,12 +4779,12 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>UAE extends corporate tax relief for small businesses until end of 2029 - Gulf News</t>
+          <t>UAE tourists can now claim VAT refunds on eligible Noon online shopping purchases - Arabian Business</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNNEo4Tm9qN1dERmwzZ0tMR0ZOSUVQTkpOTTNiTDc1U2VaSTkyRkExekRzRjUzb2xrelYzV0oydU1qS2JCbHJXd1hxeWhPdmtUN1UtcXRCOHZpSXBxMlBMdFRKbDNxYlNFaVdwRXROTUVxWC1tZUpObDVIZzNVUDEzSUZpNkIxN3ctTDRNWU9xOUx6QXZieFdVV1hkNHhlcldHUzY5b21BZ1J2VTVhMlN2a1V5V1dJRkw1OTItdWo5Qzk5N2lPX1HSAdgBQVVfeXFMTmRQM08wYWhkelVySDhudHZWLWQyZ2lyUG9TNEJhWVV6ejAybDV6QXdvUFR5ZndxZldxWHVDMjRKVm1Ndm0yeE1HZHo1LXoyVFBzMkhuUDZESEw5RUFIaWlfNEdObjNxRlc4VFpOZVQ3RDhhellsdEpYN3pLVzl1d1Fva3R0RWpDb0d5cVN0Z3I3emowS2tNbkplWTh1Z2NvVkRMd0R3STNWV3hrUVFtd3hxdjQxWjI2ZU4wVE9JTzlsWVUwYXlPTmU4YWJmazMxQk93MHVHbGZE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNSk0xOTlEQk5DQm4tczlCUE1jZ1dmamdsaUQ2TUYwWnlNd2JHMjhhVXZVUF8wNGpSVUFRNXhvU01pY01FMlUwWEt0anFyS3Q3QS0wa3BjZE1YLWtkWkpYeUJxVmlaSUhQM0Z3Mk9odUFYenhNRnBZeUkyQ0doNWJ2VGUySGY2dG9kMnlJaWhuWEMzb25aWjA1VXZkLWRwelk1MXJjbjBrV2F1Z29KZTJ3?oc=5</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr"/>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>Small businesses in UAE urged to file corporate tax returns before deadline, says FTA - khaleejtimes.com</t>
+          <t>FTA issues five binding VAT directives on tax transactions - kpmg.com</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>News — UAE Corporate Tax</t>
+          <t>News — UAE VAT</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOWnJlYmRmRm4xdy0xZ0toMUNUbnhTd3A5UW1pVzhFeXhIM2txamo4NU5qYVYwZGlQcEYwLTJhelBkOEdHajRYSE5PRnZtdmxGWmc0R2JlUVk0eVc0aW53NzdlM08zeWFzTUNocU9UcnY3UTNhTHVzZHhjRXFPZ0ZMMHMyRExEcjFiVVhKVzMxYk9FSHUxdERQRnUyZlJLWXA0ZVHSAaoBQVVfeXFMT3BwVV9lZzBQRTFjWUNVNEFzaUlhOUJuTHByVVRhdjRTbjdpajdOTjRtc2hfOEotMWlSb0FvX1F3azI2czNjMHREWnRJbFptM0F5ZHJkWUFsMW5fMDBsNU1YODgzT2VkMWZacU51MzkxaHJ0S216TF9UR241SnM0OVo2eHlDM0F6V2VfbUt4elZfZVBub2pLNW5fazhqV1hNUnBzRmkxS0NUQVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQQXptRUZOQlpWYUZiNzd1QThPVDhlUGM3TF9PU3NKZjUyS2lucEZLUUFKZFpfZVhXLWxteTBKbU1OVEU1WXdPVlViT2ZBb2h5dmlHa0Z2bjd0SzMxa1p6TzF0ajhuVFVSaUpkczUxd1lzeGVCeDNwRnpPbXJVNVNGWHB4UTcwR2dCYTJoWTVSYkJGQmxRZE42cXNmOExtclgxR28tUUdYVFRzaE92?oc=5</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr"/>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>UAE extends Corporate Tax relief until 2029 for businesses earning up to $817,000 - Arabian Business</t>
+          <t>UAE extends Corporate Tax Small Business Relief until end of 2029 - travelsdubai.com</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE5SM3FoRTVUSmJwTlpLbi1vOGFPM3RPcXpraXlCUG9iQlhuUUJ2MGRCczd6aDM0MFFNWS0yS2tNNVIxYjd2Y3AxWExhUnJNcHNXT3dLdGhyV2FBQUQwbmZ3YjRZc3NXTkNoLU5HTFRkTWRkSlZ6TEtHbg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOYzFrN28yN3RDREhxYV9CVHl3UGU1NlpvSFJqaHJGWVpraVhEOEtqTnZVQk1OTjVjX1djWENocHdtYy1WY1dBSHZncjg3aGxWOXlwcFktaVVxYzBmZllLbzBaLUUxSEpyNW1HX3V5MG9YMWhTcjNfcnZxQ1JKRHZkMjlYSjlmUHk1SGFEYy0tYmlqWE96ajBqUnNSS19TUQ?oc=5</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr"/>
@@ -4914,12 +4914,12 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Corporate Tax</t>
+          <t>VAT</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Finance announces extension of small business relief for corporate tax purposes until 31 December 2029 - Zawya</t>
+          <t>UAE seizes 3.58 million non-compliant excise goods - Gulf News</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOWVAwdTI2R09XSWRHaFNWYkNGdUJsSTNnaGpRandNeklubW8zM2h3VkNIcmRiQTVrZUxlSnhydWtqUGVTRS1vYVVQWWJfY2swUzhYOFJrdHVCQTlvTk1LNVBfWjBPbHZxWVU5Q0xQVWFHbTlLYlE0ek1aWFhqaUF3dDlTY2p2T0dtV3gzSXhaWkdFdWFBejA5ZkhDSkVPanZUWDk0d1oxNlJOUkNxMER2M1oyc3Nla2NnUW9WYmFRS04zeGlCcjQ1YVNZT2ZraU5EN0h2ZWRDaklZTjFQUklLWmRGRVFkUjhKUjBybHA5UktLZHFiVnUtOFpuNmhSZ0o3YVV3eld3WQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOOF9vUDk3UXlsY19FUWtOOEJ2V3Awam9fY09zeS1seXpTUUt2Y05TQlVUVjlwYlVuX2hRN3JBM095eTlqZ3pxWWx5ZWJzUzV1bGdCQ21JMzd1bjRIMGRMdHpiZWVOM1lmOVdtSXlicW4wYUNoYjMySjFTNl9OTnRvYWZycGdhODlTcU9sQUpwUEdJcnltNF9nSXpBWkpJbjF0VG1qeVJqTdIBugFBVV95cUxPMDVISGFVMTVqWFFiS0VMTmlzZzlyWXRVUl9BTjBGaWgtS21lN05BdlppYlVNQkNtYmZWaHRIczNlSWRmbXBBdG9zamlobjFhTFh6R2lYZFJ1RUtKWGZqOWpNd21LTmNxaUF1SjVIUm9UNjF6cmwxUGY2ZHFIVHBFdVJNMXcyeFp3dUZ2V1hpVmtnRmZOY29nLWNWQmxsQ0tHUzd0RjRyRUlZeW1adThtZEpPVl9KT1pFRUE?oc=5</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr"/>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>FTA reminds small businesses to file corporate tax returns - Sharjah24</t>
+          <t>UAE Extends Small Business Relief for Corporate Tax to 2029 - tbreak.com</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5NZ1VTdFlkVERkd0pETmFiVUQzZzEySVNaeWFyV2N3MHdhSWZreEZnUDFCYXhiWGtCOVVxMFdWUzhDa3JCU1czenE3QzJzaG0tNU5iMkFmRFRsTUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9icS1QSXhYc09ROHVJdzRtdXJTMEdLa0o5Mm5TZ3VxR002a3lTeFR5anZqRmNtcVEyQWxfQ050UFVOZnFBcFdwT1VoNGlVZU9xYkY2WkM5SlpSSnp6QkpHck5rTUxqOXNjNjM0UmFTQkFfOXZySFFON1pCSXc?oc=5</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr"/>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>UAE extends small business relief for corporate tax until December 2029 - TradeArabia</t>
+          <t>UAE extends corporate tax relief for small businesses until end of 2029 - Gulf News</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOc3RJWW11LUNyUERIeHh0dTVRVFJySzBoWVB0N1RCdVNpTVpORW03RkVXaG1pdk5HbWJfTDUzYXRIellIdlo4dVBXcXpuZHNrQXZRMk5MMGF1UkpqbGRTbXZRekZTYkU3cHpsdmJHdTVRdFFxSE1aSzZxWW1rb0RuT1RNZzVOWG91OGVTcFZVUGFVLWRUY3JsRnEtYkR4WUJjWnp6NkljSUd2NExsdUYtVA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNNEo4Tm9qN1dERmwzZ0tMR0ZOSUVQTkpOTTNiTDc1U2VaSTkyRkExekRzRjUzb2xrelYzV0oydU1qS2JCbHJXd1hxeWhPdmtUN1UtcXRCOHZpSXBxMlBMdFRKbDNxYlNFaVdwRXROTUVxWC1tZUpObDVIZzNVUDEzSUZpNkIxN3ctTDRNWU9xOUx6QXZieFdVV1hkNHhlcldHUzY5b21BZ1J2VTVhMlN2a1V5V1dJRkw1OTItdWo5Qzk5N2lPX1HSAdgBQVVfeXFMTmRQM08wYWhkelVySDhudHZWLWQyZ2lyUG9TNEJhWVV6ejAybDV6QXdvUFR5ZndxZldxWHVDMjRKVm1Ndm0yeE1HZHo1LXoyVFBzMkhuUDZESEw5RUFIaWlfNEdObjNxRlc4VFpOZVQ3RDhhellsdEpYN3pLVzl1d1Fva3R0RWpDb0d5cVN0Z3I3emowS2tNbkplWTh1Z2NvVkRMd0R3STNWV3hrUVFtd3hxdjQxWjI2ZU4wVE9JTzlsWVUwYXlPTmU4YWJmazMxQk93MHVHbGZE?oc=5</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr"/>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>UAE tax warning as thousands of businesses approach Corporate Tax deadline - Arabian Business</t>
+          <t>Small businesses in UAE urged to file corporate tax returns before deadline, says FTA - khaleejtimes.com</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBGbVZOWkkxM2FaVGlfeENJVWJXYzN6SDdmNk9nOFBYWWJDV3N6eGxVcnBRRXc5cDY5Qy1xSnNBQzVHMXR3NGpacEVucjlTMFRSaHc0dG5aZXc1aUVwSXlrTXhFTGd3RWNMbzVpWmdEVUZuUC1N?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOWnJlYmRmRm4xdy0xZ0toMUNUbnhTd3A5UW1pVzhFeXhIM2txamo4NU5qYVYwZGlQcEYwLTJhelBkOEdHajRYSE5PRnZtdmxGWmc0R2JlUVk0eVc0aW53NzdlM08zeWFzTUNocU9UcnY3UTNhTHVzZHhjRXFPZ0ZMMHMyRExEcjFiVVhKVzMxYk9FSHUxdERQRnUyZlJLWXA0ZVHSAaoBQVVfeXFMT3BwVV9lZzBQRTFjWUNVNEFzaUlhOUJuTHByVVRhdjRTbjdpajdOTjRtc2hfOEotMWlSb0FvX1F3azI2czNjMHREWnRJbFptM0F5ZHJkWUFsMW5fMDBsNU1YODgzT2VkMWZacU51MzkxaHJ0S216TF9UR241SnM0OVo2eHlDM0F6V2VfbUt4elZfZVBub2pLNW5fazhqV1hNUnBzRmkxS0NUQVE?oc=5</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr"/>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>UAE reminds small businesses to file corporate tax returns even if no tax is due - Gulf News</t>
+          <t>UAE extends Corporate Tax relief until 2029 for businesses earning up to $817,000 - Arabian Business</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOTm96UlB4Q2xPRlcybWNBanAtYXhxQkg0eHVCNDBvZlZGTWNGNzlSekNuVWZCU1JvOWR4MWxLanJMZEsyRms3NnZDSU90RnZuTkhad3pLLU1XX2VWV215T21HMTBmbVF1X0hmakhwM1BYZVNUQXZEV3A1UmR0QkZxVlJ1VDV5dGVMMFJFSGRxckpYVkVMMmFNMFBBdE9MZnlFSjJ3MDFXNzg2UXd0SUthQlZrd1Zjdy1JTVFkMEZlU0VKc3lzQW84VDBGLXFfVF93SnfSAeQBQVVfeXFMUEpicHFURTEyaDByTG44RGZUZ2R0MGJwRmdpV0hydzNTdkVYd0lFZzNITm9ueldCQ0JUZjZ3dW1TZ0xCSHM1S3c5eXExQlZac3V6bGd5Q1EzWFljOVRrZkJWRV9XcnFQWHdzRHQzWDRiUFhHaXlKMldlZHp5YW9zMHh2emxiX0R3MXdva2NFZ2JwcnVBZk52dEh2UEhvTW9FYzlJQ2xWdWZPQmpteFpaWnNUV0lpUTRiT0hNRXdHQVg1Q1VibWZqVWdocjBVVHJtVVFUbVFBdjJoRndFUS1aMTc5SEVh?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE5SM3FoRTVUSmJwTlpLbi1vOGFPM3RPcXpraXlCUG9iQlhuUUJ2MGRCczd6aDM0MFFNWS0yS2tNNVIxYjd2Y3AxWExhUnJNcHNXT3dLdGhyV2FBQUQwbmZ3YjRZc3NXTkNoLU5HTFRkTWRkSlZ6TEtHbg?oc=5</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr"/>
@@ -5139,12 +5139,12 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>Federal Tax Authority wins SAP Global Innovation Award - SAP News Center</t>
+          <t>Ministry of Finance announces extension of small business relief for corporate tax purposes until 31 December 2029 - Zawya</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYWE1ODFVeGZ2UEVVd0IyYXY0ckdPdFp4blEzcm9pZTZ5dm1MUDlocTNzNnd4dTh3cVhQb0o2aHJ2Y2VjTndrd2d6N2t1eW9OTzVtQ2JrcXVwN2NidFd2WUViQlRleTVQQXNpV2VvOVkyMFRINHhnNXpsUWdOcDhDUk1TbkpTajRkcUFGblBfWXhRZVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOWVAwdTI2R09XSWRHaFNWYkNGdUJsSTNnaGpRandNeklubW8zM2h3VkNIcmRiQTVrZUxlSnhydWtqUGVTRS1vYVVQWWJfY2swUzhYOFJrdHVCQTlvTk1LNVBfWjBPbHZxWVU5Q0xQVWFHbTlLYlE0ek1aWFhqaUF3dDlTY2p2T0dtV3gzSXhaWkdFdWFBejA5ZkhDSkVPanZUWDk0d1oxNlJOUkNxMER2M1oyc3Nla2NnUW9WYmFRS04zeGlCcjQ1YVNZT2ZraU5EN0h2ZWRDaklZTjFQUklLWmRGRVFkUjhKUjBybHA5UktLZHFiVnUtOFpuNmhSZ0o3YVV3eld3WQ?oc=5</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr"/>
@@ -5182,35 +5182,39 @@
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>official</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Finance Adopts “Aani” and “Jaywan” as New Payment Channels for Federal Service Fees and Fines</t>
+          <t>FTA reminds small businesses to file corporate tax returns - Sharjah24</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Ministry of Finance — News</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>mof.gov.ae</t>
+          <t>news.google.com</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>https://mof.gov.ae/en/news/ministry-of-finance-adopts-aani-and-jaywan-as-new-payment-channels-for-federal-service-fees-and-fines/</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5NZ1VTdFlkVERkd0pETmFiVUQzZzEySVNaeWFyV2N3MHdhSWZreEZnUDFCYXhiWGtCOVVxMFdWUzhDa3JCU1czenE3QzJzaG0tNU5iMkFmRFRsTUU?oc=5</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr"/>
@@ -5223,35 +5227,39 @@
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>Corporate Tax</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>official</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Finance Announces Decision introduces a Minimum Excise Price for Liquids Used in Electronic Smoking Devices Effective 1 September 2026</t>
+          <t>UAE extends small business relief for corporate tax until December 2029 - TradeArabia</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Ministry of Finance — News</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>mof.gov.ae</t>
+          <t>news.google.com</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>https://mof.gov.ae/en/news/ministry-of-finance-announces-decision-introduces-a-minimum-excise-price-for-liquids-used-in-electronic-smoking-devices-effective-1-september-2026/</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOc3RJWW11LUNyUERIeHh0dTVRVFJySzBoWVB0N1RCdVNpTVpORW03RkVXaG1pdk5HbWJfTDUzYXRIellIdlo4dVBXcXpuZHNrQXZRMk5MMGF1UkpqbGRTbXZRekZTYkU3cHpsdmJHdTVRdFFxSE1aSzZxWW1rb0RuT1RNZzVOWG91OGVTcFZVUGFVLWRUY3JsRnEtYkR4WUJjWnp6NkljSUd2NExsdUYtVA?oc=5</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr"/>
@@ -5264,7 +5272,11 @@
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr"/>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>Corporate Tax</t>
@@ -5272,32 +5284,245 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>official</t>
+          <t>news</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>Ministry of Finance Announces Extension of Small Business Relief for Corporate Tax Purposes until 31 December 2029</t>
+          <t>UAE tax warning as thousands of businesses approach Corporate Tax deadline - Arabian Business</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Ministry of Finance — News</t>
+          <t>News — UAE Corporate Tax</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>mof.gov.ae</t>
+          <t>news.google.com</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>https://mof.gov.ae/en/news/ministry-of-finance-announces-extension-of-small-business-relief-for-corporate-tax-purposes-until-31-december-2029/</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBGbVZOWkkxM2FaVGlfeENJVWJXYzN6SDdmNk9nOFBYWWJDV3N6eGxVcnBRRXc5cDY5Qy1xSnNBQzVHMXR3NGpacEVucjlTMFRSaHc0dG5aZXc1aUVwSXlrTXhFTGd3RWNMbzVpWmdEVUZuUC1N?oc=5</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr"/>
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Tax</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>UAE reminds small businesses to file corporate tax returns even if no tax is due - Gulf News</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE Corporate Tax</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOTm96UlB4Q2xPRlcybWNBanAtYXhxQkg0eHVCNDBvZlZGTWNGNzlSekNuVWZCU1JvOWR4MWxLanJMZEsyRms3NnZDSU90RnZuTkhad3pLLU1XX2VWV215T21HMTBmbVF1X0hmakhwM1BYZVNUQXZEV3A1UmR0QkZxVlJ1VDV5dGVMMFJFSGRxckpYVkVMMmFNMFBBdE9MZnlFSjJ3MDFXNzg2UXd0SUthQlZrd1Zjdy1JTVFkMEZlU0VKc3lzQW84VDBGLXFfVF93SnfSAeQBQVVfeXFMUEpicHFURTEyaDByTG44RGZUZ2R0MGJwRmdpV0hydzNTdkVYd0lFZzNITm9ueldCQ0JUZjZ3dW1TZ0xCSHM1S3c5eXExQlZac3V6bGd5Q1EzWFljOVRrZkJWRV9XcnFQWHdzRHQzWDRiUFhHaXlKMldlZHp5YW9zMHh2emxiX0R3MXdva2NFZ2JwcnVBZk52dEh2UEhvTW9FYzlJQ2xWdWZPQmpteFpaWnNUV0lpUTRiT0hNRXdHQVg1Q1VibWZqVWdocjBVVHJtVVFUbVFBdjJoRndFUS1aMTc5SEVh?oc=5</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>Federal Tax Authority wins SAP Global Innovation Award - SAP News Center</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>News — UAE Corporate Tax</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>news.google.com</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYWE1ODFVeGZ2UEVVd0IyYXY0ckdPdFp4blEzcm9pZTZ5dm1MUDlocTNzNnd4dTh3cVhQb0o2aHJ2Y2VjTndrd2d6N2t1eW9OTzVtQ2JrcXVwN2NidFd2WUViQlRleTVQQXNpV2VvOVkyMFRINHhnNXpsUWdOcDhDUk1TbkpTajRkcUFGblBfWXhRZVU?oc=5</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr"/>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>official</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>Ministry of Finance Adopts “Aani” and “Jaywan” as New Payment Channels for Federal Service Fees and Fines</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Ministry of Finance — News</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>mof.gov.ae</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>https://mof.gov.ae/en/news/ministry-of-finance-adopts-aani-and-jaywan-as-new-payment-channels-for-federal-service-fees-and-fines/</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr"/>
+      <c r="K111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr"/>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>official</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>Ministry of Finance Announces Decision introduces a Minimum Excise Price for Liquids Used in Electronic Smoking Devices Effective 1 September 2026</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Ministry of Finance — News</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>mof.gov.ae</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>https://mof.gov.ae/en/news/ministry-of-finance-announces-decision-introduces-a-minimum-excise-price-for-liquids-used-in-electronic-smoking-devices-effective-1-september-2026/</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr"/>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Tax</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>official</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>Ministry of Finance Announces Extension of Small Business Relief for Corporate Tax Purposes until 31 December 2029</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Ministry of Finance — News</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>mof.gov.ae</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>https://mof.gov.ae/en/news/ministry-of-finance-announces-extension-of-small-business-relief-for-corporate-tax-purposes-until-31-december-2029/</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr"/>
+      <c r="K113" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
